--- a/reports/latest-report.xlsx
+++ b/reports/latest-report.xlsx
@@ -4,32 +4,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="アプリ：リンク切れ" sheetId="1" r:id="rId1"/>
-    <sheet name="名古屋市HP：カテゴリ変更" sheetId="2" r:id="rId2"/>
-    <sheet name="履歴ログ" sheetId="3" r:id="rId3"/>
+    <sheet name="アプリ：内容変更" sheetId="2" r:id="rId2"/>
+    <sheet name="名古屋市HP：カテゴリ変更" sheetId="3" r:id="rId3"/>
+    <sheet name="履歴ログ" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -417,100 +396,100 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>✅ 正常</v>
+        <v>❌ リンク切れ</v>
       </c>
       <c r="B2" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036294.html</v>
-      </c>
-      <c r="C2">
-        <v>200</v>
+        <v>https://hikikomori.city.nagoya.jp/</v>
+      </c>
+      <c r="C2" t="str">
+        <v>TIMEOUT</v>
       </c>
       <c r="D2" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>✅ 正常</v>
+        <v>❌ リンク切れ</v>
       </c>
       <c r="B3" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/index.html</v>
-      </c>
-      <c r="C3">
-        <v>200</v>
+        <v>https://www.pref.aichi.jp/soshiki/jidoukatei/0000011250.html</v>
+      </c>
+      <c r="C3" t="str">
+        <v>TIMEOUT</v>
       </c>
       <c r="D3" t="str">
-        <v>data/districts.js, screens/DisasterScreen.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>✅ 正常</v>
+        <v>❌ リンク切れ</v>
       </c>
       <c r="B4" t="str">
-        <v>https://www.city.nagoya.jp/chikusa/kurashi/</v>
-      </c>
-      <c r="C4">
-        <v>200</v>
+        <v>https://nagoya-shakyo.jp/service/fureai-kyushoku/</v>
+      </c>
+      <c r="C4" t="str">
+        <v>TIMEOUT</v>
       </c>
       <c r="D4" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>✅ 正常</v>
+        <v>❌ リンク切れ</v>
       </c>
       <c r="B5" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036299.html</v>
-      </c>
-      <c r="C5">
-        <v>200</v>
+        <v>https://nagoya-shakyo.jp/service/ward-shakyo/</v>
+      </c>
+      <c r="C5" t="str">
+        <v>TIMEOUT</v>
       </c>
       <c r="D5" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>✅ 正常</v>
+        <v>❌ リンク切れ</v>
       </c>
       <c r="B6" t="str">
-        <v>https://www.city.nagoya.jp/higashi/kurashi/</v>
-      </c>
-      <c r="C6">
-        <v>200</v>
+        <v>https://nagoya-shakyo.jp/service/community-support/</v>
+      </c>
+      <c r="C6" t="str">
+        <v>TIMEOUT</v>
       </c>
       <c r="D6" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>✅ 正常</v>
+        <v>❌ リンク切れ</v>
       </c>
       <c r="B7" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036302.html</v>
-      </c>
-      <c r="C7">
-        <v>200</v>
+        <v>https://www.pref.aichi.jp/uploaded/attachment/620030.pdf</v>
+      </c>
+      <c r="C7" t="str">
+        <v>ERROR</v>
       </c>
       <c r="D7" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>✅ 正常</v>
+        <v>❌ リンク切れ</v>
       </c>
       <c r="B8" t="str">
-        <v>https://www.city.nagoya.jp/kita/kurashi/</v>
-      </c>
-      <c r="C8">
-        <v>200</v>
+        <v>https://www.pref.aichi.jp/soshiki/shigaku/kikanyoukenkakunin.html</v>
+      </c>
+      <c r="C8" t="str">
+        <v>ERROR</v>
       </c>
       <c r="D8" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="9">
@@ -518,7 +497,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B9" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036293.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036294.html</v>
       </c>
       <c r="C9">
         <v>200</v>
@@ -532,13 +511,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B10" t="str">
-        <v>https://www.city.nagoya.jp/nishi/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/index.html</v>
       </c>
       <c r="C10">
         <v>200</v>
       </c>
       <c r="D10" t="str">
-        <v>data/districts.js</v>
+        <v>data/districts.js, screens/DisasterScreen.js</v>
       </c>
     </row>
     <row r="11">
@@ -546,7 +525,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B11" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036297.html</v>
+        <v>https://www.city.nagoya.jp/chikusa/kurashi/</v>
       </c>
       <c r="C11">
         <v>200</v>
@@ -560,7 +539,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B12" t="str">
-        <v>https://www.city.nagoya.jp/nakamura/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036299.html</v>
       </c>
       <c r="C12">
         <v>200</v>
@@ -574,7 +553,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B13" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036295.html</v>
+        <v>https://www.city.nagoya.jp/higashi/kurashi/</v>
       </c>
       <c r="C13">
         <v>200</v>
@@ -588,7 +567,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B14" t="str">
-        <v>https://www.city.nagoya.jp/naka/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036302.html</v>
       </c>
       <c r="C14">
         <v>200</v>
@@ -602,7 +581,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B15" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036291.html</v>
+        <v>https://www.city.nagoya.jp/kita/kurashi/</v>
       </c>
       <c r="C15">
         <v>200</v>
@@ -616,7 +595,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B16" t="str">
-        <v>https://www.city.nagoya.jp/showa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036293.html</v>
       </c>
       <c r="C16">
         <v>200</v>
@@ -630,7 +609,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B17" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036292.html</v>
+        <v>https://www.city.nagoya.jp/nishi/kurashi/</v>
       </c>
       <c r="C17">
         <v>200</v>
@@ -644,7 +623,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B18" t="str">
-        <v>https://www.city.nagoya.jp/mizuho/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036297.html</v>
       </c>
       <c r="C18">
         <v>200</v>
@@ -658,7 +637,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B19" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036301.html</v>
+        <v>https://www.city.nagoya.jp/nakamura/kurashi/</v>
       </c>
       <c r="C19">
         <v>200</v>
@@ -672,7 +651,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B20" t="str">
-        <v>https://www.city.nagoya.jp/atsuta/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036295.html</v>
       </c>
       <c r="C20">
         <v>200</v>
@@ -686,7 +665,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B21" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036296.html</v>
+        <v>https://www.city.nagoya.jp/naka/kurashi/</v>
       </c>
       <c r="C21">
         <v>200</v>
@@ -700,7 +679,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B22" t="str">
-        <v>https://www.city.nagoya.jp/nakagawa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036291.html</v>
       </c>
       <c r="C22">
         <v>200</v>
@@ -714,7 +693,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B23" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036289.html</v>
+        <v>https://www.city.nagoya.jp/showa/kurashi/</v>
       </c>
       <c r="C23">
         <v>200</v>
@@ -728,7 +707,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B24" t="str">
-        <v>https://www.city.nagoya.jp/minato/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036292.html</v>
       </c>
       <c r="C24">
         <v>200</v>
@@ -742,7 +721,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B25" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036300.html</v>
+        <v>https://www.city.nagoya.jp/mizuho/kurashi/</v>
       </c>
       <c r="C25">
         <v>200</v>
@@ -756,7 +735,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B26" t="str">
-        <v>https://www.city.nagoya.jp/minami/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036301.html</v>
       </c>
       <c r="C26">
         <v>200</v>
@@ -770,7 +749,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B27" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036290.html</v>
+        <v>https://www.city.nagoya.jp/atsuta/kurashi/</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -784,7 +763,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B28" t="str">
-        <v>https://www.city.nagoya.jp/moriyama/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036296.html</v>
       </c>
       <c r="C28">
         <v>200</v>
@@ -798,7 +777,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B29" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036304.html</v>
+        <v>https://www.city.nagoya.jp/nakagawa/kurashi/</v>
       </c>
       <c r="C29">
         <v>200</v>
@@ -812,7 +791,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B30" t="str">
-        <v>https://www.city.nagoya.jp/midori/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036289.html</v>
       </c>
       <c r="C30">
         <v>200</v>
@@ -826,7 +805,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B31" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036303.html</v>
+        <v>https://www.city.nagoya.jp/minato/kurashi/</v>
       </c>
       <c r="C31">
         <v>200</v>
@@ -840,7 +819,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B32" t="str">
-        <v>https://www.city.nagoya.jp/meito/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036300.html</v>
       </c>
       <c r="C32">
         <v>200</v>
@@ -854,7 +833,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B33" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036298.html</v>
+        <v>https://www.city.nagoya.jp/minami/kurashi/</v>
       </c>
       <c r="C33">
         <v>200</v>
@@ -868,7 +847,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B34" t="str">
-        <v>https://www.city.nagoya.jp/tempaku/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036290.html</v>
       </c>
       <c r="C34">
         <v>200</v>
@@ -882,13 +861,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B35" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000034404.html</v>
+        <v>https://www.city.nagoya.jp/moriyama/kurashi/</v>
       </c>
       <c r="C35">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D35" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="36">
@@ -896,13 +875,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B36" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009333.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036304.html</v>
       </c>
       <c r="C36">
         <v>200</v>
       </c>
       <c r="D36" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="37">
@@ -910,13 +889,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B37" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1009009.html</v>
+        <v>https://www.city.nagoya.jp/midori/kurashi/</v>
       </c>
       <c r="C37">
         <v>200</v>
       </c>
       <c r="D37" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="38">
@@ -924,13 +903,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B38" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009270/1034086.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036303.html</v>
       </c>
       <c r="C38">
         <v>200</v>
       </c>
       <c r="D38" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="39">
@@ -938,13 +917,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B39" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009353/1034092.html</v>
+        <v>https://www.city.nagoya.jp/meito/kurashi/</v>
       </c>
       <c r="C39">
         <v>200</v>
       </c>
       <c r="D39" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="40">
@@ -952,13 +931,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B40" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009286/index.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036298.html</v>
       </c>
       <c r="C40">
         <v>200</v>
       </c>
       <c r="D40" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="41">
@@ -966,13 +945,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B41" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1034088.html</v>
+        <v>https://www.city.nagoya.jp/tempaku/kurashi/</v>
       </c>
       <c r="C41">
         <v>200</v>
       </c>
       <c r="D41" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="42">
@@ -980,10 +959,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B42" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009387.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000034404.html</v>
       </c>
       <c r="C42">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D42" t="str">
         <v>data/services.js</v>
@@ -994,7 +973,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B43" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009393.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009333.html</v>
       </c>
       <c r="C43">
         <v>200</v>
@@ -1008,7 +987,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B44" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011821/1011823.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1009009.html</v>
       </c>
       <c r="C44">
         <v>200</v>
@@ -1022,7 +1001,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B45" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008956.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009270/1034086.html</v>
       </c>
       <c r="C45">
         <v>200</v>
@@ -1036,7 +1015,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B46" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008955.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009353/1034092.html</v>
       </c>
       <c r="C46">
         <v>200</v>
@@ -1050,7 +1029,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B47" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/ichiran.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009286/index.html</v>
       </c>
       <c r="C47">
         <v>200</v>
@@ -1064,10 +1043,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B48" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096199.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1034088.html</v>
       </c>
       <c r="C48">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D48" t="str">
         <v>data/services.js</v>
@@ -1078,10 +1057,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B49" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000000479.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009387.html</v>
       </c>
       <c r="C49">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D49" t="str">
         <v>data/services.js</v>
@@ -1092,7 +1071,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B50" t="str">
-        <v>https://www.city.nagoya.jp/lifescene/byouki/1017964.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009393.html</v>
       </c>
       <c r="C50">
         <v>200</v>
@@ -1106,7 +1085,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B51" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/seido/toiawase/</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011821/1011823.html</v>
       </c>
       <c r="C51">
         <v>200</v>
@@ -1120,7 +1099,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B52" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016496/1016502.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008956.html</v>
       </c>
       <c r="C52">
         <v>200</v>
@@ -1134,7 +1113,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B53" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/1016536.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008955.html</v>
       </c>
       <c r="C53">
         <v>200</v>
@@ -1148,7 +1127,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B54" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011776/1034706/1011784.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/ichiran.html</v>
       </c>
       <c r="C54">
         <v>200</v>
@@ -1162,10 +1141,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B55" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009456/1009457/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096199.html</v>
       </c>
       <c r="C55">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D55" t="str">
         <v>data/services.js</v>
@@ -1176,10 +1155,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B56" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000000479.html</v>
       </c>
       <c r="C56">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D56" t="str">
         <v>data/services.js</v>
@@ -1190,7 +1169,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B57" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1012157/1033970.html</v>
+        <v>https://www.city.nagoya.jp/lifescene/byouki/1017964.html</v>
       </c>
       <c r="C57">
         <v>200</v>
@@ -1204,7 +1183,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B58" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1015763/1015815.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/seido/toiawase/</v>
       </c>
       <c r="C58">
         <v>200</v>
@@ -1218,7 +1197,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B59" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011793/1011807/1011810.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016496/1016502.html</v>
       </c>
       <c r="C59">
         <v>200</v>
@@ -1232,7 +1211,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B60" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016739.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/1016536.html</v>
       </c>
       <c r="C60">
         <v>200</v>
@@ -1246,7 +1225,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B61" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011776/1034706/1011784.html</v>
       </c>
       <c r="C61">
         <v>200</v>
@@ -1260,7 +1239,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B62" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/jutakukanri/bosyuannai.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009456/1009457/index.html</v>
       </c>
       <c r="C62">
         <v>200</v>
@@ -1274,7 +1253,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B63" t="str">
-        <v>https://www.hellowork.mhlw.go.jp/insurance/insurance_guide.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
       </c>
       <c r="C63">
         <v>200</v>
@@ -1288,7 +1267,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B64" t="str">
-        <v>https://jsite.mhlw.go.jp/aichi-hellowork/list.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1012157/1033970.html</v>
       </c>
       <c r="C64">
         <v>200</v>
@@ -1302,7 +1281,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B65" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1015763/1015815.html</v>
       </c>
       <c r="C65">
         <v>200</v>
@@ -1316,7 +1295,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B66" t="str">
-        <v>https://www.nagojob.city.nagoya.jp/</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011793/1011807/1011810.html</v>
       </c>
       <c r="C66">
         <v>200</v>
@@ -1330,7 +1309,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B67" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/tetyou/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016739.html</v>
       </c>
       <c r="C67">
         <v>200</v>
@@ -1344,7 +1323,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B68" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/soudan/fukushikakari.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/index.html</v>
       </c>
       <c r="C68">
         <v>200</v>
@@ -1358,7 +1337,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B69" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/fukushi_service.html</v>
+        <v>https://www.pref.aichi.jp/soshiki/jutakukanri/bosyuannai.html</v>
       </c>
       <c r="C69">
         <v>200</v>
@@ -1372,7 +1351,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B70" t="str">
-        <v>https://www.city.nagoya.jp/jigyou/sangyou/1026356/1035103/1026446/1026447.html</v>
+        <v>https://www.hellowork.mhlw.go.jp/insurance/insurance_guide.html</v>
       </c>
       <c r="C70">
         <v>200</v>
@@ -1386,7 +1365,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B71" t="str">
-        <v>https://weljob-nagoya.com/</v>
+        <v>https://jsite.mhlw.go.jp/aichi-hellowork/list.html</v>
       </c>
       <c r="C71">
         <v>200</v>
@@ -1400,7 +1379,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B72" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
       </c>
       <c r="C72">
         <v>200</v>
@@ -1414,7 +1393,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B73" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/622/linksweb.pdf</v>
+        <v>https://www.nagojob.city.nagoya.jp/</v>
       </c>
       <c r="C73">
         <v>200</v>
@@ -1428,7 +1407,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B74" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/tetyou/</v>
       </c>
       <c r="C74">
         <v>200</v>
@@ -1442,7 +1421,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B75" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/675/annnai.pdf</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/soudan/fukushikakari.html</v>
       </c>
       <c r="C75">
         <v>200</v>
@@ -1456,7 +1435,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B76" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/fukushi_service.html</v>
       </c>
       <c r="C76">
         <v>200</v>
@@ -1470,7 +1449,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B77" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
+        <v>https://www.city.nagoya.jp/jigyou/sangyou/1026356/1035103/1026446/1026447.html</v>
       </c>
       <c r="C77">
         <v>200</v>
@@ -1484,7 +1463,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B78" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
+        <v>https://weljob-nagoya.com/</v>
       </c>
       <c r="C78">
         <v>200</v>
@@ -1498,7 +1477,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B79" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008978.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
       </c>
       <c r="C79">
         <v>200</v>
@@ -1512,7 +1491,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B80" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/008/978/0413tirasi.pdf</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/622/linksweb.pdf</v>
       </c>
       <c r="C80">
         <v>200</v>
@@ -1526,10 +1505,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B81" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096194.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
       </c>
       <c r="C81">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D81" t="str">
         <v>data/services.js</v>
@@ -1540,7 +1519,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B82" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/009/017/r710_help.pdf</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/675/annnai.pdf</v>
       </c>
       <c r="C82">
         <v>200</v>
@@ -1554,7 +1533,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B83" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1034087.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
       </c>
       <c r="C83">
         <v>200</v>
@@ -1568,7 +1547,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B84" t="str">
-        <v>https://www.kosodate.city.nagoya.jp/kids/nobinobi.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
       </c>
       <c r="C84">
         <v>200</v>
@@ -1582,7 +1561,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B85" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1009278.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
       </c>
       <c r="C85">
         <v>200</v>
@@ -1596,7 +1575,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B86" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009024/1009026.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008978.html</v>
       </c>
       <c r="C86">
         <v>200</v>
@@ -1610,7 +1589,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B87" t="str">
-        <v>https://www.kosodate.city.nagoya.jp/play/supportbases.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/008/978/0413tirasi.pdf</v>
       </c>
       <c r="C87">
         <v>200</v>
@@ -1624,10 +1603,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B88" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034075/1009021.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096194.html</v>
       </c>
       <c r="C88">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D88" t="str">
         <v>data/services.js</v>
@@ -1638,7 +1617,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B89" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034072/1009016.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/009/017/r710_help.pdf</v>
       </c>
       <c r="C89">
         <v>200</v>
@@ -1652,7 +1631,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B90" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016744.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1034087.html</v>
       </c>
       <c r="C90">
         <v>200</v>
@@ -1666,7 +1645,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B91" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016742.html</v>
+        <v>https://www.kosodate.city.nagoya.jp/kids/nobinobi.html</v>
       </c>
       <c r="C91">
         <v>200</v>
@@ -1680,7 +1659,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B92" t="str">
-        <v>https://hikikomori.city.nagoya.jp/</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1009278.html</v>
       </c>
       <c r="C92">
         <v>200</v>
@@ -1694,10 +1673,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B93" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/category/22-5-3-0-0-0-0-0-0-0.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009024/1009026.html</v>
       </c>
       <c r="C93">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D93" t="str">
         <v>data/services.js</v>
@@ -1708,7 +1687,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B94" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009395.html</v>
+        <v>https://www.kosodate.city.nagoya.jp/play/supportbases.html</v>
       </c>
       <c r="C94">
         <v>200</v>
@@ -1722,7 +1701,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B95" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1009398.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034075/1009021.html</v>
       </c>
       <c r="C95">
         <v>200</v>
@@ -1736,10 +1715,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B96" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000137134.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034072/1009016.html</v>
       </c>
       <c r="C96">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D96" t="str">
         <v>data/services.js</v>
@@ -1750,7 +1729,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B97" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009381/1009382.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016744.html</v>
       </c>
       <c r="C97">
         <v>200</v>
@@ -1764,7 +1743,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B98" t="str">
-        <v>https://aiboren.jp/shisetsu/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016742.html</v>
       </c>
       <c r="C98">
         <v>200</v>
@@ -1778,10 +1757,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B99" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/jidoukatei/0000011250.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/category/22-5-3-0-0-0-0-0-0-0.html</v>
       </c>
       <c r="C99">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D99" t="str">
         <v>data/services.js</v>
@@ -1792,7 +1771,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B100" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016428.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009395.html</v>
       </c>
       <c r="C100">
         <v>200</v>
@@ -1806,7 +1785,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B101" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/woichiran.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1009398.html</v>
       </c>
       <c r="C101">
         <v>200</v>
@@ -1820,10 +1799,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B102" t="str">
-        <v>https://nagoya-shakyo.jp/service/fureai-kyushoku/</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000137134.html</v>
       </c>
       <c r="C102">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D102" t="str">
         <v>data/services.js</v>
@@ -1834,7 +1813,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B103" t="str">
-        <v>https://nagoya-shakyo.jp/service/ward-shakyo/</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009381/1009382.html</v>
       </c>
       <c r="C103">
         <v>200</v>
@@ -1848,7 +1827,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B104" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/company/shitei/haishoku/</v>
+        <v>https://aiboren.jp/shisetsu/</v>
       </c>
       <c r="C104">
         <v>200</v>
@@ -1862,7 +1841,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B105" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016428.html</v>
       </c>
       <c r="C105">
         <v>200</v>
@@ -1876,7 +1855,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B106" t="str">
-        <v>https://webc.sjc.ne.jp/nagoyasj/job2_7</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/woichiran.html</v>
       </c>
       <c r="C106">
         <v>200</v>
@@ -1890,10 +1869,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B107" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/page/0000132076.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/company/shitei/haishoku/</v>
       </c>
       <c r="C107">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D107" t="str">
         <v>data/services.js</v>
@@ -1904,10 +1883,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B108" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/page/0000181424.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
       </c>
       <c r="C108">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D108" t="str">
         <v>data/services.js</v>
@@ -1918,7 +1897,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B109" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016429.html</v>
+        <v>https://webc.sjc.ne.jp/nagoyasj/job2_7</v>
       </c>
       <c r="C109">
         <v>200</v>
@@ -1932,10 +1911,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B110" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009334.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/page/0000132076.html</v>
       </c>
       <c r="C110">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D110" t="str">
         <v>data/services.js</v>
@@ -1946,10 +1925,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B111" t="str">
-        <v>https://nagoya-shakyo.jp/service/community-support/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/page/0000181424.html</v>
       </c>
       <c r="C111">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D111" t="str">
         <v>data/services.js</v>
@@ -1960,7 +1939,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B112" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1012252.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016429.html</v>
       </c>
       <c r="C112">
         <v>200</v>
@@ -1974,10 +1953,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B113" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/page/0000157172.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009334.html</v>
       </c>
       <c r="C113">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D113" t="str">
         <v>data/services.js</v>
@@ -1988,7 +1967,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B114" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016488.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1012252.html</v>
       </c>
       <c r="C114">
         <v>200</v>
@@ -2002,10 +1981,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B115" t="str">
-        <v>https://www.bes-c.com/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/page/0000157172.html</v>
       </c>
       <c r="C115">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D115" t="str">
         <v>data/services.js</v>
@@ -2016,7 +1995,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B116" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016491.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016488.html</v>
       </c>
       <c r="C116">
         <v>200</v>
@@ -2030,7 +2009,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B117" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012724/1013205/1034493/1013206.html</v>
+        <v>https://www.bes-c.com/</v>
       </c>
       <c r="C117">
         <v>200</v>
@@ -2044,7 +2023,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B118" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/imu/0000050084.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016491.html</v>
       </c>
       <c r="C118">
         <v>200</v>
@@ -2058,7 +2037,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B119" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008943.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012724/1013205/1034493/1013206.html</v>
       </c>
       <c r="C119">
         <v>200</v>
@@ -2072,7 +2051,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B120" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008947.html</v>
+        <v>https://www.pref.aichi.jp/soshiki/imu/0000050084.html</v>
       </c>
       <c r="C120">
         <v>200</v>
@@ -2086,7 +2065,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B121" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008920/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008943.html</v>
       </c>
       <c r="C121">
         <v>200</v>
@@ -2100,7 +2079,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B122" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008937.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008947.html</v>
       </c>
       <c r="C122">
         <v>200</v>
@@ -2114,7 +2093,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B123" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008938.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008920/index.html</v>
       </c>
       <c r="C123">
         <v>200</v>
@@ -2128,7 +2107,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B124" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008939/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008937.html</v>
       </c>
       <c r="C124">
         <v>200</v>
@@ -2142,7 +2121,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B125" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008949.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008938.html</v>
       </c>
       <c r="C125">
         <v>200</v>
@@ -2156,7 +2135,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B126" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034084/1009261.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008939/index.html</v>
       </c>
       <c r="C126">
         <v>200</v>
@@ -2170,7 +2149,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B127" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009265.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008949.html</v>
       </c>
       <c r="C127">
         <v>200</v>
@@ -2184,7 +2163,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B128" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009264.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034084/1009261.html</v>
       </c>
       <c r="C128">
         <v>200</v>
@@ -2198,7 +2177,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B129" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009260.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009265.html</v>
       </c>
       <c r="C129">
         <v>200</v>
@@ -2212,7 +2191,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B130" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009258.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009264.html</v>
       </c>
       <c r="C130">
         <v>200</v>
@@ -2226,7 +2205,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B131" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009307/1008988.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009260.html</v>
       </c>
       <c r="C131">
         <v>200</v>
@@ -2240,7 +2219,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B132" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009258.html</v>
       </c>
       <c r="C132">
         <v>200</v>
@@ -2254,7 +2233,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B133" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034342/1008991/1036125.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009307/1008988.html</v>
       </c>
       <c r="C133">
         <v>200</v>
@@ -2268,7 +2247,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B134" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009126.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
       </c>
       <c r="C134">
         <v>200</v>
@@ -2282,10 +2261,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B135" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000048704.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034342/1008991/1036125.html</v>
       </c>
       <c r="C135">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D135" t="str">
         <v>data/services.js</v>
@@ -2296,7 +2275,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B136" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008959.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009126.html</v>
       </c>
       <c r="C136">
         <v>200</v>
@@ -2310,10 +2289,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B137" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009018.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000048704.html</v>
       </c>
       <c r="C137">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D137" t="str">
         <v>data/services.js</v>
@@ -2324,10 +2303,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B138" t="str">
-        <v>https://www.city.nagoya.jp/kyoiku/page/0000051014.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008959.html</v>
       </c>
       <c r="C138">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D138" t="str">
         <v>data/services.js</v>
@@ -2338,7 +2317,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B139" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1036101.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009018.html</v>
       </c>
       <c r="C139">
         <v>200</v>
@@ -2352,10 +2331,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B140" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1015850/1017055.html</v>
+        <v>https://www.city.nagoya.jp/kyoiku/page/0000051014.html</v>
       </c>
       <c r="C140">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D140" t="str">
         <v>data/services.js</v>
@@ -2366,7 +2345,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B141" t="str">
-        <v>https://nagoya.fureai-cloud.jp/_view/sodan/home/index</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1036101.html</v>
       </c>
       <c r="C141">
         <v>200</v>
@@ -2380,7 +2359,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B142" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009321/1009322.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1015850/1017055.html</v>
       </c>
       <c r="C142">
         <v>200</v>
@@ -2394,7 +2373,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B143" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016409.html</v>
+        <v>https://nagoya.fureai-cloud.jp/_view/sodan/home/index</v>
       </c>
       <c r="C143">
         <v>200</v>
@@ -2408,7 +2387,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B144" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015819/1038028/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009321/1009322.html</v>
       </c>
       <c r="C144">
         <v>200</v>
@@ -2422,7 +2401,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B145" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015845.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016409.html</v>
       </c>
       <c r="C145">
         <v>200</v>
@@ -2436,7 +2415,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B146" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016404.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015819/1038028/index.html</v>
       </c>
       <c r="C146">
         <v>200</v>
@@ -2450,10 +2429,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B147" t="str">
-        <v>https://www.city.nagoya.jp/sportsshimin/page/0000006195.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015845.html</v>
       </c>
       <c r="C147">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D147" t="str">
         <v>data/services.js</v>
@@ -2464,7 +2443,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B148" t="str">
-        <v>https://www.nic-nagoya.or.jp/</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016404.html</v>
       </c>
       <c r="C148">
         <v>200</v>
@@ -2478,10 +2457,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B149" t="str">
-        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
+        <v>https://www.city.nagoya.jp/sportsshimin/page/0000006195.html</v>
       </c>
       <c r="C149">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D149" t="str">
         <v>data/services.js</v>
@@ -2492,7 +2471,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B150" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016399.html</v>
+        <v>https://www.nic-nagoya.or.jp/</v>
       </c>
       <c r="C150">
         <v>200</v>
@@ -2506,10 +2485,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B151" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016734.html</v>
+        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
       </c>
       <c r="C151">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D151" t="str">
         <v>data/services.js</v>
@@ -2520,10 +2499,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B152" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000060016.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016399.html</v>
       </c>
       <c r="C152">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D152" t="str">
         <v>data/services.js</v>
@@ -2534,10 +2513,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B153" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009388.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016734.html</v>
       </c>
       <c r="C153">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D153" t="str">
         <v>data/services.js</v>
@@ -2548,10 +2527,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B154" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009391.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000060016.html</v>
       </c>
       <c r="C154">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D154" t="str">
         <v>data/services.js</v>
@@ -2562,7 +2541,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B155" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009389.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009388.html</v>
       </c>
       <c r="C155">
         <v>200</v>
@@ -2576,10 +2555,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B156" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000112089.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009391.html</v>
       </c>
       <c r="C156">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D156" t="str">
         <v>data/services.js</v>
@@ -2590,7 +2569,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B157" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1016449/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009389.html</v>
       </c>
       <c r="C157">
         <v>200</v>
@@ -2604,10 +2583,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B158" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000112089.html</v>
       </c>
       <c r="C158">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D158" t="str">
         <v>data/services.js</v>
@@ -2618,13 +2597,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B159" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/jouhou/1036432/1013386.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1016449/index.html</v>
       </c>
       <c r="C159">
         <v>200</v>
       </c>
       <c r="D159" t="str">
-        <v>data/services.js, screens/DisasterScreen.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="160">
@@ -2632,7 +2611,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B160" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/kyoujo/1036451/1013567.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/</v>
       </c>
       <c r="C160">
         <v>200</v>
@@ -2646,13 +2625,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B161" t="str">
-        <v>https://www.city.nagoya.jp/bosaikikikanri/page/0000033020.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/jouhou/1036432/1013386.html</v>
       </c>
       <c r="C161">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D161" t="str">
-        <v>data/services.js</v>
+        <v>data/services.js, screens/DisasterScreen.js</v>
       </c>
     </row>
     <row r="162">
@@ -2660,7 +2639,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B162" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008962/1008963.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/kyoujo/1036451/1013567.html</v>
       </c>
       <c r="C162">
         <v>200</v>
@@ -2674,10 +2653,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B163" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016506/1016510/1016511.html</v>
+        <v>https://www.city.nagoya.jp/bosaikikikanri/page/0000033020.html</v>
       </c>
       <c r="C163">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D163" t="str">
         <v>data/services.js</v>
@@ -2688,7 +2667,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B164" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009502/1034108.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008962/1008963.html</v>
       </c>
       <c r="C164">
         <v>200</v>
@@ -2702,7 +2681,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B165" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/todokede/1007816/1007817.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016506/1016510/1016511.html</v>
       </c>
       <c r="C165">
         <v>200</v>
@@ -2716,7 +2695,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B166" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011832/1011834.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009502/1034108.html</v>
       </c>
       <c r="C166">
         <v>200</v>
@@ -2730,7 +2709,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B167" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011868.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/todokede/1007816/1007817.html</v>
       </c>
       <c r="C167">
         <v>200</v>
@@ -2744,7 +2723,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B168" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011870.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011832/1011834.html</v>
       </c>
       <c r="C168">
         <v>200</v>
@@ -2758,7 +2737,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B169" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011868.html</v>
       </c>
       <c r="C169">
         <v>200</v>
@@ -2772,7 +2751,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B170" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1035058/1012184/1046468/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011870.html</v>
       </c>
       <c r="C170">
         <v>200</v>
@@ -2786,7 +2765,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B171" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016573/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/index.html</v>
       </c>
       <c r="C171">
         <v>200</v>
@@ -2800,7 +2779,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B172" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1035058/1012184/1046468/index.html</v>
       </c>
       <c r="C172">
         <v>200</v>
@@ -2814,10 +2793,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B173" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/category/15-7-2-0-0-0-0-0-0-0.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016573/index.html</v>
       </c>
       <c r="C173">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D173" t="str">
         <v>data/services.js</v>
@@ -2828,7 +2807,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B174" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011763/1011768.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/index.html</v>
       </c>
       <c r="C174">
         <v>200</v>
@@ -2842,10 +2821,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B175" t="str">
-        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000135090_00001.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/category/15-7-2-0-0-0-0-0-0-0.html</v>
       </c>
       <c r="C175">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D175" t="str">
         <v>data/services.js</v>
@@ -2856,7 +2835,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B176" t="str">
-        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000158665.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011763/1011768.html</v>
       </c>
       <c r="C176">
         <v>200</v>
@@ -2870,7 +2849,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B177" t="str">
-        <v>https://www.kyoukaikenpo.or.jp/benefit/injury_and_sickness_allowance/index.html</v>
+        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000135090_00001.html</v>
       </c>
       <c r="C177">
         <v>200</v>
@@ -2884,7 +2863,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B178" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011851/1011853.html</v>
+        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000158665.html</v>
       </c>
       <c r="C178">
         <v>200</v>
@@ -2898,7 +2877,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B179" t="str">
-        <v>https://www.nenkin.go.jp/service/jukyu/seido/sonota-kyufu/shienkyufukin/20190805.html</v>
+        <v>https://www.kyoukaikenpo.or.jp/benefit/injury_and_sickness_allowance/index.html</v>
       </c>
       <c r="C179">
         <v>200</v>
@@ -2912,7 +2891,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B180" t="str">
-        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011851/1011853.html</v>
       </c>
       <c r="C180">
         <v>200</v>
@@ -2926,7 +2905,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B181" t="str">
-        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm#mushoukaLink2</v>
+        <v>https://www.nenkin.go.jp/service/jukyu/seido/sonota-kyufu/shienkyufukin/20190805.html</v>
       </c>
       <c r="C181">
         <v>200</v>
@@ -2940,7 +2919,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B182" t="str">
-        <v>https://www.jasso.go.jp/shogakukin/</v>
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm</v>
       </c>
       <c r="C182">
         <v>200</v>
@@ -2954,7 +2933,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B183" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008946.html</v>
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm#mushoukaLink2</v>
       </c>
       <c r="C183">
         <v>200</v>
@@ -2968,7 +2947,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B184" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/zaimusisetsu/syuugakushienkin.html</v>
+        <v>https://www.jasso.go.jp/shogakukin/</v>
       </c>
       <c r="C184">
         <v>200</v>
@@ -2982,7 +2961,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B185" t="str">
-        <v>https://www.pref.aichi.jp/uploaded/attachment/620030.pdf</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008946.html</v>
       </c>
       <c r="C185">
         <v>200</v>
@@ -2996,7 +2975,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B186" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/shigaku/shigaku-syougakukyuhukin.html</v>
+        <v>https://www.pref.aichi.jp/soshiki/zaimusisetsu/syuugakushienkin.html</v>
       </c>
       <c r="C186">
         <v>200</v>
@@ -3010,7 +2989,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B187" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016801.html</v>
+        <v>https://www.pref.aichi.jp/soshiki/shigaku/shigaku-syougakukyuhukin.html</v>
       </c>
       <c r="C187">
         <v>200</v>
@@ -3024,7 +3003,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B188" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/801/r8syougakukin.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016801.html</v>
       </c>
       <c r="C188">
         <v>200</v>
@@ -3038,7 +3017,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B189" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016798.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/801/r8syougakukin.pdf</v>
       </c>
       <c r="C189">
         <v>200</v>
@@ -3052,7 +3031,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B190" t="str">
-        <v>https://www.city.nagoya.jp/shisei/keikaku/1034903/1004666/1004670.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016798.html</v>
       </c>
       <c r="C190">
         <v>200</v>
@@ -3066,7 +3045,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B191" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1049088.html</v>
+        <v>https://www.city.nagoya.jp/shisei/keikaku/1034903/1004666/1004670.html</v>
       </c>
       <c r="C191">
         <v>200</v>
@@ -3080,7 +3059,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B192" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034073/1009017.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1049088.html</v>
       </c>
       <c r="C192">
         <v>200</v>
@@ -3094,7 +3073,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B193" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/shigaku/kikanyoukenkakunin.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034073/1009017.html</v>
       </c>
       <c r="C193">
         <v>200</v>
@@ -3182,42 +3161,743 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:D2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>状態</v>
+        <v>URL</v>
+      </c>
+      <c r="B1" t="str">
+        <v>旧タイトル</v>
+      </c>
+      <c r="C1" t="str">
+        <v>新タイトル</v>
+      </c>
+      <c r="D1" t="str">
+        <v>参照ファイル</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>検知なし</v>
+        <v>https://www.nic-nagoya.or.jp/</v>
+      </c>
+      <c r="B2" t="str">
+        <v>One moment, please...</v>
+      </c>
+      <c r="C2" t="str">
+        <v>名古屋国際センター | Nagoya International Center</v>
+      </c>
+      <c r="D2" t="str">
+        <v>data/services.js</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E13"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>タブ</v>
+      </c>
+      <c r="B1" t="str">
+        <v>タブURL</v>
+      </c>
+      <c r="C1" t="str">
+        <v>種別</v>
+      </c>
+      <c r="D1" t="str">
+        <v>対象URL</v>
+      </c>
+      <c r="E1" t="str">
+        <v>内容</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="B2" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="C2" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D2" t="str">
+        <v>https://www.city.nagoya.jp/bousai/anzen/1014448/1014474/1050980.html</v>
+      </c>
+      <c r="E2" t="str">
+        <v>市民向け講座「令和8年度 第1回 犯罪被害を学ぶ会」を開催します（事前申込制）</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="B3" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="C3" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D3" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1051215.html</v>
+      </c>
+      <c r="E3" t="str">
+        <v>消防局PR動画について</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="B4" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="C4" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D4" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051801.html</v>
+      </c>
+      <c r="E4" t="str">
+        <v>「下水道科学館まつり」を開催します！</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="B5" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="C5" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D5" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1035058/1012184/1050522.html</v>
+      </c>
+      <c r="E5" t="str">
+        <v>令和8年10月から、粗大ごみの対象が変わります</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="B6" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="C6" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D6" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1050354.html</v>
+      </c>
+      <c r="E6" t="str">
+        <v>中央卸売市場本場 大人のための市場見学 参加者募集</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="B7" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="C7" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D7" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051655.html</v>
+      </c>
+      <c r="E7" t="str">
+        <v>環境学習センター「カーボンニュートラル★キッズラボ」</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="B8" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="C8" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D8" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1034787/1012546/1051442.html</v>
+      </c>
+      <c r="E8" t="str">
+        <v>「木に触れて森を学ぶSDGsワークショップ」参加者募集！</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="B9" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="C9" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D9" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051234.html</v>
+      </c>
+      <c r="E9" t="str">
+        <v>令和8年度「心の輪を広げる体験作文」及び「障害者週間のポスター」の作品募集</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="B10" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="C10" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D10" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1051292.html</v>
+      </c>
+      <c r="E10" t="str">
+        <v>令和8年7月25日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="B11" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="C11" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D11" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1034096.html</v>
+      </c>
+      <c r="E11" t="str">
+        <v>幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="B12" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="C12" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D12" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1027694/1034098/1051502/index.html</v>
+      </c>
+      <c r="E12" t="str">
+        <v>令和8年度 教育委員会会議結果（令和8年4月から令和9年3月まで）</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="B13" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="C13" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D13" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1051499.html</v>
+      </c>
+      <c r="E13" t="str">
+        <v>就学義務猶予免除者等の中学校卒業程度認定試験</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>状態</v>
       </c>
+      <c r="B1" t="str">
+        <v>検知日</v>
+      </c>
+      <c r="C1" t="str">
+        <v>チェック種別</v>
+      </c>
+      <c r="D1" t="str">
+        <v>URL</v>
+      </c>
+      <c r="E1" t="str">
+        <v>ステータス</v>
+      </c>
+      <c r="F1" t="str">
+        <v>参照ファイル</v>
+      </c>
+      <c r="G1" t="str">
+        <v>旧タイトル</v>
+      </c>
+      <c r="H1" t="str">
+        <v>新タイトル</v>
+      </c>
+      <c r="I1" t="str">
+        <v>タブ</v>
+      </c>
+      <c r="J1" t="str">
+        <v>タブURL</v>
+      </c>
+      <c r="K1" t="str">
+        <v>種別</v>
+      </c>
+      <c r="L1" t="str">
+        <v>対象URL</v>
+      </c>
+      <c r="M1" t="str">
+        <v>内容</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
         <v>これまでに検知された問題はありません</v>
       </c>
     </row>
+    <row r="3">
+      <c r="B3" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C3" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D3" t="str">
+        <v>https://hikikomori.city.nagoya.jp/</v>
+      </c>
+      <c r="E3" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F3" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C4" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D4" t="str">
+        <v>https://www.pref.aichi.jp/soshiki/jidoukatei/0000011250.html</v>
+      </c>
+      <c r="E4" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F4" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C5" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D5" t="str">
+        <v>https://nagoya-shakyo.jp/service/fureai-kyushoku/</v>
+      </c>
+      <c r="E5" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F5" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C6" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D6" t="str">
+        <v>https://nagoya-shakyo.jp/service/ward-shakyo/</v>
+      </c>
+      <c r="E6" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F6" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C7" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D7" t="str">
+        <v>https://nagoya-shakyo.jp/service/community-support/</v>
+      </c>
+      <c r="E7" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F7" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C8" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D8" t="str">
+        <v>https://www.pref.aichi.jp/uploaded/attachment/620030.pdf</v>
+      </c>
+      <c r="E8" t="str">
+        <v>ERROR</v>
+      </c>
+      <c r="F8" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C9" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D9" t="str">
+        <v>https://www.pref.aichi.jp/soshiki/shigaku/kikanyoukenkakunin.html</v>
+      </c>
+      <c r="E9" t="str">
+        <v>ERROR</v>
+      </c>
+      <c r="F9" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C10" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D10" t="str">
+        <v>https://www.nic-nagoya.or.jp/</v>
+      </c>
+      <c r="F10" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G10" t="str">
+        <v>One moment, please...</v>
+      </c>
+      <c r="H10" t="str">
+        <v>名古屋国際センター | Nagoya International Center</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C11" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I11" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J11" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K11" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L11" t="str">
+        <v>https://www.city.nagoya.jp/bousai/anzen/1014448/1014474/1050980.html</v>
+      </c>
+      <c r="M11" t="str">
+        <v>市民向け講座「令和8年度 第1回 犯罪被害を学ぶ会」を開催します（事前申込制）</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C12" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I12" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J12" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K12" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L12" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1051215.html</v>
+      </c>
+      <c r="M12" t="str">
+        <v>消防局PR動画について</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C13" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I13" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J13" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K13" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L13" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051801.html</v>
+      </c>
+      <c r="M13" t="str">
+        <v>「下水道科学館まつり」を開催します！</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C14" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I14" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J14" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K14" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L14" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1035058/1012184/1050522.html</v>
+      </c>
+      <c r="M14" t="str">
+        <v>令和8年10月から、粗大ごみの対象が変わります</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C15" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I15" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J15" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K15" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L15" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1050354.html</v>
+      </c>
+      <c r="M15" t="str">
+        <v>中央卸売市場本場 大人のための市場見学 参加者募集</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C16" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I16" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J16" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K16" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L16" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051655.html</v>
+      </c>
+      <c r="M16" t="str">
+        <v>環境学習センター「カーボンニュートラル★キッズラボ」</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C17" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I17" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J17" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K17" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L17" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1034787/1012546/1051442.html</v>
+      </c>
+      <c r="M17" t="str">
+        <v>「木に触れて森を学ぶSDGsワークショップ」参加者募集！</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C18" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I18" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J18" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K18" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L18" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051234.html</v>
+      </c>
+      <c r="M18" t="str">
+        <v>令和8年度「心の輪を広げる体験作文」及び「障害者週間のポスター」の作品募集</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C19" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I19" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J19" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K19" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L19" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1051292.html</v>
+      </c>
+      <c r="M19" t="str">
+        <v>令和8年7月25日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C20" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I20" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J20" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K20" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L20" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1034096.html</v>
+      </c>
+      <c r="M20" t="str">
+        <v>幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C21" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I21" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J21" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K21" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L21" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1027694/1034098/1051502/index.html</v>
+      </c>
+      <c r="M21" t="str">
+        <v>令和8年度 教育委員会会議結果（令和8年4月から令和9年3月まで）</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C22" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I22" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J22" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K22" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L22" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1051499.html</v>
+      </c>
+      <c r="M22" t="str">
+        <v>就学義務猶予免除者等の中学校卒業程度認定試験</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M22"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reports/latest-report.xlsx
+++ b/reports/latest-report.xlsx
@@ -399,7 +399,7 @@
         <v>❌ リンク切れ</v>
       </c>
       <c r="B2" t="str">
-        <v>https://hikikomori.city.nagoya.jp/</v>
+        <v>https://www.pref.aichi.jp/soshiki/jutakukanri/bosyuannai.html</v>
       </c>
       <c r="C2" t="str">
         <v>TIMEOUT</v>
@@ -413,7 +413,7 @@
         <v>❌ リンク切れ</v>
       </c>
       <c r="B3" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/jidoukatei/0000011250.html</v>
+        <v>https://www.pref.aichi.jp/soshiki/imu/0000050084.html</v>
       </c>
       <c r="C3" t="str">
         <v>TIMEOUT</v>
@@ -427,7 +427,7 @@
         <v>❌ リンク切れ</v>
       </c>
       <c r="B4" t="str">
-        <v>https://nagoya-shakyo.jp/service/fureai-kyushoku/</v>
+        <v>https://www.pref.aichi.jp/soshiki/zaimusisetsu/syuugakushienkin.html</v>
       </c>
       <c r="C4" t="str">
         <v>TIMEOUT</v>
@@ -441,7 +441,7 @@
         <v>❌ リンク切れ</v>
       </c>
       <c r="B5" t="str">
-        <v>https://nagoya-shakyo.jp/service/ward-shakyo/</v>
+        <v>https://www.pref.aichi.jp/uploaded/attachment/620030.pdf</v>
       </c>
       <c r="C5" t="str">
         <v>TIMEOUT</v>
@@ -455,7 +455,7 @@
         <v>❌ リンク切れ</v>
       </c>
       <c r="B6" t="str">
-        <v>https://nagoya-shakyo.jp/service/community-support/</v>
+        <v>https://www.pref.aichi.jp/soshiki/shigaku/shigaku-syougakukyuhukin.html</v>
       </c>
       <c r="C6" t="str">
         <v>TIMEOUT</v>
@@ -466,30 +466,30 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>❌ リンク切れ</v>
+        <v>✅ 正常</v>
       </c>
       <c r="B7" t="str">
-        <v>https://www.pref.aichi.jp/uploaded/attachment/620030.pdf</v>
-      </c>
-      <c r="C7" t="str">
-        <v>ERROR</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036294.html</v>
+      </c>
+      <c r="C7">
+        <v>200</v>
       </c>
       <c r="D7" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>❌ リンク切れ</v>
+        <v>✅ 正常</v>
       </c>
       <c r="B8" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/shigaku/kikanyoukenkakunin.html</v>
-      </c>
-      <c r="C8" t="str">
-        <v>ERROR</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/index.html</v>
+      </c>
+      <c r="C8">
+        <v>200</v>
       </c>
       <c r="D8" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js, screens/DisasterScreen.js</v>
       </c>
     </row>
     <row r="9">
@@ -497,7 +497,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B9" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036294.html</v>
+        <v>https://www.city.nagoya.jp/chikusa/kurashi/</v>
       </c>
       <c r="C9">
         <v>200</v>
@@ -511,13 +511,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B10" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/index.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036299.html</v>
       </c>
       <c r="C10">
         <v>200</v>
       </c>
       <c r="D10" t="str">
-        <v>data/districts.js, screens/DisasterScreen.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="11">
@@ -525,7 +525,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B11" t="str">
-        <v>https://www.city.nagoya.jp/chikusa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/higashi/kurashi/</v>
       </c>
       <c r="C11">
         <v>200</v>
@@ -539,7 +539,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B12" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036299.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036302.html</v>
       </c>
       <c r="C12">
         <v>200</v>
@@ -553,7 +553,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B13" t="str">
-        <v>https://www.city.nagoya.jp/higashi/kurashi/</v>
+        <v>https://www.city.nagoya.jp/kita/kurashi/</v>
       </c>
       <c r="C13">
         <v>200</v>
@@ -567,7 +567,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B14" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036302.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036293.html</v>
       </c>
       <c r="C14">
         <v>200</v>
@@ -581,7 +581,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B15" t="str">
-        <v>https://www.city.nagoya.jp/kita/kurashi/</v>
+        <v>https://www.city.nagoya.jp/nishi/kurashi/</v>
       </c>
       <c r="C15">
         <v>200</v>
@@ -595,7 +595,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B16" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036293.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036297.html</v>
       </c>
       <c r="C16">
         <v>200</v>
@@ -609,7 +609,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B17" t="str">
-        <v>https://www.city.nagoya.jp/nishi/kurashi/</v>
+        <v>https://www.city.nagoya.jp/nakamura/kurashi/</v>
       </c>
       <c r="C17">
         <v>200</v>
@@ -623,7 +623,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B18" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036297.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036295.html</v>
       </c>
       <c r="C18">
         <v>200</v>
@@ -637,7 +637,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B19" t="str">
-        <v>https://www.city.nagoya.jp/nakamura/kurashi/</v>
+        <v>https://www.city.nagoya.jp/naka/kurashi/</v>
       </c>
       <c r="C19">
         <v>200</v>
@@ -651,7 +651,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B20" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036295.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036291.html</v>
       </c>
       <c r="C20">
         <v>200</v>
@@ -665,7 +665,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B21" t="str">
-        <v>https://www.city.nagoya.jp/naka/kurashi/</v>
+        <v>https://www.city.nagoya.jp/showa/kurashi/</v>
       </c>
       <c r="C21">
         <v>200</v>
@@ -679,7 +679,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B22" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036291.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036292.html</v>
       </c>
       <c r="C22">
         <v>200</v>
@@ -693,7 +693,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B23" t="str">
-        <v>https://www.city.nagoya.jp/showa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/mizuho/kurashi/</v>
       </c>
       <c r="C23">
         <v>200</v>
@@ -707,7 +707,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B24" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036292.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036301.html</v>
       </c>
       <c r="C24">
         <v>200</v>
@@ -721,7 +721,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B25" t="str">
-        <v>https://www.city.nagoya.jp/mizuho/kurashi/</v>
+        <v>https://www.city.nagoya.jp/atsuta/kurashi/</v>
       </c>
       <c r="C25">
         <v>200</v>
@@ -735,7 +735,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B26" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036301.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036296.html</v>
       </c>
       <c r="C26">
         <v>200</v>
@@ -749,7 +749,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B27" t="str">
-        <v>https://www.city.nagoya.jp/atsuta/kurashi/</v>
+        <v>https://www.city.nagoya.jp/nakagawa/kurashi/</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -763,7 +763,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B28" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036296.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036289.html</v>
       </c>
       <c r="C28">
         <v>200</v>
@@ -777,7 +777,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B29" t="str">
-        <v>https://www.city.nagoya.jp/nakagawa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/minato/kurashi/</v>
       </c>
       <c r="C29">
         <v>200</v>
@@ -791,7 +791,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B30" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036289.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036300.html</v>
       </c>
       <c r="C30">
         <v>200</v>
@@ -805,7 +805,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B31" t="str">
-        <v>https://www.city.nagoya.jp/minato/kurashi/</v>
+        <v>https://www.city.nagoya.jp/minami/kurashi/</v>
       </c>
       <c r="C31">
         <v>200</v>
@@ -819,7 +819,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B32" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036300.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036290.html</v>
       </c>
       <c r="C32">
         <v>200</v>
@@ -833,7 +833,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B33" t="str">
-        <v>https://www.city.nagoya.jp/minami/kurashi/</v>
+        <v>https://www.city.nagoya.jp/moriyama/kurashi/</v>
       </c>
       <c r="C33">
         <v>200</v>
@@ -847,7 +847,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B34" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036290.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036304.html</v>
       </c>
       <c r="C34">
         <v>200</v>
@@ -861,7 +861,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B35" t="str">
-        <v>https://www.city.nagoya.jp/moriyama/kurashi/</v>
+        <v>https://www.city.nagoya.jp/midori/kurashi/</v>
       </c>
       <c r="C35">
         <v>200</v>
@@ -875,7 +875,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B36" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036304.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036303.html</v>
       </c>
       <c r="C36">
         <v>200</v>
@@ -889,7 +889,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B37" t="str">
-        <v>https://www.city.nagoya.jp/midori/kurashi/</v>
+        <v>https://www.city.nagoya.jp/meito/kurashi/</v>
       </c>
       <c r="C37">
         <v>200</v>
@@ -903,7 +903,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B38" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036303.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036298.html</v>
       </c>
       <c r="C38">
         <v>200</v>
@@ -917,7 +917,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B39" t="str">
-        <v>https://www.city.nagoya.jp/meito/kurashi/</v>
+        <v>https://www.city.nagoya.jp/tempaku/kurashi/</v>
       </c>
       <c r="C39">
         <v>200</v>
@@ -931,13 +931,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B40" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036298.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000034404.html</v>
       </c>
       <c r="C40">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D40" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="41">
@@ -945,13 +945,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B41" t="str">
-        <v>https://www.city.nagoya.jp/tempaku/kurashi/</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009333.html</v>
       </c>
       <c r="C41">
         <v>200</v>
       </c>
       <c r="D41" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="42">
@@ -959,10 +959,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B42" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000034404.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1009009.html</v>
       </c>
       <c r="C42">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D42" t="str">
         <v>data/services.js</v>
@@ -973,7 +973,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B43" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009333.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009270/1034086.html</v>
       </c>
       <c r="C43">
         <v>200</v>
@@ -987,7 +987,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B44" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1009009.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009353/1034092.html</v>
       </c>
       <c r="C44">
         <v>200</v>
@@ -1001,7 +1001,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B45" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009270/1034086.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009286/index.html</v>
       </c>
       <c r="C45">
         <v>200</v>
@@ -1015,7 +1015,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B46" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009353/1034092.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1034088.html</v>
       </c>
       <c r="C46">
         <v>200</v>
@@ -1029,7 +1029,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B47" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009286/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009387.html</v>
       </c>
       <c r="C47">
         <v>200</v>
@@ -1043,7 +1043,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B48" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1034088.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009393.html</v>
       </c>
       <c r="C48">
         <v>200</v>
@@ -1057,7 +1057,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B49" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009387.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011821/1011823.html</v>
       </c>
       <c r="C49">
         <v>200</v>
@@ -1071,7 +1071,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B50" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009393.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008956.html</v>
       </c>
       <c r="C50">
         <v>200</v>
@@ -1085,7 +1085,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B51" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011821/1011823.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008955.html</v>
       </c>
       <c r="C51">
         <v>200</v>
@@ -1099,7 +1099,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B52" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008956.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/ichiran.html</v>
       </c>
       <c r="C52">
         <v>200</v>
@@ -1113,10 +1113,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B53" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008955.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096199.html</v>
       </c>
       <c r="C53">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D53" t="str">
         <v>data/services.js</v>
@@ -1127,10 +1127,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B54" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/ichiran.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000000479.html</v>
       </c>
       <c r="C54">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D54" t="str">
         <v>data/services.js</v>
@@ -1141,10 +1141,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B55" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096199.html</v>
+        <v>https://www.city.nagoya.jp/lifescene/byouki/1017964.html</v>
       </c>
       <c r="C55">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D55" t="str">
         <v>data/services.js</v>
@@ -1155,10 +1155,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B56" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000000479.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/seido/toiawase/</v>
       </c>
       <c r="C56">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D56" t="str">
         <v>data/services.js</v>
@@ -1169,7 +1169,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B57" t="str">
-        <v>https://www.city.nagoya.jp/lifescene/byouki/1017964.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016496/1016502.html</v>
       </c>
       <c r="C57">
         <v>200</v>
@@ -1183,7 +1183,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B58" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/seido/toiawase/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/1016536.html</v>
       </c>
       <c r="C58">
         <v>200</v>
@@ -1197,7 +1197,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B59" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016496/1016502.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011776/1034706/1011784.html</v>
       </c>
       <c r="C59">
         <v>200</v>
@@ -1211,7 +1211,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B60" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/1016536.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009456/1009457/index.html</v>
       </c>
       <c r="C60">
         <v>200</v>
@@ -1225,7 +1225,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B61" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011776/1034706/1011784.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
       </c>
       <c r="C61">
         <v>200</v>
@@ -1239,7 +1239,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B62" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009456/1009457/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1012157/1033970.html</v>
       </c>
       <c r="C62">
         <v>200</v>
@@ -1253,7 +1253,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B63" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1015763/1015815.html</v>
       </c>
       <c r="C63">
         <v>200</v>
@@ -1267,7 +1267,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B64" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1012157/1033970.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011793/1011807/1011810.html</v>
       </c>
       <c r="C64">
         <v>200</v>
@@ -1281,7 +1281,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B65" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1015763/1015815.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016739.html</v>
       </c>
       <c r="C65">
         <v>200</v>
@@ -1295,7 +1295,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B66" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011793/1011807/1011810.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/index.html</v>
       </c>
       <c r="C66">
         <v>200</v>
@@ -1309,7 +1309,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B67" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016739.html</v>
+        <v>https://www.hellowork.mhlw.go.jp/insurance/insurance_guide.html</v>
       </c>
       <c r="C67">
         <v>200</v>
@@ -1323,7 +1323,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B68" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/index.html</v>
+        <v>https://jsite.mhlw.go.jp/aichi-hellowork/list.html</v>
       </c>
       <c r="C68">
         <v>200</v>
@@ -1337,7 +1337,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B69" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/jutakukanri/bosyuannai.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
       </c>
       <c r="C69">
         <v>200</v>
@@ -1351,7 +1351,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B70" t="str">
-        <v>https://www.hellowork.mhlw.go.jp/insurance/insurance_guide.html</v>
+        <v>https://www.nagojob.city.nagoya.jp/</v>
       </c>
       <c r="C70">
         <v>200</v>
@@ -1365,7 +1365,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B71" t="str">
-        <v>https://jsite.mhlw.go.jp/aichi-hellowork/list.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/tetyou/</v>
       </c>
       <c r="C71">
         <v>200</v>
@@ -1379,7 +1379,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B72" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/soudan/fukushikakari.html</v>
       </c>
       <c r="C72">
         <v>200</v>
@@ -1393,7 +1393,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B73" t="str">
-        <v>https://www.nagojob.city.nagoya.jp/</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/fukushi_service.html</v>
       </c>
       <c r="C73">
         <v>200</v>
@@ -1407,7 +1407,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B74" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/tetyou/</v>
+        <v>https://www.city.nagoya.jp/jigyou/sangyou/1026356/1035103/1026446/1026447.html</v>
       </c>
       <c r="C74">
         <v>200</v>
@@ -1421,7 +1421,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B75" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/soudan/fukushikakari.html</v>
+        <v>https://weljob-nagoya.com/</v>
       </c>
       <c r="C75">
         <v>200</v>
@@ -1435,7 +1435,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B76" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/fukushi_service.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
       </c>
       <c r="C76">
         <v>200</v>
@@ -1449,7 +1449,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B77" t="str">
-        <v>https://www.city.nagoya.jp/jigyou/sangyou/1026356/1035103/1026446/1026447.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/622/linksweb.pdf</v>
       </c>
       <c r="C77">
         <v>200</v>
@@ -1463,7 +1463,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B78" t="str">
-        <v>https://weljob-nagoya.com/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
       </c>
       <c r="C78">
         <v>200</v>
@@ -1477,7 +1477,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B79" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/675/annnai.pdf</v>
       </c>
       <c r="C79">
         <v>200</v>
@@ -1491,7 +1491,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B80" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/622/linksweb.pdf</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
       </c>
       <c r="C80">
         <v>200</v>
@@ -1505,7 +1505,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B81" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
       </c>
       <c r="C81">
         <v>200</v>
@@ -1519,7 +1519,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B82" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/675/annnai.pdf</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
       </c>
       <c r="C82">
         <v>200</v>
@@ -1533,7 +1533,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B83" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008978.html</v>
       </c>
       <c r="C83">
         <v>200</v>
@@ -1547,7 +1547,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B84" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/008/978/0413tirasi.pdf</v>
       </c>
       <c r="C84">
         <v>200</v>
@@ -1561,10 +1561,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B85" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096194.html</v>
       </c>
       <c r="C85">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D85" t="str">
         <v>data/services.js</v>
@@ -1575,7 +1575,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B86" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008978.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/009/017/r710_help.pdf</v>
       </c>
       <c r="C86">
         <v>200</v>
@@ -1589,7 +1589,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B87" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/008/978/0413tirasi.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1034087.html</v>
       </c>
       <c r="C87">
         <v>200</v>
@@ -1603,10 +1603,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B88" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096194.html</v>
+        <v>https://www.kosodate.city.nagoya.jp/kids/nobinobi.html</v>
       </c>
       <c r="C88">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D88" t="str">
         <v>data/services.js</v>
@@ -1617,7 +1617,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B89" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/009/017/r710_help.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1009278.html</v>
       </c>
       <c r="C89">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B90" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1034087.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009024/1009026.html</v>
       </c>
       <c r="C90">
         <v>200</v>
@@ -1645,7 +1645,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B91" t="str">
-        <v>https://www.kosodate.city.nagoya.jp/kids/nobinobi.html</v>
+        <v>https://www.kosodate.city.nagoya.jp/play/supportbases.html</v>
       </c>
       <c r="C91">
         <v>200</v>
@@ -1659,7 +1659,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B92" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1009278.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034075/1009021.html</v>
       </c>
       <c r="C92">
         <v>200</v>
@@ -1673,7 +1673,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B93" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009024/1009026.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034072/1009016.html</v>
       </c>
       <c r="C93">
         <v>200</v>
@@ -1687,7 +1687,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B94" t="str">
-        <v>https://www.kosodate.city.nagoya.jp/play/supportbases.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016744.html</v>
       </c>
       <c r="C94">
         <v>200</v>
@@ -1701,7 +1701,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B95" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034075/1009021.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016742.html</v>
       </c>
       <c r="C95">
         <v>200</v>
@@ -1715,7 +1715,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B96" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034072/1009016.html</v>
+        <v>https://hikikomori.city.nagoya.jp/</v>
       </c>
       <c r="C96">
         <v>200</v>
@@ -1729,10 +1729,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B97" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016744.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/category/22-5-3-0-0-0-0-0-0-0.html</v>
       </c>
       <c r="C97">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D97" t="str">
         <v>data/services.js</v>
@@ -1743,7 +1743,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B98" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016742.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009395.html</v>
       </c>
       <c r="C98">
         <v>200</v>
@@ -1757,10 +1757,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B99" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/category/22-5-3-0-0-0-0-0-0-0.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1009398.html</v>
       </c>
       <c r="C99">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D99" t="str">
         <v>data/services.js</v>
@@ -1771,10 +1771,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B100" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009395.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000137134.html</v>
       </c>
       <c r="C100">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D100" t="str">
         <v>data/services.js</v>
@@ -1785,7 +1785,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B101" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1009398.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009381/1009382.html</v>
       </c>
       <c r="C101">
         <v>200</v>
@@ -1799,10 +1799,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B102" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000137134.html</v>
+        <v>https://aiboren.jp/shisetsu/</v>
       </c>
       <c r="C102">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D102" t="str">
         <v>data/services.js</v>
@@ -1813,7 +1813,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B103" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009381/1009382.html</v>
+        <v>https://www.pref.aichi.jp/soshiki/jidoukatei/0000011250.html</v>
       </c>
       <c r="C103">
         <v>200</v>
@@ -1827,7 +1827,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B104" t="str">
-        <v>https://aiboren.jp/shisetsu/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016428.html</v>
       </c>
       <c r="C104">
         <v>200</v>
@@ -1841,7 +1841,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B105" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016428.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/woichiran.html</v>
       </c>
       <c r="C105">
         <v>200</v>
@@ -1855,7 +1855,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B106" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/woichiran.html</v>
+        <v>https://nagoya-shakyo.jp/service/fureai-kyushoku/</v>
       </c>
       <c r="C106">
         <v>200</v>
@@ -1869,7 +1869,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B107" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/company/shitei/haishoku/</v>
+        <v>https://nagoya-shakyo.jp/service/ward-shakyo/</v>
       </c>
       <c r="C107">
         <v>200</v>
@@ -1883,7 +1883,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B108" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/company/shitei/haishoku/</v>
       </c>
       <c r="C108">
         <v>200</v>
@@ -1897,7 +1897,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B109" t="str">
-        <v>https://webc.sjc.ne.jp/nagoyasj/job2_7</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
       </c>
       <c r="C109">
         <v>200</v>
@@ -1911,10 +1911,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B110" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/page/0000132076.html</v>
+        <v>https://webc.sjc.ne.jp/nagoyasj/job2_7</v>
       </c>
       <c r="C110">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D110" t="str">
         <v>data/services.js</v>
@@ -1925,7 +1925,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B111" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/page/0000181424.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/page/0000132076.html</v>
       </c>
       <c r="C111">
         <v>301</v>
@@ -1939,10 +1939,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B112" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016429.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/page/0000181424.html</v>
       </c>
       <c r="C112">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D112" t="str">
         <v>data/services.js</v>
@@ -1953,7 +1953,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B113" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009334.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016429.html</v>
       </c>
       <c r="C113">
         <v>200</v>
@@ -1967,7 +1967,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B114" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1012252.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009334.html</v>
       </c>
       <c r="C114">
         <v>200</v>
@@ -1981,10 +1981,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B115" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/page/0000157172.html</v>
+        <v>https://nagoya-shakyo.jp/service/community-support/</v>
       </c>
       <c r="C115">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D115" t="str">
         <v>data/services.js</v>
@@ -1995,7 +1995,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B116" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016488.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1012252.html</v>
       </c>
       <c r="C116">
         <v>200</v>
@@ -2009,10 +2009,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B117" t="str">
-        <v>https://www.bes-c.com/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/page/0000157172.html</v>
       </c>
       <c r="C117">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D117" t="str">
         <v>data/services.js</v>
@@ -2023,7 +2023,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B118" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016491.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016488.html</v>
       </c>
       <c r="C118">
         <v>200</v>
@@ -2037,7 +2037,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B119" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012724/1013205/1034493/1013206.html</v>
+        <v>https://www.bes-c.com/</v>
       </c>
       <c r="C119">
         <v>200</v>
@@ -2051,7 +2051,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B120" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/imu/0000050084.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016491.html</v>
       </c>
       <c r="C120">
         <v>200</v>
@@ -2065,7 +2065,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B121" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008943.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012724/1013205/1034493/1013206.html</v>
       </c>
       <c r="C121">
         <v>200</v>
@@ -2079,7 +2079,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B122" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008947.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008943.html</v>
       </c>
       <c r="C122">
         <v>200</v>
@@ -2093,7 +2093,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B123" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008920/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008947.html</v>
       </c>
       <c r="C123">
         <v>200</v>
@@ -2107,7 +2107,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B124" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008937.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008920/index.html</v>
       </c>
       <c r="C124">
         <v>200</v>
@@ -2121,7 +2121,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B125" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008938.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008937.html</v>
       </c>
       <c r="C125">
         <v>200</v>
@@ -2135,7 +2135,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B126" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008939/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008938.html</v>
       </c>
       <c r="C126">
         <v>200</v>
@@ -2149,7 +2149,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B127" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008949.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008939/index.html</v>
       </c>
       <c r="C127">
         <v>200</v>
@@ -2163,7 +2163,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B128" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034084/1009261.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008949.html</v>
       </c>
       <c r="C128">
         <v>200</v>
@@ -2177,7 +2177,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B129" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009265.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034084/1009261.html</v>
       </c>
       <c r="C129">
         <v>200</v>
@@ -2191,7 +2191,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B130" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009264.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009265.html</v>
       </c>
       <c r="C130">
         <v>200</v>
@@ -2205,7 +2205,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B131" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009260.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009264.html</v>
       </c>
       <c r="C131">
         <v>200</v>
@@ -2219,7 +2219,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B132" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009258.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009260.html</v>
       </c>
       <c r="C132">
         <v>200</v>
@@ -2233,7 +2233,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B133" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009307/1008988.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009258.html</v>
       </c>
       <c r="C133">
         <v>200</v>
@@ -2247,7 +2247,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B134" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009307/1008988.html</v>
       </c>
       <c r="C134">
         <v>200</v>
@@ -2261,7 +2261,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B135" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034342/1008991/1036125.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
       </c>
       <c r="C135">
         <v>200</v>
@@ -2275,7 +2275,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B136" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009126.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034342/1008991/1036125.html</v>
       </c>
       <c r="C136">
         <v>200</v>
@@ -2289,10 +2289,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B137" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000048704.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009126.html</v>
       </c>
       <c r="C137">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D137" t="str">
         <v>data/services.js</v>
@@ -2303,10 +2303,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B138" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008959.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000048704.html</v>
       </c>
       <c r="C138">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D138" t="str">
         <v>data/services.js</v>
@@ -2317,7 +2317,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B139" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009018.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008959.html</v>
       </c>
       <c r="C139">
         <v>200</v>
@@ -2331,10 +2331,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B140" t="str">
-        <v>https://www.city.nagoya.jp/kyoiku/page/0000051014.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009018.html</v>
       </c>
       <c r="C140">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D140" t="str">
         <v>data/services.js</v>
@@ -2345,10 +2345,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B141" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1036101.html</v>
+        <v>https://www.city.nagoya.jp/kyoiku/page/0000051014.html</v>
       </c>
       <c r="C141">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D141" t="str">
         <v>data/services.js</v>
@@ -2359,7 +2359,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B142" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1015850/1017055.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1036101.html</v>
       </c>
       <c r="C142">
         <v>200</v>
@@ -2373,7 +2373,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B143" t="str">
-        <v>https://nagoya.fureai-cloud.jp/_view/sodan/home/index</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1015850/1017055.html</v>
       </c>
       <c r="C143">
         <v>200</v>
@@ -2387,7 +2387,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B144" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009321/1009322.html</v>
+        <v>https://nagoya.fureai-cloud.jp/_view/sodan/home/index</v>
       </c>
       <c r="C144">
         <v>200</v>
@@ -2401,7 +2401,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B145" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016409.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009321/1009322.html</v>
       </c>
       <c r="C145">
         <v>200</v>
@@ -2415,7 +2415,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B146" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015819/1038028/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016409.html</v>
       </c>
       <c r="C146">
         <v>200</v>
@@ -2429,7 +2429,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B147" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015845.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015819/1038028/index.html</v>
       </c>
       <c r="C147">
         <v>200</v>
@@ -2443,7 +2443,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B148" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016404.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015845.html</v>
       </c>
       <c r="C148">
         <v>200</v>
@@ -2457,10 +2457,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B149" t="str">
-        <v>https://www.city.nagoya.jp/sportsshimin/page/0000006195.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016404.html</v>
       </c>
       <c r="C149">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D149" t="str">
         <v>data/services.js</v>
@@ -2471,10 +2471,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B150" t="str">
-        <v>https://www.nic-nagoya.or.jp/</v>
+        <v>https://www.city.nagoya.jp/sportsshimin/page/0000006195.html</v>
       </c>
       <c r="C150">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D150" t="str">
         <v>data/services.js</v>
@@ -2485,7 +2485,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B151" t="str">
-        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
+        <v>https://www.nic-nagoya.or.jp/</v>
       </c>
       <c r="C151">
         <v>200</v>
@@ -2499,7 +2499,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B152" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016399.html</v>
+        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
       </c>
       <c r="C152">
         <v>200</v>
@@ -2513,10 +2513,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B153" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016734.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016399.html</v>
       </c>
       <c r="C153">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D153" t="str">
         <v>data/services.js</v>
@@ -2527,7 +2527,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B154" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000060016.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016734.html</v>
       </c>
       <c r="C154">
         <v>301</v>
@@ -2541,10 +2541,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B155" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009388.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000060016.html</v>
       </c>
       <c r="C155">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D155" t="str">
         <v>data/services.js</v>
@@ -2555,7 +2555,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B156" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009391.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009388.html</v>
       </c>
       <c r="C156">
         <v>200</v>
@@ -2569,7 +2569,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B157" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009389.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009391.html</v>
       </c>
       <c r="C157">
         <v>200</v>
@@ -2583,10 +2583,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B158" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000112089.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009389.html</v>
       </c>
       <c r="C158">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D158" t="str">
         <v>data/services.js</v>
@@ -2597,10 +2597,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B159" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1016449/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000112089.html</v>
       </c>
       <c r="C159">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D159" t="str">
         <v>data/services.js</v>
@@ -2611,7 +2611,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B160" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1016449/index.html</v>
       </c>
       <c r="C160">
         <v>200</v>
@@ -2625,13 +2625,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B161" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/jouhou/1036432/1013386.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/</v>
       </c>
       <c r="C161">
         <v>200</v>
       </c>
       <c r="D161" t="str">
-        <v>data/services.js, screens/DisasterScreen.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="162">
@@ -2639,13 +2639,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B162" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/kyoujo/1036451/1013567.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/jouhou/1036432/1013386.html</v>
       </c>
       <c r="C162">
         <v>200</v>
       </c>
       <c r="D162" t="str">
-        <v>data/services.js</v>
+        <v>data/services.js, screens/DisasterScreen.js</v>
       </c>
     </row>
     <row r="163">
@@ -2653,10 +2653,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B163" t="str">
-        <v>https://www.city.nagoya.jp/bosaikikikanri/page/0000033020.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/kyoujo/1036451/1013567.html</v>
       </c>
       <c r="C163">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D163" t="str">
         <v>data/services.js</v>
@@ -2667,10 +2667,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B164" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008962/1008963.html</v>
+        <v>https://www.city.nagoya.jp/bosaikikikanri/page/0000033020.html</v>
       </c>
       <c r="C164">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D164" t="str">
         <v>data/services.js</v>
@@ -2681,7 +2681,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B165" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016506/1016510/1016511.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008962/1008963.html</v>
       </c>
       <c r="C165">
         <v>200</v>
@@ -2695,7 +2695,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B166" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009502/1034108.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016506/1016510/1016511.html</v>
       </c>
       <c r="C166">
         <v>200</v>
@@ -2709,7 +2709,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B167" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/todokede/1007816/1007817.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009502/1034108.html</v>
       </c>
       <c r="C167">
         <v>200</v>
@@ -2723,7 +2723,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B168" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011832/1011834.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/todokede/1007816/1007817.html</v>
       </c>
       <c r="C168">
         <v>200</v>
@@ -2737,7 +2737,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B169" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011868.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011832/1011834.html</v>
       </c>
       <c r="C169">
         <v>200</v>
@@ -2751,7 +2751,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B170" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011870.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011868.html</v>
       </c>
       <c r="C170">
         <v>200</v>
@@ -2765,7 +2765,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B171" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011870.html</v>
       </c>
       <c r="C171">
         <v>200</v>
@@ -2779,7 +2779,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B172" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1035058/1012184/1046468/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/index.html</v>
       </c>
       <c r="C172">
         <v>200</v>
@@ -2793,7 +2793,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B173" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016573/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1035058/1012184/1046468/index.html</v>
       </c>
       <c r="C173">
         <v>200</v>
@@ -2807,7 +2807,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B174" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016573/index.html</v>
       </c>
       <c r="C174">
         <v>200</v>
@@ -2821,10 +2821,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B175" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/category/15-7-2-0-0-0-0-0-0-0.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/index.html</v>
       </c>
       <c r="C175">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D175" t="str">
         <v>data/services.js</v>
@@ -2835,10 +2835,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B176" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011763/1011768.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/category/15-7-2-0-0-0-0-0-0-0.html</v>
       </c>
       <c r="C176">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D176" t="str">
         <v>data/services.js</v>
@@ -2849,7 +2849,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B177" t="str">
-        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000135090_00001.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011763/1011768.html</v>
       </c>
       <c r="C177">
         <v>200</v>
@@ -2863,7 +2863,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B178" t="str">
-        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000158665.html</v>
+        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000135090_00001.html</v>
       </c>
       <c r="C178">
         <v>200</v>
@@ -2877,7 +2877,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B179" t="str">
-        <v>https://www.kyoukaikenpo.or.jp/benefit/injury_and_sickness_allowance/index.html</v>
+        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000158665.html</v>
       </c>
       <c r="C179">
         <v>200</v>
@@ -2891,7 +2891,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B180" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011851/1011853.html</v>
+        <v>https://www.kyoukaikenpo.or.jp/benefit/injury_and_sickness_allowance/index.html</v>
       </c>
       <c r="C180">
         <v>200</v>
@@ -2905,7 +2905,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B181" t="str">
-        <v>https://www.nenkin.go.jp/service/jukyu/seido/sonota-kyufu/shienkyufukin/20190805.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011851/1011853.html</v>
       </c>
       <c r="C181">
         <v>200</v>
@@ -2919,7 +2919,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B182" t="str">
-        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm</v>
+        <v>https://www.nenkin.go.jp/service/jukyu/seido/sonota-kyufu/shienkyufukin/20190805.html</v>
       </c>
       <c r="C182">
         <v>200</v>
@@ -2933,7 +2933,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B183" t="str">
-        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm#mushoukaLink2</v>
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm</v>
       </c>
       <c r="C183">
         <v>200</v>
@@ -2947,7 +2947,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B184" t="str">
-        <v>https://www.jasso.go.jp/shogakukin/</v>
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm#mushoukaLink2</v>
       </c>
       <c r="C184">
         <v>200</v>
@@ -2961,7 +2961,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B185" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008946.html</v>
+        <v>https://www.jasso.go.jp/shogakukin/</v>
       </c>
       <c r="C185">
         <v>200</v>
@@ -2975,7 +2975,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B186" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/zaimusisetsu/syuugakushienkin.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008946.html</v>
       </c>
       <c r="C186">
         <v>200</v>
@@ -2989,7 +2989,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B187" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/shigaku/shigaku-syougakukyuhukin.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016801.html</v>
       </c>
       <c r="C187">
         <v>200</v>
@@ -3003,7 +3003,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B188" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016801.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/801/r8syougakukin.pdf</v>
       </c>
       <c r="C188">
         <v>200</v>
@@ -3017,7 +3017,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B189" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/801/r8syougakukin.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016798.html</v>
       </c>
       <c r="C189">
         <v>200</v>
@@ -3031,7 +3031,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B190" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016798.html</v>
+        <v>https://www.city.nagoya.jp/shisei/keikaku/1034903/1004666/1004670.html</v>
       </c>
       <c r="C190">
         <v>200</v>
@@ -3045,7 +3045,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B191" t="str">
-        <v>https://www.city.nagoya.jp/shisei/keikaku/1034903/1004666/1004670.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1049088.html</v>
       </c>
       <c r="C191">
         <v>200</v>
@@ -3059,7 +3059,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B192" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1049088.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034073/1009017.html</v>
       </c>
       <c r="C192">
         <v>200</v>
@@ -3073,7 +3073,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B193" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034073/1009017.html</v>
+        <v>https://www.pref.aichi.jp/soshiki/shigaku/kikanyoukenkakunin.html</v>
       </c>
       <c r="C193">
         <v>200</v>
@@ -3161,278 +3161,49 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:A2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>URL</v>
-      </c>
-      <c r="B1" t="str">
-        <v>旧タイトル</v>
-      </c>
-      <c r="C1" t="str">
-        <v>新タイトル</v>
-      </c>
-      <c r="D1" t="str">
-        <v>参照ファイル</v>
+        <v>状態</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>https://www.nic-nagoya.or.jp/</v>
-      </c>
-      <c r="B2" t="str">
-        <v>One moment, please...</v>
-      </c>
-      <c r="C2" t="str">
-        <v>名古屋国際センター | Nagoya International Center</v>
-      </c>
-      <c r="D2" t="str">
-        <v>data/services.js</v>
+        <v>検知なし</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:A2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>タブ</v>
-      </c>
-      <c r="B1" t="str">
-        <v>タブURL</v>
-      </c>
-      <c r="C1" t="str">
-        <v>種別</v>
-      </c>
-      <c r="D1" t="str">
-        <v>対象URL</v>
-      </c>
-      <c r="E1" t="str">
-        <v>内容</v>
+        <v>状態</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>防災・安全安心</v>
-      </c>
-      <c r="B2" t="str">
-        <v>https://www.city.nagoya.jp/bousai/index.html</v>
-      </c>
-      <c r="C2" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D2" t="str">
-        <v>https://www.city.nagoya.jp/bousai/anzen/1014448/1014474/1050980.html</v>
-      </c>
-      <c r="E2" t="str">
-        <v>市民向け講座「令和8年度 第1回 犯罪被害を学ぶ会」を開催します（事前申込制）</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>防災・安全安心</v>
-      </c>
-      <c r="B3" t="str">
-        <v>https://www.city.nagoya.jp/bousai/index.html</v>
-      </c>
-      <c r="C3" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D3" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1051215.html</v>
-      </c>
-      <c r="E3" t="str">
-        <v>消防局PR動画について</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>くらし・手続き</v>
-      </c>
-      <c r="B4" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
-      </c>
-      <c r="C4" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D4" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051801.html</v>
-      </c>
-      <c r="E4" t="str">
-        <v>「下水道科学館まつり」を開催します！</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>くらし・手続き</v>
-      </c>
-      <c r="B5" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
-      </c>
-      <c r="C5" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D5" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1035058/1012184/1050522.html</v>
-      </c>
-      <c r="E5" t="str">
-        <v>令和8年10月から、粗大ごみの対象が変わります</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>くらし・手続き</v>
-      </c>
-      <c r="B6" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
-      </c>
-      <c r="C6" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D6" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1050354.html</v>
-      </c>
-      <c r="E6" t="str">
-        <v>中央卸売市場本場 大人のための市場見学 参加者募集</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>くらし・手続き</v>
-      </c>
-      <c r="B7" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
-      </c>
-      <c r="C7" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D7" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051655.html</v>
-      </c>
-      <c r="E7" t="str">
-        <v>環境学習センター「カーボンニュートラル★キッズラボ」</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>くらし・手続き</v>
-      </c>
-      <c r="B8" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
-      </c>
-      <c r="C8" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D8" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/kankyou/1034787/1012546/1051442.html</v>
-      </c>
-      <c r="E8" t="str">
-        <v>「木に触れて森を学ぶSDGsワークショップ」参加者募集！</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>くらし・手続き</v>
-      </c>
-      <c r="B9" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
-      </c>
-      <c r="C9" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D9" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051234.html</v>
-      </c>
-      <c r="E9" t="str">
-        <v>令和8年度「心の輪を広げる体験作文」及び「障害者週間のポスター」の作品募集</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>子ども・子育て・教育</v>
-      </c>
-      <c r="B10" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
-      </c>
-      <c r="C10" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D10" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1051292.html</v>
-      </c>
-      <c r="E10" t="str">
-        <v>令和8年7月25日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>子ども・子育て・教育</v>
-      </c>
-      <c r="B11" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
-      </c>
-      <c r="C11" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D11" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1034096.html</v>
-      </c>
-      <c r="E11" t="str">
-        <v>幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>子ども・子育て・教育</v>
-      </c>
-      <c r="B12" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
-      </c>
-      <c r="C12" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D12" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1027694/1034098/1051502/index.html</v>
-      </c>
-      <c r="E12" t="str">
-        <v>令和8年度 教育委員会会議結果（令和8年4月から令和9年3月まで）</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>子ども・子育て・教育</v>
-      </c>
-      <c r="B13" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
-      </c>
-      <c r="C13" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D13" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1051499.html</v>
-      </c>
-      <c r="E13" t="str">
-        <v>就学義務猶予免除者等の中学校卒業程度認定試験</v>
+        <v>検知なし</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M27"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3895,9 +3666,94 @@
         <v>就学義務猶予免除者等の中学校卒業程度認定試験</v>
       </c>
     </row>
+    <row r="23">
+      <c r="B23" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C23" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D23" t="str">
+        <v>https://www.pref.aichi.jp/soshiki/jutakukanri/bosyuannai.html</v>
+      </c>
+      <c r="E23" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F23" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C24" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D24" t="str">
+        <v>https://www.pref.aichi.jp/soshiki/imu/0000050084.html</v>
+      </c>
+      <c r="E24" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F24" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C25" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D25" t="str">
+        <v>https://www.pref.aichi.jp/soshiki/zaimusisetsu/syuugakushienkin.html</v>
+      </c>
+      <c r="E25" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F25" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C26" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D26" t="str">
+        <v>https://www.pref.aichi.jp/uploaded/attachment/620030.pdf</v>
+      </c>
+      <c r="E26" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F26" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C27" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D27" t="str">
+        <v>https://www.pref.aichi.jp/soshiki/shigaku/shigaku-syougakukyuhukin.html</v>
+      </c>
+      <c r="E27" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F27" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M27"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reports/latest-report.xlsx
+++ b/reports/latest-report.xlsx
@@ -378,7 +378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D198"/>
+  <dimension ref="A1:D200"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,10 +427,10 @@
         <v>❌ リンク切れ</v>
       </c>
       <c r="B4" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/zaimusisetsu/syuugakushienkin.html</v>
+        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
       </c>
       <c r="C4" t="str">
-        <v>TIMEOUT</v>
+        <v>ERROR</v>
       </c>
       <c r="D4" t="str">
         <v>data/services.js</v>
@@ -444,7 +444,7 @@
         <v>https://www.pref.aichi.jp/uploaded/attachment/620030.pdf</v>
       </c>
       <c r="C5" t="str">
-        <v>TIMEOUT</v>
+        <v>ERROR</v>
       </c>
       <c r="D5" t="str">
         <v>data/services.js</v>
@@ -452,16 +452,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>❌ リンク切れ</v>
+        <v>✅ 正常</v>
       </c>
       <c r="B6" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/shigaku/shigaku-syougakukyuhukin.html</v>
-      </c>
-      <c r="C6" t="str">
-        <v>TIMEOUT</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036294.html</v>
+      </c>
+      <c r="C6">
+        <v>200</v>
       </c>
       <c r="D6" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="7">
@@ -469,13 +469,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B7" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036294.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/index.html</v>
       </c>
       <c r="C7">
         <v>200</v>
       </c>
       <c r="D7" t="str">
-        <v>data/districts.js</v>
+        <v>data/districts.js, screens/DisasterScreen.js</v>
       </c>
     </row>
     <row r="8">
@@ -483,13 +483,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B8" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/index.html</v>
+        <v>https://www.city.nagoya.jp/chikusa/kurashi/</v>
       </c>
       <c r="C8">
         <v>200</v>
       </c>
       <c r="D8" t="str">
-        <v>data/districts.js, screens/DisasterScreen.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="9">
@@ -497,7 +497,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B9" t="str">
-        <v>https://www.city.nagoya.jp/chikusa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036299.html</v>
       </c>
       <c r="C9">
         <v>200</v>
@@ -511,7 +511,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B10" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036299.html</v>
+        <v>https://www.city.nagoya.jp/higashi/kurashi/</v>
       </c>
       <c r="C10">
         <v>200</v>
@@ -525,7 +525,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B11" t="str">
-        <v>https://www.city.nagoya.jp/higashi/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036302.html</v>
       </c>
       <c r="C11">
         <v>200</v>
@@ -539,7 +539,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B12" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036302.html</v>
+        <v>https://www.city.nagoya.jp/kita/kurashi/</v>
       </c>
       <c r="C12">
         <v>200</v>
@@ -553,7 +553,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B13" t="str">
-        <v>https://www.city.nagoya.jp/kita/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036293.html</v>
       </c>
       <c r="C13">
         <v>200</v>
@@ -567,7 +567,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B14" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036293.html</v>
+        <v>https://www.city.nagoya.jp/nishi/kurashi/</v>
       </c>
       <c r="C14">
         <v>200</v>
@@ -581,7 +581,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B15" t="str">
-        <v>https://www.city.nagoya.jp/nishi/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036297.html</v>
       </c>
       <c r="C15">
         <v>200</v>
@@ -595,7 +595,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B16" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036297.html</v>
+        <v>https://www.city.nagoya.jp/nakamura/kurashi/</v>
       </c>
       <c r="C16">
         <v>200</v>
@@ -609,7 +609,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B17" t="str">
-        <v>https://www.city.nagoya.jp/nakamura/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036295.html</v>
       </c>
       <c r="C17">
         <v>200</v>
@@ -623,7 +623,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B18" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036295.html</v>
+        <v>https://www.city.nagoya.jp/naka/kurashi/</v>
       </c>
       <c r="C18">
         <v>200</v>
@@ -637,7 +637,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B19" t="str">
-        <v>https://www.city.nagoya.jp/naka/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036291.html</v>
       </c>
       <c r="C19">
         <v>200</v>
@@ -651,7 +651,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B20" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036291.html</v>
+        <v>https://www.city.nagoya.jp/showa/kurashi/</v>
       </c>
       <c r="C20">
         <v>200</v>
@@ -665,7 +665,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B21" t="str">
-        <v>https://www.city.nagoya.jp/showa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036292.html</v>
       </c>
       <c r="C21">
         <v>200</v>
@@ -679,7 +679,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B22" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036292.html</v>
+        <v>https://www.city.nagoya.jp/mizuho/kurashi/</v>
       </c>
       <c r="C22">
         <v>200</v>
@@ -693,7 +693,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B23" t="str">
-        <v>https://www.city.nagoya.jp/mizuho/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036301.html</v>
       </c>
       <c r="C23">
         <v>200</v>
@@ -707,7 +707,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B24" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036301.html</v>
+        <v>https://www.city.nagoya.jp/atsuta/kurashi/</v>
       </c>
       <c r="C24">
         <v>200</v>
@@ -721,7 +721,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B25" t="str">
-        <v>https://www.city.nagoya.jp/atsuta/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036296.html</v>
       </c>
       <c r="C25">
         <v>200</v>
@@ -735,7 +735,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B26" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036296.html</v>
+        <v>https://www.city.nagoya.jp/nakagawa/kurashi/</v>
       </c>
       <c r="C26">
         <v>200</v>
@@ -749,7 +749,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B27" t="str">
-        <v>https://www.city.nagoya.jp/nakagawa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036289.html</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -763,7 +763,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B28" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036289.html</v>
+        <v>https://www.city.nagoya.jp/minato/kurashi/</v>
       </c>
       <c r="C28">
         <v>200</v>
@@ -777,7 +777,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B29" t="str">
-        <v>https://www.city.nagoya.jp/minato/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036300.html</v>
       </c>
       <c r="C29">
         <v>200</v>
@@ -791,7 +791,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B30" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036300.html</v>
+        <v>https://www.city.nagoya.jp/minami/kurashi/</v>
       </c>
       <c r="C30">
         <v>200</v>
@@ -805,7 +805,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B31" t="str">
-        <v>https://www.city.nagoya.jp/minami/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036290.html</v>
       </c>
       <c r="C31">
         <v>200</v>
@@ -819,7 +819,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B32" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036290.html</v>
+        <v>https://www.city.nagoya.jp/moriyama/kurashi/</v>
       </c>
       <c r="C32">
         <v>200</v>
@@ -833,7 +833,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B33" t="str">
-        <v>https://www.city.nagoya.jp/moriyama/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036304.html</v>
       </c>
       <c r="C33">
         <v>200</v>
@@ -847,7 +847,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B34" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036304.html</v>
+        <v>https://www.city.nagoya.jp/midori/kurashi/</v>
       </c>
       <c r="C34">
         <v>200</v>
@@ -861,7 +861,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B35" t="str">
-        <v>https://www.city.nagoya.jp/midori/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036303.html</v>
       </c>
       <c r="C35">
         <v>200</v>
@@ -875,7 +875,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B36" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036303.html</v>
+        <v>https://www.city.nagoya.jp/meito/kurashi/</v>
       </c>
       <c r="C36">
         <v>200</v>
@@ -889,7 +889,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B37" t="str">
-        <v>https://www.city.nagoya.jp/meito/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036298.html</v>
       </c>
       <c r="C37">
         <v>200</v>
@@ -903,7 +903,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B38" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036298.html</v>
+        <v>https://www.city.nagoya.jp/tempaku/kurashi/</v>
       </c>
       <c r="C38">
         <v>200</v>
@@ -917,13 +917,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B39" t="str">
-        <v>https://www.city.nagoya.jp/tempaku/kurashi/</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000034404.html</v>
       </c>
       <c r="C39">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D39" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="40">
@@ -931,10 +931,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B40" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000034404.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009333.html</v>
       </c>
       <c r="C40">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D40" t="str">
         <v>data/services.js</v>
@@ -945,7 +945,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B41" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009333.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1009009.html</v>
       </c>
       <c r="C41">
         <v>200</v>
@@ -959,7 +959,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B42" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1009009.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009270/1034086.html</v>
       </c>
       <c r="C42">
         <v>200</v>
@@ -973,7 +973,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B43" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009270/1034086.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009353/1034092.html</v>
       </c>
       <c r="C43">
         <v>200</v>
@@ -987,7 +987,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B44" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009353/1034092.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009286/index.html</v>
       </c>
       <c r="C44">
         <v>200</v>
@@ -1001,7 +1001,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B45" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009286/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1034088.html</v>
       </c>
       <c r="C45">
         <v>200</v>
@@ -1015,7 +1015,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B46" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1034088.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009387.html</v>
       </c>
       <c r="C46">
         <v>200</v>
@@ -1029,7 +1029,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B47" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009387.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009393.html</v>
       </c>
       <c r="C47">
         <v>200</v>
@@ -1043,7 +1043,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B48" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009393.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011821/1011823.html</v>
       </c>
       <c r="C48">
         <v>200</v>
@@ -1057,7 +1057,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B49" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011821/1011823.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008956.html</v>
       </c>
       <c r="C49">
         <v>200</v>
@@ -1071,7 +1071,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B50" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008956.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008955.html</v>
       </c>
       <c r="C50">
         <v>200</v>
@@ -1085,7 +1085,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B51" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008955.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/ichiran.html</v>
       </c>
       <c r="C51">
         <v>200</v>
@@ -1099,10 +1099,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B52" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/ichiran.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096199.html</v>
       </c>
       <c r="C52">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D52" t="str">
         <v>data/services.js</v>
@@ -1113,7 +1113,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B53" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096199.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000000479.html</v>
       </c>
       <c r="C53">
         <v>301</v>
@@ -1127,10 +1127,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B54" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000000479.html</v>
+        <v>https://www.city.nagoya.jp/lifescene/byouki/1017964.html</v>
       </c>
       <c r="C54">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D54" t="str">
         <v>data/services.js</v>
@@ -1141,7 +1141,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B55" t="str">
-        <v>https://www.city.nagoya.jp/lifescene/byouki/1017964.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/seido/toiawase/</v>
       </c>
       <c r="C55">
         <v>200</v>
@@ -1155,7 +1155,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B56" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/seido/toiawase/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016496/1016502.html</v>
       </c>
       <c r="C56">
         <v>200</v>
@@ -1169,7 +1169,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B57" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016496/1016502.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/1016536.html</v>
       </c>
       <c r="C57">
         <v>200</v>
@@ -1183,7 +1183,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B58" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/1016536.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011776/1034706/1011784.html</v>
       </c>
       <c r="C58">
         <v>200</v>
@@ -1197,7 +1197,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B59" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011776/1034706/1011784.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009456/1009457/index.html</v>
       </c>
       <c r="C59">
         <v>200</v>
@@ -1211,7 +1211,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B60" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009456/1009457/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
       </c>
       <c r="C60">
         <v>200</v>
@@ -1225,7 +1225,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B61" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1012157/1033970.html</v>
       </c>
       <c r="C61">
         <v>200</v>
@@ -1239,7 +1239,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B62" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1012157/1033970.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1015763/1015815.html</v>
       </c>
       <c r="C62">
         <v>200</v>
@@ -1253,7 +1253,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B63" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1015763/1015815.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011793/1011807/1011810.html</v>
       </c>
       <c r="C63">
         <v>200</v>
@@ -1267,7 +1267,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B64" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011793/1011807/1011810.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016739.html</v>
       </c>
       <c r="C64">
         <v>200</v>
@@ -1281,7 +1281,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B65" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016739.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/index.html</v>
       </c>
       <c r="C65">
         <v>200</v>
@@ -1295,7 +1295,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B66" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/index.html</v>
+        <v>https://www.hellowork.mhlw.go.jp/insurance/insurance_guide.html</v>
       </c>
       <c r="C66">
         <v>200</v>
@@ -1309,7 +1309,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B67" t="str">
-        <v>https://www.hellowork.mhlw.go.jp/insurance/insurance_guide.html</v>
+        <v>https://jsite.mhlw.go.jp/aichi-hellowork/list.html</v>
       </c>
       <c r="C67">
         <v>200</v>
@@ -1323,7 +1323,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B68" t="str">
-        <v>https://jsite.mhlw.go.jp/aichi-hellowork/list.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
       </c>
       <c r="C68">
         <v>200</v>
@@ -1337,7 +1337,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B69" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
+        <v>https://www.nagojob.city.nagoya.jp/</v>
       </c>
       <c r="C69">
         <v>200</v>
@@ -1351,7 +1351,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B70" t="str">
-        <v>https://www.nagojob.city.nagoya.jp/</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/tetyou/</v>
       </c>
       <c r="C70">
         <v>200</v>
@@ -1365,7 +1365,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B71" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/tetyou/</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/soudan/fukushikakari.html</v>
       </c>
       <c r="C71">
         <v>200</v>
@@ -1379,7 +1379,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B72" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/soudan/fukushikakari.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/fukushi_service.html</v>
       </c>
       <c r="C72">
         <v>200</v>
@@ -1393,7 +1393,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B73" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/fukushi_service.html</v>
+        <v>https://www.city.nagoya.jp/jigyou/sangyou/1026356/1035103/1026446/1026447.html</v>
       </c>
       <c r="C73">
         <v>200</v>
@@ -1407,7 +1407,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B74" t="str">
-        <v>https://www.city.nagoya.jp/jigyou/sangyou/1026356/1035103/1026446/1026447.html</v>
+        <v>https://weljob-nagoya.com/</v>
       </c>
       <c r="C74">
         <v>200</v>
@@ -1421,7 +1421,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B75" t="str">
-        <v>https://weljob-nagoya.com/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
       </c>
       <c r="C75">
         <v>200</v>
@@ -1435,7 +1435,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B76" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/622/linksweb.pdf</v>
       </c>
       <c r="C76">
         <v>200</v>
@@ -1449,7 +1449,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B77" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/622/linksweb.pdf</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
       </c>
       <c r="C77">
         <v>200</v>
@@ -1463,7 +1463,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B78" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/675/annnai.pdf</v>
       </c>
       <c r="C78">
         <v>200</v>
@@ -1477,7 +1477,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B79" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/675/annnai.pdf</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
       </c>
       <c r="C79">
         <v>200</v>
@@ -1491,7 +1491,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B80" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
       </c>
       <c r="C80">
         <v>200</v>
@@ -1505,7 +1505,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B81" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
       </c>
       <c r="C81">
         <v>200</v>
@@ -1519,7 +1519,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B82" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008978.html</v>
       </c>
       <c r="C82">
         <v>200</v>
@@ -1533,7 +1533,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B83" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008978.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/008/978/0413tirasi.pdf</v>
       </c>
       <c r="C83">
         <v>200</v>
@@ -1547,10 +1547,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B84" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/008/978/0413tirasi.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096194.html</v>
       </c>
       <c r="C84">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D84" t="str">
         <v>data/services.js</v>
@@ -1561,10 +1561,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B85" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096194.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/009/017/r710_help.pdf</v>
       </c>
       <c r="C85">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D85" t="str">
         <v>data/services.js</v>
@@ -1575,7 +1575,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B86" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/009/017/r710_help.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1034087.html</v>
       </c>
       <c r="C86">
         <v>200</v>
@@ -1589,7 +1589,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B87" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1034087.html</v>
+        <v>https://www.kosodate.city.nagoya.jp/kids/nobinobi.html</v>
       </c>
       <c r="C87">
         <v>200</v>
@@ -1603,7 +1603,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B88" t="str">
-        <v>https://www.kosodate.city.nagoya.jp/kids/nobinobi.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1009278.html</v>
       </c>
       <c r="C88">
         <v>200</v>
@@ -1617,7 +1617,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B89" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1009278.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009024/1009026.html</v>
       </c>
       <c r="C89">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B90" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009024/1009026.html</v>
+        <v>https://www.kosodate.city.nagoya.jp/play/supportbases.html</v>
       </c>
       <c r="C90">
         <v>200</v>
@@ -1645,7 +1645,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B91" t="str">
-        <v>https://www.kosodate.city.nagoya.jp/play/supportbases.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034075/1009021.html</v>
       </c>
       <c r="C91">
         <v>200</v>
@@ -1659,7 +1659,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B92" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034075/1009021.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034072/1009016.html</v>
       </c>
       <c r="C92">
         <v>200</v>
@@ -1673,7 +1673,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B93" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034072/1009016.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016744.html</v>
       </c>
       <c r="C93">
         <v>200</v>
@@ -1687,7 +1687,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B94" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016744.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016742.html</v>
       </c>
       <c r="C94">
         <v>200</v>
@@ -1701,7 +1701,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B95" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016742.html</v>
+        <v>https://hikikomori.city.nagoya.jp/</v>
       </c>
       <c r="C95">
         <v>200</v>
@@ -1715,10 +1715,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B96" t="str">
-        <v>https://hikikomori.city.nagoya.jp/</v>
+        <v>https://www.city.nagoya.jp/kurashi/category/22-5-3-0-0-0-0-0-0-0.html</v>
       </c>
       <c r="C96">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D96" t="str">
         <v>data/services.js</v>
@@ -1729,10 +1729,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B97" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/category/22-5-3-0-0-0-0-0-0-0.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009395.html</v>
       </c>
       <c r="C97">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D97" t="str">
         <v>data/services.js</v>
@@ -1743,7 +1743,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B98" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009395.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1009398.html</v>
       </c>
       <c r="C98">
         <v>200</v>
@@ -1757,10 +1757,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B99" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1009398.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000137134.html</v>
       </c>
       <c r="C99">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D99" t="str">
         <v>data/services.js</v>
@@ -1771,10 +1771,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B100" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000137134.html</v>
+        <v>https://aiboren.jp/shisetsu/</v>
       </c>
       <c r="C100">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D100" t="str">
         <v>data/services.js</v>
@@ -1785,7 +1785,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B101" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009381/1009382.html</v>
+        <v>https://www.pref.aichi.jp/soshiki/jidoukatei/0000011250.html</v>
       </c>
       <c r="C101">
         <v>200</v>
@@ -1799,7 +1799,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B102" t="str">
-        <v>https://aiboren.jp/shisetsu/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016428.html</v>
       </c>
       <c r="C102">
         <v>200</v>
@@ -1813,7 +1813,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B103" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/jidoukatei/0000011250.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/woichiran.html</v>
       </c>
       <c r="C103">
         <v>200</v>
@@ -1827,7 +1827,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B104" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016428.html</v>
+        <v>https://nagoya-shakyo.jp/service/fureai-kyushoku/</v>
       </c>
       <c r="C104">
         <v>200</v>
@@ -1841,7 +1841,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B105" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/woichiran.html</v>
+        <v>https://nagoya-shakyo.jp/service/ward-shakyo/</v>
       </c>
       <c r="C105">
         <v>200</v>
@@ -1855,7 +1855,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B106" t="str">
-        <v>https://nagoya-shakyo.jp/service/fureai-kyushoku/</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/company/shitei/haishoku/</v>
       </c>
       <c r="C106">
         <v>200</v>
@@ -1869,7 +1869,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B107" t="str">
-        <v>https://nagoya-shakyo.jp/service/ward-shakyo/</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
       </c>
       <c r="C107">
         <v>200</v>
@@ -1883,7 +1883,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B108" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/company/shitei/haishoku/</v>
+        <v>https://webc.sjc.ne.jp/nagoyasj/job2_7</v>
       </c>
       <c r="C108">
         <v>200</v>
@@ -1897,10 +1897,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B109" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/page/0000132076.html</v>
       </c>
       <c r="C109">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D109" t="str">
         <v>data/services.js</v>
@@ -1911,10 +1911,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B110" t="str">
-        <v>https://webc.sjc.ne.jp/nagoyasj/job2_7</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/page/0000181424.html</v>
       </c>
       <c r="C110">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D110" t="str">
         <v>data/services.js</v>
@@ -1925,10 +1925,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B111" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/page/0000132076.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016429.html</v>
       </c>
       <c r="C111">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D111" t="str">
         <v>data/services.js</v>
@@ -1939,10 +1939,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B112" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/page/0000181424.html</v>
+        <v>https://nagoya-shakyo.jp/service/community-support/</v>
       </c>
       <c r="C112">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D112" t="str">
         <v>data/services.js</v>
@@ -1953,7 +1953,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B113" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016429.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1012252.html</v>
       </c>
       <c r="C113">
         <v>200</v>
@@ -1967,10 +1967,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B114" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009334.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/page/0000157172.html</v>
       </c>
       <c r="C114">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D114" t="str">
         <v>data/services.js</v>
@@ -1981,7 +1981,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B115" t="str">
-        <v>https://nagoya-shakyo.jp/service/community-support/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016488.html</v>
       </c>
       <c r="C115">
         <v>200</v>
@@ -1995,7 +1995,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B116" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1012252.html</v>
+        <v>https://www.bes-c.com/</v>
       </c>
       <c r="C116">
         <v>200</v>
@@ -2009,10 +2009,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B117" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/page/0000157172.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016491.html</v>
       </c>
       <c r="C117">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D117" t="str">
         <v>data/services.js</v>
@@ -2023,7 +2023,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B118" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016488.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012724/1013205/1034493/1013206.html</v>
       </c>
       <c r="C118">
         <v>200</v>
@@ -2037,7 +2037,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B119" t="str">
-        <v>https://www.bes-c.com/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008943.html</v>
       </c>
       <c r="C119">
         <v>200</v>
@@ -2051,7 +2051,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B120" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016491.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008947.html</v>
       </c>
       <c r="C120">
         <v>200</v>
@@ -2065,7 +2065,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B121" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012724/1013205/1034493/1013206.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/index.html</v>
       </c>
       <c r="C121">
         <v>200</v>
@@ -2079,7 +2079,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B122" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008943.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008920/index.html</v>
       </c>
       <c r="C122">
         <v>200</v>
@@ -2093,7 +2093,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B123" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008947.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008937.html</v>
       </c>
       <c r="C123">
         <v>200</v>
@@ -2107,7 +2107,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B124" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008920/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008938.html</v>
       </c>
       <c r="C124">
         <v>200</v>
@@ -2121,7 +2121,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B125" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008937.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008939/index.html</v>
       </c>
       <c r="C125">
         <v>200</v>
@@ -2135,7 +2135,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B126" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008938.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008949.html</v>
       </c>
       <c r="C126">
         <v>200</v>
@@ -2149,7 +2149,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B127" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008939/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034084/1009261.html</v>
       </c>
       <c r="C127">
         <v>200</v>
@@ -2163,7 +2163,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B128" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008949.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009265.html</v>
       </c>
       <c r="C128">
         <v>200</v>
@@ -2177,7 +2177,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B129" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034084/1009261.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009264.html</v>
       </c>
       <c r="C129">
         <v>200</v>
@@ -2191,7 +2191,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B130" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009265.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009260.html</v>
       </c>
       <c r="C130">
         <v>200</v>
@@ -2205,7 +2205,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B131" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009264.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009258.html</v>
       </c>
       <c r="C131">
         <v>200</v>
@@ -2219,7 +2219,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B132" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009260.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009307/1008988.html</v>
       </c>
       <c r="C132">
         <v>200</v>
@@ -2233,7 +2233,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B133" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009258.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
       </c>
       <c r="C133">
         <v>200</v>
@@ -2247,7 +2247,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B134" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009307/1008988.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034342/1008991/1036125.html</v>
       </c>
       <c r="C134">
         <v>200</v>
@@ -2261,7 +2261,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B135" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009126.html</v>
       </c>
       <c r="C135">
         <v>200</v>
@@ -2275,10 +2275,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B136" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034342/1008991/1036125.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000048704.html</v>
       </c>
       <c r="C136">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D136" t="str">
         <v>data/services.js</v>
@@ -2289,7 +2289,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B137" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009126.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008959.html</v>
       </c>
       <c r="C137">
         <v>200</v>
@@ -2303,10 +2303,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B138" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000048704.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009018.html</v>
       </c>
       <c r="C138">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D138" t="str">
         <v>data/services.js</v>
@@ -2317,10 +2317,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B139" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008959.html</v>
+        <v>https://www.city.nagoya.jp/kyoiku/page/0000051014.html</v>
       </c>
       <c r="C139">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D139" t="str">
         <v>data/services.js</v>
@@ -2331,7 +2331,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B140" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009018.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1036101.html</v>
       </c>
       <c r="C140">
         <v>200</v>
@@ -2345,10 +2345,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B141" t="str">
-        <v>https://www.city.nagoya.jp/kyoiku/page/0000051014.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1015850/1017055.html</v>
       </c>
       <c r="C141">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D141" t="str">
         <v>data/services.js</v>
@@ -2359,7 +2359,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B142" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1036101.html</v>
+        <v>https://nagoya.fureai-cloud.jp/_view/sodan/home/index</v>
       </c>
       <c r="C142">
         <v>200</v>
@@ -2373,7 +2373,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B143" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1015850/1017055.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009321/1009322.html</v>
       </c>
       <c r="C143">
         <v>200</v>
@@ -2387,7 +2387,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B144" t="str">
-        <v>https://nagoya.fureai-cloud.jp/_view/sodan/home/index</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016409.html</v>
       </c>
       <c r="C144">
         <v>200</v>
@@ -2401,7 +2401,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B145" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009321/1009322.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015819/1038028/index.html</v>
       </c>
       <c r="C145">
         <v>200</v>
@@ -2415,7 +2415,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B146" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016409.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015845.html</v>
       </c>
       <c r="C146">
         <v>200</v>
@@ -2429,7 +2429,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B147" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015819/1038028/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016404.html</v>
       </c>
       <c r="C147">
         <v>200</v>
@@ -2443,10 +2443,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B148" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015845.html</v>
+        <v>https://www.city.nagoya.jp/sportsshimin/page/0000006195.html</v>
       </c>
       <c r="C148">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D148" t="str">
         <v>data/services.js</v>
@@ -2457,7 +2457,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B149" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016404.html</v>
+        <v>https://www.nic-nagoya.or.jp/</v>
       </c>
       <c r="C149">
         <v>200</v>
@@ -2471,10 +2471,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B150" t="str">
-        <v>https://www.city.nagoya.jp/sportsshimin/page/0000006195.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016399.html</v>
       </c>
       <c r="C150">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D150" t="str">
         <v>data/services.js</v>
@@ -2485,10 +2485,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B151" t="str">
-        <v>https://www.nic-nagoya.or.jp/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016734.html</v>
       </c>
       <c r="C151">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D151" t="str">
         <v>data/services.js</v>
@@ -2499,10 +2499,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B152" t="str">
-        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000060016.html</v>
       </c>
       <c r="C152">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D152" t="str">
         <v>data/services.js</v>
@@ -2513,7 +2513,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B153" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016399.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009388.html</v>
       </c>
       <c r="C153">
         <v>200</v>
@@ -2527,10 +2527,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B154" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016734.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009391.html</v>
       </c>
       <c r="C154">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D154" t="str">
         <v>data/services.js</v>
@@ -2541,10 +2541,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B155" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000060016.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009381/1009382.html</v>
       </c>
       <c r="C155">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D155" t="str">
         <v>data/services.js</v>
@@ -2555,7 +2555,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B156" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009388.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009334.html</v>
       </c>
       <c r="C156">
         <v>200</v>
@@ -2569,7 +2569,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B157" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009391.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009389.html</v>
       </c>
       <c r="C157">
         <v>200</v>
@@ -2583,10 +2583,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B158" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009389.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000112089.html</v>
       </c>
       <c r="C158">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D158" t="str">
         <v>data/services.js</v>
@@ -2597,10 +2597,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B159" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000112089.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1016449/index.html</v>
       </c>
       <c r="C159">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D159" t="str">
         <v>data/services.js</v>
@@ -2611,7 +2611,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B160" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1016449/index.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/</v>
       </c>
       <c r="C160">
         <v>200</v>
@@ -2625,13 +2625,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B161" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/jouhou/1036432/1013386.html</v>
       </c>
       <c r="C161">
         <v>200</v>
       </c>
       <c r="D161" t="str">
-        <v>data/services.js</v>
+        <v>data/services.js, screens/DisasterScreen.js</v>
       </c>
     </row>
     <row r="162">
@@ -2639,13 +2639,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B162" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/jouhou/1036432/1013386.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/kyoujo/1036451/1013567.html</v>
       </c>
       <c r="C162">
         <v>200</v>
       </c>
       <c r="D162" t="str">
-        <v>data/services.js, screens/DisasterScreen.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="163">
@@ -2653,10 +2653,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B163" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/kyoujo/1036451/1013567.html</v>
+        <v>https://www.city.nagoya.jp/bosaikikikanri/page/0000033020.html</v>
       </c>
       <c r="C163">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D163" t="str">
         <v>data/services.js</v>
@@ -2667,10 +2667,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B164" t="str">
-        <v>https://www.city.nagoya.jp/bosaikikikanri/page/0000033020.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008962/1008963.html</v>
       </c>
       <c r="C164">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D164" t="str">
         <v>data/services.js</v>
@@ -2681,7 +2681,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B165" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008962/1008963.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016506/1016510/1016511.html</v>
       </c>
       <c r="C165">
         <v>200</v>
@@ -2695,7 +2695,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B166" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016506/1016510/1016511.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009502/1034108.html</v>
       </c>
       <c r="C166">
         <v>200</v>
@@ -2709,7 +2709,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B167" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009502/1034108.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/todokede/1007816/1007817.html</v>
       </c>
       <c r="C167">
         <v>200</v>
@@ -2723,7 +2723,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B168" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/todokede/1007816/1007817.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011832/1011834.html</v>
       </c>
       <c r="C168">
         <v>200</v>
@@ -2737,7 +2737,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B169" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011832/1011834.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011868.html</v>
       </c>
       <c r="C169">
         <v>200</v>
@@ -2751,7 +2751,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B170" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011868.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011870.html</v>
       </c>
       <c r="C170">
         <v>200</v>
@@ -2765,7 +2765,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B171" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011870.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/index.html</v>
       </c>
       <c r="C171">
         <v>200</v>
@@ -2779,7 +2779,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B172" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1035058/1012184/1046468/index.html</v>
       </c>
       <c r="C172">
         <v>200</v>
@@ -2793,7 +2793,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B173" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1035058/1012184/1046468/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016573/index.html</v>
       </c>
       <c r="C173">
         <v>200</v>
@@ -2807,7 +2807,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B174" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016573/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/index.html</v>
       </c>
       <c r="C174">
         <v>200</v>
@@ -2821,10 +2821,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B175" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/category/15-7-2-0-0-0-0-0-0-0.html</v>
       </c>
       <c r="C175">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D175" t="str">
         <v>data/services.js</v>
@@ -2835,10 +2835,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B176" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/category/15-7-2-0-0-0-0-0-0-0.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011763/1011768.html</v>
       </c>
       <c r="C176">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D176" t="str">
         <v>data/services.js</v>
@@ -2849,7 +2849,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B177" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011763/1011768.html</v>
+        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000135090_00001.html</v>
       </c>
       <c r="C177">
         <v>200</v>
@@ -2863,7 +2863,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B178" t="str">
-        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000135090_00001.html</v>
+        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000158665.html</v>
       </c>
       <c r="C178">
         <v>200</v>
@@ -2877,7 +2877,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B179" t="str">
-        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000158665.html</v>
+        <v>https://www.kyoukaikenpo.or.jp/benefit/injury_and_sickness_allowance/index.html</v>
       </c>
       <c r="C179">
         <v>200</v>
@@ -2891,7 +2891,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B180" t="str">
-        <v>https://www.kyoukaikenpo.or.jp/benefit/injury_and_sickness_allowance/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011851/1011853.html</v>
       </c>
       <c r="C180">
         <v>200</v>
@@ -2905,7 +2905,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B181" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011851/1011853.html</v>
+        <v>https://www.nenkin.go.jp/service/jukyu/seido/sonota-kyufu/shienkyufukin/20190805.html</v>
       </c>
       <c r="C181">
         <v>200</v>
@@ -2919,7 +2919,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B182" t="str">
-        <v>https://www.nenkin.go.jp/service/jukyu/seido/sonota-kyufu/shienkyufukin/20190805.html</v>
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm</v>
       </c>
       <c r="C182">
         <v>200</v>
@@ -2933,7 +2933,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B183" t="str">
-        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm</v>
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm#mushoukaLink2</v>
       </c>
       <c r="C183">
         <v>200</v>
@@ -2947,7 +2947,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B184" t="str">
-        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm#mushoukaLink2</v>
+        <v>https://www.jasso.go.jp/shogakukin/</v>
       </c>
       <c r="C184">
         <v>200</v>
@@ -2961,7 +2961,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B185" t="str">
-        <v>https://www.jasso.go.jp/shogakukin/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008946.html</v>
       </c>
       <c r="C185">
         <v>200</v>
@@ -2975,7 +2975,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B186" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008946.html</v>
+        <v>https://www.pref.aichi.jp/soshiki/zaimusisetsu/syuugakushienkin.html</v>
       </c>
       <c r="C186">
         <v>200</v>
@@ -2989,7 +2989,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B187" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016801.html</v>
+        <v>https://www.pref.aichi.jp/soshiki/shigaku/shigaku-syougakukyuhukin.html</v>
       </c>
       <c r="C187">
         <v>200</v>
@@ -3003,7 +3003,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B188" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/801/r8syougakukin.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016801.html</v>
       </c>
       <c r="C188">
         <v>200</v>
@@ -3017,7 +3017,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B189" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016798.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/801/r8syougakukin.pdf</v>
       </c>
       <c r="C189">
         <v>200</v>
@@ -3031,7 +3031,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B190" t="str">
-        <v>https://www.city.nagoya.jp/shisei/keikaku/1034903/1004666/1004670.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016798.html</v>
       </c>
       <c r="C190">
         <v>200</v>
@@ -3045,7 +3045,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B191" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1049088.html</v>
+        <v>https://www.city.nagoya.jp/shisei/keikaku/1034903/1004666/1004670.html</v>
       </c>
       <c r="C191">
         <v>200</v>
@@ -3059,7 +3059,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B192" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034073/1009017.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1049088.html</v>
       </c>
       <c r="C192">
         <v>200</v>
@@ -3073,7 +3073,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B193" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/shigaku/kikanyoukenkakunin.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034073/1009017.html</v>
       </c>
       <c r="C193">
         <v>200</v>
@@ -3087,7 +3087,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B194" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1050641.html</v>
+        <v>https://www.pref.aichi.jp/soshiki/zaimusisetsu/koutoukyouikumusyouka.html</v>
       </c>
       <c r="C194">
         <v>200</v>
@@ -3101,13 +3101,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B195" t="str">
-        <v>https://www.city.nagoya.jp/</v>
+        <v>https://www.pref.aichi.jp/soshiki/shigaku/kikanyoukenkakunin.html</v>
       </c>
       <c r="C195">
         <v>200</v>
       </c>
       <c r="D195" t="str">
-        <v>screens/DetailScreen.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="196">
@@ -3115,13 +3115,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B196" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/jigyosho/</v>
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1050641.html</v>
       </c>
       <c r="C196">
         <v>200</v>
       </c>
       <c r="D196" t="str">
-        <v>screens/DetailScreen.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="197">
@@ -3129,13 +3129,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B197" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/1013492.html</v>
+        <v>https://www.city.nagoya.jp/</v>
       </c>
       <c r="C197">
         <v>200</v>
       </c>
       <c r="D197" t="str">
-        <v>screens/DisasterScreen.js</v>
+        <v>screens/DetailScreen.js</v>
       </c>
     </row>
     <row r="198">
@@ -3143,67 +3143,516 @@
         <v>✅ 正常</v>
       </c>
       <c r="B198" t="str">
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/jigyosho/</v>
+      </c>
+      <c r="C198">
+        <v>200</v>
+      </c>
+      <c r="D198" t="str">
+        <v>screens/DetailScreen.js</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B199" t="str">
+        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/1013492.html</v>
+      </c>
+      <c r="C199">
+        <v>200</v>
+      </c>
+      <c r="D199" t="str">
+        <v>screens/DisasterScreen.js</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B200" t="str">
         <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036428.html</v>
       </c>
-      <c r="C198">
-        <v>200</v>
-      </c>
-      <c r="D198" t="str">
+      <c r="C200">
+        <v>200</v>
+      </c>
+      <c r="D200" t="str">
         <v>screens/DisasterScreen.js</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D198"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D200"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>状態</v>
+        <v>URL</v>
+      </c>
+      <c r="B1" t="str">
+        <v>旧タイトル</v>
+      </c>
+      <c r="C1" t="str">
+        <v>新タイトル</v>
+      </c>
+      <c r="D1" t="str">
+        <v>参照ファイル</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>検知なし</v>
+        <v>https://www.bes-c.com/</v>
+      </c>
+      <c r="B2" t="str">
+        <v>名古屋市高齢者就業支援センター</v>
+      </c>
+      <c r="C2" t="str">
+        <v>名古屋市高齢者就業支援センター</v>
+      </c>
+      <c r="D2" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016409.html</v>
+      </c>
+      <c r="B3" t="str">
+        <v>名古屋市子どもの権利相談室「なごもっか」｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="C3" t="str">
+        <v>名古屋市子どもの権利相談室「なごもっか」｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="D3" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>https://www.nic-nagoya.or.jp/</v>
+      </c>
+      <c r="B4" t="str">
+        <v>名古屋国際センター | Nagoya International Center</v>
+      </c>
+      <c r="C4" t="str">
+        <v>One moment, please...</v>
+      </c>
+      <c r="D4" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
+      </c>
+      <c r="B5" t="str">
+        <v>行政相談 | 名古屋国際センター | Nagoya International Center</v>
+      </c>
+      <c r="C5" t="str">
+        <v>One moment, please...</v>
+      </c>
+      <c r="D5" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/1013492.html</v>
+      </c>
+      <c r="B6" t="str">
+        <v>指定緊急避難場所・指定避難所の指定｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="C6" t="str">
+        <v>指定緊急避難場所・指定避難所の指定｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="D6" t="str">
+        <v>screens/DisasterScreen.js</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>状態</v>
+        <v>タブ</v>
+      </c>
+      <c r="B1" t="str">
+        <v>タブURL</v>
+      </c>
+      <c r="C1" t="str">
+        <v>種別</v>
+      </c>
+      <c r="D1" t="str">
+        <v>対象URL</v>
+      </c>
+      <c r="E1" t="str">
+        <v>内容</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>検知なし</v>
+        <v>防災・安全安心</v>
+      </c>
+      <c r="B2" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="C2" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D2" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012913/1012914/1052131.html</v>
+      </c>
+      <c r="E2" t="str">
+        <v>消防職員の熱中症対策として製氷機を寄贈頂きました</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="B3" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="C3" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D3" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1013090/1013096/1051100.html</v>
+      </c>
+      <c r="E3" t="str">
+        <v>令和8年度名東の日を開催しました！</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="B4" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="C4" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D4" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/zeikin/1007927/1050342.html</v>
+      </c>
+      <c r="E4" t="str">
+        <v>税務証明等手数料の改定のお知らせ（令和8年10月1日から）</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="B5" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="C5" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D5" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/douro/1014806/1034763/1014850.html</v>
+      </c>
+      <c r="E5" t="str">
+        <v>堀川ギャラリー</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="B6" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="C6" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D6" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051109.html</v>
+      </c>
+      <c r="E6" t="str">
+        <v>めざせ！！水の環復活－学んでみよう、水のことー浄水場と水循環</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="B7" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="C7" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D7" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051801.html</v>
+      </c>
+      <c r="E7" t="str">
+        <v>「下水道科学館まつり」を開催します！</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="B8" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="C8" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D8" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1035058/1012184/1050522.html</v>
+      </c>
+      <c r="E8" t="str">
+        <v>令和8年10月から、粗大ごみの対象が変わります</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="B9" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="C9" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D9" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1050354.html</v>
+      </c>
+      <c r="E9" t="str">
+        <v>中央卸売市場本場 大人のための市場見学 参加者募集</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="B10" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="C10" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D10" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034338/1051902.html</v>
+      </c>
+      <c r="E10" t="str">
+        <v>令和8年度 里親制度説明＆里親の体験談を聞く会</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="B11" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="C11" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D11" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/jisedai/1009754/1009755/1052076.html</v>
+      </c>
+      <c r="E11" t="str">
+        <v>令和8年度なごっちフレンズワークショップ (令和8年8月25日)</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="B12" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="C12" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D12" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1034069/1051899.html</v>
+      </c>
+      <c r="E12" t="str">
+        <v>災害の備えどうしてる？－慢性疾患のある子どもと家族のための災害対策を見直そうー</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="B13" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="C13" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D13" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1051292.html</v>
+      </c>
+      <c r="E13" t="str">
+        <v>令和8年7月25日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="B14" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="C14" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D14" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1034096.html</v>
+      </c>
+      <c r="E14" t="str">
+        <v>幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="B15" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="C15" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D15" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017010/1051839.html</v>
+      </c>
+      <c r="E15" t="str">
+        <v>学習用端末の準備について[市立高等学校・特別支援学校高等部]</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="B16" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="C16" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D16" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1035053/1051909.html</v>
+      </c>
+      <c r="E16" t="str">
+        <v>令和8年度音訳ボランティア養成講座</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="B17" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="C17" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D17" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1011432/1051796.html</v>
+      </c>
+      <c r="E17" t="str">
+        <v>専用水道に関する届出</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="B18" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="C18" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D18" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1034419/1050801.html</v>
+      </c>
+      <c r="E18" t="str">
+        <v>令和8年度つながり・支えあおう地域福祉のすゝめ（イベントのご案内）</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="B19" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="C19" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D19" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/1016644/1041946/1050026.html</v>
+      </c>
+      <c r="E19" t="str">
+        <v>NHKハートフォーラム・名古屋市発達障害者支援センターりんくす名古屋講演会「実は身近な発達障害 援助を求める力と合理的配慮 －『困った』を伝える・受けとめる－」のご案内</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="B20" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="C20" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D20" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016746/1051650.html</v>
+      </c>
+      <c r="E20" t="str">
+        <v>愛知県市民後見人等養成研修について</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="B21" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="C21" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D21" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1051406/1051435.html</v>
+      </c>
+      <c r="E21" t="str">
+        <v>民生委員・児童委員専用サイト（名古屋市民生委員・児童委員の部屋）</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E21"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M56"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3751,9 +4200,637 @@
         <v>data/services.js</v>
       </c>
     </row>
+    <row r="28">
+      <c r="B28" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C28" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D28" t="str">
+        <v>https://www.pref.aichi.jp/soshiki/jutakukanri/bosyuannai.html</v>
+      </c>
+      <c r="E28" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F28" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C29" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D29" t="str">
+        <v>https://www.pref.aichi.jp/soshiki/imu/0000050084.html</v>
+      </c>
+      <c r="E29" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F29" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C30" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D30" t="str">
+        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
+      </c>
+      <c r="E30" t="str">
+        <v>ERROR</v>
+      </c>
+      <c r="F30" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C31" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D31" t="str">
+        <v>https://www.pref.aichi.jp/uploaded/attachment/620030.pdf</v>
+      </c>
+      <c r="E31" t="str">
+        <v>ERROR</v>
+      </c>
+      <c r="F31" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C32" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D32" t="str">
+        <v>https://www.bes-c.com/</v>
+      </c>
+      <c r="F32" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G32" t="str">
+        <v>名古屋市高齢者就業支援センター</v>
+      </c>
+      <c r="H32" t="str">
+        <v>名古屋市高齢者就業支援センター</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C33" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D33" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016409.html</v>
+      </c>
+      <c r="F33" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G33" t="str">
+        <v>名古屋市子どもの権利相談室「なごもっか」｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="H33" t="str">
+        <v>名古屋市子どもの権利相談室「なごもっか」｜名古屋市公式ウェブサイト</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C34" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D34" t="str">
+        <v>https://www.nic-nagoya.or.jp/</v>
+      </c>
+      <c r="F34" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G34" t="str">
+        <v>名古屋国際センター | Nagoya International Center</v>
+      </c>
+      <c r="H34" t="str">
+        <v>One moment, please...</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C35" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D35" t="str">
+        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
+      </c>
+      <c r="F35" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G35" t="str">
+        <v>行政相談 | 名古屋国際センター | Nagoya International Center</v>
+      </c>
+      <c r="H35" t="str">
+        <v>One moment, please...</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C36" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D36" t="str">
+        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/1013492.html</v>
+      </c>
+      <c r="F36" t="str">
+        <v>screens/DisasterScreen.js</v>
+      </c>
+      <c r="G36" t="str">
+        <v>指定緊急避難場所・指定避難所の指定｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="H36" t="str">
+        <v>指定緊急避難場所・指定避難所の指定｜名古屋市公式ウェブサイト</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C37" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I37" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J37" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K37" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L37" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012913/1012914/1052131.html</v>
+      </c>
+      <c r="M37" t="str">
+        <v>消防職員の熱中症対策として製氷機を寄贈頂きました</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C38" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I38" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J38" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K38" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L38" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1013090/1013096/1051100.html</v>
+      </c>
+      <c r="M38" t="str">
+        <v>令和8年度名東の日を開催しました！</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C39" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I39" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J39" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K39" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L39" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/zeikin/1007927/1050342.html</v>
+      </c>
+      <c r="M39" t="str">
+        <v>税務証明等手数料の改定のお知らせ（令和8年10月1日から）</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C40" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I40" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J40" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K40" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L40" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/douro/1014806/1034763/1014850.html</v>
+      </c>
+      <c r="M40" t="str">
+        <v>堀川ギャラリー</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C41" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I41" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J41" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K41" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L41" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051109.html</v>
+      </c>
+      <c r="M41" t="str">
+        <v>めざせ！！水の環復活－学んでみよう、水のことー浄水場と水循環</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C42" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I42" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J42" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K42" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L42" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051801.html</v>
+      </c>
+      <c r="M42" t="str">
+        <v>「下水道科学館まつり」を開催します！</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C43" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I43" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J43" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K43" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L43" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1035058/1012184/1050522.html</v>
+      </c>
+      <c r="M43" t="str">
+        <v>令和8年10月から、粗大ごみの対象が変わります</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C44" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I44" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J44" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K44" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L44" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1050354.html</v>
+      </c>
+      <c r="M44" t="str">
+        <v>中央卸売市場本場 大人のための市場見学 参加者募集</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C45" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I45" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J45" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K45" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L45" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034338/1051902.html</v>
+      </c>
+      <c r="M45" t="str">
+        <v>令和8年度 里親制度説明＆里親の体験談を聞く会</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C46" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I46" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J46" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K46" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L46" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/jisedai/1009754/1009755/1052076.html</v>
+      </c>
+      <c r="M46" t="str">
+        <v>令和8年度なごっちフレンズワークショップ (令和8年8月25日)</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C47" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I47" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J47" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K47" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L47" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1034069/1051899.html</v>
+      </c>
+      <c r="M47" t="str">
+        <v>災害の備えどうしてる？－慢性疾患のある子どもと家族のための災害対策を見直そうー</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C48" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I48" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J48" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K48" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L48" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1051292.html</v>
+      </c>
+      <c r="M48" t="str">
+        <v>令和8年7月25日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C49" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I49" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J49" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K49" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L49" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1034096.html</v>
+      </c>
+      <c r="M49" t="str">
+        <v>幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C50" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I50" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J50" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K50" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L50" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017010/1051839.html</v>
+      </c>
+      <c r="M50" t="str">
+        <v>学習用端末の準備について[市立高等学校・特別支援学校高等部]</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C51" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I51" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J51" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K51" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L51" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1035053/1051909.html</v>
+      </c>
+      <c r="M51" t="str">
+        <v>令和8年度音訳ボランティア養成講座</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C52" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I52" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J52" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K52" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L52" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1011432/1051796.html</v>
+      </c>
+      <c r="M52" t="str">
+        <v>専用水道に関する届出</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C53" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I53" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J53" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K53" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L53" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1034419/1050801.html</v>
+      </c>
+      <c r="M53" t="str">
+        <v>令和8年度つながり・支えあおう地域福祉のすゝめ（イベントのご案内）</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C54" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I54" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J54" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K54" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L54" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/1016644/1041946/1050026.html</v>
+      </c>
+      <c r="M54" t="str">
+        <v>NHKハートフォーラム・名古屋市発達障害者支援センターりんくす名古屋講演会「実は身近な発達障害 援助を求める力と合理的配慮 －『困った』を伝える・受けとめる－」のご案内</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C55" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I55" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J55" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K55" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L55" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016746/1051650.html</v>
+      </c>
+      <c r="M55" t="str">
+        <v>愛知県市民後見人等養成研修について</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="C56" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I56" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J56" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K56" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L56" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1051406/1051435.html</v>
+      </c>
+      <c r="M56" t="str">
+        <v>民生委員・児童委員専用サイト（名古屋市民生委員・児童委員の部屋）</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M56"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reports/latest-report.xlsx
+++ b/reports/latest-report.xlsx
@@ -378,7 +378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D200"/>
+  <dimension ref="A1:D231"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,7 +413,7 @@
         <v>❌ リンク切れ</v>
       </c>
       <c r="B3" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/imu/0000050084.html</v>
+        <v>https://hikikomori.city.nagoya.jp/</v>
       </c>
       <c r="C3" t="str">
         <v>TIMEOUT</v>
@@ -427,10 +427,10 @@
         <v>❌ リンク切れ</v>
       </c>
       <c r="B4" t="str">
-        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
+        <v>https://www.pref.aichi.jp/soshiki/jidoukatei/0000011250.html</v>
       </c>
       <c r="C4" t="str">
-        <v>ERROR</v>
+        <v>TIMEOUT</v>
       </c>
       <c r="D4" t="str">
         <v>data/services.js</v>
@@ -441,10 +441,10 @@
         <v>❌ リンク切れ</v>
       </c>
       <c r="B5" t="str">
-        <v>https://www.pref.aichi.jp/uploaded/attachment/620030.pdf</v>
+        <v>https://nagoya-shakyo.jp/service/fureai-kyushoku/</v>
       </c>
       <c r="C5" t="str">
-        <v>ERROR</v>
+        <v>TIMEOUT</v>
       </c>
       <c r="D5" t="str">
         <v>data/services.js</v>
@@ -452,100 +452,100 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>✅ 正常</v>
+        <v>❌ リンク切れ</v>
       </c>
       <c r="B6" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036294.html</v>
-      </c>
-      <c r="C6">
-        <v>200</v>
+        <v>https://nagoya-shakyo.jp/service/ward-shakyo/</v>
+      </c>
+      <c r="C6" t="str">
+        <v>TIMEOUT</v>
       </c>
       <c r="D6" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>✅ 正常</v>
+        <v>❌ リンク切れ</v>
       </c>
       <c r="B7" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/index.html</v>
-      </c>
-      <c r="C7">
-        <v>200</v>
+        <v>https://nagoya-shakyo.jp/service/community-support/</v>
+      </c>
+      <c r="C7" t="str">
+        <v>TIMEOUT</v>
       </c>
       <c r="D7" t="str">
-        <v>data/districts.js, screens/DisasterScreen.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>✅ 正常</v>
+        <v>❌ リンク切れ</v>
       </c>
       <c r="B8" t="str">
-        <v>https://www.city.nagoya.jp/chikusa/kurashi/</v>
-      </c>
-      <c r="C8">
-        <v>200</v>
+        <v>https://www.pref.aichi.jp/soshiki/imu/0000050084.html</v>
+      </c>
+      <c r="C8" t="str">
+        <v>TIMEOUT</v>
       </c>
       <c r="D8" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>✅ 正常</v>
+        <v>❌ リンク切れ</v>
       </c>
       <c r="B9" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036299.html</v>
-      </c>
-      <c r="C9">
-        <v>200</v>
+        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
+      </c>
+      <c r="C9" t="str">
+        <v>ERROR</v>
       </c>
       <c r="D9" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>✅ 正常</v>
+        <v>❌ リンク切れ</v>
       </c>
       <c r="B10" t="str">
-        <v>https://www.city.nagoya.jp/higashi/kurashi/</v>
-      </c>
-      <c r="C10">
-        <v>200</v>
+        <v>https://www.pref.aichi.jp/soshiki/zaimusisetsu/syuugakushienkin.html</v>
+      </c>
+      <c r="C10" t="str">
+        <v>TIMEOUT</v>
       </c>
       <c r="D10" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>✅ 正常</v>
+        <v>❌ リンク切れ</v>
       </c>
       <c r="B11" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036302.html</v>
-      </c>
-      <c r="C11">
-        <v>200</v>
+        <v>https://www.pref.aichi.jp/uploaded/attachment/620030.pdf</v>
+      </c>
+      <c r="C11" t="str">
+        <v>TIMEOUT</v>
       </c>
       <c r="D11" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>✅ 正常</v>
+        <v>❌ リンク切れ</v>
       </c>
       <c r="B12" t="str">
-        <v>https://www.city.nagoya.jp/kita/kurashi/</v>
-      </c>
-      <c r="C12">
-        <v>200</v>
+        <v>https://www.pref.aichi.jp/soshiki/shigaku/shigaku-syougakukyuhukin.html</v>
+      </c>
+      <c r="C12" t="str">
+        <v>TIMEOUT</v>
       </c>
       <c r="D12" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="13">
@@ -553,7 +553,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B13" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036293.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036294.html</v>
       </c>
       <c r="C13">
         <v>200</v>
@@ -567,13 +567,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B14" t="str">
-        <v>https://www.city.nagoya.jp/nishi/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/index.html</v>
       </c>
       <c r="C14">
         <v>200</v>
       </c>
       <c r="D14" t="str">
-        <v>data/districts.js</v>
+        <v>data/districts.js, screens/DisasterScreen.js</v>
       </c>
     </row>
     <row r="15">
@@ -581,7 +581,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B15" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036297.html</v>
+        <v>https://www.city.nagoya.jp/chikusa/kurashi/</v>
       </c>
       <c r="C15">
         <v>200</v>
@@ -595,7 +595,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B16" t="str">
-        <v>https://www.city.nagoya.jp/nakamura/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036299.html</v>
       </c>
       <c r="C16">
         <v>200</v>
@@ -609,7 +609,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B17" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036295.html</v>
+        <v>https://www.city.nagoya.jp/higashi/kurashi/</v>
       </c>
       <c r="C17">
         <v>200</v>
@@ -623,7 +623,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B18" t="str">
-        <v>https://www.city.nagoya.jp/naka/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036302.html</v>
       </c>
       <c r="C18">
         <v>200</v>
@@ -637,7 +637,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B19" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036291.html</v>
+        <v>https://www.city.nagoya.jp/kita/kurashi/</v>
       </c>
       <c r="C19">
         <v>200</v>
@@ -651,7 +651,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B20" t="str">
-        <v>https://www.city.nagoya.jp/showa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036293.html</v>
       </c>
       <c r="C20">
         <v>200</v>
@@ -665,7 +665,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B21" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036292.html</v>
+        <v>https://www.city.nagoya.jp/nishi/kurashi/</v>
       </c>
       <c r="C21">
         <v>200</v>
@@ -679,7 +679,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B22" t="str">
-        <v>https://www.city.nagoya.jp/mizuho/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036297.html</v>
       </c>
       <c r="C22">
         <v>200</v>
@@ -693,7 +693,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B23" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036301.html</v>
+        <v>https://www.city.nagoya.jp/nakamura/kurashi/</v>
       </c>
       <c r="C23">
         <v>200</v>
@@ -707,7 +707,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B24" t="str">
-        <v>https://www.city.nagoya.jp/atsuta/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036295.html</v>
       </c>
       <c r="C24">
         <v>200</v>
@@ -721,7 +721,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B25" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036296.html</v>
+        <v>https://www.city.nagoya.jp/naka/kurashi/</v>
       </c>
       <c r="C25">
         <v>200</v>
@@ -735,7 +735,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B26" t="str">
-        <v>https://www.city.nagoya.jp/nakagawa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036291.html</v>
       </c>
       <c r="C26">
         <v>200</v>
@@ -749,7 +749,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B27" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036289.html</v>
+        <v>https://www.city.nagoya.jp/showa/kurashi/</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -763,7 +763,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B28" t="str">
-        <v>https://www.city.nagoya.jp/minato/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036292.html</v>
       </c>
       <c r="C28">
         <v>200</v>
@@ -777,7 +777,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B29" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036300.html</v>
+        <v>https://www.city.nagoya.jp/mizuho/kurashi/</v>
       </c>
       <c r="C29">
         <v>200</v>
@@ -791,7 +791,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B30" t="str">
-        <v>https://www.city.nagoya.jp/minami/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036301.html</v>
       </c>
       <c r="C30">
         <v>200</v>
@@ -805,7 +805,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B31" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036290.html</v>
+        <v>https://www.city.nagoya.jp/atsuta/kurashi/</v>
       </c>
       <c r="C31">
         <v>200</v>
@@ -819,7 +819,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B32" t="str">
-        <v>https://www.city.nagoya.jp/moriyama/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036296.html</v>
       </c>
       <c r="C32">
         <v>200</v>
@@ -833,7 +833,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B33" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036304.html</v>
+        <v>https://www.city.nagoya.jp/nakagawa/kurashi/</v>
       </c>
       <c r="C33">
         <v>200</v>
@@ -847,7 +847,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B34" t="str">
-        <v>https://www.city.nagoya.jp/midori/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036289.html</v>
       </c>
       <c r="C34">
         <v>200</v>
@@ -861,7 +861,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B35" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036303.html</v>
+        <v>https://www.city.nagoya.jp/minato/kurashi/</v>
       </c>
       <c r="C35">
         <v>200</v>
@@ -875,7 +875,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B36" t="str">
-        <v>https://www.city.nagoya.jp/meito/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036300.html</v>
       </c>
       <c r="C36">
         <v>200</v>
@@ -889,7 +889,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B37" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036298.html</v>
+        <v>https://www.city.nagoya.jp/minami/kurashi/</v>
       </c>
       <c r="C37">
         <v>200</v>
@@ -903,7 +903,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B38" t="str">
-        <v>https://www.city.nagoya.jp/tempaku/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036290.html</v>
       </c>
       <c r="C38">
         <v>200</v>
@@ -917,13 +917,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B39" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000034404.html</v>
+        <v>https://www.city.nagoya.jp/moriyama/kurashi/</v>
       </c>
       <c r="C39">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D39" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="40">
@@ -931,13 +931,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B40" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009333.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036304.html</v>
       </c>
       <c r="C40">
         <v>200</v>
       </c>
       <c r="D40" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="41">
@@ -945,13 +945,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B41" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1009009.html</v>
+        <v>https://www.city.nagoya.jp/midori/kurashi/</v>
       </c>
       <c r="C41">
         <v>200</v>
       </c>
       <c r="D41" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="42">
@@ -959,13 +959,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B42" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009270/1034086.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036303.html</v>
       </c>
       <c r="C42">
         <v>200</v>
       </c>
       <c r="D42" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="43">
@@ -973,13 +973,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B43" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009353/1034092.html</v>
+        <v>https://www.city.nagoya.jp/meito/kurashi/</v>
       </c>
       <c r="C43">
         <v>200</v>
       </c>
       <c r="D43" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="44">
@@ -987,13 +987,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B44" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009286/index.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036298.html</v>
       </c>
       <c r="C44">
         <v>200</v>
       </c>
       <c r="D44" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="45">
@@ -1001,13 +1001,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B45" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1034088.html</v>
+        <v>https://www.city.nagoya.jp/tempaku/kurashi/</v>
       </c>
       <c r="C45">
         <v>200</v>
       </c>
       <c r="D45" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="46">
@@ -1015,7 +1015,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B46" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009387.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008973.html</v>
       </c>
       <c r="C46">
         <v>200</v>
@@ -1029,7 +1029,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B47" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009393.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009333.html</v>
       </c>
       <c r="C47">
         <v>200</v>
@@ -1043,7 +1043,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B48" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011821/1011823.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1009009.html</v>
       </c>
       <c r="C48">
         <v>200</v>
@@ -1057,7 +1057,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B49" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008956.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009270/1034086.html</v>
       </c>
       <c r="C49">
         <v>200</v>
@@ -1071,7 +1071,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B50" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008955.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009353/1034092.html</v>
       </c>
       <c r="C50">
         <v>200</v>
@@ -1085,7 +1085,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B51" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/ichiran.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009286/index.html</v>
       </c>
       <c r="C51">
         <v>200</v>
@@ -1099,10 +1099,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B52" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096199.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1034088.html</v>
       </c>
       <c r="C52">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D52" t="str">
         <v>data/services.js</v>
@@ -1113,10 +1113,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B53" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000000479.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009387.html</v>
       </c>
       <c r="C53">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D53" t="str">
         <v>data/services.js</v>
@@ -1127,7 +1127,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B54" t="str">
-        <v>https://www.city.nagoya.jp/lifescene/byouki/1017964.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009393.html</v>
       </c>
       <c r="C54">
         <v>200</v>
@@ -1141,7 +1141,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B55" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/seido/toiawase/</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011821/1011823.html</v>
       </c>
       <c r="C55">
         <v>200</v>
@@ -1155,7 +1155,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B56" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016496/1016502.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008956.html</v>
       </c>
       <c r="C56">
         <v>200</v>
@@ -1169,7 +1169,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B57" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/1016536.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008955.html</v>
       </c>
       <c r="C57">
         <v>200</v>
@@ -1183,7 +1183,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B58" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011776/1034706/1011784.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/ichiran.html</v>
       </c>
       <c r="C58">
         <v>200</v>
@@ -1197,7 +1197,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B59" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009456/1009457/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008960.html</v>
       </c>
       <c r="C59">
         <v>200</v>
@@ -1211,7 +1211,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B60" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009019.html</v>
       </c>
       <c r="C60">
         <v>200</v>
@@ -1225,7 +1225,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B61" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1012157/1033970.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008974.html</v>
       </c>
       <c r="C61">
         <v>200</v>
@@ -1239,7 +1239,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B62" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1015763/1015815.html</v>
+        <v>https://www.city.nagoya.jp/lifescene/byouki/1017964.html</v>
       </c>
       <c r="C62">
         <v>200</v>
@@ -1253,7 +1253,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B63" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011793/1011807/1011810.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/seido/toiawase/</v>
       </c>
       <c r="C63">
         <v>200</v>
@@ -1267,7 +1267,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B64" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016739.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016496/1016502.html</v>
       </c>
       <c r="C64">
         <v>200</v>
@@ -1281,7 +1281,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B65" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/1016536.html</v>
       </c>
       <c r="C65">
         <v>200</v>
@@ -1295,7 +1295,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B66" t="str">
-        <v>https://www.hellowork.mhlw.go.jp/insurance/insurance_guide.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011776/1034706/1011784.html</v>
       </c>
       <c r="C66">
         <v>200</v>
@@ -1309,7 +1309,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B67" t="str">
-        <v>https://jsite.mhlw.go.jp/aichi-hellowork/list.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009456/1009457/index.html</v>
       </c>
       <c r="C67">
         <v>200</v>
@@ -1323,7 +1323,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B68" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
       </c>
       <c r="C68">
         <v>200</v>
@@ -1337,7 +1337,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B69" t="str">
-        <v>https://www.nagojob.city.nagoya.jp/</v>
+        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1012157/1033970.html</v>
       </c>
       <c r="C69">
         <v>200</v>
@@ -1351,7 +1351,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B70" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/tetyou/</v>
+        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1015763/1015815.html</v>
       </c>
       <c r="C70">
         <v>200</v>
@@ -1365,7 +1365,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B71" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/soudan/fukushikakari.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011793/1011807/1011810.html</v>
       </c>
       <c r="C71">
         <v>200</v>
@@ -1379,7 +1379,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B72" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/fukushi_service.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016739.html</v>
       </c>
       <c r="C72">
         <v>200</v>
@@ -1393,7 +1393,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B73" t="str">
-        <v>https://www.city.nagoya.jp/jigyou/sangyou/1026356/1035103/1026446/1026447.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/index.html</v>
       </c>
       <c r="C73">
         <v>200</v>
@@ -1407,7 +1407,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B74" t="str">
-        <v>https://weljob-nagoya.com/</v>
+        <v>https://www.hellowork.mhlw.go.jp/insurance/insurance_guide.html</v>
       </c>
       <c r="C74">
         <v>200</v>
@@ -1421,7 +1421,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B75" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
+        <v>https://jsite.mhlw.go.jp/aichi-hellowork/list.html</v>
       </c>
       <c r="C75">
         <v>200</v>
@@ -1435,7 +1435,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B76" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/622/linksweb.pdf</v>
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
       </c>
       <c r="C76">
         <v>200</v>
@@ -1449,7 +1449,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B77" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
+        <v>https://www.nagojob.city.nagoya.jp/</v>
       </c>
       <c r="C77">
         <v>200</v>
@@ -1463,7 +1463,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B78" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/675/annnai.pdf</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/tetyou/</v>
       </c>
       <c r="C78">
         <v>200</v>
@@ -1477,7 +1477,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B79" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/soudan/fukushikakari.html</v>
       </c>
       <c r="C79">
         <v>200</v>
@@ -1491,7 +1491,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B80" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/fukushi_service.html</v>
       </c>
       <c r="C80">
         <v>200</v>
@@ -1505,7 +1505,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B81" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
+        <v>https://www.city.nagoya.jp/jigyou/sangyou/1026356/1035103/1026446/1026447.html</v>
       </c>
       <c r="C81">
         <v>200</v>
@@ -1519,7 +1519,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B82" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008978.html</v>
+        <v>https://weljob-nagoya.com/</v>
       </c>
       <c r="C82">
         <v>200</v>
@@ -1533,7 +1533,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B83" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/008/978/0413tirasi.pdf</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
       </c>
       <c r="C83">
         <v>200</v>
@@ -1547,10 +1547,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B84" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096194.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/622/linksweb.pdf</v>
       </c>
       <c r="C84">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D84" t="str">
         <v>data/services.js</v>
@@ -1561,7 +1561,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B85" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/009/017/r710_help.pdf</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
       </c>
       <c r="C85">
         <v>200</v>
@@ -1575,7 +1575,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B86" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1034087.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/675/annnai.pdf</v>
       </c>
       <c r="C86">
         <v>200</v>
@@ -1589,7 +1589,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B87" t="str">
-        <v>https://www.kosodate.city.nagoya.jp/kids/nobinobi.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
       </c>
       <c r="C87">
         <v>200</v>
@@ -1603,7 +1603,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B88" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1009278.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
       </c>
       <c r="C88">
         <v>200</v>
@@ -1617,7 +1617,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B89" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009024/1009026.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
       </c>
       <c r="C89">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B90" t="str">
-        <v>https://www.kosodate.city.nagoya.jp/play/supportbases.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008978.html</v>
       </c>
       <c r="C90">
         <v>200</v>
@@ -1645,7 +1645,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B91" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034075/1009021.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/008/978/0413tirasi.pdf</v>
       </c>
       <c r="C91">
         <v>200</v>
@@ -1659,7 +1659,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B92" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034072/1009016.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034073/1009017.html</v>
       </c>
       <c r="C92">
         <v>200</v>
@@ -1673,7 +1673,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B93" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016744.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/009/017/r710_help.pdf</v>
       </c>
       <c r="C93">
         <v>200</v>
@@ -1687,7 +1687,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B94" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016742.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1034087.html</v>
       </c>
       <c r="C94">
         <v>200</v>
@@ -1701,7 +1701,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B95" t="str">
-        <v>https://hikikomori.city.nagoya.jp/</v>
+        <v>https://www.kosodate.city.nagoya.jp/kids/nobinobi.html</v>
       </c>
       <c r="C95">
         <v>200</v>
@@ -1715,10 +1715,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B96" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/category/22-5-3-0-0-0-0-0-0-0.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1009278.html</v>
       </c>
       <c r="C96">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D96" t="str">
         <v>data/services.js</v>
@@ -1729,7 +1729,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B97" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009395.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009024/1009026.html</v>
       </c>
       <c r="C97">
         <v>200</v>
@@ -1743,7 +1743,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B98" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1009398.html</v>
+        <v>https://www.kosodate.city.nagoya.jp/play/supportbases.html</v>
       </c>
       <c r="C98">
         <v>200</v>
@@ -1757,10 +1757,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B99" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000137134.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034075/1009021.html</v>
       </c>
       <c r="C99">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D99" t="str">
         <v>data/services.js</v>
@@ -1771,7 +1771,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B100" t="str">
-        <v>https://aiboren.jp/shisetsu/</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034072/1009016.html</v>
       </c>
       <c r="C100">
         <v>200</v>
@@ -1785,7 +1785,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B101" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/jidoukatei/0000011250.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016744.html</v>
       </c>
       <c r="C101">
         <v>200</v>
@@ -1799,7 +1799,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B102" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016428.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016742.html</v>
       </c>
       <c r="C102">
         <v>200</v>
@@ -1813,7 +1813,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B103" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/woichiran.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016586/1033908.html</v>
       </c>
       <c r="C103">
         <v>200</v>
@@ -1827,7 +1827,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B104" t="str">
-        <v>https://nagoya-shakyo.jp/service/fureai-kyushoku/</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009395.html</v>
       </c>
       <c r="C104">
         <v>200</v>
@@ -1841,7 +1841,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B105" t="str">
-        <v>https://nagoya-shakyo.jp/service/ward-shakyo/</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1009398.html</v>
       </c>
       <c r="C105">
         <v>200</v>
@@ -1855,7 +1855,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B106" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/company/shitei/haishoku/</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009380.html</v>
       </c>
       <c r="C106">
         <v>200</v>
@@ -1869,7 +1869,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B107" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
+        <v>https://aiboren.jp/shisetsu/</v>
       </c>
       <c r="C107">
         <v>200</v>
@@ -1883,7 +1883,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B108" t="str">
-        <v>https://webc.sjc.ne.jp/nagoyasj/job2_7</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016428.html</v>
       </c>
       <c r="C108">
         <v>200</v>
@@ -1897,10 +1897,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B109" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/page/0000132076.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/woichiran.html</v>
       </c>
       <c r="C109">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D109" t="str">
         <v>data/services.js</v>
@@ -1911,10 +1911,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B110" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/page/0000181424.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/company/shitei/haishoku/</v>
       </c>
       <c r="C110">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D110" t="str">
         <v>data/services.js</v>
@@ -1925,7 +1925,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B111" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016429.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
       </c>
       <c r="C111">
         <v>200</v>
@@ -1939,7 +1939,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B112" t="str">
-        <v>https://nagoya-shakyo.jp/service/community-support/</v>
+        <v>https://webc.sjc.ne.jp/nagoyasj/job2_7</v>
       </c>
       <c r="C112">
         <v>200</v>
@@ -1953,7 +1953,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B113" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1012252.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016431.html</v>
       </c>
       <c r="C113">
         <v>200</v>
@@ -1967,10 +1967,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B114" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/page/0000157172.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016433.html</v>
       </c>
       <c r="C114">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D114" t="str">
         <v>data/services.js</v>
@@ -1981,7 +1981,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B115" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016488.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016429.html</v>
       </c>
       <c r="C115">
         <v>200</v>
@@ -1995,7 +1995,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B116" t="str">
-        <v>https://www.bes-c.com/</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1012252.html</v>
       </c>
       <c r="C116">
         <v>200</v>
@@ -2009,7 +2009,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B117" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016491.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016440.html</v>
       </c>
       <c r="C117">
         <v>200</v>
@@ -2023,7 +2023,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B118" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012724/1013205/1034493/1013206.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016488.html</v>
       </c>
       <c r="C118">
         <v>200</v>
@@ -2037,7 +2037,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B119" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008943.html</v>
+        <v>https://www.bes-c.com/</v>
       </c>
       <c r="C119">
         <v>200</v>
@@ -2051,7 +2051,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B120" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008947.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016491.html</v>
       </c>
       <c r="C120">
         <v>200</v>
@@ -2065,7 +2065,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B121" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/index.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012724/1013205/1034493/1013206.html</v>
       </c>
       <c r="C121">
         <v>200</v>
@@ -2079,7 +2079,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B122" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008920/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008943.html</v>
       </c>
       <c r="C122">
         <v>200</v>
@@ -2093,7 +2093,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B123" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008937.html</v>
+        <v>https://www.qq.pref.aichi.jp/</v>
       </c>
       <c r="C123">
         <v>200</v>
@@ -2107,7 +2107,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B124" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008938.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008947.html</v>
       </c>
       <c r="C124">
         <v>200</v>
@@ -2121,7 +2121,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B125" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008939/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/index.html</v>
       </c>
       <c r="C125">
         <v>200</v>
@@ -2135,7 +2135,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B126" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008949.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008920/index.html</v>
       </c>
       <c r="C126">
         <v>200</v>
@@ -2149,7 +2149,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B127" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034084/1009261.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008937.html</v>
       </c>
       <c r="C127">
         <v>200</v>
@@ -2163,7 +2163,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B128" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009265.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008938.html</v>
       </c>
       <c r="C128">
         <v>200</v>
@@ -2177,7 +2177,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B129" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009264.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008939/index.html</v>
       </c>
       <c r="C129">
         <v>200</v>
@@ -2191,7 +2191,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B130" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009260.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008949.html</v>
       </c>
       <c r="C130">
         <v>200</v>
@@ -2205,7 +2205,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B131" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009258.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034084/1009261.html</v>
       </c>
       <c r="C131">
         <v>200</v>
@@ -2219,7 +2219,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B132" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009307/1008988.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009265.html</v>
       </c>
       <c r="C132">
         <v>200</v>
@@ -2233,7 +2233,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B133" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009264.html</v>
       </c>
       <c r="C133">
         <v>200</v>
@@ -2247,7 +2247,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B134" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034342/1008991/1036125.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009260.html</v>
       </c>
       <c r="C134">
         <v>200</v>
@@ -2261,7 +2261,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B135" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009126.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009258.html</v>
       </c>
       <c r="C135">
         <v>200</v>
@@ -2275,10 +2275,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B136" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000048704.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009307/1008988.html</v>
       </c>
       <c r="C136">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D136" t="str">
         <v>data/services.js</v>
@@ -2289,7 +2289,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B137" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008959.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
       </c>
       <c r="C137">
         <v>200</v>
@@ -2303,7 +2303,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B138" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009018.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034342/1008991/1036125.html</v>
       </c>
       <c r="C138">
         <v>200</v>
@@ -2317,10 +2317,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B139" t="str">
-        <v>https://www.city.nagoya.jp/kyoiku/page/0000051014.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009126.html</v>
       </c>
       <c r="C139">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D139" t="str">
         <v>data/services.js</v>
@@ -2331,7 +2331,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B140" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1036101.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1037093/1016989.html</v>
       </c>
       <c r="C140">
         <v>200</v>
@@ -2345,7 +2345,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B141" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1015850/1017055.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008959.html</v>
       </c>
       <c r="C141">
         <v>200</v>
@@ -2359,7 +2359,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B142" t="str">
-        <v>https://nagoya.fureai-cloud.jp/_view/sodan/home/index</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009018.html</v>
       </c>
       <c r="C142">
         <v>200</v>
@@ -2373,7 +2373,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B143" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009321/1009322.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016781.html</v>
       </c>
       <c r="C143">
         <v>200</v>
@@ -2387,7 +2387,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B144" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016409.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1036101.html</v>
       </c>
       <c r="C144">
         <v>200</v>
@@ -2401,7 +2401,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B145" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015819/1038028/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1015850/1017055.html</v>
       </c>
       <c r="C145">
         <v>200</v>
@@ -2415,7 +2415,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B146" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015845.html</v>
+        <v>https://nagoya.fureai-cloud.jp/_view/sodan/home/index</v>
       </c>
       <c r="C146">
         <v>200</v>
@@ -2429,7 +2429,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B147" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016404.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009321/1009322.html</v>
       </c>
       <c r="C147">
         <v>200</v>
@@ -2443,10 +2443,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B148" t="str">
-        <v>https://www.city.nagoya.jp/sportsshimin/page/0000006195.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016409.html</v>
       </c>
       <c r="C148">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D148" t="str">
         <v>data/services.js</v>
@@ -2457,7 +2457,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B149" t="str">
-        <v>https://www.nic-nagoya.or.jp/</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015819/1038028/index.html</v>
       </c>
       <c r="C149">
         <v>200</v>
@@ -2471,7 +2471,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B150" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016399.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015845.html</v>
       </c>
       <c r="C150">
         <v>200</v>
@@ -2485,10 +2485,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B151" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016734.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016404.html</v>
       </c>
       <c r="C151">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D151" t="str">
         <v>data/services.js</v>
@@ -2499,10 +2499,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B152" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000060016.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016402.html</v>
       </c>
       <c r="C152">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D152" t="str">
         <v>data/services.js</v>
@@ -2513,7 +2513,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B153" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009388.html</v>
+        <v>https://www.nic-nagoya.or.jp/</v>
       </c>
       <c r="C153">
         <v>200</v>
@@ -2527,7 +2527,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B154" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009391.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016399.html</v>
       </c>
       <c r="C154">
         <v>200</v>
@@ -2541,10 +2541,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B155" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009381/1009382.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016734.html</v>
       </c>
       <c r="C155">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D155" t="str">
         <v>data/services.js</v>
@@ -2555,7 +2555,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B156" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009334.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008983/1008984.html</v>
       </c>
       <c r="C156">
         <v>200</v>
@@ -2569,7 +2569,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B157" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009389.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009388.html</v>
       </c>
       <c r="C157">
         <v>200</v>
@@ -2583,10 +2583,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B158" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000112089.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009391.html</v>
       </c>
       <c r="C158">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D158" t="str">
         <v>data/services.js</v>
@@ -2597,7 +2597,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B159" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1016449/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009381/1009382.html</v>
       </c>
       <c r="C159">
         <v>200</v>
@@ -2611,7 +2611,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B160" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009334.html</v>
       </c>
       <c r="C160">
         <v>200</v>
@@ -2625,13 +2625,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B161" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/jouhou/1036432/1013386.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009389.html</v>
       </c>
       <c r="C161">
         <v>200</v>
       </c>
       <c r="D161" t="str">
-        <v>data/services.js, screens/DisasterScreen.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="162">
@@ -2639,7 +2639,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B162" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/kyoujo/1036451/1013567.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009374.html</v>
       </c>
       <c r="C162">
         <v>200</v>
@@ -2653,10 +2653,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B163" t="str">
-        <v>https://www.city.nagoya.jp/bosaikikikanri/page/0000033020.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1016449/index.html</v>
       </c>
       <c r="C163">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D163" t="str">
         <v>data/services.js</v>
@@ -2667,7 +2667,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B164" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008962/1008963.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/</v>
       </c>
       <c r="C164">
         <v>200</v>
@@ -2681,13 +2681,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B165" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016506/1016510/1016511.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/jouhou/1036432/1013386.html</v>
       </c>
       <c r="C165">
         <v>200</v>
       </c>
       <c r="D165" t="str">
-        <v>data/services.js</v>
+        <v>data/services.js, screens/DisasterScreen.js</v>
       </c>
     </row>
     <row r="166">
@@ -2695,7 +2695,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B166" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009502/1034108.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/kyoujo/1036451/1013567.html</v>
       </c>
       <c r="C166">
         <v>200</v>
@@ -2709,7 +2709,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B167" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/todokede/1007816/1007817.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008962/1008963.html</v>
       </c>
       <c r="C167">
         <v>200</v>
@@ -2723,7 +2723,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B168" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011832/1011834.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016506/1016510/1016511.html</v>
       </c>
       <c r="C168">
         <v>200</v>
@@ -2737,7 +2737,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B169" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011868.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009502/1034108.html</v>
       </c>
       <c r="C169">
         <v>200</v>
@@ -2751,7 +2751,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B170" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011870.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/todokede/1007816/1007817.html</v>
       </c>
       <c r="C170">
         <v>200</v>
@@ -2765,7 +2765,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B171" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011854/index.html</v>
       </c>
       <c r="C171">
         <v>200</v>
@@ -2779,7 +2779,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B172" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1035058/1012184/1046468/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011868.html</v>
       </c>
       <c r="C172">
         <v>200</v>
@@ -2793,7 +2793,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B173" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016573/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011870.html</v>
       </c>
       <c r="C173">
         <v>200</v>
@@ -2807,7 +2807,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B174" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/index.html</v>
       </c>
       <c r="C174">
         <v>200</v>
@@ -2821,10 +2821,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B175" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/category/15-7-2-0-0-0-0-0-0-0.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1035058/1012184/1046468/index.html</v>
       </c>
       <c r="C175">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D175" t="str">
         <v>data/services.js</v>
@@ -2835,7 +2835,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B176" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011763/1011768.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016573/index.html</v>
       </c>
       <c r="C176">
         <v>200</v>
@@ -2849,7 +2849,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B177" t="str">
-        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000135090_00001.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/pet/1015473/index.html</v>
       </c>
       <c r="C177">
         <v>200</v>
@@ -2863,7 +2863,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B178" t="str">
-        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000158665.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011763/1011768.html</v>
       </c>
       <c r="C178">
         <v>200</v>
@@ -2877,7 +2877,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B179" t="str">
-        <v>https://www.kyoukaikenpo.or.jp/benefit/injury_and_sickness_allowance/index.html</v>
+        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000135090_00001.html</v>
       </c>
       <c r="C179">
         <v>200</v>
@@ -2891,7 +2891,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B180" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011851/1011853.html</v>
+        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000158665.html</v>
       </c>
       <c r="C180">
         <v>200</v>
@@ -2905,7 +2905,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B181" t="str">
-        <v>https://www.nenkin.go.jp/service/jukyu/seido/sonota-kyufu/shienkyufukin/20190805.html</v>
+        <v>https://www.kyoukaikenpo.or.jp/benefit/injury_and_sickness_allowance/index.html</v>
       </c>
       <c r="C181">
         <v>200</v>
@@ -2919,7 +2919,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B182" t="str">
-        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011851/1011853.html</v>
       </c>
       <c r="C182">
         <v>200</v>
@@ -2933,7 +2933,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B183" t="str">
-        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm#mushoukaLink2</v>
+        <v>https://www.nenkin.go.jp/service/jukyu/seido/sonota-kyufu/shienkyufukin/20190805.html</v>
       </c>
       <c r="C183">
         <v>200</v>
@@ -2947,7 +2947,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B184" t="str">
-        <v>https://www.jasso.go.jp/shogakukin/</v>
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm</v>
       </c>
       <c r="C184">
         <v>200</v>
@@ -2961,7 +2961,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B185" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008946.html</v>
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm#mushoukaLink2</v>
       </c>
       <c r="C185">
         <v>200</v>
@@ -2975,7 +2975,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B186" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/zaimusisetsu/syuugakushienkin.html</v>
+        <v>https://www.jasso.go.jp/shogakukin/</v>
       </c>
       <c r="C186">
         <v>200</v>
@@ -2989,7 +2989,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B187" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/shigaku/shigaku-syougakukyuhukin.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008946.html</v>
       </c>
       <c r="C187">
         <v>200</v>
@@ -3073,7 +3073,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B193" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034073/1009017.html</v>
+        <v>https://www.pref.aichi.jp/soshiki/zaimusisetsu/koutoukyouikumusyouka.html</v>
       </c>
       <c r="C193">
         <v>200</v>
@@ -3087,7 +3087,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B194" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/zaimusisetsu/koutoukyouikumusyouka.html</v>
+        <v>https://www.pref.aichi.jp/soshiki/shigaku/kikanyoukenkakunin.html</v>
       </c>
       <c r="C194">
         <v>200</v>
@@ -3101,7 +3101,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B195" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/shigaku/kikanyoukenkakunin.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1050641.html</v>
       </c>
       <c r="C195">
         <v>200</v>
@@ -3115,7 +3115,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B196" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1050641.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016987.html</v>
       </c>
       <c r="C196">
         <v>200</v>
@@ -3129,13 +3129,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B197" t="str">
-        <v>https://www.city.nagoya.jp/</v>
+        <v>https://nagoyalink.net/</v>
       </c>
       <c r="C197">
         <v>200</v>
       </c>
       <c r="D197" t="str">
-        <v>screens/DetailScreen.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="198">
@@ -3143,13 +3143,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B198" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/jigyosho/</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016705.html</v>
       </c>
       <c r="C198">
         <v>200</v>
       </c>
       <c r="D198" t="str">
-        <v>screens/DetailScreen.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="199">
@@ -3157,13 +3157,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B199" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/1013492.html</v>
+        <v>http://nagosapo.icds.jp/</v>
       </c>
       <c r="C199">
         <v>200</v>
       </c>
       <c r="D199" t="str">
-        <v>screens/DisasterScreen.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="200">
@@ -3171,25 +3171,459 @@
         <v>✅ 正常</v>
       </c>
       <c r="B200" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016706.html</v>
+      </c>
+      <c r="C200">
+        <v>200</v>
+      </c>
+      <c r="D200" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B201" t="str">
+        <v>http://maejob.icds.jp/index.html</v>
+      </c>
+      <c r="C201">
+        <v>200</v>
+      </c>
+      <c r="D201" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B202" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1011883/1011892.html</v>
+      </c>
+      <c r="C202">
+        <v>200</v>
+      </c>
+      <c r="D202" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B203" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011842/1011845.html</v>
+      </c>
+      <c r="C203">
+        <v>200</v>
+      </c>
+      <c r="D203" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B204" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011769/1011773.html</v>
+      </c>
+      <c r="C204">
+        <v>200</v>
+      </c>
+      <c r="D204" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B205" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009386.html</v>
+      </c>
+      <c r="C205">
+        <v>200</v>
+      </c>
+      <c r="D205" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B206" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009394.html</v>
+      </c>
+      <c r="C206">
+        <v>200</v>
+      </c>
+      <c r="D206" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B207" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017010/1017016.html</v>
+      </c>
+      <c r="C207">
+        <v>200</v>
+      </c>
+      <c r="D207" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B208" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016972/1016979.html</v>
+      </c>
+      <c r="C208">
+        <v>200</v>
+      </c>
+      <c r="D208" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B209" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017053.html</v>
+      </c>
+      <c r="C209">
+        <v>200</v>
+      </c>
+      <c r="D209" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B210" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017056.html</v>
+      </c>
+      <c r="C210">
+        <v>200</v>
+      </c>
+      <c r="D210" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B211" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008983/1042086.html</v>
+      </c>
+      <c r="C211">
+        <v>200</v>
+      </c>
+      <c r="D211" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B212" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016704.html</v>
+      </c>
+      <c r="C212">
+        <v>200</v>
+      </c>
+      <c r="D212" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B213" t="str">
+        <v>https://www.kosodate-ouen.city.nagoya.jp/</v>
+      </c>
+      <c r="C213">
+        <v>200</v>
+      </c>
+      <c r="D213" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B214" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009108/1009109.html</v>
+      </c>
+      <c r="C214">
+        <v>200</v>
+      </c>
+      <c r="D214" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B215" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009280.html</v>
+      </c>
+      <c r="C215">
+        <v>200</v>
+      </c>
+      <c r="D215" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B216" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016448/1016483.html</v>
+      </c>
+      <c r="C216">
+        <v>200</v>
+      </c>
+      <c r="D216" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B217" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009410/1040316.html</v>
+      </c>
+      <c r="C217">
+        <v>200</v>
+      </c>
+      <c r="D217" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B218" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009525/1009528.html</v>
+      </c>
+      <c r="C218">
+        <v>200</v>
+      </c>
+      <c r="D218" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B219" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009525/1033517.html</v>
+      </c>
+      <c r="C219">
+        <v>200</v>
+      </c>
+      <c r="D219" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B220" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009535/1009537.html</v>
+      </c>
+      <c r="C220">
+        <v>200</v>
+      </c>
+      <c r="D220" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B221" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009535/1009539.html</v>
+      </c>
+      <c r="C221">
+        <v>200</v>
+      </c>
+      <c r="D221" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B222" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1045911/1045913.html</v>
+      </c>
+      <c r="C222">
+        <v>200</v>
+      </c>
+      <c r="D222" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B223" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016443.html</v>
+      </c>
+      <c r="C223">
+        <v>200</v>
+      </c>
+      <c r="D223" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B224" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016553/1016554.html</v>
+      </c>
+      <c r="C224">
+        <v>200</v>
+      </c>
+      <c r="D224" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B225" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016553/1034838.html</v>
+      </c>
+      <c r="C225">
+        <v>200</v>
+      </c>
+      <c r="D225" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B226" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016663.html</v>
+      </c>
+      <c r="C226">
+        <v>200</v>
+      </c>
+      <c r="D226" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B227" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016738.html</v>
+      </c>
+      <c r="C227">
+        <v>200</v>
+      </c>
+      <c r="D227" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B228" t="str">
+        <v>https://www.city.nagoya.jp/</v>
+      </c>
+      <c r="C228">
+        <v>200</v>
+      </c>
+      <c r="D228" t="str">
+        <v>screens/DetailScreen.js</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B229" t="str">
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/jigyosho/</v>
+      </c>
+      <c r="C229">
+        <v>200</v>
+      </c>
+      <c r="D229" t="str">
+        <v>screens/DetailScreen.js</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B230" t="str">
+        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/1013492.html</v>
+      </c>
+      <c r="C230">
+        <v>200</v>
+      </c>
+      <c r="D230" t="str">
+        <v>screens/DisasterScreen.js</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B231" t="str">
         <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036428.html</v>
       </c>
-      <c r="C200">
-        <v>200</v>
-      </c>
-      <c r="D200" t="str">
+      <c r="C231">
+        <v>200</v>
+      </c>
+      <c r="D231" t="str">
         <v>screens/DisasterScreen.js</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D231"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3207,84 +3641,28 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>https://www.bes-c.com/</v>
+        <v>https://www.pref.aichi.jp/soshiki/zaimusisetsu/syuugakushienkin.html</v>
       </c>
       <c r="B2" t="str">
-        <v>名古屋市高齢者就業支援センター</v>
+        <v>県立高等学校等就学支援金制度 - 愛知県</v>
       </c>
       <c r="C2" t="str">
-        <v>名古屋市高齢者就業支援センター</v>
+        <v>Loading</v>
       </c>
       <c r="D2" t="str">
         <v>data/services.js</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016409.html</v>
-      </c>
-      <c r="B3" t="str">
-        <v>名古屋市子どもの権利相談室「なごもっか」｜名古屋市公式ウェブサイト</v>
-      </c>
-      <c r="C3" t="str">
-        <v>名古屋市子どもの権利相談室「なごもっか」｜名古屋市公式ウェブサイト</v>
-      </c>
-      <c r="D3" t="str">
-        <v>data/services.js</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>https://www.nic-nagoya.or.jp/</v>
-      </c>
-      <c r="B4" t="str">
-        <v>名古屋国際センター | Nagoya International Center</v>
-      </c>
-      <c r="C4" t="str">
-        <v>One moment, please...</v>
-      </c>
-      <c r="D4" t="str">
-        <v>data/services.js</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
-      </c>
-      <c r="B5" t="str">
-        <v>行政相談 | 名古屋国際センター | Nagoya International Center</v>
-      </c>
-      <c r="C5" t="str">
-        <v>One moment, please...</v>
-      </c>
-      <c r="D5" t="str">
-        <v>data/services.js</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/1013492.html</v>
-      </c>
-      <c r="B6" t="str">
-        <v>指定緊急避難場所・指定避難所の指定｜名古屋市公式ウェブサイト</v>
-      </c>
-      <c r="C6" t="str">
-        <v>指定緊急避難場所・指定避難所の指定｜名古屋市公式ウェブサイト</v>
-      </c>
-      <c r="D6" t="str">
-        <v>screens/DisasterScreen.js</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3314,10 +3692,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D2" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012913/1012914/1052131.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1013090/1013096/1051100.html</v>
       </c>
       <c r="E2" t="str">
-        <v>消防職員の熱中症対策として製氷機を寄贈頂きました</v>
+        <v>令和8年度名東の日を開催しました！</v>
       </c>
     </row>
     <row r="3">
@@ -3331,10 +3709,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D3" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1013090/1013096/1051100.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012913/1045614/1051635.html</v>
       </c>
       <c r="E3" t="str">
-        <v>令和8年度名東の日を開催しました！</v>
+        <v>予防課からのお知らせ</v>
       </c>
     </row>
     <row r="4">
@@ -3348,10 +3726,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D4" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/zeikin/1007927/1050342.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/1034008/1052263.html</v>
       </c>
       <c r="E4" t="str">
-        <v>税務証明等手数料の改定のお知らせ（令和8年10月1日から）</v>
+        <v>令和8年（2026年）熊本地震で被災された方への市営住宅の提供</v>
       </c>
     </row>
     <row r="5">
@@ -3365,10 +3743,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D5" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/douro/1014806/1034763/1014850.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shiminsanka/1011147/1052132.html</v>
       </c>
       <c r="E5" t="str">
-        <v>堀川ギャラリー</v>
+        <v>令和8年熊本地震災害義援金の募集</v>
       </c>
     </row>
     <row r="6">
@@ -3382,10 +3760,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D6" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051109.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052096.html</v>
       </c>
       <c r="E6" t="str">
-        <v>めざせ！！水の環復活－学んでみよう、水のことー浄水場と水循環</v>
+        <v>蓬左文庫企画展 生誕140年 没後50年記念 旅する侯爵 徳川義親</v>
       </c>
     </row>
     <row r="7">
@@ -3399,10 +3777,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D7" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051801.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/zeikin/1007927/1050342.html</v>
       </c>
       <c r="E7" t="str">
-        <v>「下水道科学館まつり」を開催します！</v>
+        <v>税務証明等手数料の改定のお知らせ（令和8年10月1日から）</v>
       </c>
     </row>
     <row r="8">
@@ -3416,10 +3794,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D8" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1035058/1012184/1050522.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/douro/1014806/1034763/1014850.html</v>
       </c>
       <c r="E8" t="str">
-        <v>令和8年10月から、粗大ごみの対象が変わります</v>
+        <v>堀川ギャラリー</v>
       </c>
     </row>
     <row r="9">
@@ -3433,10 +3811,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D9" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1050354.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051109.html</v>
       </c>
       <c r="E9" t="str">
-        <v>中央卸売市場本場 大人のための市場見学 参加者募集</v>
+        <v>めざせ！！水の環復活－学んでみよう、水のことー浄水場と水循環</v>
       </c>
     </row>
     <row r="10">
@@ -3450,10 +3828,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D10" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034338/1051902.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1052219.html</v>
       </c>
       <c r="E10" t="str">
-        <v>令和8年度 里親制度説明＆里親の体験談を聞く会</v>
+        <v>令和8年度トワイライトスクール・ルームに関するアンケート調査について</v>
       </c>
     </row>
     <row r="11">
@@ -3467,10 +3845,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D11" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/jisedai/1009754/1009755/1052076.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1051827.html</v>
       </c>
       <c r="E11" t="str">
-        <v>令和8年度なごっちフレンズワークショップ (令和8年8月25日)</v>
+        <v>令和8年8月10日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
       </c>
     </row>
     <row r="12">
@@ -3484,10 +3862,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D12" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1034069/1051899.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1034096.html</v>
       </c>
       <c r="E12" t="str">
-        <v>災害の備えどうしてる？－慢性疾患のある子どもと家族のための災害対策を見直そうー</v>
+        <v>幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
       </c>
     </row>
     <row r="13">
@@ -3501,10 +3879,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D13" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1051292.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034338/1051902.html</v>
       </c>
       <c r="E13" t="str">
-        <v>令和8年7月25日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+        <v>令和8年度 里親制度説明＆里親の体験談を聞く会</v>
       </c>
     </row>
     <row r="14">
@@ -3518,10 +3896,10 @@
         <v>➖ 削除</v>
       </c>
       <c r="D14" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1034096.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/jisedai/1009754/1009755/1052076.html</v>
       </c>
       <c r="E14" t="str">
-        <v>幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+        <v>令和8年度なごっちフレンズワークショップ (令和8年8月25日)</v>
       </c>
     </row>
     <row r="15">
@@ -3535,124 +3913,22 @@
         <v>➖ 削除</v>
       </c>
       <c r="D15" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017010/1051839.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1034069/1051899.html</v>
       </c>
       <c r="E15" t="str">
-        <v>学習用端末の準備について[市立高等学校・特別支援学校高等部]</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B16" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C16" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D16" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1035053/1051909.html</v>
-      </c>
-      <c r="E16" t="str">
-        <v>令和8年度音訳ボランティア養成講座</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B17" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C17" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D17" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1011432/1051796.html</v>
-      </c>
-      <c r="E17" t="str">
-        <v>専用水道に関する届出</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B18" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C18" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D18" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1034419/1050801.html</v>
-      </c>
-      <c r="E18" t="str">
-        <v>令和8年度つながり・支えあおう地域福祉のすゝめ（イベントのご案内）</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B19" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C19" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D19" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/1016644/1041946/1050026.html</v>
-      </c>
-      <c r="E19" t="str">
-        <v>NHKハートフォーラム・名古屋市発達障害者支援センターりんくす名古屋講演会「実は身近な発達障害 援助を求める力と合理的配慮 －『困った』を伝える・受けとめる－」のご案内</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B20" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C20" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D20" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016746/1051650.html</v>
-      </c>
-      <c r="E20" t="str">
-        <v>愛知県市民後見人等養成研修について</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B21" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C21" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D21" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1051406/1051435.html</v>
-      </c>
-      <c r="E21" t="str">
-        <v>民生委員・児童委員専用サイト（名古屋市民生委員・児童委員の部屋）</v>
+        <v>災害の備えどうしてる？－慢性疾患のある子どもと家族のための災害対策を見直そうー</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E15"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M82"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4828,9 +5104,538 @@
         <v>民生委員・児童委員専用サイト（名古屋市民生委員・児童委員の部屋）</v>
       </c>
     </row>
+    <row r="57">
+      <c r="B57" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C57" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D57" t="str">
+        <v>https://www.pref.aichi.jp/soshiki/jutakukanri/bosyuannai.html</v>
+      </c>
+      <c r="E57" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F57" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C58" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D58" t="str">
+        <v>https://hikikomori.city.nagoya.jp/</v>
+      </c>
+      <c r="E58" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F58" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C59" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D59" t="str">
+        <v>https://www.pref.aichi.jp/soshiki/jidoukatei/0000011250.html</v>
+      </c>
+      <c r="E59" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F59" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C60" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D60" t="str">
+        <v>https://nagoya-shakyo.jp/service/fureai-kyushoku/</v>
+      </c>
+      <c r="E60" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F60" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C61" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D61" t="str">
+        <v>https://nagoya-shakyo.jp/service/ward-shakyo/</v>
+      </c>
+      <c r="E61" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F61" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C62" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D62" t="str">
+        <v>https://nagoya-shakyo.jp/service/community-support/</v>
+      </c>
+      <c r="E62" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F62" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C63" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D63" t="str">
+        <v>https://www.pref.aichi.jp/soshiki/imu/0000050084.html</v>
+      </c>
+      <c r="E63" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F63" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C64" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D64" t="str">
+        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
+      </c>
+      <c r="E64" t="str">
+        <v>ERROR</v>
+      </c>
+      <c r="F64" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C65" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D65" t="str">
+        <v>https://www.pref.aichi.jp/soshiki/zaimusisetsu/syuugakushienkin.html</v>
+      </c>
+      <c r="E65" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F65" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C66" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D66" t="str">
+        <v>https://www.pref.aichi.jp/uploaded/attachment/620030.pdf</v>
+      </c>
+      <c r="E66" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F66" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C67" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D67" t="str">
+        <v>https://www.pref.aichi.jp/soshiki/shigaku/shigaku-syougakukyuhukin.html</v>
+      </c>
+      <c r="E67" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F67" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C68" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D68" t="str">
+        <v>https://www.pref.aichi.jp/soshiki/zaimusisetsu/syuugakushienkin.html</v>
+      </c>
+      <c r="F68" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G68" t="str">
+        <v>県立高等学校等就学支援金制度 - 愛知県</v>
+      </c>
+      <c r="H68" t="str">
+        <v>Loading</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C69" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I69" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J69" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K69" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L69" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1013090/1013096/1051100.html</v>
+      </c>
+      <c r="M69" t="str">
+        <v>令和8年度名東の日を開催しました！</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C70" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I70" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J70" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K70" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L70" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012913/1045614/1051635.html</v>
+      </c>
+      <c r="M70" t="str">
+        <v>予防課からのお知らせ</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C71" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I71" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J71" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K71" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L71" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/1034008/1052263.html</v>
+      </c>
+      <c r="M71" t="str">
+        <v>令和8年（2026年）熊本地震で被災された方への市営住宅の提供</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C72" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I72" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J72" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K72" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L72" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/shiminsanka/1011147/1052132.html</v>
+      </c>
+      <c r="M72" t="str">
+        <v>令和8年熊本地震災害義援金の募集</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C73" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I73" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J73" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K73" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L73" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052096.html</v>
+      </c>
+      <c r="M73" t="str">
+        <v>蓬左文庫企画展 生誕140年 没後50年記念 旅する侯爵 徳川義親</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C74" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I74" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J74" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K74" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L74" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/zeikin/1007927/1050342.html</v>
+      </c>
+      <c r="M74" t="str">
+        <v>税務証明等手数料の改定のお知らせ（令和8年10月1日から）</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C75" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I75" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J75" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K75" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L75" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/douro/1014806/1034763/1014850.html</v>
+      </c>
+      <c r="M75" t="str">
+        <v>堀川ギャラリー</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C76" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I76" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J76" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K76" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L76" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051109.html</v>
+      </c>
+      <c r="M76" t="str">
+        <v>めざせ！！水の環復活－学んでみよう、水のことー浄水場と水循環</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C77" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I77" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J77" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K77" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L77" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1052219.html</v>
+      </c>
+      <c r="M77" t="str">
+        <v>令和8年度トワイライトスクール・ルームに関するアンケート調査について</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C78" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I78" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J78" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K78" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L78" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1051827.html</v>
+      </c>
+      <c r="M78" t="str">
+        <v>令和8年8月10日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C79" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I79" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J79" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K79" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L79" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1034096.html</v>
+      </c>
+      <c r="M79" t="str">
+        <v>幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C80" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I80" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J80" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K80" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L80" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034338/1051902.html</v>
+      </c>
+      <c r="M80" t="str">
+        <v>令和8年度 里親制度説明＆里親の体験談を聞く会</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C81" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I81" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J81" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K81" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L81" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/jisedai/1009754/1009755/1052076.html</v>
+      </c>
+      <c r="M81" t="str">
+        <v>令和8年度なごっちフレンズワークショップ (令和8年8月25日)</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="C82" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I82" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J82" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K82" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L82" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1034069/1051899.html</v>
+      </c>
+      <c r="M82" t="str">
+        <v>災害の備えどうしてる？－慢性疾患のある子どもと家族のための災害対策を見直そうー</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M56"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M82"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reports/latest-report.xlsx
+++ b/reports/latest-report.xlsx
@@ -399,7 +399,7 @@
         <v>❌ リンク切れ</v>
       </c>
       <c r="B2" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/jutakukanri/bosyuannai.html</v>
+        <v>https://hikikomori.city.nagoya.jp/</v>
       </c>
       <c r="C2" t="str">
         <v>TIMEOUT</v>
@@ -413,7 +413,7 @@
         <v>❌ リンク切れ</v>
       </c>
       <c r="B3" t="str">
-        <v>https://hikikomori.city.nagoya.jp/</v>
+        <v>https://nagoya-shakyo.jp/service/fureai-kyushoku/</v>
       </c>
       <c r="C3" t="str">
         <v>TIMEOUT</v>
@@ -427,7 +427,7 @@
         <v>❌ リンク切れ</v>
       </c>
       <c r="B4" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/jidoukatei/0000011250.html</v>
+        <v>https://nagoya-shakyo.jp/service/ward-shakyo/</v>
       </c>
       <c r="C4" t="str">
         <v>TIMEOUT</v>
@@ -441,7 +441,7 @@
         <v>❌ リンク切れ</v>
       </c>
       <c r="B5" t="str">
-        <v>https://nagoya-shakyo.jp/service/fureai-kyushoku/</v>
+        <v>https://nagoya-shakyo.jp/service/community-support/</v>
       </c>
       <c r="C5" t="str">
         <v>TIMEOUT</v>
@@ -455,10 +455,10 @@
         <v>❌ リンク切れ</v>
       </c>
       <c r="B6" t="str">
-        <v>https://nagoya-shakyo.jp/service/ward-shakyo/</v>
+        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
       </c>
       <c r="C6" t="str">
-        <v>TIMEOUT</v>
+        <v>ERROR</v>
       </c>
       <c r="D6" t="str">
         <v>data/services.js</v>
@@ -466,86 +466,86 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>❌ リンク切れ</v>
+        <v>✅ 正常</v>
       </c>
       <c r="B7" t="str">
-        <v>https://nagoya-shakyo.jp/service/community-support/</v>
-      </c>
-      <c r="C7" t="str">
-        <v>TIMEOUT</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036294.html</v>
+      </c>
+      <c r="C7">
+        <v>200</v>
       </c>
       <c r="D7" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>❌ リンク切れ</v>
+        <v>✅ 正常</v>
       </c>
       <c r="B8" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/imu/0000050084.html</v>
-      </c>
-      <c r="C8" t="str">
-        <v>TIMEOUT</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/index.html</v>
+      </c>
+      <c r="C8">
+        <v>200</v>
       </c>
       <c r="D8" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js, screens/DisasterScreen.js</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>❌ リンク切れ</v>
+        <v>✅ 正常</v>
       </c>
       <c r="B9" t="str">
-        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
-      </c>
-      <c r="C9" t="str">
-        <v>ERROR</v>
+        <v>https://www.city.nagoya.jp/chikusa/kurashi/</v>
+      </c>
+      <c r="C9">
+        <v>200</v>
       </c>
       <c r="D9" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>❌ リンク切れ</v>
+        <v>✅ 正常</v>
       </c>
       <c r="B10" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/zaimusisetsu/syuugakushienkin.html</v>
-      </c>
-      <c r="C10" t="str">
-        <v>TIMEOUT</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036299.html</v>
+      </c>
+      <c r="C10">
+        <v>200</v>
       </c>
       <c r="D10" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>❌ リンク切れ</v>
+        <v>✅ 正常</v>
       </c>
       <c r="B11" t="str">
-        <v>https://www.pref.aichi.jp/uploaded/attachment/620030.pdf</v>
-      </c>
-      <c r="C11" t="str">
-        <v>TIMEOUT</v>
+        <v>https://www.city.nagoya.jp/higashi/kurashi/</v>
+      </c>
+      <c r="C11">
+        <v>200</v>
       </c>
       <c r="D11" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>❌ リンク切れ</v>
+        <v>✅ 正常</v>
       </c>
       <c r="B12" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/shigaku/shigaku-syougakukyuhukin.html</v>
-      </c>
-      <c r="C12" t="str">
-        <v>TIMEOUT</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036302.html</v>
+      </c>
+      <c r="C12">
+        <v>200</v>
       </c>
       <c r="D12" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="13">
@@ -553,7 +553,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B13" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036294.html</v>
+        <v>https://www.city.nagoya.jp/kita/kurashi/</v>
       </c>
       <c r="C13">
         <v>200</v>
@@ -567,13 +567,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B14" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/index.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036293.html</v>
       </c>
       <c r="C14">
         <v>200</v>
       </c>
       <c r="D14" t="str">
-        <v>data/districts.js, screens/DisasterScreen.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="15">
@@ -581,7 +581,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B15" t="str">
-        <v>https://www.city.nagoya.jp/chikusa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/nishi/kurashi/</v>
       </c>
       <c r="C15">
         <v>200</v>
@@ -595,7 +595,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B16" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036299.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036297.html</v>
       </c>
       <c r="C16">
         <v>200</v>
@@ -609,7 +609,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B17" t="str">
-        <v>https://www.city.nagoya.jp/higashi/kurashi/</v>
+        <v>https://www.city.nagoya.jp/nakamura/kurashi/</v>
       </c>
       <c r="C17">
         <v>200</v>
@@ -623,7 +623,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B18" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036302.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036295.html</v>
       </c>
       <c r="C18">
         <v>200</v>
@@ -637,7 +637,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B19" t="str">
-        <v>https://www.city.nagoya.jp/kita/kurashi/</v>
+        <v>https://www.city.nagoya.jp/naka/kurashi/</v>
       </c>
       <c r="C19">
         <v>200</v>
@@ -651,7 +651,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B20" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036293.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036291.html</v>
       </c>
       <c r="C20">
         <v>200</v>
@@ -665,7 +665,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B21" t="str">
-        <v>https://www.city.nagoya.jp/nishi/kurashi/</v>
+        <v>https://www.city.nagoya.jp/showa/kurashi/</v>
       </c>
       <c r="C21">
         <v>200</v>
@@ -679,7 +679,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B22" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036297.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036292.html</v>
       </c>
       <c r="C22">
         <v>200</v>
@@ -693,7 +693,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B23" t="str">
-        <v>https://www.city.nagoya.jp/nakamura/kurashi/</v>
+        <v>https://www.city.nagoya.jp/mizuho/kurashi/</v>
       </c>
       <c r="C23">
         <v>200</v>
@@ -707,7 +707,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B24" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036295.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036301.html</v>
       </c>
       <c r="C24">
         <v>200</v>
@@ -721,7 +721,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B25" t="str">
-        <v>https://www.city.nagoya.jp/naka/kurashi/</v>
+        <v>https://www.city.nagoya.jp/atsuta/kurashi/</v>
       </c>
       <c r="C25">
         <v>200</v>
@@ -735,7 +735,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B26" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036291.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036296.html</v>
       </c>
       <c r="C26">
         <v>200</v>
@@ -749,7 +749,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B27" t="str">
-        <v>https://www.city.nagoya.jp/showa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/nakagawa/kurashi/</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -763,7 +763,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B28" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036292.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036289.html</v>
       </c>
       <c r="C28">
         <v>200</v>
@@ -777,7 +777,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B29" t="str">
-        <v>https://www.city.nagoya.jp/mizuho/kurashi/</v>
+        <v>https://www.city.nagoya.jp/minato/kurashi/</v>
       </c>
       <c r="C29">
         <v>200</v>
@@ -791,7 +791,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B30" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036301.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036300.html</v>
       </c>
       <c r="C30">
         <v>200</v>
@@ -805,7 +805,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B31" t="str">
-        <v>https://www.city.nagoya.jp/atsuta/kurashi/</v>
+        <v>https://www.city.nagoya.jp/minami/kurashi/</v>
       </c>
       <c r="C31">
         <v>200</v>
@@ -819,7 +819,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B32" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036296.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036290.html</v>
       </c>
       <c r="C32">
         <v>200</v>
@@ -833,7 +833,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B33" t="str">
-        <v>https://www.city.nagoya.jp/nakagawa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/moriyama/kurashi/</v>
       </c>
       <c r="C33">
         <v>200</v>
@@ -847,7 +847,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B34" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036289.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036304.html</v>
       </c>
       <c r="C34">
         <v>200</v>
@@ -861,7 +861,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B35" t="str">
-        <v>https://www.city.nagoya.jp/minato/kurashi/</v>
+        <v>https://www.city.nagoya.jp/midori/kurashi/</v>
       </c>
       <c r="C35">
         <v>200</v>
@@ -875,7 +875,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B36" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036300.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036303.html</v>
       </c>
       <c r="C36">
         <v>200</v>
@@ -889,7 +889,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B37" t="str">
-        <v>https://www.city.nagoya.jp/minami/kurashi/</v>
+        <v>https://www.city.nagoya.jp/meito/kurashi/</v>
       </c>
       <c r="C37">
         <v>200</v>
@@ -903,7 +903,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B38" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036290.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036298.html</v>
       </c>
       <c r="C38">
         <v>200</v>
@@ -917,7 +917,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B39" t="str">
-        <v>https://www.city.nagoya.jp/moriyama/kurashi/</v>
+        <v>https://www.city.nagoya.jp/tempaku/kurashi/</v>
       </c>
       <c r="C39">
         <v>200</v>
@@ -931,13 +931,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B40" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036304.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008973.html</v>
       </c>
       <c r="C40">
         <v>200</v>
       </c>
       <c r="D40" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="41">
@@ -945,13 +945,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B41" t="str">
-        <v>https://www.city.nagoya.jp/midori/kurashi/</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009333.html</v>
       </c>
       <c r="C41">
         <v>200</v>
       </c>
       <c r="D41" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="42">
@@ -959,13 +959,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B42" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036303.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1009009.html</v>
       </c>
       <c r="C42">
         <v>200</v>
       </c>
       <c r="D42" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="43">
@@ -973,13 +973,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B43" t="str">
-        <v>https://www.city.nagoya.jp/meito/kurashi/</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009270/1034086.html</v>
       </c>
       <c r="C43">
         <v>200</v>
       </c>
       <c r="D43" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="44">
@@ -987,13 +987,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B44" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036298.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009353/1034092.html</v>
       </c>
       <c r="C44">
         <v>200</v>
       </c>
       <c r="D44" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="45">
@@ -1001,13 +1001,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B45" t="str">
-        <v>https://www.city.nagoya.jp/tempaku/kurashi/</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009286/index.html</v>
       </c>
       <c r="C45">
         <v>200</v>
       </c>
       <c r="D45" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="46">
@@ -1015,7 +1015,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B46" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008973.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1034088.html</v>
       </c>
       <c r="C46">
         <v>200</v>
@@ -1029,7 +1029,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B47" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009333.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009387.html</v>
       </c>
       <c r="C47">
         <v>200</v>
@@ -1043,7 +1043,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B48" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1009009.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009393.html</v>
       </c>
       <c r="C48">
         <v>200</v>
@@ -1057,7 +1057,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B49" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009270/1034086.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011821/1011823.html</v>
       </c>
       <c r="C49">
         <v>200</v>
@@ -1071,7 +1071,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B50" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009353/1034092.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008956.html</v>
       </c>
       <c r="C50">
         <v>200</v>
@@ -1085,7 +1085,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B51" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009286/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008955.html</v>
       </c>
       <c r="C51">
         <v>200</v>
@@ -1099,7 +1099,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B52" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1034088.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/ichiran.html</v>
       </c>
       <c r="C52">
         <v>200</v>
@@ -1113,7 +1113,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B53" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009387.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008960.html</v>
       </c>
       <c r="C53">
         <v>200</v>
@@ -1127,7 +1127,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B54" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009393.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009019.html</v>
       </c>
       <c r="C54">
         <v>200</v>
@@ -1141,7 +1141,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B55" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011821/1011823.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008974.html</v>
       </c>
       <c r="C55">
         <v>200</v>
@@ -1155,7 +1155,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B56" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008956.html</v>
+        <v>https://www.city.nagoya.jp/lifescene/byouki/1017964.html</v>
       </c>
       <c r="C56">
         <v>200</v>
@@ -1169,7 +1169,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B57" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008955.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/seido/toiawase/</v>
       </c>
       <c r="C57">
         <v>200</v>
@@ -1183,7 +1183,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B58" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/ichiran.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016496/1016502.html</v>
       </c>
       <c r="C58">
         <v>200</v>
@@ -1197,7 +1197,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B59" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008960.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/1016536.html</v>
       </c>
       <c r="C59">
         <v>200</v>
@@ -1211,7 +1211,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B60" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009019.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011776/1034706/1011784.html</v>
       </c>
       <c r="C60">
         <v>200</v>
@@ -1225,7 +1225,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B61" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008974.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009456/1009457/index.html</v>
       </c>
       <c r="C61">
         <v>200</v>
@@ -1239,7 +1239,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B62" t="str">
-        <v>https://www.city.nagoya.jp/lifescene/byouki/1017964.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
       </c>
       <c r="C62">
         <v>200</v>
@@ -1253,7 +1253,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B63" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/seido/toiawase/</v>
+        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1012157/1033970.html</v>
       </c>
       <c r="C63">
         <v>200</v>
@@ -1267,7 +1267,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B64" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016496/1016502.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1015763/1015815.html</v>
       </c>
       <c r="C64">
         <v>200</v>
@@ -1281,7 +1281,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B65" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/1016536.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011793/1011807/1011810.html</v>
       </c>
       <c r="C65">
         <v>200</v>
@@ -1295,7 +1295,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B66" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011776/1034706/1011784.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016739.html</v>
       </c>
       <c r="C66">
         <v>200</v>
@@ -1309,7 +1309,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B67" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009456/1009457/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/index.html</v>
       </c>
       <c r="C67">
         <v>200</v>
@@ -1323,7 +1323,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B68" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
+        <v>https://www.pref.aichi.jp/soshiki/jutakukanri/bosyuannai.html</v>
       </c>
       <c r="C68">
         <v>200</v>
@@ -1337,7 +1337,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B69" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1012157/1033970.html</v>
+        <v>https://www.hellowork.mhlw.go.jp/insurance/insurance_guide.html</v>
       </c>
       <c r="C69">
         <v>200</v>
@@ -1351,7 +1351,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B70" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1015763/1015815.html</v>
+        <v>https://jsite.mhlw.go.jp/aichi-hellowork/list.html</v>
       </c>
       <c r="C70">
         <v>200</v>
@@ -1365,7 +1365,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B71" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011793/1011807/1011810.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
       </c>
       <c r="C71">
         <v>200</v>
@@ -1379,7 +1379,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B72" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016739.html</v>
+        <v>https://www.nagojob.city.nagoya.jp/</v>
       </c>
       <c r="C72">
         <v>200</v>
@@ -1393,7 +1393,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B73" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/index.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/tetyou/</v>
       </c>
       <c r="C73">
         <v>200</v>
@@ -1407,7 +1407,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B74" t="str">
-        <v>https://www.hellowork.mhlw.go.jp/insurance/insurance_guide.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/soudan/fukushikakari.html</v>
       </c>
       <c r="C74">
         <v>200</v>
@@ -1421,7 +1421,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B75" t="str">
-        <v>https://jsite.mhlw.go.jp/aichi-hellowork/list.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/fukushi_service.html</v>
       </c>
       <c r="C75">
         <v>200</v>
@@ -1435,7 +1435,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B76" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
+        <v>https://www.city.nagoya.jp/jigyou/sangyou/1026356/1035103/1026446/1026447.html</v>
       </c>
       <c r="C76">
         <v>200</v>
@@ -1449,7 +1449,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B77" t="str">
-        <v>https://www.nagojob.city.nagoya.jp/</v>
+        <v>https://weljob-nagoya.com/</v>
       </c>
       <c r="C77">
         <v>200</v>
@@ -1463,7 +1463,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B78" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/tetyou/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
       </c>
       <c r="C78">
         <v>200</v>
@@ -1477,7 +1477,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B79" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/soudan/fukushikakari.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/622/linksweb.pdf</v>
       </c>
       <c r="C79">
         <v>200</v>
@@ -1491,7 +1491,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B80" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/fukushi_service.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
       </c>
       <c r="C80">
         <v>200</v>
@@ -1505,7 +1505,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B81" t="str">
-        <v>https://www.city.nagoya.jp/jigyou/sangyou/1026356/1035103/1026446/1026447.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/675/annnai.pdf</v>
       </c>
       <c r="C81">
         <v>200</v>
@@ -1519,7 +1519,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B82" t="str">
-        <v>https://weljob-nagoya.com/</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
       </c>
       <c r="C82">
         <v>200</v>
@@ -1533,7 +1533,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B83" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
       </c>
       <c r="C83">
         <v>200</v>
@@ -1547,7 +1547,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B84" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/622/linksweb.pdf</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
       </c>
       <c r="C84">
         <v>200</v>
@@ -1561,7 +1561,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B85" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008978.html</v>
       </c>
       <c r="C85">
         <v>200</v>
@@ -1575,7 +1575,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B86" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/675/annnai.pdf</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/008/978/0413tirasi.pdf</v>
       </c>
       <c r="C86">
         <v>200</v>
@@ -1589,7 +1589,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B87" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034073/1009017.html</v>
       </c>
       <c r="C87">
         <v>200</v>
@@ -1603,7 +1603,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B88" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/009/017/r710_help.pdf</v>
       </c>
       <c r="C88">
         <v>200</v>
@@ -1617,7 +1617,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B89" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1034087.html</v>
       </c>
       <c r="C89">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B90" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008978.html</v>
+        <v>https://www.kosodate.city.nagoya.jp/kids/nobinobi.html</v>
       </c>
       <c r="C90">
         <v>200</v>
@@ -1645,7 +1645,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B91" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/008/978/0413tirasi.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1009278.html</v>
       </c>
       <c r="C91">
         <v>200</v>
@@ -1659,7 +1659,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B92" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034073/1009017.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009024/1009026.html</v>
       </c>
       <c r="C92">
         <v>200</v>
@@ -1673,7 +1673,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B93" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/009/017/r710_help.pdf</v>
+        <v>https://www.kosodate.city.nagoya.jp/play/supportbases.html</v>
       </c>
       <c r="C93">
         <v>200</v>
@@ -1687,7 +1687,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B94" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1034087.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034075/1009021.html</v>
       </c>
       <c r="C94">
         <v>200</v>
@@ -1701,7 +1701,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B95" t="str">
-        <v>https://www.kosodate.city.nagoya.jp/kids/nobinobi.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034072/1009016.html</v>
       </c>
       <c r="C95">
         <v>200</v>
@@ -1715,7 +1715,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B96" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1009278.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016744.html</v>
       </c>
       <c r="C96">
         <v>200</v>
@@ -1729,7 +1729,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B97" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009024/1009026.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016742.html</v>
       </c>
       <c r="C97">
         <v>200</v>
@@ -1743,7 +1743,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B98" t="str">
-        <v>https://www.kosodate.city.nagoya.jp/play/supportbases.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016586/1033908.html</v>
       </c>
       <c r="C98">
         <v>200</v>
@@ -1757,7 +1757,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B99" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034075/1009021.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009395.html</v>
       </c>
       <c r="C99">
         <v>200</v>
@@ -1771,7 +1771,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B100" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034072/1009016.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1009398.html</v>
       </c>
       <c r="C100">
         <v>200</v>
@@ -1785,7 +1785,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B101" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016744.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009380.html</v>
       </c>
       <c r="C101">
         <v>200</v>
@@ -1799,7 +1799,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B102" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016742.html</v>
+        <v>https://aiboren.jp/shisetsu/</v>
       </c>
       <c r="C102">
         <v>200</v>
@@ -1813,7 +1813,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B103" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016586/1033908.html</v>
+        <v>https://www.pref.aichi.jp/soshiki/jidoukatei/0000011250.html</v>
       </c>
       <c r="C103">
         <v>200</v>
@@ -1827,7 +1827,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B104" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009395.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016428.html</v>
       </c>
       <c r="C104">
         <v>200</v>
@@ -1841,7 +1841,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B105" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1009398.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/woichiran.html</v>
       </c>
       <c r="C105">
         <v>200</v>
@@ -1855,7 +1855,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B106" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009380.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/company/shitei/haishoku/</v>
       </c>
       <c r="C106">
         <v>200</v>
@@ -1869,7 +1869,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B107" t="str">
-        <v>https://aiboren.jp/shisetsu/</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
       </c>
       <c r="C107">
         <v>200</v>
@@ -1883,7 +1883,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B108" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016428.html</v>
+        <v>https://webc.sjc.ne.jp/nagoyasj/job2_7</v>
       </c>
       <c r="C108">
         <v>200</v>
@@ -1897,7 +1897,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B109" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/woichiran.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016431.html</v>
       </c>
       <c r="C109">
         <v>200</v>
@@ -1911,7 +1911,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B110" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/company/shitei/haishoku/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016433.html</v>
       </c>
       <c r="C110">
         <v>200</v>
@@ -1925,7 +1925,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B111" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016429.html</v>
       </c>
       <c r="C111">
         <v>200</v>
@@ -1939,7 +1939,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B112" t="str">
-        <v>https://webc.sjc.ne.jp/nagoyasj/job2_7</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1012252.html</v>
       </c>
       <c r="C112">
         <v>200</v>
@@ -1953,7 +1953,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B113" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016431.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016440.html</v>
       </c>
       <c r="C113">
         <v>200</v>
@@ -1967,7 +1967,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B114" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016433.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016488.html</v>
       </c>
       <c r="C114">
         <v>200</v>
@@ -1981,7 +1981,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B115" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016429.html</v>
+        <v>https://www.bes-c.com/</v>
       </c>
       <c r="C115">
         <v>200</v>
@@ -1995,7 +1995,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B116" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1012252.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016491.html</v>
       </c>
       <c r="C116">
         <v>200</v>
@@ -2009,7 +2009,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B117" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016440.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012724/1013205/1034493/1013206.html</v>
       </c>
       <c r="C117">
         <v>200</v>
@@ -2023,7 +2023,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B118" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016488.html</v>
+        <v>https://www.pref.aichi.jp/soshiki/imu/0000050084.html</v>
       </c>
       <c r="C118">
         <v>200</v>
@@ -2037,7 +2037,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B119" t="str">
-        <v>https://www.bes-c.com/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008943.html</v>
       </c>
       <c r="C119">
         <v>200</v>
@@ -2051,7 +2051,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B120" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016491.html</v>
+        <v>https://www.qq.pref.aichi.jp/</v>
       </c>
       <c r="C120">
         <v>200</v>
@@ -2065,7 +2065,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B121" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012724/1013205/1034493/1013206.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008947.html</v>
       </c>
       <c r="C121">
         <v>200</v>
@@ -2079,7 +2079,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B122" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008943.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/index.html</v>
       </c>
       <c r="C122">
         <v>200</v>
@@ -2093,7 +2093,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B123" t="str">
-        <v>https://www.qq.pref.aichi.jp/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008920/index.html</v>
       </c>
       <c r="C123">
         <v>200</v>
@@ -2107,7 +2107,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B124" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008947.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008937.html</v>
       </c>
       <c r="C124">
         <v>200</v>
@@ -2121,7 +2121,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B125" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008938.html</v>
       </c>
       <c r="C125">
         <v>200</v>
@@ -2135,7 +2135,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B126" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008920/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008939/index.html</v>
       </c>
       <c r="C126">
         <v>200</v>
@@ -2149,7 +2149,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B127" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008937.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008949.html</v>
       </c>
       <c r="C127">
         <v>200</v>
@@ -2163,7 +2163,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B128" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008938.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034084/1009261.html</v>
       </c>
       <c r="C128">
         <v>200</v>
@@ -2177,7 +2177,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B129" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008939/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009265.html</v>
       </c>
       <c r="C129">
         <v>200</v>
@@ -2191,7 +2191,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B130" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008949.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009264.html</v>
       </c>
       <c r="C130">
         <v>200</v>
@@ -2205,7 +2205,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B131" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034084/1009261.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009260.html</v>
       </c>
       <c r="C131">
         <v>200</v>
@@ -2219,7 +2219,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B132" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009265.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009258.html</v>
       </c>
       <c r="C132">
         <v>200</v>
@@ -2233,7 +2233,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B133" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009264.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009307/1008988.html</v>
       </c>
       <c r="C133">
         <v>200</v>
@@ -2247,7 +2247,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B134" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009260.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
       </c>
       <c r="C134">
         <v>200</v>
@@ -2261,7 +2261,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B135" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009258.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034342/1008991/1036125.html</v>
       </c>
       <c r="C135">
         <v>200</v>
@@ -2275,7 +2275,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B136" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009307/1008988.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009126.html</v>
       </c>
       <c r="C136">
         <v>200</v>
@@ -2289,7 +2289,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B137" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1037093/1016989.html</v>
       </c>
       <c r="C137">
         <v>200</v>
@@ -2303,7 +2303,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B138" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034342/1008991/1036125.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008959.html</v>
       </c>
       <c r="C138">
         <v>200</v>
@@ -2317,7 +2317,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B139" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009126.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009018.html</v>
       </c>
       <c r="C139">
         <v>200</v>
@@ -2331,7 +2331,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B140" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1037093/1016989.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016781.html</v>
       </c>
       <c r="C140">
         <v>200</v>
@@ -2345,7 +2345,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B141" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008959.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1036101.html</v>
       </c>
       <c r="C141">
         <v>200</v>
@@ -2359,7 +2359,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B142" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009018.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1015850/1017055.html</v>
       </c>
       <c r="C142">
         <v>200</v>
@@ -2373,7 +2373,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B143" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016781.html</v>
+        <v>https://nagoya.fureai-cloud.jp/_view/sodan/home/index</v>
       </c>
       <c r="C143">
         <v>200</v>
@@ -2387,7 +2387,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B144" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1036101.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009321/1009322.html</v>
       </c>
       <c r="C144">
         <v>200</v>
@@ -2401,7 +2401,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B145" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1015850/1017055.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016409.html</v>
       </c>
       <c r="C145">
         <v>200</v>
@@ -2415,7 +2415,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B146" t="str">
-        <v>https://nagoya.fureai-cloud.jp/_view/sodan/home/index</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015819/1038028/index.html</v>
       </c>
       <c r="C146">
         <v>200</v>
@@ -2429,7 +2429,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B147" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009321/1009322.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015845.html</v>
       </c>
       <c r="C147">
         <v>200</v>
@@ -2443,7 +2443,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B148" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016409.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016404.html</v>
       </c>
       <c r="C148">
         <v>200</v>
@@ -2457,7 +2457,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B149" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015819/1038028/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016402.html</v>
       </c>
       <c r="C149">
         <v>200</v>
@@ -2471,7 +2471,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B150" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015845.html</v>
+        <v>https://www.nic-nagoya.or.jp/</v>
       </c>
       <c r="C150">
         <v>200</v>
@@ -2485,7 +2485,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B151" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016404.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016399.html</v>
       </c>
       <c r="C151">
         <v>200</v>
@@ -2499,10 +2499,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B152" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016402.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016734.html</v>
       </c>
       <c r="C152">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D152" t="str">
         <v>data/services.js</v>
@@ -2513,7 +2513,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B153" t="str">
-        <v>https://www.nic-nagoya.or.jp/</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008983/1008984.html</v>
       </c>
       <c r="C153">
         <v>200</v>
@@ -2527,7 +2527,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B154" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016399.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009388.html</v>
       </c>
       <c r="C154">
         <v>200</v>
@@ -2541,10 +2541,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B155" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016734.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009391.html</v>
       </c>
       <c r="C155">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D155" t="str">
         <v>data/services.js</v>
@@ -2555,7 +2555,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B156" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008983/1008984.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009381/1009382.html</v>
       </c>
       <c r="C156">
         <v>200</v>
@@ -2569,7 +2569,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B157" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009388.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009334.html</v>
       </c>
       <c r="C157">
         <v>200</v>
@@ -2583,7 +2583,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B158" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009391.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009389.html</v>
       </c>
       <c r="C158">
         <v>200</v>
@@ -2597,7 +2597,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B159" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009381/1009382.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009374.html</v>
       </c>
       <c r="C159">
         <v>200</v>
@@ -2611,7 +2611,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B160" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009334.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1016449/index.html</v>
       </c>
       <c r="C160">
         <v>200</v>
@@ -2625,7 +2625,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B161" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009389.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/</v>
       </c>
       <c r="C161">
         <v>200</v>
@@ -2639,13 +2639,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B162" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009374.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/jouhou/1036432/1013386.html</v>
       </c>
       <c r="C162">
         <v>200</v>
       </c>
       <c r="D162" t="str">
-        <v>data/services.js</v>
+        <v>data/services.js, screens/DisasterScreen.js</v>
       </c>
     </row>
     <row r="163">
@@ -2653,7 +2653,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B163" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1016449/index.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/kyoujo/1036451/1013567.html</v>
       </c>
       <c r="C163">
         <v>200</v>
@@ -2667,7 +2667,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B164" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008962/1008963.html</v>
       </c>
       <c r="C164">
         <v>200</v>
@@ -2681,13 +2681,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B165" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/jouhou/1036432/1013386.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016506/1016510/1016511.html</v>
       </c>
       <c r="C165">
         <v>200</v>
       </c>
       <c r="D165" t="str">
-        <v>data/services.js, screens/DisasterScreen.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="166">
@@ -2695,7 +2695,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B166" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/kyoujo/1036451/1013567.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009502/1034108.html</v>
       </c>
       <c r="C166">
         <v>200</v>
@@ -2709,7 +2709,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B167" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008962/1008963.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/todokede/1007816/1007817.html</v>
       </c>
       <c r="C167">
         <v>200</v>
@@ -2723,7 +2723,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B168" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016506/1016510/1016511.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011854/index.html</v>
       </c>
       <c r="C168">
         <v>200</v>
@@ -2737,7 +2737,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B169" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009502/1034108.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011868.html</v>
       </c>
       <c r="C169">
         <v>200</v>
@@ -2751,7 +2751,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B170" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/todokede/1007816/1007817.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011870.html</v>
       </c>
       <c r="C170">
         <v>200</v>
@@ -2765,7 +2765,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B171" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011854/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/index.html</v>
       </c>
       <c r="C171">
         <v>200</v>
@@ -2779,7 +2779,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B172" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011868.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1035058/1012184/1046468/index.html</v>
       </c>
       <c r="C172">
         <v>200</v>
@@ -2793,7 +2793,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B173" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011870.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016573/index.html</v>
       </c>
       <c r="C173">
         <v>200</v>
@@ -2807,7 +2807,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B174" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/pet/1015473/index.html</v>
       </c>
       <c r="C174">
         <v>200</v>
@@ -2821,7 +2821,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B175" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1035058/1012184/1046468/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011763/1011768.html</v>
       </c>
       <c r="C175">
         <v>200</v>
@@ -2835,7 +2835,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B176" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016573/index.html</v>
+        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000135090_00001.html</v>
       </c>
       <c r="C176">
         <v>200</v>
@@ -2849,7 +2849,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B177" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/pet/1015473/index.html</v>
+        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000158665.html</v>
       </c>
       <c r="C177">
         <v>200</v>
@@ -2863,7 +2863,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B178" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011763/1011768.html</v>
+        <v>https://www.kyoukaikenpo.or.jp/benefit/injury_and_sickness_allowance/index.html</v>
       </c>
       <c r="C178">
         <v>200</v>
@@ -2877,7 +2877,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B179" t="str">
-        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000135090_00001.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011851/1011853.html</v>
       </c>
       <c r="C179">
         <v>200</v>
@@ -2891,7 +2891,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B180" t="str">
-        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000158665.html</v>
+        <v>https://www.nenkin.go.jp/service/jukyu/seido/sonota-kyufu/shienkyufukin/20190805.html</v>
       </c>
       <c r="C180">
         <v>200</v>
@@ -2905,7 +2905,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B181" t="str">
-        <v>https://www.kyoukaikenpo.or.jp/benefit/injury_and_sickness_allowance/index.html</v>
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm</v>
       </c>
       <c r="C181">
         <v>200</v>
@@ -2919,7 +2919,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B182" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011851/1011853.html</v>
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm#mushoukaLink2</v>
       </c>
       <c r="C182">
         <v>200</v>
@@ -2933,7 +2933,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B183" t="str">
-        <v>https://www.nenkin.go.jp/service/jukyu/seido/sonota-kyufu/shienkyufukin/20190805.html</v>
+        <v>https://www.jasso.go.jp/shogakukin/</v>
       </c>
       <c r="C183">
         <v>200</v>
@@ -2947,7 +2947,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B184" t="str">
-        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008946.html</v>
       </c>
       <c r="C184">
         <v>200</v>
@@ -2961,7 +2961,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B185" t="str">
-        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm#mushoukaLink2</v>
+        <v>https://www.pref.aichi.jp/soshiki/zaimusisetsu/syuugakushienkin.html</v>
       </c>
       <c r="C185">
         <v>200</v>
@@ -2975,7 +2975,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B186" t="str">
-        <v>https://www.jasso.go.jp/shogakukin/</v>
+        <v>https://www.pref.aichi.jp/uploaded/attachment/620030.pdf</v>
       </c>
       <c r="C186">
         <v>200</v>
@@ -2989,7 +2989,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B187" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008946.html</v>
+        <v>https://www.pref.aichi.jp/soshiki/shigaku/shigaku-syougakukyuhukin.html</v>
       </c>
       <c r="C187">
         <v>200</v>
@@ -3644,10 +3644,10 @@
         <v>https://www.pref.aichi.jp/soshiki/zaimusisetsu/syuugakushienkin.html</v>
       </c>
       <c r="B2" t="str">
+        <v>Loading</v>
+      </c>
+      <c r="C2" t="str">
         <v>県立高等学校等就学支援金制度 - 愛知県</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Loading</v>
       </c>
       <c r="D2" t="str">
         <v>data/services.js</v>
@@ -3662,7 +3662,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3692,10 +3692,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D2" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1013090/1013096/1051100.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1050592/1051513.html</v>
       </c>
       <c r="E2" t="str">
-        <v>令和8年度名東の日を開催しました！</v>
+        <v>【重要】電気火災が増えています</v>
       </c>
     </row>
     <row r="3">
@@ -3706,81 +3706,81 @@
         <v>https://www.city.nagoya.jp/bousai/index.html</v>
       </c>
       <c r="C3" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D3" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012913/1045614/1051635.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1051487/index.html</v>
       </c>
       <c r="E3" t="str">
-        <v>予防課からのお知らせ</v>
+        <v>熱田消防署について</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>くらし・手続き</v>
+        <v>防災・安全安心</v>
       </c>
       <c r="B4" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
       </c>
       <c r="C4" t="str">
         <v>➕ 追加</v>
       </c>
       <c r="D4" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/1034008/1052263.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1051487/1051409.html</v>
       </c>
       <c r="E4" t="str">
-        <v>令和8年（2026年）熊本地震で被災された方への市営住宅の提供</v>
+        <v>熱田消防署へのアクセス（公共交通機関）</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>くらし・手続き</v>
+        <v>防災・安全安心</v>
       </c>
       <c r="B5" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
       </c>
       <c r="C5" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D5" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shiminsanka/1011147/1052132.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012913/1012914/1052131.html</v>
       </c>
       <c r="E5" t="str">
-        <v>令和8年熊本地震災害義援金の募集</v>
+        <v>消防職員の熱中症対策として製氷機を寄贈頂きました</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>くらし・手続き</v>
+        <v>防災・安全安心</v>
       </c>
       <c r="B6" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
       </c>
       <c r="C6" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D6" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052096.html</v>
+        <v>https://www.city.nagoya.jp/bousai/anzen/1014448/1014474/1050980.html</v>
       </c>
       <c r="E6" t="str">
-        <v>蓬左文庫企画展 生誕140年 没後50年記念 旅する侯爵 徳川義親</v>
+        <v>市民向け講座「令和8年度 第1回 犯罪被害を学ぶ会」を開催します（事前申込制）</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>くらし・手続き</v>
+        <v>防災・安全安心</v>
       </c>
       <c r="B7" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
       </c>
       <c r="C7" t="str">
         <v>➖ 削除</v>
       </c>
       <c r="D7" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/zeikin/1007927/1050342.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1013090/1013096/1051100.html</v>
       </c>
       <c r="E7" t="str">
-        <v>税務証明等手数料の改定のお知らせ（令和8年10月1日から）</v>
+        <v>令和8年度名東の日を開催しました！</v>
       </c>
     </row>
     <row r="8">
@@ -3791,13 +3791,13 @@
         <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C8" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D8" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/douro/1014806/1034763/1014850.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1034811/1012684/1012697/1034060/1051886.html</v>
       </c>
       <c r="E8" t="str">
-        <v>堀川ギャラリー</v>
+        <v>ぜん息予防サッカー教室</v>
       </c>
     </row>
     <row r="9">
@@ -3808,81 +3808,81 @@
         <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C9" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D9" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051109.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1050836.html</v>
       </c>
       <c r="E9" t="str">
-        <v>めざせ！！水の環復活－学んでみよう、水のことー浄水場と水循環</v>
+        <v>ソレイユプラザなごや「家族で楽しむ体験イベント」レゴランド(R)（上付き）・ジャパンのワークショップで多様性を学ぼう！</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>子ども・子育て・教育</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B10" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C10" t="str">
         <v>➕ 追加</v>
       </c>
       <c r="D10" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1052219.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1015518/1052115.html</v>
       </c>
       <c r="E10" t="str">
-        <v>令和8年度トワイライトスクール・ルームに関するアンケート調査について</v>
+        <v>消費生活相談員になりませんか？</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>子ども・子育て・教育</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B11" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C11" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D11" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1051827.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/1034008/1052263.html</v>
       </c>
       <c r="E11" t="str">
-        <v>令和8年8月10日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+        <v>令和8年（2026年）熊本地震で被災された方への市営住宅の提供</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>子ども・子育て・教育</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B12" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C12" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D12" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1034096.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shiminsanka/1011147/1052132.html</v>
       </c>
       <c r="E12" t="str">
-        <v>幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+        <v>令和8年熊本地震災害義援金の募集</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>子ども・子育て・教育</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B13" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C13" t="str">
         <v>➖ 削除</v>
       </c>
       <c r="D13" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034338/1051902.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052096.html</v>
       </c>
       <c r="E13" t="str">
-        <v>令和8年度 里親制度説明＆里親の体験談を聞く会</v>
+        <v>蓬左文庫企画展 生誕140年 没後50年記念 旅する侯爵 徳川義親</v>
       </c>
     </row>
     <row r="14">
@@ -3893,13 +3893,13 @@
         <v>https://www.city.nagoya.jp/kodomo/index.html</v>
       </c>
       <c r="C14" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D14" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/jisedai/1009754/1009755/1052076.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1027694/1052246.html</v>
       </c>
       <c r="E14" t="str">
-        <v>令和8年度なごっちフレンズワークショップ (令和8年8月25日)</v>
+        <v>令和8年度 教育委員会8月臨時会</v>
       </c>
     </row>
     <row r="15">
@@ -3913,22 +3913,90 @@
         <v>➖ 削除</v>
       </c>
       <c r="D15" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1034069/1051899.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1034096.html</v>
       </c>
       <c r="E15" t="str">
-        <v>災害の備えどうしてる？－慢性疾患のある子どもと家族のための災害対策を見直そうー</v>
+        <v>幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="B16" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="C16" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D16" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1035053/1052496.html</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Zoomによる初めてのオンライン手話講座（令和8年9月金曜コース）</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="B17" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="C17" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D17" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016414/1051383.html</v>
+      </c>
+      <c r="E17" t="str">
+        <v>令和8年度「敬老の日」における市民利用施設の無料開放等実施のお知らせ</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="B18" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="C18" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D18" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1011432/1051796.html</v>
+      </c>
+      <c r="E18" t="str">
+        <v>専用水道に関する届出</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="B19" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="C19" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D19" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1034419/1050801.html</v>
+      </c>
+      <c r="E19" t="str">
+        <v>令和8年度つながり・支えあおう地域福祉のすゝめ（イベントのご案内）</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E19"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M106"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5633,9 +5701,528 @@
         <v>災害の備えどうしてる？－慢性疾患のある子どもと家族のための災害対策を見直そうー</v>
       </c>
     </row>
+    <row r="83">
+      <c r="B83" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C83" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D83" t="str">
+        <v>https://hikikomori.city.nagoya.jp/</v>
+      </c>
+      <c r="E83" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F83" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C84" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D84" t="str">
+        <v>https://nagoya-shakyo.jp/service/fureai-kyushoku/</v>
+      </c>
+      <c r="E84" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F84" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C85" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D85" t="str">
+        <v>https://nagoya-shakyo.jp/service/ward-shakyo/</v>
+      </c>
+      <c r="E85" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F85" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C86" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D86" t="str">
+        <v>https://nagoya-shakyo.jp/service/community-support/</v>
+      </c>
+      <c r="E86" t="str">
+        <v>TIMEOUT</v>
+      </c>
+      <c r="F86" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C87" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D87" t="str">
+        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
+      </c>
+      <c r="E87" t="str">
+        <v>ERROR</v>
+      </c>
+      <c r="F87" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C88" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D88" t="str">
+        <v>https://www.pref.aichi.jp/soshiki/zaimusisetsu/syuugakushienkin.html</v>
+      </c>
+      <c r="F88" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G88" t="str">
+        <v>Loading</v>
+      </c>
+      <c r="H88" t="str">
+        <v>県立高等学校等就学支援金制度 - 愛知県</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C89" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I89" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J89" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K89" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L89" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1050592/1051513.html</v>
+      </c>
+      <c r="M89" t="str">
+        <v>【重要】電気火災が増えています</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C90" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I90" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J90" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K90" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L90" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1051487/index.html</v>
+      </c>
+      <c r="M90" t="str">
+        <v>熱田消防署について</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C91" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I91" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J91" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K91" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L91" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1051487/1051409.html</v>
+      </c>
+      <c r="M91" t="str">
+        <v>熱田消防署へのアクセス（公共交通機関）</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C92" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I92" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J92" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K92" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L92" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012913/1012914/1052131.html</v>
+      </c>
+      <c r="M92" t="str">
+        <v>消防職員の熱中症対策として製氷機を寄贈頂きました</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C93" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I93" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J93" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K93" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L93" t="str">
+        <v>https://www.city.nagoya.jp/bousai/anzen/1014448/1014474/1050980.html</v>
+      </c>
+      <c r="M93" t="str">
+        <v>市民向け講座「令和8年度 第1回 犯罪被害を学ぶ会」を開催します（事前申込制）</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C94" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I94" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J94" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K94" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L94" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1013090/1013096/1051100.html</v>
+      </c>
+      <c r="M94" t="str">
+        <v>令和8年度名東の日を開催しました！</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C95" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I95" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J95" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K95" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L95" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1034811/1012684/1012697/1034060/1051886.html</v>
+      </c>
+      <c r="M95" t="str">
+        <v>ぜん息予防サッカー教室</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C96" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I96" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J96" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K96" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L96" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1050836.html</v>
+      </c>
+      <c r="M96" t="str">
+        <v>ソレイユプラザなごや「家族で楽しむ体験イベント」レゴランド(R)（上付き）・ジャパンのワークショップで多様性を学ぼう！</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C97" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I97" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J97" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K97" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L97" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1015518/1052115.html</v>
+      </c>
+      <c r="M97" t="str">
+        <v>消費生活相談員になりませんか？</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C98" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I98" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J98" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K98" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L98" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/1034008/1052263.html</v>
+      </c>
+      <c r="M98" t="str">
+        <v>令和8年（2026年）熊本地震で被災された方への市営住宅の提供</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C99" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I99" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J99" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K99" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L99" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/shiminsanka/1011147/1052132.html</v>
+      </c>
+      <c r="M99" t="str">
+        <v>令和8年熊本地震災害義援金の募集</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C100" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I100" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J100" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K100" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L100" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052096.html</v>
+      </c>
+      <c r="M100" t="str">
+        <v>蓬左文庫企画展 生誕140年 没後50年記念 旅する侯爵 徳川義親</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C101" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I101" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J101" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K101" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L101" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1027694/1052246.html</v>
+      </c>
+      <c r="M101" t="str">
+        <v>令和8年度 教育委員会8月臨時会</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C102" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I102" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J102" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K102" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L102" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1034096.html</v>
+      </c>
+      <c r="M102" t="str">
+        <v>幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C103" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I103" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J103" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K103" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L103" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1035053/1052496.html</v>
+      </c>
+      <c r="M103" t="str">
+        <v>Zoomによる初めてのオンライン手話講座（令和8年9月金曜コース）</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C104" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I104" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J104" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K104" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L104" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016414/1051383.html</v>
+      </c>
+      <c r="M104" t="str">
+        <v>令和8年度「敬老の日」における市民利用施設の無料開放等実施のお知らせ</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C105" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I105" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J105" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K105" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L105" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1011432/1051796.html</v>
+      </c>
+      <c r="M105" t="str">
+        <v>専用水道に関する届出</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="C106" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I106" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J106" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K106" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L106" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1034419/1050801.html</v>
+      </c>
+      <c r="M106" t="str">
+        <v>令和8年度つながり・支えあおう地域福祉のすゝめ（イベントのご案内）</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M82"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M106"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reports/latest-report.xlsx
+++ b/reports/latest-report.xlsx
@@ -378,7 +378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D231"/>
+  <dimension ref="A1:D224"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -396,72 +396,72 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>❌ リンク切れ</v>
+        <v>✅ 正常</v>
       </c>
       <c r="B2" t="str">
-        <v>https://hikikomori.city.nagoya.jp/</v>
-      </c>
-      <c r="C2" t="str">
-        <v>TIMEOUT</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036294.html</v>
+      </c>
+      <c r="C2">
+        <v>200</v>
       </c>
       <c r="D2" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>❌ リンク切れ</v>
+        <v>✅ 正常</v>
       </c>
       <c r="B3" t="str">
-        <v>https://nagoya-shakyo.jp/service/fureai-kyushoku/</v>
-      </c>
-      <c r="C3" t="str">
-        <v>TIMEOUT</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/index.html</v>
+      </c>
+      <c r="C3">
+        <v>200</v>
       </c>
       <c r="D3" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js, screens/DisasterScreen.js</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>❌ リンク切れ</v>
+        <v>✅ 正常</v>
       </c>
       <c r="B4" t="str">
-        <v>https://nagoya-shakyo.jp/service/ward-shakyo/</v>
-      </c>
-      <c r="C4" t="str">
-        <v>TIMEOUT</v>
+        <v>https://www.city.nagoya.jp/chikusa/kurashi/</v>
+      </c>
+      <c r="C4">
+        <v>200</v>
       </c>
       <c r="D4" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>❌ リンク切れ</v>
+        <v>✅ 正常</v>
       </c>
       <c r="B5" t="str">
-        <v>https://nagoya-shakyo.jp/service/community-support/</v>
-      </c>
-      <c r="C5" t="str">
-        <v>TIMEOUT</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036299.html</v>
+      </c>
+      <c r="C5">
+        <v>200</v>
       </c>
       <c r="D5" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>❌ リンク切れ</v>
+        <v>✅ 正常</v>
       </c>
       <c r="B6" t="str">
-        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
-      </c>
-      <c r="C6" t="str">
-        <v>ERROR</v>
+        <v>https://www.city.nagoya.jp/higashi/kurashi/</v>
+      </c>
+      <c r="C6">
+        <v>200</v>
       </c>
       <c r="D6" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="7">
@@ -469,7 +469,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B7" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036294.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036302.html</v>
       </c>
       <c r="C7">
         <v>200</v>
@@ -483,13 +483,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B8" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/index.html</v>
+        <v>https://www.city.nagoya.jp/kita/kurashi/</v>
       </c>
       <c r="C8">
         <v>200</v>
       </c>
       <c r="D8" t="str">
-        <v>data/districts.js, screens/DisasterScreen.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="9">
@@ -497,7 +497,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B9" t="str">
-        <v>https://www.city.nagoya.jp/chikusa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036293.html</v>
       </c>
       <c r="C9">
         <v>200</v>
@@ -511,7 +511,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B10" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036299.html</v>
+        <v>https://www.city.nagoya.jp/nishi/kurashi/</v>
       </c>
       <c r="C10">
         <v>200</v>
@@ -525,7 +525,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B11" t="str">
-        <v>https://www.city.nagoya.jp/higashi/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036297.html</v>
       </c>
       <c r="C11">
         <v>200</v>
@@ -539,7 +539,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B12" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036302.html</v>
+        <v>https://www.city.nagoya.jp/nakamura/kurashi/</v>
       </c>
       <c r="C12">
         <v>200</v>
@@ -553,7 +553,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B13" t="str">
-        <v>https://www.city.nagoya.jp/kita/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036295.html</v>
       </c>
       <c r="C13">
         <v>200</v>
@@ -567,7 +567,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B14" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036293.html</v>
+        <v>https://www.city.nagoya.jp/naka/kurashi/</v>
       </c>
       <c r="C14">
         <v>200</v>
@@ -581,7 +581,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B15" t="str">
-        <v>https://www.city.nagoya.jp/nishi/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036291.html</v>
       </c>
       <c r="C15">
         <v>200</v>
@@ -595,7 +595,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B16" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036297.html</v>
+        <v>https://www.city.nagoya.jp/showa/kurashi/</v>
       </c>
       <c r="C16">
         <v>200</v>
@@ -609,7 +609,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B17" t="str">
-        <v>https://www.city.nagoya.jp/nakamura/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036292.html</v>
       </c>
       <c r="C17">
         <v>200</v>
@@ -623,7 +623,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B18" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036295.html</v>
+        <v>https://www.city.nagoya.jp/mizuho/kurashi/</v>
       </c>
       <c r="C18">
         <v>200</v>
@@ -637,7 +637,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B19" t="str">
-        <v>https://www.city.nagoya.jp/naka/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036301.html</v>
       </c>
       <c r="C19">
         <v>200</v>
@@ -651,7 +651,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B20" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036291.html</v>
+        <v>https://www.city.nagoya.jp/atsuta/kurashi/</v>
       </c>
       <c r="C20">
         <v>200</v>
@@ -665,7 +665,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B21" t="str">
-        <v>https://www.city.nagoya.jp/showa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036296.html</v>
       </c>
       <c r="C21">
         <v>200</v>
@@ -679,7 +679,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B22" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036292.html</v>
+        <v>https://www.city.nagoya.jp/nakagawa/kurashi/</v>
       </c>
       <c r="C22">
         <v>200</v>
@@ -693,7 +693,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B23" t="str">
-        <v>https://www.city.nagoya.jp/mizuho/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036289.html</v>
       </c>
       <c r="C23">
         <v>200</v>
@@ -707,7 +707,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B24" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036301.html</v>
+        <v>https://www.city.nagoya.jp/minato/kurashi/</v>
       </c>
       <c r="C24">
         <v>200</v>
@@ -721,7 +721,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B25" t="str">
-        <v>https://www.city.nagoya.jp/atsuta/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036300.html</v>
       </c>
       <c r="C25">
         <v>200</v>
@@ -735,7 +735,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B26" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036296.html</v>
+        <v>https://www.city.nagoya.jp/minami/kurashi/</v>
       </c>
       <c r="C26">
         <v>200</v>
@@ -749,7 +749,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B27" t="str">
-        <v>https://www.city.nagoya.jp/nakagawa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036290.html</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -763,7 +763,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B28" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036289.html</v>
+        <v>https://www.city.nagoya.jp/moriyama/kurashi/</v>
       </c>
       <c r="C28">
         <v>200</v>
@@ -777,7 +777,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B29" t="str">
-        <v>https://www.city.nagoya.jp/minato/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036304.html</v>
       </c>
       <c r="C29">
         <v>200</v>
@@ -791,7 +791,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B30" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036300.html</v>
+        <v>https://www.city.nagoya.jp/midori/kurashi/</v>
       </c>
       <c r="C30">
         <v>200</v>
@@ -805,7 +805,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B31" t="str">
-        <v>https://www.city.nagoya.jp/minami/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036303.html</v>
       </c>
       <c r="C31">
         <v>200</v>
@@ -819,7 +819,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B32" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036290.html</v>
+        <v>https://www.city.nagoya.jp/meito/kurashi/</v>
       </c>
       <c r="C32">
         <v>200</v>
@@ -833,7 +833,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B33" t="str">
-        <v>https://www.city.nagoya.jp/moriyama/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036298.html</v>
       </c>
       <c r="C33">
         <v>200</v>
@@ -847,7 +847,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B34" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036304.html</v>
+        <v>https://www.city.nagoya.jp/tempaku/kurashi/</v>
       </c>
       <c r="C34">
         <v>200</v>
@@ -861,13 +861,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B35" t="str">
-        <v>https://www.city.nagoya.jp/midori/kurashi/</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008973.html</v>
       </c>
       <c r="C35">
         <v>200</v>
       </c>
       <c r="D35" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="36">
@@ -875,13 +875,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B36" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036303.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009333.html</v>
       </c>
       <c r="C36">
         <v>200</v>
       </c>
       <c r="D36" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="37">
@@ -889,13 +889,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B37" t="str">
-        <v>https://www.city.nagoya.jp/meito/kurashi/</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1009009.html</v>
       </c>
       <c r="C37">
         <v>200</v>
       </c>
       <c r="D37" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="38">
@@ -903,13 +903,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B38" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036298.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009270/1034086.html</v>
       </c>
       <c r="C38">
         <v>200</v>
       </c>
       <c r="D38" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="39">
@@ -917,13 +917,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B39" t="str">
-        <v>https://www.city.nagoya.jp/tempaku/kurashi/</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009353/1034092.html</v>
       </c>
       <c r="C39">
         <v>200</v>
       </c>
       <c r="D39" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="40">
@@ -931,7 +931,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B40" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008973.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009286/index.html</v>
       </c>
       <c r="C40">
         <v>200</v>
@@ -945,7 +945,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B41" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009333.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1034088.html</v>
       </c>
       <c r="C41">
         <v>200</v>
@@ -959,7 +959,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B42" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1009009.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009387.html</v>
       </c>
       <c r="C42">
         <v>200</v>
@@ -973,7 +973,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B43" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009270/1034086.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009393.html</v>
       </c>
       <c r="C43">
         <v>200</v>
@@ -987,7 +987,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B44" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009353/1034092.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011821/1011823.html</v>
       </c>
       <c r="C44">
         <v>200</v>
@@ -1001,7 +1001,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B45" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009286/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008956.html</v>
       </c>
       <c r="C45">
         <v>200</v>
@@ -1015,7 +1015,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B46" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1034088.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008955.html</v>
       </c>
       <c r="C46">
         <v>200</v>
@@ -1029,7 +1029,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B47" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009387.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/ichiran.html</v>
       </c>
       <c r="C47">
         <v>200</v>
@@ -1043,7 +1043,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B48" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009393.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008960.html</v>
       </c>
       <c r="C48">
         <v>200</v>
@@ -1057,7 +1057,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B49" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011821/1011823.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009019.html</v>
       </c>
       <c r="C49">
         <v>200</v>
@@ -1071,7 +1071,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B50" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008956.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008974.html</v>
       </c>
       <c r="C50">
         <v>200</v>
@@ -1085,7 +1085,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B51" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008955.html</v>
+        <v>https://www.city.nagoya.jp/lifescene/byouki/1017964.html</v>
       </c>
       <c r="C51">
         <v>200</v>
@@ -1099,7 +1099,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B52" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/ichiran.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/seido/toiawase/</v>
       </c>
       <c r="C52">
         <v>200</v>
@@ -1113,7 +1113,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B53" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008960.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016496/1016502.html</v>
       </c>
       <c r="C53">
         <v>200</v>
@@ -1127,7 +1127,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B54" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009019.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/1016536.html</v>
       </c>
       <c r="C54">
         <v>200</v>
@@ -1141,7 +1141,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B55" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008974.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011776/1034706/1011784.html</v>
       </c>
       <c r="C55">
         <v>200</v>
@@ -1155,7 +1155,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B56" t="str">
-        <v>https://www.city.nagoya.jp/lifescene/byouki/1017964.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009456/1009457/index.html</v>
       </c>
       <c r="C56">
         <v>200</v>
@@ -1169,7 +1169,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B57" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/seido/toiawase/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
       </c>
       <c r="C57">
         <v>200</v>
@@ -1183,7 +1183,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B58" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016496/1016502.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1012157/1033970.html</v>
       </c>
       <c r="C58">
         <v>200</v>
@@ -1197,7 +1197,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B59" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/1016536.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1015763/1015815.html</v>
       </c>
       <c r="C59">
         <v>200</v>
@@ -1211,7 +1211,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B60" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011776/1034706/1011784.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011793/1011807/1011810.html</v>
       </c>
       <c r="C60">
         <v>200</v>
@@ -1225,7 +1225,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B61" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009456/1009457/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016739.html</v>
       </c>
       <c r="C61">
         <v>200</v>
@@ -1239,7 +1239,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B62" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/index.html</v>
       </c>
       <c r="C62">
         <v>200</v>
@@ -1253,7 +1253,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B63" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1012157/1033970.html</v>
+        <v>https://www.hellowork.mhlw.go.jp/insurance/insurance_guide.html</v>
       </c>
       <c r="C63">
         <v>200</v>
@@ -1267,7 +1267,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B64" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1015763/1015815.html</v>
+        <v>https://jsite.mhlw.go.jp/aichi-hellowork/list.html</v>
       </c>
       <c r="C64">
         <v>200</v>
@@ -1281,7 +1281,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B65" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011793/1011807/1011810.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
       </c>
       <c r="C65">
         <v>200</v>
@@ -1295,7 +1295,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B66" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016739.html</v>
+        <v>https://www.nagojob.city.nagoya.jp/</v>
       </c>
       <c r="C66">
         <v>200</v>
@@ -1309,7 +1309,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B67" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/index.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/tetyou/</v>
       </c>
       <c r="C67">
         <v>200</v>
@@ -1323,7 +1323,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B68" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/jutakukanri/bosyuannai.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/soudan/fukushikakari.html</v>
       </c>
       <c r="C68">
         <v>200</v>
@@ -1337,7 +1337,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B69" t="str">
-        <v>https://www.hellowork.mhlw.go.jp/insurance/insurance_guide.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/fukushi_service.html</v>
       </c>
       <c r="C69">
         <v>200</v>
@@ -1351,7 +1351,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B70" t="str">
-        <v>https://jsite.mhlw.go.jp/aichi-hellowork/list.html</v>
+        <v>https://www.city.nagoya.jp/jigyou/sangyou/1026356/1035103/1026446/1026447.html</v>
       </c>
       <c r="C70">
         <v>200</v>
@@ -1365,7 +1365,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B71" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
+        <v>https://weljob-nagoya.com/</v>
       </c>
       <c r="C71">
         <v>200</v>
@@ -1379,7 +1379,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B72" t="str">
-        <v>https://www.nagojob.city.nagoya.jp/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
       </c>
       <c r="C72">
         <v>200</v>
@@ -1393,7 +1393,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B73" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/tetyou/</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/622/linksweb.pdf</v>
       </c>
       <c r="C73">
         <v>200</v>
@@ -1407,7 +1407,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B74" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/soudan/fukushikakari.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
       </c>
       <c r="C74">
         <v>200</v>
@@ -1421,7 +1421,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B75" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/fukushi_service.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/675/annnai.pdf</v>
       </c>
       <c r="C75">
         <v>200</v>
@@ -1435,7 +1435,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B76" t="str">
-        <v>https://www.city.nagoya.jp/jigyou/sangyou/1026356/1035103/1026446/1026447.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
       </c>
       <c r="C76">
         <v>200</v>
@@ -1449,7 +1449,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B77" t="str">
-        <v>https://weljob-nagoya.com/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
       </c>
       <c r="C77">
         <v>200</v>
@@ -1463,7 +1463,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B78" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
       </c>
       <c r="C78">
         <v>200</v>
@@ -1477,7 +1477,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B79" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/622/linksweb.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008978.html</v>
       </c>
       <c r="C79">
         <v>200</v>
@@ -1491,7 +1491,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B80" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/008/978/0413tirasi.pdf</v>
       </c>
       <c r="C80">
         <v>200</v>
@@ -1505,7 +1505,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B81" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/675/annnai.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034073/1009017.html</v>
       </c>
       <c r="C81">
         <v>200</v>
@@ -1519,7 +1519,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B82" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/009/017/r710_help.pdf</v>
       </c>
       <c r="C82">
         <v>200</v>
@@ -1533,7 +1533,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B83" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1034087.html</v>
       </c>
       <c r="C83">
         <v>200</v>
@@ -1547,7 +1547,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B84" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
+        <v>https://www.kosodate.city.nagoya.jp/kids/nobinobi.html</v>
       </c>
       <c r="C84">
         <v>200</v>
@@ -1561,7 +1561,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B85" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008978.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1009278.html</v>
       </c>
       <c r="C85">
         <v>200</v>
@@ -1575,7 +1575,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B86" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/008/978/0413tirasi.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009024/1009026.html</v>
       </c>
       <c r="C86">
         <v>200</v>
@@ -1589,7 +1589,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B87" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034073/1009017.html</v>
+        <v>https://www.kosodate.city.nagoya.jp/play/supportbases.html</v>
       </c>
       <c r="C87">
         <v>200</v>
@@ -1603,7 +1603,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B88" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/009/017/r710_help.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034075/1009021.html</v>
       </c>
       <c r="C88">
         <v>200</v>
@@ -1617,7 +1617,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B89" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1034087.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034072/1009016.html</v>
       </c>
       <c r="C89">
         <v>200</v>
@@ -1631,10 +1631,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B90" t="str">
-        <v>https://www.kosodate.city.nagoya.jp/kids/nobinobi.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096177.html</v>
       </c>
       <c r="C90">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D90" t="str">
         <v>data/services.js</v>
@@ -1645,7 +1645,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B91" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1009278.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016744.html</v>
       </c>
       <c r="C91">
         <v>200</v>
@@ -1659,7 +1659,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B92" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009024/1009026.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016742.html</v>
       </c>
       <c r="C92">
         <v>200</v>
@@ -1673,7 +1673,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B93" t="str">
-        <v>https://www.kosodate.city.nagoya.jp/play/supportbases.html</v>
+        <v>https://hikikomori.city.nagoya.jp/</v>
       </c>
       <c r="C93">
         <v>200</v>
@@ -1687,7 +1687,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B94" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034075/1009021.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016586/1033908.html</v>
       </c>
       <c r="C94">
         <v>200</v>
@@ -1701,7 +1701,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B95" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034072/1009016.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009395.html</v>
       </c>
       <c r="C95">
         <v>200</v>
@@ -1715,7 +1715,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B96" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016744.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1009398.html</v>
       </c>
       <c r="C96">
         <v>200</v>
@@ -1729,7 +1729,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B97" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016742.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009380.html</v>
       </c>
       <c r="C97">
         <v>200</v>
@@ -1743,7 +1743,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B98" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016586/1033908.html</v>
+        <v>https://aiboren.jp/shisetsu/</v>
       </c>
       <c r="C98">
         <v>200</v>
@@ -1757,7 +1757,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B99" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009395.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016428.html</v>
       </c>
       <c r="C99">
         <v>200</v>
@@ -1771,7 +1771,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B100" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1009398.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/woichiran.html</v>
       </c>
       <c r="C100">
         <v>200</v>
@@ -1785,7 +1785,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B101" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009380.html</v>
+        <v>https://nagoya-shakyo.jp/service/fureai-kyushoku/</v>
       </c>
       <c r="C101">
         <v>200</v>
@@ -1799,7 +1799,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B102" t="str">
-        <v>https://aiboren.jp/shisetsu/</v>
+        <v>https://nagoya-shakyo.jp/service/ward-shakyo/</v>
       </c>
       <c r="C102">
         <v>200</v>
@@ -1813,7 +1813,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B103" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/jidoukatei/0000011250.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/company/shitei/haishoku/</v>
       </c>
       <c r="C103">
         <v>200</v>
@@ -1827,7 +1827,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B104" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016428.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
       </c>
       <c r="C104">
         <v>200</v>
@@ -1841,7 +1841,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B105" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/woichiran.html</v>
+        <v>https://webc.sjc.ne.jp/nagoyasj/job2_7</v>
       </c>
       <c r="C105">
         <v>200</v>
@@ -1855,7 +1855,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B106" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/company/shitei/haishoku/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016431.html</v>
       </c>
       <c r="C106">
         <v>200</v>
@@ -1869,7 +1869,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B107" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016433.html</v>
       </c>
       <c r="C107">
         <v>200</v>
@@ -1883,7 +1883,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B108" t="str">
-        <v>https://webc.sjc.ne.jp/nagoyasj/job2_7</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016429.html</v>
       </c>
       <c r="C108">
         <v>200</v>
@@ -1897,7 +1897,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B109" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016431.html</v>
+        <v>https://nagoya-shakyo.jp/service/community-support/</v>
       </c>
       <c r="C109">
         <v>200</v>
@@ -1911,7 +1911,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B110" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016433.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1012252.html</v>
       </c>
       <c r="C110">
         <v>200</v>
@@ -1925,7 +1925,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B111" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016429.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016440.html</v>
       </c>
       <c r="C111">
         <v>200</v>
@@ -1939,7 +1939,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B112" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1012252.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016488.html</v>
       </c>
       <c r="C112">
         <v>200</v>
@@ -1953,7 +1953,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B113" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016440.html</v>
+        <v>https://www.bes-c.com/</v>
       </c>
       <c r="C113">
         <v>200</v>
@@ -1967,7 +1967,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B114" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016488.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016491.html</v>
       </c>
       <c r="C114">
         <v>200</v>
@@ -1981,7 +1981,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B115" t="str">
-        <v>https://www.bes-c.com/</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012724/1013205/1034493/1013206.html</v>
       </c>
       <c r="C115">
         <v>200</v>
@@ -1995,7 +1995,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B116" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016491.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008943.html</v>
       </c>
       <c r="C116">
         <v>200</v>
@@ -2009,7 +2009,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B117" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012724/1013205/1034493/1013206.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008947.html</v>
       </c>
       <c r="C117">
         <v>200</v>
@@ -2023,7 +2023,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B118" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/imu/0000050084.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/index.html</v>
       </c>
       <c r="C118">
         <v>200</v>
@@ -2037,7 +2037,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B119" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008943.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008920/index.html</v>
       </c>
       <c r="C119">
         <v>200</v>
@@ -2051,7 +2051,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B120" t="str">
-        <v>https://www.qq.pref.aichi.jp/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008937.html</v>
       </c>
       <c r="C120">
         <v>200</v>
@@ -2065,7 +2065,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B121" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008947.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008938.html</v>
       </c>
       <c r="C121">
         <v>200</v>
@@ -2079,7 +2079,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B122" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008939/index.html</v>
       </c>
       <c r="C122">
         <v>200</v>
@@ -2093,7 +2093,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B123" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008920/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008949.html</v>
       </c>
       <c r="C123">
         <v>200</v>
@@ -2107,7 +2107,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B124" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008937.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034084/1009261.html</v>
       </c>
       <c r="C124">
         <v>200</v>
@@ -2121,7 +2121,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B125" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008938.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009265.html</v>
       </c>
       <c r="C125">
         <v>200</v>
@@ -2135,7 +2135,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B126" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008939/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009264.html</v>
       </c>
       <c r="C126">
         <v>200</v>
@@ -2149,7 +2149,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B127" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008949.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009260.html</v>
       </c>
       <c r="C127">
         <v>200</v>
@@ -2163,7 +2163,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B128" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034084/1009261.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009258.html</v>
       </c>
       <c r="C128">
         <v>200</v>
@@ -2177,7 +2177,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B129" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009265.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009307/1008988.html</v>
       </c>
       <c r="C129">
         <v>200</v>
@@ -2191,7 +2191,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B130" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009264.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
       </c>
       <c r="C130">
         <v>200</v>
@@ -2205,7 +2205,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B131" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009260.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034342/1008991/1036125.html</v>
       </c>
       <c r="C131">
         <v>200</v>
@@ -2219,7 +2219,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B132" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009258.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009126.html</v>
       </c>
       <c r="C132">
         <v>200</v>
@@ -2233,7 +2233,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B133" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009307/1008988.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1037093/1016989.html</v>
       </c>
       <c r="C133">
         <v>200</v>
@@ -2247,7 +2247,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B134" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008959.html</v>
       </c>
       <c r="C134">
         <v>200</v>
@@ -2261,7 +2261,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B135" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034342/1008991/1036125.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009018.html</v>
       </c>
       <c r="C135">
         <v>200</v>
@@ -2275,7 +2275,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B136" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009126.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016781.html</v>
       </c>
       <c r="C136">
         <v>200</v>
@@ -2289,7 +2289,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B137" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1037093/1016989.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1036101.html</v>
       </c>
       <c r="C137">
         <v>200</v>
@@ -2303,7 +2303,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B138" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008959.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1015850/1017055.html</v>
       </c>
       <c r="C138">
         <v>200</v>
@@ -2317,7 +2317,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B139" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009018.html</v>
+        <v>https://nagoya.fureai-cloud.jp/_view/sodan/home/index</v>
       </c>
       <c r="C139">
         <v>200</v>
@@ -2331,7 +2331,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B140" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016781.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009321/1009322.html</v>
       </c>
       <c r="C140">
         <v>200</v>
@@ -2345,7 +2345,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B141" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1036101.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016409.html</v>
       </c>
       <c r="C141">
         <v>200</v>
@@ -2359,7 +2359,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B142" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1015850/1017055.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015819/1038028/index.html</v>
       </c>
       <c r="C142">
         <v>200</v>
@@ -2373,7 +2373,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B143" t="str">
-        <v>https://nagoya.fureai-cloud.jp/_view/sodan/home/index</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015845.html</v>
       </c>
       <c r="C143">
         <v>200</v>
@@ -2387,7 +2387,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B144" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009321/1009322.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016404.html</v>
       </c>
       <c r="C144">
         <v>200</v>
@@ -2401,7 +2401,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B145" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016409.html</v>
+        <v>https://www.caa.go.jp/policies/policy/local_cooperation/local_consumer_administration/hotline/</v>
       </c>
       <c r="C145">
         <v>200</v>
@@ -2415,7 +2415,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B146" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015819/1038028/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016402.html</v>
       </c>
       <c r="C146">
         <v>200</v>
@@ -2429,7 +2429,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B147" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015845.html</v>
+        <v>https://www.nic-nagoya.or.jp/</v>
       </c>
       <c r="C147">
         <v>200</v>
@@ -2443,7 +2443,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B148" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016404.html</v>
+        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
       </c>
       <c r="C148">
         <v>200</v>
@@ -2457,7 +2457,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B149" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016402.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016399.html</v>
       </c>
       <c r="C149">
         <v>200</v>
@@ -2471,10 +2471,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B150" t="str">
-        <v>https://www.nic-nagoya.or.jp/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016734.html</v>
       </c>
       <c r="C150">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D150" t="str">
         <v>data/services.js</v>
@@ -2485,7 +2485,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B151" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016399.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008983/1008984.html</v>
       </c>
       <c r="C151">
         <v>200</v>
@@ -2499,10 +2499,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B152" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016734.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009388.html</v>
       </c>
       <c r="C152">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D152" t="str">
         <v>data/services.js</v>
@@ -2513,7 +2513,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B153" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008983/1008984.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009391.html</v>
       </c>
       <c r="C153">
         <v>200</v>
@@ -2527,7 +2527,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B154" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009388.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009381/1009382.html</v>
       </c>
       <c r="C154">
         <v>200</v>
@@ -2541,7 +2541,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B155" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009391.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009334.html</v>
       </c>
       <c r="C155">
         <v>200</v>
@@ -2555,7 +2555,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B156" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009381/1009382.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009389.html</v>
       </c>
       <c r="C156">
         <v>200</v>
@@ -2569,7 +2569,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B157" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009334.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009374.html</v>
       </c>
       <c r="C157">
         <v>200</v>
@@ -2583,7 +2583,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B158" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009389.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1016449/index.html</v>
       </c>
       <c r="C158">
         <v>200</v>
@@ -2597,7 +2597,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B159" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009374.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/</v>
       </c>
       <c r="C159">
         <v>200</v>
@@ -2611,13 +2611,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B160" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1016449/index.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/jouhou/1036432/1013386.html</v>
       </c>
       <c r="C160">
         <v>200</v>
       </c>
       <c r="D160" t="str">
-        <v>data/services.js</v>
+        <v>data/services.js, screens/DisasterScreen.js</v>
       </c>
     </row>
     <row r="161">
@@ -2625,7 +2625,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B161" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/kyoujo/1036451/1013567.html</v>
       </c>
       <c r="C161">
         <v>200</v>
@@ -2639,13 +2639,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B162" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/jouhou/1036432/1013386.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008962/1008963.html</v>
       </c>
       <c r="C162">
         <v>200</v>
       </c>
       <c r="D162" t="str">
-        <v>data/services.js, screens/DisasterScreen.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="163">
@@ -2653,7 +2653,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B163" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/kyoujo/1036451/1013567.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016506/1016510/1016511.html</v>
       </c>
       <c r="C163">
         <v>200</v>
@@ -2667,7 +2667,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B164" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008962/1008963.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009502/1034108.html</v>
       </c>
       <c r="C164">
         <v>200</v>
@@ -2681,7 +2681,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B165" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016506/1016510/1016511.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/todokede/1007816/1007817.html</v>
       </c>
       <c r="C165">
         <v>200</v>
@@ -2695,7 +2695,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B166" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009502/1034108.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011854/index.html</v>
       </c>
       <c r="C166">
         <v>200</v>
@@ -2709,7 +2709,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B167" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/todokede/1007816/1007817.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011868.html</v>
       </c>
       <c r="C167">
         <v>200</v>
@@ -2723,7 +2723,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B168" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011854/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011870.html</v>
       </c>
       <c r="C168">
         <v>200</v>
@@ -2737,7 +2737,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B169" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011868.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/index.html</v>
       </c>
       <c r="C169">
         <v>200</v>
@@ -2751,7 +2751,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B170" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011870.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1035058/1012184/1046468/index.html</v>
       </c>
       <c r="C170">
         <v>200</v>
@@ -2765,7 +2765,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B171" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016573/index.html</v>
       </c>
       <c r="C171">
         <v>200</v>
@@ -2779,7 +2779,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B172" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1035058/1012184/1046468/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/pet/1015473/index.html</v>
       </c>
       <c r="C172">
         <v>200</v>
@@ -2793,7 +2793,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B173" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016573/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011763/1011768.html</v>
       </c>
       <c r="C173">
         <v>200</v>
@@ -2807,7 +2807,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B174" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/pet/1015473/index.html</v>
+        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000135090_00001.html</v>
       </c>
       <c r="C174">
         <v>200</v>
@@ -2821,7 +2821,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B175" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011763/1011768.html</v>
+        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000158665.html</v>
       </c>
       <c r="C175">
         <v>200</v>
@@ -2835,7 +2835,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B176" t="str">
-        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000135090_00001.html</v>
+        <v>https://www.kyoukaikenpo.or.jp/benefit/injury_and_sickness_allowance/index.html</v>
       </c>
       <c r="C176">
         <v>200</v>
@@ -2849,7 +2849,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B177" t="str">
-        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000158665.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011851/1011853.html</v>
       </c>
       <c r="C177">
         <v>200</v>
@@ -2863,7 +2863,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B178" t="str">
-        <v>https://www.kyoukaikenpo.or.jp/benefit/injury_and_sickness_allowance/index.html</v>
+        <v>https://www.nenkin.go.jp/service/jukyu/seido/sonota-kyufu/shienkyufukin/20190805.html</v>
       </c>
       <c r="C178">
         <v>200</v>
@@ -2877,7 +2877,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B179" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011851/1011853.html</v>
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm</v>
       </c>
       <c r="C179">
         <v>200</v>
@@ -2891,7 +2891,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B180" t="str">
-        <v>https://www.nenkin.go.jp/service/jukyu/seido/sonota-kyufu/shienkyufukin/20190805.html</v>
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm#mushoukaLink2</v>
       </c>
       <c r="C180">
         <v>200</v>
@@ -2905,7 +2905,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B181" t="str">
-        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm</v>
+        <v>https://www.jasso.go.jp/shogakukin/</v>
       </c>
       <c r="C181">
         <v>200</v>
@@ -2919,7 +2919,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B182" t="str">
-        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm#mushoukaLink2</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008946.html</v>
       </c>
       <c r="C182">
         <v>200</v>
@@ -2933,7 +2933,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B183" t="str">
-        <v>https://www.jasso.go.jp/shogakukin/</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016801.html</v>
       </c>
       <c r="C183">
         <v>200</v>
@@ -2947,7 +2947,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B184" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008946.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/801/r8syougakukin.pdf</v>
       </c>
       <c r="C184">
         <v>200</v>
@@ -2961,7 +2961,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B185" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/zaimusisetsu/syuugakushienkin.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016798.html</v>
       </c>
       <c r="C185">
         <v>200</v>
@@ -2975,7 +2975,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B186" t="str">
-        <v>https://www.pref.aichi.jp/uploaded/attachment/620030.pdf</v>
+        <v>https://www.city.nagoya.jp/shisei/keikaku/1034903/1004666/1004670.html</v>
       </c>
       <c r="C186">
         <v>200</v>
@@ -2989,7 +2989,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B187" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/shigaku/shigaku-syougakukyuhukin.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1049088.html</v>
       </c>
       <c r="C187">
         <v>200</v>
@@ -3003,7 +3003,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B188" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016801.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1050641.html</v>
       </c>
       <c r="C188">
         <v>200</v>
@@ -3017,7 +3017,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B189" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/801/r8syougakukin.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016987.html</v>
       </c>
       <c r="C189">
         <v>200</v>
@@ -3031,7 +3031,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B190" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016798.html</v>
+        <v>https://nagoyalink.net/</v>
       </c>
       <c r="C190">
         <v>200</v>
@@ -3045,7 +3045,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B191" t="str">
-        <v>https://www.city.nagoya.jp/shisei/keikaku/1034903/1004666/1004670.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016705.html</v>
       </c>
       <c r="C191">
         <v>200</v>
@@ -3059,10 +3059,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B192" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1049088.html</v>
+        <v>http://nagosapo.icds.jp/</v>
       </c>
       <c r="C192">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D192" t="str">
         <v>data/services.js</v>
@@ -3073,7 +3073,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B193" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/zaimusisetsu/koutoukyouikumusyouka.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016706.html</v>
       </c>
       <c r="C193">
         <v>200</v>
@@ -3087,10 +3087,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B194" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/shigaku/kikanyoukenkakunin.html</v>
+        <v>http://maejob.icds.jp/index.html</v>
       </c>
       <c r="C194">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D194" t="str">
         <v>data/services.js</v>
@@ -3101,7 +3101,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B195" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1050641.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1011883/1011892.html</v>
       </c>
       <c r="C195">
         <v>200</v>
@@ -3115,7 +3115,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B196" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016987.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011842/1011845.html</v>
       </c>
       <c r="C196">
         <v>200</v>
@@ -3129,7 +3129,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B197" t="str">
-        <v>https://nagoyalink.net/</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011769/1011773.html</v>
       </c>
       <c r="C197">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B198" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016705.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009386.html</v>
       </c>
       <c r="C198">
         <v>200</v>
@@ -3157,7 +3157,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B199" t="str">
-        <v>http://nagosapo.icds.jp/</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009394.html</v>
       </c>
       <c r="C199">
         <v>200</v>
@@ -3171,7 +3171,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B200" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016706.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017010/1017016.html</v>
       </c>
       <c r="C200">
         <v>200</v>
@@ -3185,7 +3185,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B201" t="str">
-        <v>http://maejob.icds.jp/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016972/1016979.html</v>
       </c>
       <c r="C201">
         <v>200</v>
@@ -3199,7 +3199,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B202" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1011883/1011892.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017053.html</v>
       </c>
       <c r="C202">
         <v>200</v>
@@ -3213,7 +3213,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B203" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011842/1011845.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017056.html</v>
       </c>
       <c r="C203">
         <v>200</v>
@@ -3227,7 +3227,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B204" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011769/1011773.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008983/1042086.html</v>
       </c>
       <c r="C204">
         <v>200</v>
@@ -3241,7 +3241,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B205" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009386.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016704.html</v>
       </c>
       <c r="C205">
         <v>200</v>
@@ -3255,7 +3255,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B206" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009394.html</v>
+        <v>https://www.kosodate-ouen.city.nagoya.jp/</v>
       </c>
       <c r="C206">
         <v>200</v>
@@ -3269,7 +3269,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B207" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017010/1017016.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009108/1009109.html</v>
       </c>
       <c r="C207">
         <v>200</v>
@@ -3283,7 +3283,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B208" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016972/1016979.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009280.html</v>
       </c>
       <c r="C208">
         <v>200</v>
@@ -3297,7 +3297,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B209" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017053.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016448/1016483.html</v>
       </c>
       <c r="C209">
         <v>200</v>
@@ -3311,7 +3311,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B210" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017056.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009410/1040316.html</v>
       </c>
       <c r="C210">
         <v>200</v>
@@ -3325,7 +3325,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B211" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008983/1042086.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009525/1009528.html</v>
       </c>
       <c r="C211">
         <v>200</v>
@@ -3339,7 +3339,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B212" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016704.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009525/1033517.html</v>
       </c>
       <c r="C212">
         <v>200</v>
@@ -3353,7 +3353,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B213" t="str">
-        <v>https://www.kosodate-ouen.city.nagoya.jp/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009535/1009537.html</v>
       </c>
       <c r="C213">
         <v>200</v>
@@ -3367,7 +3367,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B214" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009108/1009109.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009535/1009539.html</v>
       </c>
       <c r="C214">
         <v>200</v>
@@ -3381,7 +3381,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B215" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009280.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1045911/1045913.html</v>
       </c>
       <c r="C215">
         <v>200</v>
@@ -3395,7 +3395,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B216" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016448/1016483.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016443.html</v>
       </c>
       <c r="C216">
         <v>200</v>
@@ -3409,7 +3409,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B217" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009410/1040316.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016553/1016554.html</v>
       </c>
       <c r="C217">
         <v>200</v>
@@ -3423,7 +3423,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B218" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009525/1009528.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016553/1034838.html</v>
       </c>
       <c r="C218">
         <v>200</v>
@@ -3437,7 +3437,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B219" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009525/1033517.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016663.html</v>
       </c>
       <c r="C219">
         <v>200</v>
@@ -3451,7 +3451,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B220" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009535/1009537.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016738.html</v>
       </c>
       <c r="C220">
         <v>200</v>
@@ -3465,13 +3465,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B221" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009535/1009539.html</v>
+        <v>https://www.city.nagoya.jp/</v>
       </c>
       <c r="C221">
         <v>200</v>
       </c>
       <c r="D221" t="str">
-        <v>data/services.js</v>
+        <v>screens/DetailScreen.js</v>
       </c>
     </row>
     <row r="222">
@@ -3479,13 +3479,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B222" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1045911/1045913.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/jigyosho/</v>
       </c>
       <c r="C222">
         <v>200</v>
       </c>
       <c r="D222" t="str">
-        <v>data/services.js</v>
+        <v>screens/DetailScreen.js</v>
       </c>
     </row>
     <row r="223">
@@ -3493,13 +3493,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B223" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016443.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/1013492.html</v>
       </c>
       <c r="C223">
         <v>200</v>
       </c>
       <c r="D223" t="str">
-        <v>data/services.js</v>
+        <v>screens/DisasterScreen.js</v>
       </c>
     </row>
     <row r="224">
@@ -3507,123 +3507,25 @@
         <v>✅ 正常</v>
       </c>
       <c r="B224" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016553/1016554.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036428.html</v>
       </c>
       <c r="C224">
         <v>200</v>
       </c>
       <c r="D224" t="str">
-        <v>data/services.js</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="str">
-        <v>✅ 正常</v>
-      </c>
-      <c r="B225" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016553/1034838.html</v>
-      </c>
-      <c r="C225">
-        <v>200</v>
-      </c>
-      <c r="D225" t="str">
-        <v>data/services.js</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="str">
-        <v>✅ 正常</v>
-      </c>
-      <c r="B226" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016663.html</v>
-      </c>
-      <c r="C226">
-        <v>200</v>
-      </c>
-      <c r="D226" t="str">
-        <v>data/services.js</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="str">
-        <v>✅ 正常</v>
-      </c>
-      <c r="B227" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016738.html</v>
-      </c>
-      <c r="C227">
-        <v>200</v>
-      </c>
-      <c r="D227" t="str">
-        <v>data/services.js</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="str">
-        <v>✅ 正常</v>
-      </c>
-      <c r="B228" t="str">
-        <v>https://www.city.nagoya.jp/</v>
-      </c>
-      <c r="C228">
-        <v>200</v>
-      </c>
-      <c r="D228" t="str">
-        <v>screens/DetailScreen.js</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="str">
-        <v>✅ 正常</v>
-      </c>
-      <c r="B229" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/jigyosho/</v>
-      </c>
-      <c r="C229">
-        <v>200</v>
-      </c>
-      <c r="D229" t="str">
-        <v>screens/DetailScreen.js</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="str">
-        <v>✅ 正常</v>
-      </c>
-      <c r="B230" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/1013492.html</v>
-      </c>
-      <c r="C230">
-        <v>200</v>
-      </c>
-      <c r="D230" t="str">
-        <v>screens/DisasterScreen.js</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="str">
-        <v>✅ 正常</v>
-      </c>
-      <c r="B231" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036428.html</v>
-      </c>
-      <c r="C231">
-        <v>200</v>
-      </c>
-      <c r="D231" t="str">
         <v>screens/DisasterScreen.js</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D231"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D224"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3641,28 +3543,70 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>https://www.pref.aichi.jp/soshiki/zaimusisetsu/syuugakushienkin.html</v>
+        <v>https://www.nic-nagoya.or.jp/</v>
       </c>
       <c r="B2" t="str">
-        <v>Loading</v>
+        <v>One moment, please...</v>
       </c>
       <c r="C2" t="str">
-        <v>県立高等学校等就学支援金制度 - 愛知県</v>
+        <v>名古屋国際センター | Nagoya International Center</v>
       </c>
       <c r="D2" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
+      </c>
+      <c r="B3" t="str">
+        <v>One moment, please...</v>
+      </c>
+      <c r="C3" t="str">
+        <v>行政相談 | 名古屋国際センター | Nagoya International Center</v>
+      </c>
+      <c r="D3" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>http://nagosapo.icds.jp/</v>
+      </c>
+      <c r="B4" t="str">
+        <v>One moment, please...</v>
+      </c>
+      <c r="C4" t="str">
+        <v>301 Moved Permanently</v>
+      </c>
+      <c r="D4" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>http://maejob.icds.jp/index.html</v>
+      </c>
+      <c r="B5" t="str">
+        <v>One moment, please...</v>
+      </c>
+      <c r="C5" t="str">
+        <v>301 Moved Permanently</v>
+      </c>
+      <c r="D5" t="str">
         <v>data/services.js</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3692,10 +3636,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D2" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1050592/1051513.html</v>
+        <v>https://www.city.nagoya.jp/bousai/anzen/1014533/1052292.html</v>
       </c>
       <c r="E2" t="str">
-        <v>【重要】電気火災が増えています</v>
+        <v>全市一斉クリーンキャンペーンなごや2026の取り組み</v>
       </c>
     </row>
     <row r="3">
@@ -3706,81 +3650,81 @@
         <v>https://www.city.nagoya.jp/bousai/index.html</v>
       </c>
       <c r="C3" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D3" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1051487/index.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1051487/1051409.html</v>
       </c>
       <c r="E3" t="str">
-        <v>熱田消防署について</v>
+        <v>熱田消防署へのアクセス（公共交通機関）</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>防災・安全安心</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B4" t="str">
-        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C4" t="str">
         <v>➕ 追加</v>
       </c>
       <c r="D4" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1051487/1051409.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052147.html</v>
       </c>
       <c r="E4" t="str">
-        <v>熱田消防署へのアクセス（公共交通機関）</v>
+        <v>終活・相続セミナー＆個別相談会</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>防災・安全安心</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B5" t="str">
-        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C5" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D5" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012913/1012914/1052131.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1050841.html</v>
       </c>
       <c r="E5" t="str">
-        <v>消防職員の熱中症対策として製氷機を寄贈頂きました</v>
+        <v>市民活動推進センター講座（10/21・11/18）</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>防災・安全安心</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B6" t="str">
-        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C6" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D6" t="str">
-        <v>https://www.city.nagoya.jp/bousai/anzen/1014448/1014474/1050980.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052466.html</v>
       </c>
       <c r="E6" t="str">
-        <v>市民向け講座「令和8年度 第1回 犯罪被害を学ぶ会」を開催します（事前申込制）</v>
+        <v>市立大学 市民公開講座（第5回から第11回）</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>防災・安全安心</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B7" t="str">
-        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C7" t="str">
         <v>➖ 削除</v>
       </c>
       <c r="D7" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1013090/1013096/1051100.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1034811/1012684/1012697/1034060/1051886.html</v>
       </c>
       <c r="E7" t="str">
-        <v>令和8年度名東の日を開催しました！</v>
+        <v>ぜん息予防サッカー教室</v>
       </c>
     </row>
     <row r="8">
@@ -3791,13 +3735,13 @@
         <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C8" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D8" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/kankyou/1034811/1012684/1012697/1034060/1051886.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1050836.html</v>
       </c>
       <c r="E8" t="str">
-        <v>ぜん息予防サッカー教室</v>
+        <v>ソレイユプラザなごや「家族で楽しむ体験イベント」レゴランド(R)（上付き）・ジャパンのワークショップで多様性を学ぼう！</v>
       </c>
     </row>
     <row r="9">
@@ -3808,195 +3752,93 @@
         <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C9" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D9" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1050836.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1015518/1052115.html</v>
       </c>
       <c r="E9" t="str">
-        <v>ソレイユプラザなごや「家族で楽しむ体験イベント」レゴランド(R)（上付き）・ジャパンのワークショップで多様性を学ぼう！</v>
+        <v>消費生活相談員になりませんか？</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>くらし・手続き</v>
+        <v>子ども・子育て・教育</v>
       </c>
       <c r="B10" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
       </c>
       <c r="C10" t="str">
         <v>➕ 追加</v>
       </c>
       <c r="D10" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1015518/1052115.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1016995/1016810/1016833/1016858/1052437.html</v>
       </c>
       <c r="E10" t="str">
-        <v>消費生活相談員になりませんか？</v>
+        <v>本地丘小学校、森孝東小学校及び森孝西小学校の統合並びに森孝中学校との併設に関する個別プラン（答申）(令和8年8月6日)</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>くらし・手続き</v>
+        <v>子ども・子育て・教育</v>
       </c>
       <c r="B11" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
       </c>
       <c r="C11" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D11" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/1034008/1052263.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1016995/1016810/1016811/1016816/1052451.html</v>
       </c>
       <c r="E11" t="str">
-        <v>令和8年（2026年）熊本地震で被災された方への市営住宅の提供</v>
+        <v>令和8年度第2回名古屋市子どもいきいき学校づくり推進審議会 令和8年8月6日</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>くらし・手続き</v>
+        <v>子ども・子育て・教育</v>
       </c>
       <c r="B12" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
       </c>
       <c r="C12" t="str">
         <v>➖ 削除</v>
       </c>
       <c r="D12" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shiminsanka/1011147/1052132.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1052219.html</v>
       </c>
       <c r="E12" t="str">
-        <v>令和8年熊本地震災害義援金の募集</v>
+        <v>令和8年度トワイライトスクール・ルームに関するアンケート調査について</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>くらし・手続き</v>
+        <v>子ども・子育て・教育</v>
       </c>
       <c r="B13" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
       </c>
       <c r="C13" t="str">
         <v>➖ 削除</v>
       </c>
       <c r="D13" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052096.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1051827.html</v>
       </c>
       <c r="E13" t="str">
-        <v>蓬左文庫企画展 生誕140年 没後50年記念 旅する侯爵 徳川義親</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>子ども・子育て・教育</v>
-      </c>
-      <c r="B14" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
-      </c>
-      <c r="C14" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D14" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1027694/1052246.html</v>
-      </c>
-      <c r="E14" t="str">
-        <v>令和8年度 教育委員会8月臨時会</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>子ども・子育て・教育</v>
-      </c>
-      <c r="B15" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
-      </c>
-      <c r="C15" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D15" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1034096.html</v>
-      </c>
-      <c r="E15" t="str">
-        <v>幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B16" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C16" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D16" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1035053/1052496.html</v>
-      </c>
-      <c r="E16" t="str">
-        <v>Zoomによる初めてのオンライン手話講座（令和8年9月金曜コース）</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B17" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C17" t="str">
-        <v>➕ 追加</v>
-      </c>
-      <c r="D17" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016414/1051383.html</v>
-      </c>
-      <c r="E17" t="str">
-        <v>令和8年度「敬老の日」における市民利用施設の無料開放等実施のお知らせ</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B18" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C18" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D18" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1011432/1051796.html</v>
-      </c>
-      <c r="E18" t="str">
-        <v>専用水道に関する届出</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>健康・医療・福祉</v>
-      </c>
-      <c r="B19" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
-      </c>
-      <c r="C19" t="str">
-        <v>➖ 削除</v>
-      </c>
-      <c r="D19" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1034419/1050801.html</v>
-      </c>
-      <c r="E19" t="str">
-        <v>令和8年度つながり・支えあおう地域福祉のすゝめ（イベントのご案内）</v>
+        <v>令和8年8月10日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M106"/>
+  <dimension ref="A1:M122"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6220,9 +6062,365 @@
         <v>令和8年度つながり・支えあおう地域福祉のすゝめ（イベントのご案内）</v>
       </c>
     </row>
+    <row r="107">
+      <c r="B107" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="C107" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D107" t="str">
+        <v>https://www.nic-nagoya.or.jp/</v>
+      </c>
+      <c r="F107" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G107" t="str">
+        <v>One moment, please...</v>
+      </c>
+      <c r="H107" t="str">
+        <v>名古屋国際センター | Nagoya International Center</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="C108" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D108" t="str">
+        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
+      </c>
+      <c r="F108" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G108" t="str">
+        <v>One moment, please...</v>
+      </c>
+      <c r="H108" t="str">
+        <v>行政相談 | 名古屋国際センター | Nagoya International Center</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="C109" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D109" t="str">
+        <v>http://nagosapo.icds.jp/</v>
+      </c>
+      <c r="F109" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G109" t="str">
+        <v>One moment, please...</v>
+      </c>
+      <c r="H109" t="str">
+        <v>301 Moved Permanently</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="C110" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D110" t="str">
+        <v>http://maejob.icds.jp/index.html</v>
+      </c>
+      <c r="F110" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G110" t="str">
+        <v>One moment, please...</v>
+      </c>
+      <c r="H110" t="str">
+        <v>301 Moved Permanently</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="C111" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I111" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J111" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K111" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L111" t="str">
+        <v>https://www.city.nagoya.jp/bousai/anzen/1014533/1052292.html</v>
+      </c>
+      <c r="M111" t="str">
+        <v>全市一斉クリーンキャンペーンなごや2026の取り組み</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="C112" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I112" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J112" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K112" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L112" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1051487/1051409.html</v>
+      </c>
+      <c r="M112" t="str">
+        <v>熱田消防署へのアクセス（公共交通機関）</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="C113" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I113" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J113" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K113" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L113" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052147.html</v>
+      </c>
+      <c r="M113" t="str">
+        <v>終活・相続セミナー＆個別相談会</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="C114" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I114" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J114" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K114" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L114" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1050841.html</v>
+      </c>
+      <c r="M114" t="str">
+        <v>市民活動推進センター講座（10/21・11/18）</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="C115" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I115" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J115" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K115" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L115" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052466.html</v>
+      </c>
+      <c r="M115" t="str">
+        <v>市立大学 市民公開講座（第5回から第11回）</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="C116" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I116" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J116" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K116" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L116" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1034811/1012684/1012697/1034060/1051886.html</v>
+      </c>
+      <c r="M116" t="str">
+        <v>ぜん息予防サッカー教室</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="C117" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I117" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J117" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K117" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L117" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1050836.html</v>
+      </c>
+      <c r="M117" t="str">
+        <v>ソレイユプラザなごや「家族で楽しむ体験イベント」レゴランド(R)（上付き）・ジャパンのワークショップで多様性を学ぼう！</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="C118" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I118" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J118" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K118" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L118" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1015518/1052115.html</v>
+      </c>
+      <c r="M118" t="str">
+        <v>消費生活相談員になりませんか？</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="C119" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I119" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J119" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K119" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L119" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1016995/1016810/1016833/1016858/1052437.html</v>
+      </c>
+      <c r="M119" t="str">
+        <v>本地丘小学校、森孝東小学校及び森孝西小学校の統合並びに森孝中学校との併設に関する個別プラン（答申）(令和8年8月6日)</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="C120" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I120" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J120" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K120" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L120" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1016995/1016810/1016811/1016816/1052451.html</v>
+      </c>
+      <c r="M120" t="str">
+        <v>令和8年度第2回名古屋市子どもいきいき学校づくり推進審議会 令和8年8月6日</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="C121" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I121" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J121" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K121" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L121" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1052219.html</v>
+      </c>
+      <c r="M121" t="str">
+        <v>令和8年度トワイライトスクール・ルームに関するアンケート調査について</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="C122" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I122" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J122" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K122" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L122" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1051827.html</v>
+      </c>
+      <c r="M122" t="str">
+        <v>令和8年8月10日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M106"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M122"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reports/latest-report.xlsx
+++ b/reports/latest-report.xlsx
@@ -378,7 +378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D224"/>
+  <dimension ref="A1:D225"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1127,7 +1127,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B54" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/1016536.html</v>
+        <v>http://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
       </c>
       <c r="C54">
         <v>200</v>
@@ -1141,7 +1141,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B55" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011776/1034706/1011784.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/1016536.html</v>
       </c>
       <c r="C55">
         <v>200</v>
@@ -1155,7 +1155,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B56" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009456/1009457/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011776/1034706/1011784.html</v>
       </c>
       <c r="C56">
         <v>200</v>
@@ -1169,7 +1169,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B57" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009456/1009457/index.html</v>
       </c>
       <c r="C57">
         <v>200</v>
@@ -1183,7 +1183,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B58" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1012157/1033970.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
       </c>
       <c r="C58">
         <v>200</v>
@@ -1197,7 +1197,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B59" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1015763/1015815.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1012157/1033970.html</v>
       </c>
       <c r="C59">
         <v>200</v>
@@ -1211,7 +1211,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B60" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011793/1011807/1011810.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1015763/1015815.html</v>
       </c>
       <c r="C60">
         <v>200</v>
@@ -1225,7 +1225,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B61" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016739.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011793/1011807/1011810.html</v>
       </c>
       <c r="C61">
         <v>200</v>
@@ -1239,7 +1239,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B62" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016739.html</v>
       </c>
       <c r="C62">
         <v>200</v>
@@ -1253,7 +1253,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B63" t="str">
-        <v>https://www.hellowork.mhlw.go.jp/insurance/insurance_guide.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/index.html</v>
       </c>
       <c r="C63">
         <v>200</v>
@@ -1267,7 +1267,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B64" t="str">
-        <v>https://jsite.mhlw.go.jp/aichi-hellowork/list.html</v>
+        <v>https://www.hellowork.mhlw.go.jp/insurance/insurance_guide.html</v>
       </c>
       <c r="C64">
         <v>200</v>
@@ -1281,7 +1281,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B65" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
+        <v>https://jsite.mhlw.go.jp/aichi-hellowork/list.html</v>
       </c>
       <c r="C65">
         <v>200</v>
@@ -1295,7 +1295,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B66" t="str">
-        <v>https://www.nagojob.city.nagoya.jp/</v>
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
       </c>
       <c r="C66">
         <v>200</v>
@@ -1309,7 +1309,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B67" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/tetyou/</v>
+        <v>https://www.nagojob.city.nagoya.jp/</v>
       </c>
       <c r="C67">
         <v>200</v>
@@ -1323,7 +1323,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B68" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/soudan/fukushikakari.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/tetyou/</v>
       </c>
       <c r="C68">
         <v>200</v>
@@ -1337,7 +1337,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B69" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/fukushi_service.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/soudan/fukushikakari.html</v>
       </c>
       <c r="C69">
         <v>200</v>
@@ -1351,7 +1351,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B70" t="str">
-        <v>https://www.city.nagoya.jp/jigyou/sangyou/1026356/1035103/1026446/1026447.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/fukushi_service.html</v>
       </c>
       <c r="C70">
         <v>200</v>
@@ -1365,7 +1365,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B71" t="str">
-        <v>https://weljob-nagoya.com/</v>
+        <v>https://www.city.nagoya.jp/jigyou/sangyou/1026356/1035103/1026446/1026447.html</v>
       </c>
       <c r="C71">
         <v>200</v>
@@ -1379,7 +1379,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B72" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
+        <v>https://weljob-nagoya.com/</v>
       </c>
       <c r="C72">
         <v>200</v>
@@ -1393,7 +1393,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B73" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/622/linksweb.pdf</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
       </c>
       <c r="C73">
         <v>200</v>
@@ -1407,7 +1407,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B74" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/622/linksweb.pdf</v>
       </c>
       <c r="C74">
         <v>200</v>
@@ -1421,7 +1421,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B75" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/675/annnai.pdf</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
       </c>
       <c r="C75">
         <v>200</v>
@@ -1435,7 +1435,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B76" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/675/annnai.pdf</v>
       </c>
       <c r="C76">
         <v>200</v>
@@ -1449,7 +1449,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B77" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
       </c>
       <c r="C77">
         <v>200</v>
@@ -1463,7 +1463,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B78" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
       </c>
       <c r="C78">
         <v>200</v>
@@ -1477,7 +1477,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B79" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008978.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
       </c>
       <c r="C79">
         <v>200</v>
@@ -1491,7 +1491,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B80" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/008/978/0413tirasi.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008978.html</v>
       </c>
       <c r="C80">
         <v>200</v>
@@ -1505,7 +1505,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B81" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034073/1009017.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/008/978/0413tirasi.pdf</v>
       </c>
       <c r="C81">
         <v>200</v>
@@ -1519,7 +1519,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B82" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/009/017/r710_help.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034073/1009017.html</v>
       </c>
       <c r="C82">
         <v>200</v>
@@ -1533,7 +1533,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B83" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1034087.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/009/017/r710_help.pdf</v>
       </c>
       <c r="C83">
         <v>200</v>
@@ -1547,7 +1547,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B84" t="str">
-        <v>https://www.kosodate.city.nagoya.jp/kids/nobinobi.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1034087.html</v>
       </c>
       <c r="C84">
         <v>200</v>
@@ -1561,7 +1561,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B85" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1009278.html</v>
+        <v>https://www.kosodate.city.nagoya.jp/kids/nobinobi.html</v>
       </c>
       <c r="C85">
         <v>200</v>
@@ -1575,7 +1575,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B86" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009024/1009026.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1009278.html</v>
       </c>
       <c r="C86">
         <v>200</v>
@@ -1589,7 +1589,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B87" t="str">
-        <v>https://www.kosodate.city.nagoya.jp/play/supportbases.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009024/1009026.html</v>
       </c>
       <c r="C87">
         <v>200</v>
@@ -1603,7 +1603,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B88" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034075/1009021.html</v>
+        <v>https://www.kosodate.city.nagoya.jp/play/supportbases.html</v>
       </c>
       <c r="C88">
         <v>200</v>
@@ -1617,7 +1617,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B89" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034072/1009016.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034075/1009021.html</v>
       </c>
       <c r="C89">
         <v>200</v>
@@ -1631,10 +1631,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B90" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096177.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034072/1009016.html</v>
       </c>
       <c r="C90">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D90" t="str">
         <v>data/services.js</v>
@@ -1645,10 +1645,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B91" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016744.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096177.html</v>
       </c>
       <c r="C91">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D91" t="str">
         <v>data/services.js</v>
@@ -1659,7 +1659,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B92" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016742.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016744.html</v>
       </c>
       <c r="C92">
         <v>200</v>
@@ -1673,7 +1673,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B93" t="str">
-        <v>https://hikikomori.city.nagoya.jp/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016742.html</v>
       </c>
       <c r="C93">
         <v>200</v>
@@ -1687,7 +1687,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B94" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016586/1033908.html</v>
+        <v>https://hikikomori.city.nagoya.jp/</v>
       </c>
       <c r="C94">
         <v>200</v>
@@ -1701,7 +1701,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B95" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009395.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016586/1033908.html</v>
       </c>
       <c r="C95">
         <v>200</v>
@@ -1715,7 +1715,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B96" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1009398.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009395.html</v>
       </c>
       <c r="C96">
         <v>200</v>
@@ -1729,7 +1729,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B97" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009380.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1009398.html</v>
       </c>
       <c r="C97">
         <v>200</v>
@@ -1743,7 +1743,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B98" t="str">
-        <v>https://aiboren.jp/shisetsu/</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009380.html</v>
       </c>
       <c r="C98">
         <v>200</v>
@@ -1757,7 +1757,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B99" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016428.html</v>
+        <v>https://aiboren.jp/shisetsu/</v>
       </c>
       <c r="C99">
         <v>200</v>
@@ -1771,7 +1771,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B100" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/woichiran.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016428.html</v>
       </c>
       <c r="C100">
         <v>200</v>
@@ -1785,7 +1785,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B101" t="str">
-        <v>https://nagoya-shakyo.jp/service/fureai-kyushoku/</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/woichiran.html</v>
       </c>
       <c r="C101">
         <v>200</v>
@@ -1799,7 +1799,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B102" t="str">
-        <v>https://nagoya-shakyo.jp/service/ward-shakyo/</v>
+        <v>https://nagoya-shakyo.jp/service/fureai-kyushoku/</v>
       </c>
       <c r="C102">
         <v>200</v>
@@ -1813,7 +1813,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B103" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/company/shitei/haishoku/</v>
+        <v>https://nagoya-shakyo.jp/service/ward-shakyo/</v>
       </c>
       <c r="C103">
         <v>200</v>
@@ -1827,7 +1827,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B104" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/company/shitei/haishoku/</v>
       </c>
       <c r="C104">
         <v>200</v>
@@ -1841,7 +1841,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B105" t="str">
-        <v>https://webc.sjc.ne.jp/nagoyasj/job2_7</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
       </c>
       <c r="C105">
         <v>200</v>
@@ -1855,7 +1855,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B106" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016431.html</v>
+        <v>https://webc.sjc.ne.jp/nagoyasj/job2_7</v>
       </c>
       <c r="C106">
         <v>200</v>
@@ -1869,7 +1869,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B107" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016433.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016431.html</v>
       </c>
       <c r="C107">
         <v>200</v>
@@ -1883,7 +1883,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B108" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016429.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016433.html</v>
       </c>
       <c r="C108">
         <v>200</v>
@@ -1897,7 +1897,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B109" t="str">
-        <v>https://nagoya-shakyo.jp/service/community-support/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016429.html</v>
       </c>
       <c r="C109">
         <v>200</v>
@@ -1911,7 +1911,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B110" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1012252.html</v>
+        <v>https://nagoya-shakyo.jp/service/community-support/</v>
       </c>
       <c r="C110">
         <v>200</v>
@@ -1925,7 +1925,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B111" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016440.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1012252.html</v>
       </c>
       <c r="C111">
         <v>200</v>
@@ -1939,7 +1939,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B112" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016488.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016440.html</v>
       </c>
       <c r="C112">
         <v>200</v>
@@ -1953,7 +1953,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B113" t="str">
-        <v>https://www.bes-c.com/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016488.html</v>
       </c>
       <c r="C113">
         <v>200</v>
@@ -1967,7 +1967,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B114" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016491.html</v>
+        <v>https://www.bes-c.com/</v>
       </c>
       <c r="C114">
         <v>200</v>
@@ -1981,7 +1981,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B115" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012724/1013205/1034493/1013206.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016491.html</v>
       </c>
       <c r="C115">
         <v>200</v>
@@ -1995,7 +1995,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B116" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008943.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012724/1013205/1034493/1013206.html</v>
       </c>
       <c r="C116">
         <v>200</v>
@@ -2009,7 +2009,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B117" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008947.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008943.html</v>
       </c>
       <c r="C117">
         <v>200</v>
@@ -2023,7 +2023,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B118" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008947.html</v>
       </c>
       <c r="C118">
         <v>200</v>
@@ -2037,7 +2037,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B119" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008920/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/index.html</v>
       </c>
       <c r="C119">
         <v>200</v>
@@ -2051,7 +2051,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B120" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008937.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008920/index.html</v>
       </c>
       <c r="C120">
         <v>200</v>
@@ -2065,7 +2065,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B121" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008938.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008937.html</v>
       </c>
       <c r="C121">
         <v>200</v>
@@ -2079,7 +2079,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B122" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008939/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008938.html</v>
       </c>
       <c r="C122">
         <v>200</v>
@@ -2093,7 +2093,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B123" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008949.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008939/index.html</v>
       </c>
       <c r="C123">
         <v>200</v>
@@ -2107,7 +2107,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B124" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034084/1009261.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008949.html</v>
       </c>
       <c r="C124">
         <v>200</v>
@@ -2121,7 +2121,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B125" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009265.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034084/1009261.html</v>
       </c>
       <c r="C125">
         <v>200</v>
@@ -2135,7 +2135,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B126" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009264.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009265.html</v>
       </c>
       <c r="C126">
         <v>200</v>
@@ -2149,7 +2149,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B127" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009260.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009264.html</v>
       </c>
       <c r="C127">
         <v>200</v>
@@ -2163,7 +2163,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B128" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009258.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009260.html</v>
       </c>
       <c r="C128">
         <v>200</v>
@@ -2177,7 +2177,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B129" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009307/1008988.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009258.html</v>
       </c>
       <c r="C129">
         <v>200</v>
@@ -2191,7 +2191,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B130" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009307/1008988.html</v>
       </c>
       <c r="C130">
         <v>200</v>
@@ -2205,7 +2205,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B131" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034342/1008991/1036125.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
       </c>
       <c r="C131">
         <v>200</v>
@@ -2219,7 +2219,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B132" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009126.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034342/1008991/1036125.html</v>
       </c>
       <c r="C132">
         <v>200</v>
@@ -2233,7 +2233,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B133" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1037093/1016989.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009126.html</v>
       </c>
       <c r="C133">
         <v>200</v>
@@ -2247,7 +2247,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B134" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008959.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1037093/1016989.html</v>
       </c>
       <c r="C134">
         <v>200</v>
@@ -2261,7 +2261,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B135" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009018.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008959.html</v>
       </c>
       <c r="C135">
         <v>200</v>
@@ -2275,7 +2275,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B136" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016781.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009018.html</v>
       </c>
       <c r="C136">
         <v>200</v>
@@ -2289,7 +2289,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B137" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1036101.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016781.html</v>
       </c>
       <c r="C137">
         <v>200</v>
@@ -2303,7 +2303,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B138" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1015850/1017055.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1036101.html</v>
       </c>
       <c r="C138">
         <v>200</v>
@@ -2317,7 +2317,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B139" t="str">
-        <v>https://nagoya.fureai-cloud.jp/_view/sodan/home/index</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1015850/1017055.html</v>
       </c>
       <c r="C139">
         <v>200</v>
@@ -2331,7 +2331,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B140" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009321/1009322.html</v>
+        <v>https://nagoya.fureai-cloud.jp/_view/sodan/home/index</v>
       </c>
       <c r="C140">
         <v>200</v>
@@ -2345,7 +2345,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B141" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016409.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009321/1009322.html</v>
       </c>
       <c r="C141">
         <v>200</v>
@@ -2359,7 +2359,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B142" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015819/1038028/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016409.html</v>
       </c>
       <c r="C142">
         <v>200</v>
@@ -2373,7 +2373,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B143" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015845.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015819/1038028/index.html</v>
       </c>
       <c r="C143">
         <v>200</v>
@@ -2387,7 +2387,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B144" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016404.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015845.html</v>
       </c>
       <c r="C144">
         <v>200</v>
@@ -2401,7 +2401,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B145" t="str">
-        <v>https://www.caa.go.jp/policies/policy/local_cooperation/local_consumer_administration/hotline/</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016404.html</v>
       </c>
       <c r="C145">
         <v>200</v>
@@ -2415,7 +2415,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B146" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016402.html</v>
+        <v>https://www.caa.go.jp/policies/policy/local_cooperation/local_consumer_administration/hotline/</v>
       </c>
       <c r="C146">
         <v>200</v>
@@ -2429,7 +2429,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B147" t="str">
-        <v>https://www.nic-nagoya.or.jp/</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016402.html</v>
       </c>
       <c r="C147">
         <v>200</v>
@@ -2443,7 +2443,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B148" t="str">
-        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
+        <v>https://www.nic-nagoya.or.jp/</v>
       </c>
       <c r="C148">
         <v>200</v>
@@ -2457,7 +2457,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B149" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016399.html</v>
+        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
       </c>
       <c r="C149">
         <v>200</v>
@@ -2471,10 +2471,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B150" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016734.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016399.html</v>
       </c>
       <c r="C150">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D150" t="str">
         <v>data/services.js</v>
@@ -2485,10 +2485,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B151" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008983/1008984.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016734.html</v>
       </c>
       <c r="C151">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D151" t="str">
         <v>data/services.js</v>
@@ -2499,7 +2499,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B152" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009388.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008983/1008984.html</v>
       </c>
       <c r="C152">
         <v>200</v>
@@ -2513,7 +2513,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B153" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009391.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009388.html</v>
       </c>
       <c r="C153">
         <v>200</v>
@@ -2527,7 +2527,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B154" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009381/1009382.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009391.html</v>
       </c>
       <c r="C154">
         <v>200</v>
@@ -2541,7 +2541,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B155" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009334.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009381/1009382.html</v>
       </c>
       <c r="C155">
         <v>200</v>
@@ -2555,7 +2555,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B156" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009389.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009334.html</v>
       </c>
       <c r="C156">
         <v>200</v>
@@ -2569,7 +2569,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B157" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009374.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009389.html</v>
       </c>
       <c r="C157">
         <v>200</v>
@@ -2583,7 +2583,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B158" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1016449/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009374.html</v>
       </c>
       <c r="C158">
         <v>200</v>
@@ -2597,7 +2597,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B159" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1016449/index.html</v>
       </c>
       <c r="C159">
         <v>200</v>
@@ -2611,13 +2611,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B160" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/jouhou/1036432/1013386.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/</v>
       </c>
       <c r="C160">
         <v>200</v>
       </c>
       <c r="D160" t="str">
-        <v>data/services.js, screens/DisasterScreen.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="161">
@@ -2625,13 +2625,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B161" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/kyoujo/1036451/1013567.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/jouhou/1036432/1013386.html</v>
       </c>
       <c r="C161">
         <v>200</v>
       </c>
       <c r="D161" t="str">
-        <v>data/services.js</v>
+        <v>data/services.js, screens/DisasterScreen.js</v>
       </c>
     </row>
     <row r="162">
@@ -2639,7 +2639,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B162" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008962/1008963.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/kyoujo/1036451/1013567.html</v>
       </c>
       <c r="C162">
         <v>200</v>
@@ -2653,7 +2653,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B163" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016506/1016510/1016511.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008962/1008963.html</v>
       </c>
       <c r="C163">
         <v>200</v>
@@ -2667,7 +2667,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B164" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009502/1034108.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016506/1016510/1016511.html</v>
       </c>
       <c r="C164">
         <v>200</v>
@@ -2681,7 +2681,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B165" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/todokede/1007816/1007817.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009502/1034108.html</v>
       </c>
       <c r="C165">
         <v>200</v>
@@ -2695,7 +2695,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B166" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011854/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/todokede/1007816/1007817.html</v>
       </c>
       <c r="C166">
         <v>200</v>
@@ -2709,7 +2709,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B167" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011868.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011854/index.html</v>
       </c>
       <c r="C167">
         <v>200</v>
@@ -2723,7 +2723,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B168" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011870.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011868.html</v>
       </c>
       <c r="C168">
         <v>200</v>
@@ -2737,7 +2737,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B169" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011870.html</v>
       </c>
       <c r="C169">
         <v>200</v>
@@ -2751,7 +2751,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B170" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1035058/1012184/1046468/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/index.html</v>
       </c>
       <c r="C170">
         <v>200</v>
@@ -2765,7 +2765,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B171" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016573/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1035058/1012184/1046468/index.html</v>
       </c>
       <c r="C171">
         <v>200</v>
@@ -2779,7 +2779,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B172" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/pet/1015473/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016573/index.html</v>
       </c>
       <c r="C172">
         <v>200</v>
@@ -2793,7 +2793,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B173" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011763/1011768.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/pet/1015473/index.html</v>
       </c>
       <c r="C173">
         <v>200</v>
@@ -2807,7 +2807,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B174" t="str">
-        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000135090_00001.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011763/1011768.html</v>
       </c>
       <c r="C174">
         <v>200</v>
@@ -2821,7 +2821,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B175" t="str">
-        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000158665.html</v>
+        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000135090_00001.html</v>
       </c>
       <c r="C175">
         <v>200</v>
@@ -2835,7 +2835,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B176" t="str">
-        <v>https://www.kyoukaikenpo.or.jp/benefit/injury_and_sickness_allowance/index.html</v>
+        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000158665.html</v>
       </c>
       <c r="C176">
         <v>200</v>
@@ -2849,7 +2849,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B177" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011851/1011853.html</v>
+        <v>https://www.kyoukaikenpo.or.jp/benefit/injury_and_sickness_allowance/index.html</v>
       </c>
       <c r="C177">
         <v>200</v>
@@ -2863,7 +2863,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B178" t="str">
-        <v>https://www.nenkin.go.jp/service/jukyu/seido/sonota-kyufu/shienkyufukin/20190805.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011851/1011853.html</v>
       </c>
       <c r="C178">
         <v>200</v>
@@ -2877,7 +2877,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B179" t="str">
-        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm</v>
+        <v>https://www.nenkin.go.jp/service/jukyu/seido/sonota-kyufu/shienkyufukin/20190805.html</v>
       </c>
       <c r="C179">
         <v>200</v>
@@ -2891,7 +2891,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B180" t="str">
-        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm#mushoukaLink2</v>
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm</v>
       </c>
       <c r="C180">
         <v>200</v>
@@ -2905,7 +2905,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B181" t="str">
-        <v>https://www.jasso.go.jp/shogakukin/</v>
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm#mushoukaLink2</v>
       </c>
       <c r="C181">
         <v>200</v>
@@ -2919,7 +2919,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B182" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008946.html</v>
+        <v>https://www.jasso.go.jp/shogakukin/</v>
       </c>
       <c r="C182">
         <v>200</v>
@@ -2933,7 +2933,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B183" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016801.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008946.html</v>
       </c>
       <c r="C183">
         <v>200</v>
@@ -2947,7 +2947,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B184" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/801/r8syougakukin.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016801.html</v>
       </c>
       <c r="C184">
         <v>200</v>
@@ -2961,7 +2961,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B185" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016798.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/801/r8syougakukin.pdf</v>
       </c>
       <c r="C185">
         <v>200</v>
@@ -2975,7 +2975,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B186" t="str">
-        <v>https://www.city.nagoya.jp/shisei/keikaku/1034903/1004666/1004670.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016798.html</v>
       </c>
       <c r="C186">
         <v>200</v>
@@ -2989,7 +2989,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B187" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1049088.html</v>
+        <v>https://www.city.nagoya.jp/shisei/keikaku/1034903/1004666/1004670.html</v>
       </c>
       <c r="C187">
         <v>200</v>
@@ -3003,7 +3003,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B188" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1050641.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1049088.html</v>
       </c>
       <c r="C188">
         <v>200</v>
@@ -3017,7 +3017,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B189" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016987.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1050641.html</v>
       </c>
       <c r="C189">
         <v>200</v>
@@ -3031,7 +3031,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B190" t="str">
-        <v>https://nagoyalink.net/</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016987.html</v>
       </c>
       <c r="C190">
         <v>200</v>
@@ -3045,7 +3045,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B191" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016705.html</v>
+        <v>https://nagoyalink.net/</v>
       </c>
       <c r="C191">
         <v>200</v>
@@ -3059,10 +3059,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B192" t="str">
-        <v>http://nagosapo.icds.jp/</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016705.html</v>
       </c>
       <c r="C192">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D192" t="str">
         <v>data/services.js</v>
@@ -3073,7 +3073,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B193" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016706.html</v>
+        <v>https://nagosapo.icds.jp/</v>
       </c>
       <c r="C193">
         <v>200</v>
@@ -3087,10 +3087,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B194" t="str">
-        <v>http://maejob.icds.jp/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016706.html</v>
       </c>
       <c r="C194">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D194" t="str">
         <v>data/services.js</v>
@@ -3101,7 +3101,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B195" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1011883/1011892.html</v>
+        <v>https://maejob.icds.jp/index.html</v>
       </c>
       <c r="C195">
         <v>200</v>
@@ -3115,7 +3115,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B196" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011842/1011845.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1011883/1011892.html</v>
       </c>
       <c r="C196">
         <v>200</v>
@@ -3129,7 +3129,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B197" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011769/1011773.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011842/1011845.html</v>
       </c>
       <c r="C197">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B198" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009386.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011769/1011773.html</v>
       </c>
       <c r="C198">
         <v>200</v>
@@ -3157,7 +3157,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B199" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009394.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009386.html</v>
       </c>
       <c r="C199">
         <v>200</v>
@@ -3171,7 +3171,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B200" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017010/1017016.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009394.html</v>
       </c>
       <c r="C200">
         <v>200</v>
@@ -3185,7 +3185,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B201" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016972/1016979.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017010/1017016.html</v>
       </c>
       <c r="C201">
         <v>200</v>
@@ -3199,7 +3199,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B202" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017053.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016972/1016979.html</v>
       </c>
       <c r="C202">
         <v>200</v>
@@ -3213,7 +3213,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B203" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017056.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017053.html</v>
       </c>
       <c r="C203">
         <v>200</v>
@@ -3227,7 +3227,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B204" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008983/1042086.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017056.html</v>
       </c>
       <c r="C204">
         <v>200</v>
@@ -3241,7 +3241,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B205" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016704.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008983/1042086.html</v>
       </c>
       <c r="C205">
         <v>200</v>
@@ -3255,7 +3255,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B206" t="str">
-        <v>https://www.kosodate-ouen.city.nagoya.jp/</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016704.html</v>
       </c>
       <c r="C206">
         <v>200</v>
@@ -3269,7 +3269,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B207" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009108/1009109.html</v>
+        <v>https://www.kosodate-ouen.city.nagoya.jp/</v>
       </c>
       <c r="C207">
         <v>200</v>
@@ -3283,7 +3283,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B208" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009280.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009108/1009109.html</v>
       </c>
       <c r="C208">
         <v>200</v>
@@ -3297,7 +3297,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B209" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016448/1016483.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009280.html</v>
       </c>
       <c r="C209">
         <v>200</v>
@@ -3311,7 +3311,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B210" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009410/1040316.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016448/1016483.html</v>
       </c>
       <c r="C210">
         <v>200</v>
@@ -3325,7 +3325,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B211" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009525/1009528.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009410/1040316.html</v>
       </c>
       <c r="C211">
         <v>200</v>
@@ -3339,7 +3339,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B212" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009525/1033517.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009525/1009528.html</v>
       </c>
       <c r="C212">
         <v>200</v>
@@ -3353,7 +3353,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B213" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009535/1009537.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009525/1033517.html</v>
       </c>
       <c r="C213">
         <v>200</v>
@@ -3367,7 +3367,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B214" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009535/1009539.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009535/1009537.html</v>
       </c>
       <c r="C214">
         <v>200</v>
@@ -3381,7 +3381,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B215" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1045911/1045913.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009535/1009539.html</v>
       </c>
       <c r="C215">
         <v>200</v>
@@ -3395,7 +3395,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B216" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016443.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1045911/1045913.html</v>
       </c>
       <c r="C216">
         <v>200</v>
@@ -3409,7 +3409,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B217" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016553/1016554.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016443.html</v>
       </c>
       <c r="C217">
         <v>200</v>
@@ -3423,7 +3423,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B218" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016553/1034838.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016553/1016554.html</v>
       </c>
       <c r="C218">
         <v>200</v>
@@ -3437,7 +3437,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B219" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016663.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016553/1034838.html</v>
       </c>
       <c r="C219">
         <v>200</v>
@@ -3451,7 +3451,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B220" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016738.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016663.html</v>
       </c>
       <c r="C220">
         <v>200</v>
@@ -3465,13 +3465,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B221" t="str">
-        <v>https://www.city.nagoya.jp/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016738.html</v>
       </c>
       <c r="C221">
         <v>200</v>
       </c>
       <c r="D221" t="str">
-        <v>screens/DetailScreen.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="222">
@@ -3479,7 +3479,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B222" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/jigyosho/</v>
+        <v>https://www.city.nagoya.jp/</v>
       </c>
       <c r="C222">
         <v>200</v>
@@ -3493,13 +3493,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B223" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/1013492.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/jigyosho/</v>
       </c>
       <c r="C223">
         <v>200</v>
       </c>
       <c r="D223" t="str">
-        <v>screens/DisasterScreen.js</v>
+        <v>screens/DetailScreen.js</v>
       </c>
     </row>
     <row r="224">
@@ -3507,7 +3507,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B224" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036428.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/1013492.html</v>
       </c>
       <c r="C224">
         <v>200</v>
@@ -3516,16 +3516,30 @@
         <v>screens/DisasterScreen.js</v>
       </c>
     </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>✅ 正常</v>
+      </c>
+      <c r="B225" t="str">
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036428.html</v>
+      </c>
+      <c r="C225">
+        <v>200</v>
+      </c>
+      <c r="D225" t="str">
+        <v>screens/DisasterScreen.js</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D224"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D225"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3543,13 +3557,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>https://www.nic-nagoya.or.jp/</v>
+        <v>https://www.bes-c.com/</v>
       </c>
       <c r="B2" t="str">
-        <v>One moment, please...</v>
+        <v>名古屋市高齢者就業支援センター</v>
       </c>
       <c r="C2" t="str">
-        <v>名古屋国際センター | Nagoya International Center</v>
+        <v>名古屋市高齢者就業支援センター</v>
       </c>
       <c r="D2" t="str">
         <v>data/services.js</v>
@@ -3557,56 +3571,28 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034342/1008991/1036125.html</v>
       </c>
       <c r="B3" t="str">
-        <v>One moment, please...</v>
+        <v>子どもの体験活動交通費助成モデル事業｜名古屋市公式ウェブサイト</v>
       </c>
       <c r="C3" t="str">
-        <v>行政相談 | 名古屋国際センター | Nagoya International Center</v>
+        <v>子どもの体験活動交通費助成モデル事業｜名古屋市公式ウェブサイト</v>
       </c>
       <c r="D3" t="str">
-        <v>data/services.js</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>http://nagosapo.icds.jp/</v>
-      </c>
-      <c r="B4" t="str">
-        <v>One moment, please...</v>
-      </c>
-      <c r="C4" t="str">
-        <v>301 Moved Permanently</v>
-      </c>
-      <c r="D4" t="str">
-        <v>data/services.js</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>http://maejob.icds.jp/index.html</v>
-      </c>
-      <c r="B5" t="str">
-        <v>One moment, please...</v>
-      </c>
-      <c r="C5" t="str">
-        <v>301 Moved Permanently</v>
-      </c>
-      <c r="D5" t="str">
         <v>data/services.js</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3636,10 +3622,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D2" t="str">
-        <v>https://www.city.nagoya.jp/bousai/anzen/1014533/1052292.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1050595/index.html</v>
       </c>
       <c r="E2" t="str">
-        <v>全市一斉クリーンキャンペーンなごや2026の取り組み</v>
+        <v>熱田区の消防団について</v>
       </c>
     </row>
     <row r="3">
@@ -3650,81 +3636,81 @@
         <v>https://www.city.nagoya.jp/bousai/index.html</v>
       </c>
       <c r="C3" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D3" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1051487/1051409.html</v>
+        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014550/1034531/1014563.html</v>
       </c>
       <c r="E3" t="str">
-        <v>熱田消防署へのアクセス（公共交通機関）</v>
+        <v>空き家の発生を抑制するための特例措置（令和6年1月1日以降の譲渡）</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>くらし・手続き</v>
+        <v>防災・安全安心</v>
       </c>
       <c r="B4" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
       </c>
       <c r="C4" t="str">
         <v>➕ 追加</v>
       </c>
       <c r="D4" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052147.html</v>
+        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014550/1034531/1014557.html</v>
       </c>
       <c r="E4" t="str">
-        <v>終活・相続セミナー＆個別相談会</v>
+        <v>名古屋市老朽危険空家等除却費補助金</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>くらし・手続き</v>
+        <v>防災・安全安心</v>
       </c>
       <c r="B5" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
       </c>
       <c r="C5" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D5" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1050841.html</v>
+        <v>https://www.city.nagoya.jp/bousai/anzen/1014533/1052292.html</v>
       </c>
       <c r="E5" t="str">
-        <v>市民活動推進センター講座（10/21・11/18）</v>
+        <v>全市一斉クリーンキャンペーンなごや2026の取り組み</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>くらし・手続き</v>
+        <v>防災・安全安心</v>
       </c>
       <c r="B6" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
       </c>
       <c r="C6" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D6" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052466.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1050592/1051513.html</v>
       </c>
       <c r="E6" t="str">
-        <v>市立大学 市民公開講座（第5回から第11回）</v>
+        <v>【重要】電気火災が増えています</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>くらし・手続き</v>
+        <v>防災・安全安心</v>
       </c>
       <c r="B7" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
       </c>
       <c r="C7" t="str">
         <v>➖ 削除</v>
       </c>
       <c r="D7" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/kankyou/1034811/1012684/1012697/1034060/1051886.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1051487/index.html</v>
       </c>
       <c r="E7" t="str">
-        <v>ぜん息予防サッカー教室</v>
+        <v>熱田消防署について</v>
       </c>
     </row>
     <row r="8">
@@ -3735,13 +3721,13 @@
         <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C8" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D8" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1050836.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shiminsanka/1011147/1052643.html</v>
       </c>
       <c r="E8" t="str">
-        <v>ソレイユプラザなごや「家族で楽しむ体験イベント」レゴランド(R)（上付き）・ジャパンのワークショップで多様性を学ぼう！</v>
+        <v>令和8年熊本地震名古屋市義援金</v>
       </c>
     </row>
     <row r="9">
@@ -3752,93 +3738,127 @@
         <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C9" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D9" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1015518/1052115.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012463/1034808/1051962.html</v>
       </c>
       <c r="E9" t="str">
-        <v>消費生活相談員になりませんか？</v>
+        <v>藤前干潟わくわくフェスタ 見て・知って・守ろう！</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>子ども・子育て・教育</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B10" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C10" t="str">
         <v>➕ 追加</v>
       </c>
       <c r="D10" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1016995/1016810/1016833/1016858/1052437.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052454.html</v>
       </c>
       <c r="E10" t="str">
-        <v>本地丘小学校、森孝東小学校及び森孝西小学校の統合並びに森孝中学校との併設に関する個別プラン（答申）(令和8年8月6日)</v>
+        <v>アジア競技大会・アジアパラ競技大会 競技会場巡礼ウォーク</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>子ども・子育て・教育</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B11" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C11" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D11" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1016995/1016810/1016811/1016816/1052451.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052147.html</v>
       </c>
       <c r="E11" t="str">
-        <v>令和8年度第2回名古屋市子どもいきいき学校づくり推進審議会 令和8年8月6日</v>
+        <v>終活・相続セミナー＆個別相談会</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>子ども・子育て・教育</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B12" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C12" t="str">
         <v>➖ 削除</v>
       </c>
       <c r="D12" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1052219.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1050841.html</v>
       </c>
       <c r="E12" t="str">
-        <v>令和8年度トワイライトスクール・ルームに関するアンケート調査について</v>
+        <v>市民活動推進センター講座（10/21・11/18）</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>子ども・子育て・教育</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B13" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C13" t="str">
         <v>➖ 削除</v>
       </c>
       <c r="D13" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1051827.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052466.html</v>
       </c>
       <c r="E13" t="str">
-        <v>令和8年8月10日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+        <v>市立大学 市民公開講座（第5回から第11回）</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="B14" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="C14" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D14" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017010/1051545.html</v>
+      </c>
+      <c r="E14" t="str">
+        <v>特別支援学校および特別支援学級・通級指導教室の設置校一覧</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="B15" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="C15" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D15" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1027694/1052246.html</v>
+      </c>
+      <c r="E15" t="str">
+        <v>令和8年度 教育委員会8月臨時会</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E15"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M122"/>
+  <dimension ref="A1:M138"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6418,9 +6438,371 @@
         <v>令和8年8月10日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
       </c>
     </row>
+    <row r="123">
+      <c r="B123" t="str">
+        <v>2026-08-24</v>
+      </c>
+      <c r="C123" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D123" t="str">
+        <v>https://www.bes-c.com/</v>
+      </c>
+      <c r="F123" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G123" t="str">
+        <v>名古屋市高齢者就業支援センター</v>
+      </c>
+      <c r="H123" t="str">
+        <v>名古屋市高齢者就業支援センター</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="str">
+        <v>2026-08-24</v>
+      </c>
+      <c r="C124" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D124" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034342/1008991/1036125.html</v>
+      </c>
+      <c r="F124" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G124" t="str">
+        <v>子どもの体験活動交通費助成モデル事業｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="H124" t="str">
+        <v>子どもの体験活動交通費助成モデル事業｜名古屋市公式ウェブサイト</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="str">
+        <v>2026-08-24</v>
+      </c>
+      <c r="C125" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I125" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J125" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K125" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L125" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1050595/index.html</v>
+      </c>
+      <c r="M125" t="str">
+        <v>熱田区の消防団について</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="str">
+        <v>2026-08-24</v>
+      </c>
+      <c r="C126" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I126" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J126" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K126" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L126" t="str">
+        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014550/1034531/1014563.html</v>
+      </c>
+      <c r="M126" t="str">
+        <v>空き家の発生を抑制するための特例措置（令和6年1月1日以降の譲渡）</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="str">
+        <v>2026-08-24</v>
+      </c>
+      <c r="C127" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I127" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J127" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K127" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L127" t="str">
+        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014550/1034531/1014557.html</v>
+      </c>
+      <c r="M127" t="str">
+        <v>名古屋市老朽危険空家等除却費補助金</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="str">
+        <v>2026-08-24</v>
+      </c>
+      <c r="C128" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I128" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J128" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K128" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L128" t="str">
+        <v>https://www.city.nagoya.jp/bousai/anzen/1014533/1052292.html</v>
+      </c>
+      <c r="M128" t="str">
+        <v>全市一斉クリーンキャンペーンなごや2026の取り組み</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="str">
+        <v>2026-08-24</v>
+      </c>
+      <c r="C129" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I129" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J129" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K129" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L129" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1050592/1051513.html</v>
+      </c>
+      <c r="M129" t="str">
+        <v>【重要】電気火災が増えています</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="str">
+        <v>2026-08-24</v>
+      </c>
+      <c r="C130" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I130" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J130" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K130" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L130" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1051487/index.html</v>
+      </c>
+      <c r="M130" t="str">
+        <v>熱田消防署について</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="str">
+        <v>2026-08-24</v>
+      </c>
+      <c r="C131" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I131" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J131" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K131" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L131" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/shiminsanka/1011147/1052643.html</v>
+      </c>
+      <c r="M131" t="str">
+        <v>令和8年熊本地震名古屋市義援金</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="str">
+        <v>2026-08-24</v>
+      </c>
+      <c r="C132" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I132" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J132" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K132" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L132" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012463/1034808/1051962.html</v>
+      </c>
+      <c r="M132" t="str">
+        <v>藤前干潟わくわくフェスタ 見て・知って・守ろう！</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="str">
+        <v>2026-08-24</v>
+      </c>
+      <c r="C133" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I133" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J133" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K133" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L133" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052454.html</v>
+      </c>
+      <c r="M133" t="str">
+        <v>アジア競技大会・アジアパラ競技大会 競技会場巡礼ウォーク</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="str">
+        <v>2026-08-24</v>
+      </c>
+      <c r="C134" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I134" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J134" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K134" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L134" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052147.html</v>
+      </c>
+      <c r="M134" t="str">
+        <v>終活・相続セミナー＆個別相談会</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="str">
+        <v>2026-08-24</v>
+      </c>
+      <c r="C135" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I135" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J135" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K135" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L135" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1050841.html</v>
+      </c>
+      <c r="M135" t="str">
+        <v>市民活動推進センター講座（10/21・11/18）</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="str">
+        <v>2026-08-24</v>
+      </c>
+      <c r="C136" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I136" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J136" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K136" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L136" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052466.html</v>
+      </c>
+      <c r="M136" t="str">
+        <v>市立大学 市民公開講座（第5回から第11回）</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="str">
+        <v>2026-08-24</v>
+      </c>
+      <c r="C137" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I137" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J137" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K137" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L137" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017010/1051545.html</v>
+      </c>
+      <c r="M137" t="str">
+        <v>特別支援学校および特別支援学級・通級指導教室の設置校一覧</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="str">
+        <v>2026-08-24</v>
+      </c>
+      <c r="C138" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I138" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J138" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K138" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L138" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1027694/1052246.html</v>
+      </c>
+      <c r="M138" t="str">
+        <v>令和8年度 教育委員会8月臨時会</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M122"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M138"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reports/latest-report.xlsx
+++ b/reports/latest-report.xlsx
@@ -396,16 +396,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>✅ 正常</v>
+        <v>❌ リンク切れ</v>
       </c>
       <c r="B2" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036294.html</v>
+        <v>https://webc.sjc.ne.jp/nagoyasj/job2_7</v>
       </c>
       <c r="C2">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="D2" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="3">
@@ -413,13 +413,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B3" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/index.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036294.html</v>
       </c>
       <c r="C3">
         <v>200</v>
       </c>
       <c r="D3" t="str">
-        <v>data/districts.js, screens/DisasterScreen.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="4">
@@ -427,13 +427,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B4" t="str">
-        <v>https://www.city.nagoya.jp/chikusa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/index.html</v>
       </c>
       <c r="C4">
         <v>200</v>
       </c>
       <c r="D4" t="str">
-        <v>data/districts.js</v>
+        <v>data/districts.js, screens/DisasterScreen.js</v>
       </c>
     </row>
     <row r="5">
@@ -441,7 +441,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B5" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036299.html</v>
+        <v>https://www.city.nagoya.jp/chikusa/kurashi/</v>
       </c>
       <c r="C5">
         <v>200</v>
@@ -455,7 +455,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B6" t="str">
-        <v>https://www.city.nagoya.jp/higashi/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036299.html</v>
       </c>
       <c r="C6">
         <v>200</v>
@@ -469,7 +469,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B7" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036302.html</v>
+        <v>https://www.city.nagoya.jp/higashi/kurashi/</v>
       </c>
       <c r="C7">
         <v>200</v>
@@ -483,7 +483,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B8" t="str">
-        <v>https://www.city.nagoya.jp/kita/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036302.html</v>
       </c>
       <c r="C8">
         <v>200</v>
@@ -497,7 +497,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B9" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036293.html</v>
+        <v>https://www.city.nagoya.jp/kita/kurashi/</v>
       </c>
       <c r="C9">
         <v>200</v>
@@ -511,7 +511,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B10" t="str">
-        <v>https://www.city.nagoya.jp/nishi/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036293.html</v>
       </c>
       <c r="C10">
         <v>200</v>
@@ -525,7 +525,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B11" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036297.html</v>
+        <v>https://www.city.nagoya.jp/nishi/kurashi/</v>
       </c>
       <c r="C11">
         <v>200</v>
@@ -539,7 +539,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B12" t="str">
-        <v>https://www.city.nagoya.jp/nakamura/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036297.html</v>
       </c>
       <c r="C12">
         <v>200</v>
@@ -553,7 +553,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B13" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036295.html</v>
+        <v>https://www.city.nagoya.jp/nakamura/kurashi/</v>
       </c>
       <c r="C13">
         <v>200</v>
@@ -567,7 +567,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B14" t="str">
-        <v>https://www.city.nagoya.jp/naka/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036295.html</v>
       </c>
       <c r="C14">
         <v>200</v>
@@ -581,7 +581,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B15" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036291.html</v>
+        <v>https://www.city.nagoya.jp/naka/kurashi/</v>
       </c>
       <c r="C15">
         <v>200</v>
@@ -595,7 +595,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B16" t="str">
-        <v>https://www.city.nagoya.jp/showa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036291.html</v>
       </c>
       <c r="C16">
         <v>200</v>
@@ -609,7 +609,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B17" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036292.html</v>
+        <v>https://www.city.nagoya.jp/showa/kurashi/</v>
       </c>
       <c r="C17">
         <v>200</v>
@@ -623,7 +623,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B18" t="str">
-        <v>https://www.city.nagoya.jp/mizuho/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036292.html</v>
       </c>
       <c r="C18">
         <v>200</v>
@@ -637,7 +637,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B19" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036301.html</v>
+        <v>https://www.city.nagoya.jp/mizuho/kurashi/</v>
       </c>
       <c r="C19">
         <v>200</v>
@@ -651,7 +651,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B20" t="str">
-        <v>https://www.city.nagoya.jp/atsuta/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036301.html</v>
       </c>
       <c r="C20">
         <v>200</v>
@@ -665,7 +665,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B21" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036296.html</v>
+        <v>https://www.city.nagoya.jp/atsuta/kurashi/</v>
       </c>
       <c r="C21">
         <v>200</v>
@@ -679,7 +679,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B22" t="str">
-        <v>https://www.city.nagoya.jp/nakagawa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036296.html</v>
       </c>
       <c r="C22">
         <v>200</v>
@@ -693,7 +693,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B23" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036289.html</v>
+        <v>https://www.city.nagoya.jp/nakagawa/kurashi/</v>
       </c>
       <c r="C23">
         <v>200</v>
@@ -707,7 +707,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B24" t="str">
-        <v>https://www.city.nagoya.jp/minato/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036289.html</v>
       </c>
       <c r="C24">
         <v>200</v>
@@ -721,7 +721,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B25" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036300.html</v>
+        <v>https://www.city.nagoya.jp/minato/kurashi/</v>
       </c>
       <c r="C25">
         <v>200</v>
@@ -735,7 +735,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B26" t="str">
-        <v>https://www.city.nagoya.jp/minami/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036300.html</v>
       </c>
       <c r="C26">
         <v>200</v>
@@ -749,7 +749,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B27" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036290.html</v>
+        <v>https://www.city.nagoya.jp/minami/kurashi/</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -763,7 +763,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B28" t="str">
-        <v>https://www.city.nagoya.jp/moriyama/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036290.html</v>
       </c>
       <c r="C28">
         <v>200</v>
@@ -777,7 +777,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B29" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036304.html</v>
+        <v>https://www.city.nagoya.jp/moriyama/kurashi/</v>
       </c>
       <c r="C29">
         <v>200</v>
@@ -791,7 +791,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B30" t="str">
-        <v>https://www.city.nagoya.jp/midori/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036304.html</v>
       </c>
       <c r="C30">
         <v>200</v>
@@ -805,7 +805,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B31" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036303.html</v>
+        <v>https://www.city.nagoya.jp/midori/kurashi/</v>
       </c>
       <c r="C31">
         <v>200</v>
@@ -819,7 +819,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B32" t="str">
-        <v>https://www.city.nagoya.jp/meito/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036303.html</v>
       </c>
       <c r="C32">
         <v>200</v>
@@ -833,7 +833,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B33" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036298.html</v>
+        <v>https://www.city.nagoya.jp/meito/kurashi/</v>
       </c>
       <c r="C33">
         <v>200</v>
@@ -847,7 +847,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B34" t="str">
-        <v>https://www.city.nagoya.jp/tempaku/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036298.html</v>
       </c>
       <c r="C34">
         <v>200</v>
@@ -861,13 +861,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B35" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008973.html</v>
+        <v>https://www.city.nagoya.jp/tempaku/kurashi/</v>
       </c>
       <c r="C35">
         <v>200</v>
       </c>
       <c r="D35" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="36">
@@ -875,7 +875,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B36" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009333.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008973.html</v>
       </c>
       <c r="C36">
         <v>200</v>
@@ -889,7 +889,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B37" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1009009.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009333.html</v>
       </c>
       <c r="C37">
         <v>200</v>
@@ -903,7 +903,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B38" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009270/1034086.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1009009.html</v>
       </c>
       <c r="C38">
         <v>200</v>
@@ -917,7 +917,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B39" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009353/1034092.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009270/1034086.html</v>
       </c>
       <c r="C39">
         <v>200</v>
@@ -931,7 +931,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B40" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009286/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009353/1034092.html</v>
       </c>
       <c r="C40">
         <v>200</v>
@@ -945,7 +945,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B41" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1034088.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009286/index.html</v>
       </c>
       <c r="C41">
         <v>200</v>
@@ -959,7 +959,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B42" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009387.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1034088.html</v>
       </c>
       <c r="C42">
         <v>200</v>
@@ -973,7 +973,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B43" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009393.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009387.html</v>
       </c>
       <c r="C43">
         <v>200</v>
@@ -987,7 +987,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B44" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011821/1011823.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009393.html</v>
       </c>
       <c r="C44">
         <v>200</v>
@@ -1001,7 +1001,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B45" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008956.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011821/1011823.html</v>
       </c>
       <c r="C45">
         <v>200</v>
@@ -1015,7 +1015,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B46" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008955.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008956.html</v>
       </c>
       <c r="C46">
         <v>200</v>
@@ -1029,7 +1029,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B47" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/ichiran.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008955.html</v>
       </c>
       <c r="C47">
         <v>200</v>
@@ -1043,7 +1043,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B48" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008960.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/ichiran.html</v>
       </c>
       <c r="C48">
         <v>200</v>
@@ -1057,7 +1057,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B49" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009019.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008960.html</v>
       </c>
       <c r="C49">
         <v>200</v>
@@ -1071,7 +1071,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B50" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008974.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009019.html</v>
       </c>
       <c r="C50">
         <v>200</v>
@@ -1085,7 +1085,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B51" t="str">
-        <v>https://www.city.nagoya.jp/lifescene/byouki/1017964.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008974.html</v>
       </c>
       <c r="C51">
         <v>200</v>
@@ -1099,7 +1099,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B52" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/seido/toiawase/</v>
+        <v>https://www.city.nagoya.jp/lifescene/byouki/1017964.html</v>
       </c>
       <c r="C52">
         <v>200</v>
@@ -1113,7 +1113,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B53" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016496/1016502.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/seido/toiawase/</v>
       </c>
       <c r="C53">
         <v>200</v>
@@ -1127,7 +1127,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B54" t="str">
-        <v>http://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016496/1016502.html</v>
       </c>
       <c r="C54">
         <v>200</v>
@@ -1141,7 +1141,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B55" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/1016536.html</v>
+        <v>http://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
       </c>
       <c r="C55">
         <v>200</v>
@@ -1155,7 +1155,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B56" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011776/1034706/1011784.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/1016536.html</v>
       </c>
       <c r="C56">
         <v>200</v>
@@ -1169,7 +1169,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B57" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009456/1009457/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011776/1034706/1011784.html</v>
       </c>
       <c r="C57">
         <v>200</v>
@@ -1183,7 +1183,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B58" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009456/1009457/index.html</v>
       </c>
       <c r="C58">
         <v>200</v>
@@ -1197,7 +1197,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B59" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1012157/1033970.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
       </c>
       <c r="C59">
         <v>200</v>
@@ -1211,7 +1211,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B60" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1015763/1015815.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1012157/1033970.html</v>
       </c>
       <c r="C60">
         <v>200</v>
@@ -1225,7 +1225,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B61" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011793/1011807/1011810.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1015763/1015815.html</v>
       </c>
       <c r="C61">
         <v>200</v>
@@ -1239,7 +1239,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B62" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016739.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011793/1011807/1011810.html</v>
       </c>
       <c r="C62">
         <v>200</v>
@@ -1253,7 +1253,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B63" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016739.html</v>
       </c>
       <c r="C63">
         <v>200</v>
@@ -1267,7 +1267,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B64" t="str">
-        <v>https://www.hellowork.mhlw.go.jp/insurance/insurance_guide.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/index.html</v>
       </c>
       <c r="C64">
         <v>200</v>
@@ -1281,7 +1281,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B65" t="str">
-        <v>https://jsite.mhlw.go.jp/aichi-hellowork/list.html</v>
+        <v>https://www.hellowork.mhlw.go.jp/insurance/insurance_guide.html</v>
       </c>
       <c r="C65">
         <v>200</v>
@@ -1295,7 +1295,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B66" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
+        <v>https://jsite.mhlw.go.jp/aichi-hellowork/list.html</v>
       </c>
       <c r="C66">
         <v>200</v>
@@ -1309,7 +1309,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B67" t="str">
-        <v>https://www.nagojob.city.nagoya.jp/</v>
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
       </c>
       <c r="C67">
         <v>200</v>
@@ -1323,7 +1323,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B68" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/tetyou/</v>
+        <v>https://www.nagojob.city.nagoya.jp/</v>
       </c>
       <c r="C68">
         <v>200</v>
@@ -1337,7 +1337,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B69" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/soudan/fukushikakari.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/tetyou/</v>
       </c>
       <c r="C69">
         <v>200</v>
@@ -1351,7 +1351,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B70" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/fukushi_service.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/soudan/fukushikakari.html</v>
       </c>
       <c r="C70">
         <v>200</v>
@@ -1365,7 +1365,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B71" t="str">
-        <v>https://www.city.nagoya.jp/jigyou/sangyou/1026356/1035103/1026446/1026447.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/fukushi_service.html</v>
       </c>
       <c r="C71">
         <v>200</v>
@@ -1379,7 +1379,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B72" t="str">
-        <v>https://weljob-nagoya.com/</v>
+        <v>https://www.city.nagoya.jp/jigyou/sangyou/1026356/1035103/1026446/1026447.html</v>
       </c>
       <c r="C72">
         <v>200</v>
@@ -1393,7 +1393,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B73" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
+        <v>https://weljob-nagoya.com/</v>
       </c>
       <c r="C73">
         <v>200</v>
@@ -1407,7 +1407,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B74" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/622/linksweb.pdf</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
       </c>
       <c r="C74">
         <v>200</v>
@@ -1421,7 +1421,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B75" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/622/linksweb.pdf</v>
       </c>
       <c r="C75">
         <v>200</v>
@@ -1435,7 +1435,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B76" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/675/annnai.pdf</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
       </c>
       <c r="C76">
         <v>200</v>
@@ -1449,7 +1449,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B77" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/675/annnai.pdf</v>
       </c>
       <c r="C77">
         <v>200</v>
@@ -1463,7 +1463,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B78" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
       </c>
       <c r="C78">
         <v>200</v>
@@ -1477,7 +1477,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B79" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
       </c>
       <c r="C79">
         <v>200</v>
@@ -1491,7 +1491,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B80" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008978.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
       </c>
       <c r="C80">
         <v>200</v>
@@ -1505,7 +1505,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B81" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/008/978/0413tirasi.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008978.html</v>
       </c>
       <c r="C81">
         <v>200</v>
@@ -1519,7 +1519,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B82" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034073/1009017.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/008/978/0413tirasi.pdf</v>
       </c>
       <c r="C82">
         <v>200</v>
@@ -1533,7 +1533,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B83" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/009/017/r710_help.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034073/1009017.html</v>
       </c>
       <c r="C83">
         <v>200</v>
@@ -1547,7 +1547,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B84" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1034087.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/009/017/r710_help.pdf</v>
       </c>
       <c r="C84">
         <v>200</v>
@@ -1561,7 +1561,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B85" t="str">
-        <v>https://www.kosodate.city.nagoya.jp/kids/nobinobi.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1034087.html</v>
       </c>
       <c r="C85">
         <v>200</v>
@@ -1575,7 +1575,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B86" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1009278.html</v>
+        <v>https://www.kosodate.city.nagoya.jp/kids/nobinobi.html</v>
       </c>
       <c r="C86">
         <v>200</v>
@@ -1589,7 +1589,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B87" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009024/1009026.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1009278.html</v>
       </c>
       <c r="C87">
         <v>200</v>
@@ -1603,7 +1603,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B88" t="str">
-        <v>https://www.kosodate.city.nagoya.jp/play/supportbases.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009024/1009026.html</v>
       </c>
       <c r="C88">
         <v>200</v>
@@ -1617,7 +1617,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B89" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034075/1009021.html</v>
+        <v>https://www.kosodate.city.nagoya.jp/play/supportbases.html</v>
       </c>
       <c r="C89">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B90" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034072/1009016.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034075/1009021.html</v>
       </c>
       <c r="C90">
         <v>200</v>
@@ -1645,10 +1645,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B91" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096177.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034072/1009016.html</v>
       </c>
       <c r="C91">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D91" t="str">
         <v>data/services.js</v>
@@ -1659,10 +1659,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B92" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016744.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096177.html</v>
       </c>
       <c r="C92">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D92" t="str">
         <v>data/services.js</v>
@@ -1673,7 +1673,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B93" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016742.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016744.html</v>
       </c>
       <c r="C93">
         <v>200</v>
@@ -1687,7 +1687,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B94" t="str">
-        <v>https://hikikomori.city.nagoya.jp/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016742.html</v>
       </c>
       <c r="C94">
         <v>200</v>
@@ -1701,7 +1701,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B95" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016586/1033908.html</v>
+        <v>https://hikikomori.city.nagoya.jp/</v>
       </c>
       <c r="C95">
         <v>200</v>
@@ -1715,7 +1715,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B96" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009395.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016586/1033908.html</v>
       </c>
       <c r="C96">
         <v>200</v>
@@ -1729,7 +1729,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B97" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1009398.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009395.html</v>
       </c>
       <c r="C97">
         <v>200</v>
@@ -1743,7 +1743,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B98" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009380.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1009398.html</v>
       </c>
       <c r="C98">
         <v>200</v>
@@ -1757,7 +1757,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B99" t="str">
-        <v>https://aiboren.jp/shisetsu/</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009380.html</v>
       </c>
       <c r="C99">
         <v>200</v>
@@ -1771,7 +1771,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B100" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016428.html</v>
+        <v>https://aiboren.jp/shisetsu/</v>
       </c>
       <c r="C100">
         <v>200</v>
@@ -1785,7 +1785,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B101" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/woichiran.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016428.html</v>
       </c>
       <c r="C101">
         <v>200</v>
@@ -1799,7 +1799,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B102" t="str">
-        <v>https://nagoya-shakyo.jp/service/fureai-kyushoku/</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/woichiran.html</v>
       </c>
       <c r="C102">
         <v>200</v>
@@ -1813,7 +1813,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B103" t="str">
-        <v>https://nagoya-shakyo.jp/service/ward-shakyo/</v>
+        <v>https://nagoya-shakyo.jp/service/fureai-kyushoku/</v>
       </c>
       <c r="C103">
         <v>200</v>
@@ -1827,7 +1827,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B104" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/company/shitei/haishoku/</v>
+        <v>https://nagoya-shakyo.jp/service/ward-shakyo/</v>
       </c>
       <c r="C104">
         <v>200</v>
@@ -1841,7 +1841,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B105" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/company/shitei/haishoku/</v>
       </c>
       <c r="C105">
         <v>200</v>
@@ -1855,7 +1855,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B106" t="str">
-        <v>https://webc.sjc.ne.jp/nagoyasj/job2_7</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
       </c>
       <c r="C106">
         <v>200</v>
@@ -3539,7 +3539,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3557,13 +3557,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>https://www.bes-c.com/</v>
+        <v>https://webc.sjc.ne.jp/nagoyasj/job2_7</v>
       </c>
       <c r="B2" t="str">
-        <v>名古屋市高齢者就業支援センター</v>
+        <v>ひとに、ときめきを。公益社団法人名古屋市シルバー人材センター【公式】</v>
       </c>
       <c r="C2" t="str">
-        <v>名古屋市高齢者就業支援センター</v>
+        <v/>
       </c>
       <c r="D2" t="str">
         <v>data/services.js</v>
@@ -3571,21 +3571,35 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034342/1008991/1036125.html</v>
+        <v>https://www.bes-c.com/</v>
       </c>
       <c r="B3" t="str">
-        <v>子どもの体験活動交通費助成モデル事業｜名古屋市公式ウェブサイト</v>
+        <v>名古屋市高齢者就業支援センター</v>
       </c>
       <c r="C3" t="str">
-        <v>子どもの体験活動交通費助成モデル事業｜名古屋市公式ウェブサイト</v>
+        <v>名古屋市高齢者就業支援センター</v>
       </c>
       <c r="D3" t="str">
         <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/1013492.html</v>
+      </c>
+      <c r="B4" t="str">
+        <v>指定緊急避難場所・指定避難所の指定｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="C4" t="str">
+        <v>指定緊急避難場所・指定避難所の指定｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="D4" t="str">
+        <v>screens/DisasterScreen.js</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3622,10 +3636,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D2" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1050595/index.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012834/1044832/1052173.html</v>
       </c>
       <c r="E2" t="str">
-        <v>熱田区の消防団について</v>
+        <v>令和8年 中区消防団連合観閲式のお知らせ</v>
       </c>
     </row>
     <row r="3">
@@ -3636,81 +3650,81 @@
         <v>https://www.city.nagoya.jp/bousai/index.html</v>
       </c>
       <c r="C3" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D3" t="str">
-        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014550/1034531/1014563.html</v>
+        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014550/1034531/1014557.html</v>
       </c>
       <c r="E3" t="str">
-        <v>空き家の発生を抑制するための特例措置（令和6年1月1日以降の譲渡）</v>
+        <v>名古屋市老朽危険空家等除却費補助金</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>防災・安全安心</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B4" t="str">
-        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C4" t="str">
         <v>➕ 追加</v>
       </c>
       <c r="D4" t="str">
-        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014550/1034531/1014557.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/douro/1014853/1014872/1052271.html</v>
       </c>
       <c r="E4" t="str">
-        <v>名古屋市老朽危険空家等除却費補助金</v>
+        <v>スポーツ教室開催計画書・地元説明報告書の提出先</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>防災・安全安心</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B5" t="str">
-        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C5" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D5" t="str">
-        <v>https://www.city.nagoya.jp/bousai/anzen/1014533/1052292.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/douro/1014853/1014872/1052148.html</v>
       </c>
       <c r="E5" t="str">
-        <v>全市一斉クリーンキャンペーンなごや2026の取り組み</v>
+        <v>公園でスポーツ教室を開催したい</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>防災・安全安心</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B6" t="str">
-        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C6" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D6" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1050592/1051513.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051352.html</v>
       </c>
       <c r="E6" t="str">
-        <v>【重要】電気火災が増えています</v>
+        <v>森づくり体験会 炭焼き窯で竹炭ができるまでを体験しよう（大高緑地）</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>防災・安全安心</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B7" t="str">
-        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C7" t="str">
         <v>➖ 削除</v>
       </c>
       <c r="D7" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1051487/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shiminsanka/1011147/1052643.html</v>
       </c>
       <c r="E7" t="str">
-        <v>熱田消防署について</v>
+        <v>令和8年熊本地震名古屋市義援金</v>
       </c>
     </row>
     <row r="8">
@@ -3721,13 +3735,13 @@
         <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C8" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D8" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shiminsanka/1011147/1052643.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012463/1034808/1051962.html</v>
       </c>
       <c r="E8" t="str">
-        <v>令和8年熊本地震名古屋市義援金</v>
+        <v>藤前干潟わくわくフェスタ 見て・知って・守ろう！</v>
       </c>
     </row>
     <row r="9">
@@ -3738,115 +3752,115 @@
         <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C9" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D9" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012463/1034808/1051962.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052454.html</v>
       </c>
       <c r="E9" t="str">
-        <v>藤前干潟わくわくフェスタ 見て・知って・守ろう！</v>
+        <v>アジア競技大会・アジアパラ競技大会 競技会場巡礼ウォーク</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>くらし・手続き</v>
+        <v>子ども・子育て・教育</v>
       </c>
       <c r="B10" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
       </c>
       <c r="C10" t="str">
         <v>➕ 追加</v>
       </c>
       <c r="D10" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052454.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1034096.html</v>
       </c>
       <c r="E10" t="str">
-        <v>アジア競技大会・アジアパラ競技大会 競技会場巡礼ウォーク</v>
+        <v>幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>くらし・手続き</v>
+        <v>子ども・子育て・教育</v>
       </c>
       <c r="B11" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
       </c>
       <c r="C11" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D11" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052147.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1052121.html</v>
       </c>
       <c r="E11" t="str">
-        <v>終活・相続セミナー＆個別相談会</v>
+        <v>令和8年8月25日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>くらし・手続き</v>
+        <v>子ども・子育て・教育</v>
       </c>
       <c r="B12" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
       </c>
       <c r="C12" t="str">
         <v>➖ 削除</v>
       </c>
       <c r="D12" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1050841.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1016995/1016810/1016833/1016858/1052437.html</v>
       </c>
       <c r="E12" t="str">
-        <v>市民活動推進センター講座（10/21・11/18）</v>
+        <v>本地丘小学校、森孝東小学校及び森孝西小学校の統合並びに森孝中学校との併設に関する個別プラン（答申）(令和8年8月6日)</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>くらし・手続き</v>
+        <v>子ども・子育て・教育</v>
       </c>
       <c r="B13" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
       </c>
       <c r="C13" t="str">
         <v>➖ 削除</v>
       </c>
       <c r="D13" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052466.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1016995/1016810/1016811/1016816/1052451.html</v>
       </c>
       <c r="E13" t="str">
-        <v>市立大学 市民公開講座（第5回から第11回）</v>
+        <v>令和8年度第2回名古屋市子どもいきいき学校づくり推進審議会 令和8年8月6日</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>子ども・子育て・教育</v>
+        <v>健康・医療・福祉</v>
       </c>
       <c r="B14" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
       </c>
       <c r="C14" t="str">
         <v>➕ 追加</v>
       </c>
       <c r="D14" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017010/1051545.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015269/1034849/1034132/1052633.html</v>
       </c>
       <c r="E14" t="str">
-        <v>特別支援学校および特別支援学級・通級指導教室の設置校一覧</v>
+        <v>令和8年度「衛研だより」</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>子ども・子育て・教育</v>
+        <v>健康・医療・福祉</v>
       </c>
       <c r="B15" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
       </c>
       <c r="C15" t="str">
         <v>➖ 削除</v>
       </c>
       <c r="D15" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1027694/1052246.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1035053/1051909.html</v>
       </c>
       <c r="E15" t="str">
-        <v>令和8年度 教育委員会8月臨時会</v>
+        <v>令和8年度音訳ボランティア養成講座</v>
       </c>
     </row>
   </sheetData>
@@ -3858,7 +3872,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M138"/>
+  <dimension ref="A1:M156"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6800,9 +6814,408 @@
         <v>令和8年度 教育委員会8月臨時会</v>
       </c>
     </row>
+    <row r="139">
+      <c r="B139" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="C139" t="str">
+        <v>リンク切れ</v>
+      </c>
+      <c r="D139" t="str">
+        <v>https://webc.sjc.ne.jp/nagoyasj/job2_7</v>
+      </c>
+      <c r="E139">
+        <v>403</v>
+      </c>
+      <c r="F139" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="C140" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D140" t="str">
+        <v>https://webc.sjc.ne.jp/nagoyasj/job2_7</v>
+      </c>
+      <c r="F140" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G140" t="str">
+        <v>ひとに、ときめきを。公益社団法人名古屋市シルバー人材センター【公式】</v>
+      </c>
+      <c r="H140" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="C141" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D141" t="str">
+        <v>https://www.bes-c.com/</v>
+      </c>
+      <c r="F141" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G141" t="str">
+        <v>名古屋市高齢者就業支援センター</v>
+      </c>
+      <c r="H141" t="str">
+        <v>名古屋市高齢者就業支援センター</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="C142" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D142" t="str">
+        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/1013492.html</v>
+      </c>
+      <c r="F142" t="str">
+        <v>screens/DisasterScreen.js</v>
+      </c>
+      <c r="G142" t="str">
+        <v>指定緊急避難場所・指定避難所の指定｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="H142" t="str">
+        <v>指定緊急避難場所・指定避難所の指定｜名古屋市公式ウェブサイト</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="C143" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I143" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J143" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K143" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L143" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012834/1044832/1052173.html</v>
+      </c>
+      <c r="M143" t="str">
+        <v>令和8年 中区消防団連合観閲式のお知らせ</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="C144" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I144" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J144" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K144" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L144" t="str">
+        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014550/1034531/1014557.html</v>
+      </c>
+      <c r="M144" t="str">
+        <v>名古屋市老朽危険空家等除却費補助金</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="C145" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I145" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J145" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K145" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L145" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/douro/1014853/1014872/1052271.html</v>
+      </c>
+      <c r="M145" t="str">
+        <v>スポーツ教室開催計画書・地元説明報告書の提出先</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="C146" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I146" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J146" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K146" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L146" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/douro/1014853/1014872/1052148.html</v>
+      </c>
+      <c r="M146" t="str">
+        <v>公園でスポーツ教室を開催したい</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="C147" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I147" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J147" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K147" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L147" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051352.html</v>
+      </c>
+      <c r="M147" t="str">
+        <v>森づくり体験会 炭焼き窯で竹炭ができるまでを体験しよう（大高緑地）</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="C148" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I148" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J148" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K148" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L148" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/shiminsanka/1011147/1052643.html</v>
+      </c>
+      <c r="M148" t="str">
+        <v>令和8年熊本地震名古屋市義援金</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="C149" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I149" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J149" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K149" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L149" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012463/1034808/1051962.html</v>
+      </c>
+      <c r="M149" t="str">
+        <v>藤前干潟わくわくフェスタ 見て・知って・守ろう！</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="C150" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I150" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J150" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K150" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L150" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052454.html</v>
+      </c>
+      <c r="M150" t="str">
+        <v>アジア競技大会・アジアパラ競技大会 競技会場巡礼ウォーク</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="C151" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I151" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J151" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K151" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L151" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1034096.html</v>
+      </c>
+      <c r="M151" t="str">
+        <v>幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="C152" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I152" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J152" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K152" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L152" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1052121.html</v>
+      </c>
+      <c r="M152" t="str">
+        <v>令和8年8月25日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="C153" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I153" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J153" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K153" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L153" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1016995/1016810/1016833/1016858/1052437.html</v>
+      </c>
+      <c r="M153" t="str">
+        <v>本地丘小学校、森孝東小学校及び森孝西小学校の統合並びに森孝中学校との併設に関する個別プラン（答申）(令和8年8月6日)</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="C154" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I154" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J154" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K154" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L154" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1016995/1016810/1016811/1016816/1052451.html</v>
+      </c>
+      <c r="M154" t="str">
+        <v>令和8年度第2回名古屋市子どもいきいき学校づくり推進審議会 令和8年8月6日</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="C155" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I155" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J155" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K155" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L155" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015269/1034849/1034132/1052633.html</v>
+      </c>
+      <c r="M155" t="str">
+        <v>令和8年度「衛研だより」</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="C156" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I156" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J156" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K156" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L156" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1035053/1051909.html</v>
+      </c>
+      <c r="M156" t="str">
+        <v>令和8年度音訳ボランティア養成講座</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M138"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M156"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reports/latest-report.xlsx
+++ b/reports/latest-report.xlsx
@@ -378,7 +378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D225"/>
+  <dimension ref="A1:D224"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -396,16 +396,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>❌ リンク切れ</v>
+        <v>✅ 正常</v>
       </c>
       <c r="B2" t="str">
-        <v>https://webc.sjc.ne.jp/nagoyasj/job2_7</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036294.html</v>
       </c>
       <c r="C2">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="D2" t="str">
-        <v>data/services.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="3">
@@ -413,13 +413,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B3" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036294.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/index.html</v>
       </c>
       <c r="C3">
         <v>200</v>
       </c>
       <c r="D3" t="str">
-        <v>data/districts.js</v>
+        <v>data/districts.js, screens/DisasterScreen.js</v>
       </c>
     </row>
     <row r="4">
@@ -427,13 +427,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B4" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/index.html</v>
+        <v>https://www.city.nagoya.jp/chikusa/kurashi/</v>
       </c>
       <c r="C4">
         <v>200</v>
       </c>
       <c r="D4" t="str">
-        <v>data/districts.js, screens/DisasterScreen.js</v>
+        <v>data/districts.js</v>
       </c>
     </row>
     <row r="5">
@@ -441,7 +441,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B5" t="str">
-        <v>https://www.city.nagoya.jp/chikusa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036299.html</v>
       </c>
       <c r="C5">
         <v>200</v>
@@ -455,7 +455,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B6" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036299.html</v>
+        <v>https://www.city.nagoya.jp/higashi/kurashi/</v>
       </c>
       <c r="C6">
         <v>200</v>
@@ -469,7 +469,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B7" t="str">
-        <v>https://www.city.nagoya.jp/higashi/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036302.html</v>
       </c>
       <c r="C7">
         <v>200</v>
@@ -483,7 +483,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B8" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036302.html</v>
+        <v>https://www.city.nagoya.jp/kita/kurashi/</v>
       </c>
       <c r="C8">
         <v>200</v>
@@ -497,7 +497,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B9" t="str">
-        <v>https://www.city.nagoya.jp/kita/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036293.html</v>
       </c>
       <c r="C9">
         <v>200</v>
@@ -511,7 +511,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B10" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036293.html</v>
+        <v>https://www.city.nagoya.jp/nishi/kurashi/</v>
       </c>
       <c r="C10">
         <v>200</v>
@@ -525,7 +525,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B11" t="str">
-        <v>https://www.city.nagoya.jp/nishi/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036297.html</v>
       </c>
       <c r="C11">
         <v>200</v>
@@ -539,7 +539,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B12" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036297.html</v>
+        <v>https://www.city.nagoya.jp/nakamura/kurashi/</v>
       </c>
       <c r="C12">
         <v>200</v>
@@ -553,7 +553,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B13" t="str">
-        <v>https://www.city.nagoya.jp/nakamura/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036295.html</v>
       </c>
       <c r="C13">
         <v>200</v>
@@ -567,7 +567,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B14" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036295.html</v>
+        <v>https://www.city.nagoya.jp/naka/kurashi/</v>
       </c>
       <c r="C14">
         <v>200</v>
@@ -581,7 +581,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B15" t="str">
-        <v>https://www.city.nagoya.jp/naka/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036291.html</v>
       </c>
       <c r="C15">
         <v>200</v>
@@ -595,7 +595,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B16" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036291.html</v>
+        <v>https://www.city.nagoya.jp/showa/kurashi/</v>
       </c>
       <c r="C16">
         <v>200</v>
@@ -609,7 +609,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B17" t="str">
-        <v>https://www.city.nagoya.jp/showa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036292.html</v>
       </c>
       <c r="C17">
         <v>200</v>
@@ -623,7 +623,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B18" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036292.html</v>
+        <v>https://www.city.nagoya.jp/mizuho/kurashi/</v>
       </c>
       <c r="C18">
         <v>200</v>
@@ -637,7 +637,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B19" t="str">
-        <v>https://www.city.nagoya.jp/mizuho/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036301.html</v>
       </c>
       <c r="C19">
         <v>200</v>
@@ -651,7 +651,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B20" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036301.html</v>
+        <v>https://www.city.nagoya.jp/atsuta/kurashi/</v>
       </c>
       <c r="C20">
         <v>200</v>
@@ -665,7 +665,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B21" t="str">
-        <v>https://www.city.nagoya.jp/atsuta/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036296.html</v>
       </c>
       <c r="C21">
         <v>200</v>
@@ -679,7 +679,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B22" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036296.html</v>
+        <v>https://www.city.nagoya.jp/nakagawa/kurashi/</v>
       </c>
       <c r="C22">
         <v>200</v>
@@ -693,7 +693,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B23" t="str">
-        <v>https://www.city.nagoya.jp/nakagawa/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036289.html</v>
       </c>
       <c r="C23">
         <v>200</v>
@@ -707,7 +707,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B24" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036289.html</v>
+        <v>https://www.city.nagoya.jp/minato/kurashi/</v>
       </c>
       <c r="C24">
         <v>200</v>
@@ -721,7 +721,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B25" t="str">
-        <v>https://www.city.nagoya.jp/minato/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036300.html</v>
       </c>
       <c r="C25">
         <v>200</v>
@@ -735,7 +735,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B26" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036300.html</v>
+        <v>https://www.city.nagoya.jp/minami/kurashi/</v>
       </c>
       <c r="C26">
         <v>200</v>
@@ -749,7 +749,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B27" t="str">
-        <v>https://www.city.nagoya.jp/minami/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036290.html</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -763,7 +763,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B28" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036290.html</v>
+        <v>https://www.city.nagoya.jp/moriyama/kurashi/</v>
       </c>
       <c r="C28">
         <v>200</v>
@@ -777,7 +777,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B29" t="str">
-        <v>https://www.city.nagoya.jp/moriyama/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036304.html</v>
       </c>
       <c r="C29">
         <v>200</v>
@@ -791,7 +791,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B30" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036304.html</v>
+        <v>https://www.city.nagoya.jp/midori/kurashi/</v>
       </c>
       <c r="C30">
         <v>200</v>
@@ -805,7 +805,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B31" t="str">
-        <v>https://www.city.nagoya.jp/midori/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036303.html</v>
       </c>
       <c r="C31">
         <v>200</v>
@@ -819,7 +819,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B32" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036303.html</v>
+        <v>https://www.city.nagoya.jp/meito/kurashi/</v>
       </c>
       <c r="C32">
         <v>200</v>
@@ -833,7 +833,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B33" t="str">
-        <v>https://www.city.nagoya.jp/meito/kurashi/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036298.html</v>
       </c>
       <c r="C33">
         <v>200</v>
@@ -847,7 +847,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B34" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036429/1036298.html</v>
+        <v>https://www.city.nagoya.jp/tempaku/kurashi/</v>
       </c>
       <c r="C34">
         <v>200</v>
@@ -861,13 +861,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B35" t="str">
-        <v>https://www.city.nagoya.jp/tempaku/kurashi/</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008973.html</v>
       </c>
       <c r="C35">
         <v>200</v>
       </c>
       <c r="D35" t="str">
-        <v>data/districts.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="36">
@@ -875,7 +875,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B36" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008973.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009333.html</v>
       </c>
       <c r="C36">
         <v>200</v>
@@ -889,7 +889,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B37" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009333.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1009009.html</v>
       </c>
       <c r="C37">
         <v>200</v>
@@ -903,7 +903,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B38" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1008992/1009002/1009009.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009270/1034086.html</v>
       </c>
       <c r="C38">
         <v>200</v>
@@ -917,7 +917,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B39" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009270/1034086.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009353/1034092.html</v>
       </c>
       <c r="C39">
         <v>200</v>
@@ -931,7 +931,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B40" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009353/1034092.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009286/index.html</v>
       </c>
       <c r="C40">
         <v>200</v>
@@ -945,7 +945,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B41" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009286/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1034088.html</v>
       </c>
       <c r="C41">
         <v>200</v>
@@ -959,7 +959,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B42" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009281/1034088.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009387.html</v>
       </c>
       <c r="C42">
         <v>200</v>
@@ -973,7 +973,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B43" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009387.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009393.html</v>
       </c>
       <c r="C43">
         <v>200</v>
@@ -987,7 +987,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B44" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009393.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011821/1011823.html</v>
       </c>
       <c r="C44">
         <v>200</v>
@@ -1001,7 +1001,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B45" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011821/1011823.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008956.html</v>
       </c>
       <c r="C45">
         <v>200</v>
@@ -1015,7 +1015,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B46" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008956.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008955.html</v>
       </c>
       <c r="C46">
         <v>200</v>
@@ -1029,7 +1029,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B47" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008951/1008955.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/ichiran.html</v>
       </c>
       <c r="C47">
         <v>200</v>
@@ -1043,7 +1043,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B48" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/ichiran.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008960.html</v>
       </c>
       <c r="C48">
         <v>200</v>
@@ -1057,7 +1057,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B49" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008960.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009019.html</v>
       </c>
       <c r="C49">
         <v>200</v>
@@ -1071,7 +1071,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B50" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009019.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008974.html</v>
       </c>
       <c r="C50">
         <v>200</v>
@@ -1085,7 +1085,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B51" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008974.html</v>
+        <v>https://www.city.nagoya.jp/lifescene/byouki/1017964.html</v>
       </c>
       <c r="C51">
         <v>200</v>
@@ -1099,7 +1099,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B52" t="str">
-        <v>https://www.city.nagoya.jp/lifescene/byouki/1017964.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/seido/toiawase/</v>
       </c>
       <c r="C52">
         <v>200</v>
@@ -1113,7 +1113,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B53" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/seido/toiawase/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016496/1016502.html</v>
       </c>
       <c r="C53">
         <v>200</v>
@@ -1127,7 +1127,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B54" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016496/1016502.html</v>
+        <v>http://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
       </c>
       <c r="C54">
         <v>200</v>
@@ -1141,7 +1141,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B55" t="str">
-        <v>http://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/1016536.html</v>
       </c>
       <c r="C55">
         <v>200</v>
@@ -1155,7 +1155,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B56" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016534/1016536.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011776/1034706/1011784.html</v>
       </c>
       <c r="C56">
         <v>200</v>
@@ -1169,7 +1169,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B57" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011776/1034706/1011784.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009456/1009457/index.html</v>
       </c>
       <c r="C57">
         <v>200</v>
@@ -1183,7 +1183,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B58" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009456/1009457/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
       </c>
       <c r="C58">
         <v>200</v>
@@ -1197,7 +1197,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B59" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1012157/1033970.html</v>
       </c>
       <c r="C59">
         <v>200</v>
@@ -1211,7 +1211,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B60" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1012157/1033970.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1015763/1015815.html</v>
       </c>
       <c r="C60">
         <v>200</v>
@@ -1225,7 +1225,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B61" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shisetsu/1015763/1015815.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011793/1011807/1011810.html</v>
       </c>
       <c r="C61">
         <v>200</v>
@@ -1239,7 +1239,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B62" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011793/1011807/1011810.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016739.html</v>
       </c>
       <c r="C62">
         <v>200</v>
@@ -1253,7 +1253,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B63" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016739.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/index.html</v>
       </c>
       <c r="C63">
         <v>200</v>
@@ -1267,7 +1267,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B64" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/juutaku/1014583/1014585/1014586/1014587/index.html</v>
+        <v>https://www.hellowork.mhlw.go.jp/insurance/insurance_guide.html</v>
       </c>
       <c r="C64">
         <v>200</v>
@@ -1281,7 +1281,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B65" t="str">
-        <v>https://www.hellowork.mhlw.go.jp/insurance/insurance_guide.html</v>
+        <v>https://jsite.mhlw.go.jp/aichi-hellowork/list.html</v>
       </c>
       <c r="C65">
         <v>200</v>
@@ -1295,7 +1295,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B66" t="str">
-        <v>https://jsite.mhlw.go.jp/aichi-hellowork/list.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
       </c>
       <c r="C66">
         <v>200</v>
@@ -1309,7 +1309,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B67" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1016700.html</v>
+        <v>https://www.nagojob.city.nagoya.jp/</v>
       </c>
       <c r="C67">
         <v>200</v>
@@ -1323,7 +1323,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B68" t="str">
-        <v>https://www.nagojob.city.nagoya.jp/</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/tetyou/</v>
       </c>
       <c r="C68">
         <v>200</v>
@@ -1337,7 +1337,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B69" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/tetyou/</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/soudan/fukushikakari.html</v>
       </c>
       <c r="C69">
         <v>200</v>
@@ -1351,7 +1351,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B70" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/soudan/fukushikakari.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/fukushi_service.html</v>
       </c>
       <c r="C70">
         <v>200</v>
@@ -1365,7 +1365,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B71" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/shiori/fukushi_service.html</v>
+        <v>https://www.city.nagoya.jp/jigyou/sangyou/1026356/1035103/1026446/1026447.html</v>
       </c>
       <c r="C71">
         <v>200</v>
@@ -1379,7 +1379,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B72" t="str">
-        <v>https://www.city.nagoya.jp/jigyou/sangyou/1026356/1035103/1026446/1026447.html</v>
+        <v>https://weljob-nagoya.com/</v>
       </c>
       <c r="C72">
         <v>200</v>
@@ -1393,7 +1393,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B73" t="str">
-        <v>https://weljob-nagoya.com/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
       </c>
       <c r="C73">
         <v>200</v>
@@ -1407,7 +1407,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B74" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/622/linksweb.pdf</v>
       </c>
       <c r="C74">
         <v>200</v>
@@ -1421,7 +1421,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B75" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/622/linksweb.pdf</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
       </c>
       <c r="C75">
         <v>200</v>
@@ -1435,7 +1435,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B76" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/675/annnai.pdf</v>
       </c>
       <c r="C76">
         <v>200</v>
@@ -1449,7 +1449,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B77" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/675/annnai.pdf</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
       </c>
       <c r="C77">
         <v>200</v>
@@ -1463,7 +1463,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B78" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
       </c>
       <c r="C78">
         <v>200</v>
@@ -1477,7 +1477,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B79" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
       </c>
       <c r="C79">
         <v>200</v>
@@ -1491,7 +1491,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B80" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008978.html</v>
       </c>
       <c r="C80">
         <v>200</v>
@@ -1505,7 +1505,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B81" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008971/1008978.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/008/978/0413tirasi.pdf</v>
       </c>
       <c r="C81">
         <v>200</v>
@@ -1519,7 +1519,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B82" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/008/978/0413tirasi.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034073/1009017.html</v>
       </c>
       <c r="C82">
         <v>200</v>
@@ -1533,7 +1533,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B83" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034073/1009017.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/009/017/r710_help.pdf</v>
       </c>
       <c r="C83">
         <v>200</v>
@@ -1547,7 +1547,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B84" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/009/017/r710_help.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1034087.html</v>
       </c>
       <c r="C84">
         <v>200</v>
@@ -1561,7 +1561,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B85" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1034087.html</v>
+        <v>https://www.kosodate.city.nagoya.jp/kids/nobinobi.html</v>
       </c>
       <c r="C85">
         <v>200</v>
@@ -1575,7 +1575,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B86" t="str">
-        <v>https://www.kosodate.city.nagoya.jp/kids/nobinobi.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1009278.html</v>
       </c>
       <c r="C86">
         <v>200</v>
@@ -1589,7 +1589,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B87" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009276/1009278.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009024/1009026.html</v>
       </c>
       <c r="C87">
         <v>200</v>
@@ -1603,7 +1603,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B88" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009024/1009026.html</v>
+        <v>https://www.kosodate.city.nagoya.jp/play/supportbases.html</v>
       </c>
       <c r="C88">
         <v>200</v>
@@ -1617,7 +1617,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B89" t="str">
-        <v>https://www.kosodate.city.nagoya.jp/play/supportbases.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034075/1009021.html</v>
       </c>
       <c r="C89">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B90" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034075/1009021.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034072/1009016.html</v>
       </c>
       <c r="C90">
         <v>200</v>
@@ -1645,10 +1645,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B91" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034072/1009016.html</v>
+        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096177.html</v>
       </c>
       <c r="C91">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D91" t="str">
         <v>data/services.js</v>
@@ -1659,10 +1659,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B92" t="str">
-        <v>https://www.city.nagoya.jp/kodomoseishonen/page/0000096177.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016744.html</v>
       </c>
       <c r="C92">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D92" t="str">
         <v>data/services.js</v>
@@ -1673,7 +1673,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B93" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016744.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016742.html</v>
       </c>
       <c r="C93">
         <v>200</v>
@@ -1687,7 +1687,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B94" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016741/1016742.html</v>
+        <v>https://hikikomori.city.nagoya.jp/</v>
       </c>
       <c r="C94">
         <v>200</v>
@@ -1701,7 +1701,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B95" t="str">
-        <v>https://hikikomori.city.nagoya.jp/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016586/1033908.html</v>
       </c>
       <c r="C95">
         <v>200</v>
@@ -1715,7 +1715,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B96" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016586/1033908.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009395.html</v>
       </c>
       <c r="C96">
         <v>200</v>
@@ -1729,7 +1729,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B97" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009395.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1009398.html</v>
       </c>
       <c r="C97">
         <v>200</v>
@@ -1743,7 +1743,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B98" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1009398.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009380.html</v>
       </c>
       <c r="C98">
         <v>200</v>
@@ -1757,7 +1757,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B99" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009380.html</v>
+        <v>https://aiboren.jp/shisetsu/</v>
       </c>
       <c r="C99">
         <v>200</v>
@@ -1771,7 +1771,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B100" t="str">
-        <v>https://aiboren.jp/shisetsu/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016428.html</v>
       </c>
       <c r="C100">
         <v>200</v>
@@ -1785,7 +1785,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B101" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016428.html</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/woichiran.html</v>
       </c>
       <c r="C101">
         <v>200</v>
@@ -1799,7 +1799,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B102" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/woichiran.html</v>
+        <v>https://nagoya-shakyo.jp/service/fureai-kyushoku/</v>
       </c>
       <c r="C102">
         <v>200</v>
@@ -1813,7 +1813,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B103" t="str">
-        <v>https://nagoya-shakyo.jp/service/fureai-kyushoku/</v>
+        <v>https://nagoya-shakyo.jp/service/ward-shakyo/</v>
       </c>
       <c r="C103">
         <v>200</v>
@@ -1827,7 +1827,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B104" t="str">
-        <v>https://nagoya-shakyo.jp/service/ward-shakyo/</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/company/shitei/haishoku/</v>
       </c>
       <c r="C104">
         <v>200</v>
@@ -1841,7 +1841,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B105" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/company/shitei/haishoku/</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
       </c>
       <c r="C105">
         <v>200</v>
@@ -1855,7 +1855,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B106" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016431.html</v>
       </c>
       <c r="C106">
         <v>200</v>
@@ -1869,7 +1869,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B107" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016431.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016433.html</v>
       </c>
       <c r="C107">
         <v>200</v>
@@ -1883,7 +1883,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B108" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016433.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016429.html</v>
       </c>
       <c r="C108">
         <v>200</v>
@@ -1897,7 +1897,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B109" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016429.html</v>
+        <v>https://nagoya-shakyo.jp/service/community-support/</v>
       </c>
       <c r="C109">
         <v>200</v>
@@ -1911,7 +1911,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B110" t="str">
-        <v>https://nagoya-shakyo.jp/service/community-support/</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1012252.html</v>
       </c>
       <c r="C110">
         <v>200</v>
@@ -1925,7 +1925,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B111" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1012252.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016440.html</v>
       </c>
       <c r="C111">
         <v>200</v>
@@ -1939,7 +1939,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B112" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016440.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016488.html</v>
       </c>
       <c r="C112">
         <v>200</v>
@@ -1953,7 +1953,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B113" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016488.html</v>
+        <v>https://www.bes-c.com/</v>
       </c>
       <c r="C113">
         <v>200</v>
@@ -1967,7 +1967,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B114" t="str">
-        <v>https://www.bes-c.com/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016491.html</v>
       </c>
       <c r="C114">
         <v>200</v>
@@ -1981,7 +1981,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B115" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016484/1016491.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012724/1013205/1034493/1013206.html</v>
       </c>
       <c r="C115">
         <v>200</v>
@@ -1995,7 +1995,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B116" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012724/1013205/1034493/1013206.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008943.html</v>
       </c>
       <c r="C116">
         <v>200</v>
@@ -2009,7 +2009,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B117" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008943.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008947.html</v>
       </c>
       <c r="C117">
         <v>200</v>
@@ -2023,7 +2023,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B118" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008947.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/index.html</v>
       </c>
       <c r="C118">
         <v>200</v>
@@ -2037,7 +2037,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B119" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008920/index.html</v>
       </c>
       <c r="C119">
         <v>200</v>
@@ -2051,7 +2051,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B120" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008920/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008937.html</v>
       </c>
       <c r="C120">
         <v>200</v>
@@ -2065,7 +2065,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B121" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008937.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008938.html</v>
       </c>
       <c r="C121">
         <v>200</v>
@@ -2079,7 +2079,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B122" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008938.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008939/index.html</v>
       </c>
       <c r="C122">
         <v>200</v>
@@ -2093,7 +2093,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B123" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008939/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008949.html</v>
       </c>
       <c r="C123">
         <v>200</v>
@@ -2107,7 +2107,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B124" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008949.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034084/1009261.html</v>
       </c>
       <c r="C124">
         <v>200</v>
@@ -2121,7 +2121,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B125" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034084/1009261.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009265.html</v>
       </c>
       <c r="C125">
         <v>200</v>
@@ -2135,7 +2135,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B126" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009265.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009264.html</v>
       </c>
       <c r="C126">
         <v>200</v>
@@ -2149,7 +2149,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B127" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034085/1009264.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009260.html</v>
       </c>
       <c r="C127">
         <v>200</v>
@@ -2163,7 +2163,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B128" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009260.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009258.html</v>
       </c>
       <c r="C128">
         <v>200</v>
@@ -2177,7 +2177,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B129" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009255/1034083/1009258.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009307/1008988.html</v>
       </c>
       <c r="C129">
         <v>200</v>
@@ -2191,7 +2191,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B130" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009307/1008988.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
       </c>
       <c r="C130">
         <v>200</v>
@@ -2205,7 +2205,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B131" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017057.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034342/1008991/1036125.html</v>
       </c>
       <c r="C131">
         <v>200</v>
@@ -2219,7 +2219,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B132" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1034342/1008991/1036125.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009126.html</v>
       </c>
       <c r="C132">
         <v>200</v>
@@ -2233,7 +2233,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B133" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1009125/1009126.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1037093/1016989.html</v>
       </c>
       <c r="C133">
         <v>200</v>
@@ -2247,7 +2247,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B134" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1037093/1016989.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008959.html</v>
       </c>
       <c r="C134">
         <v>200</v>
@@ -2261,7 +2261,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B135" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008958/1008959.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009018.html</v>
       </c>
       <c r="C135">
         <v>200</v>
@@ -2275,7 +2275,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B136" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009013/1034074/1009018.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016781.html</v>
       </c>
       <c r="C136">
         <v>200</v>
@@ -2289,7 +2289,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B137" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016781.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1036101.html</v>
       </c>
       <c r="C137">
         <v>200</v>
@@ -2303,7 +2303,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B138" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1036101.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1015850/1017055.html</v>
       </c>
       <c r="C138">
         <v>200</v>
@@ -2317,7 +2317,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B139" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1015850/1017055.html</v>
+        <v>https://nagoya.fureai-cloud.jp/_view/sodan/home/index</v>
       </c>
       <c r="C139">
         <v>200</v>
@@ -2331,7 +2331,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B140" t="str">
-        <v>https://nagoya.fureai-cloud.jp/_view/sodan/home/index</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009321/1009322.html</v>
       </c>
       <c r="C140">
         <v>200</v>
@@ -2345,7 +2345,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B141" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009321/1009322.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016409.html</v>
       </c>
       <c r="C141">
         <v>200</v>
@@ -2359,7 +2359,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B142" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016409.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015819/1038028/index.html</v>
       </c>
       <c r="C142">
         <v>200</v>
@@ -2373,7 +2373,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B143" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015819/1038028/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015845.html</v>
       </c>
       <c r="C143">
         <v>200</v>
@@ -2387,7 +2387,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B144" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034350/1015845.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016404.html</v>
       </c>
       <c r="C144">
         <v>200</v>
@@ -2401,7 +2401,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B145" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016404.html</v>
+        <v>https://www.caa.go.jp/policies/policy/local_cooperation/local_consumer_administration/hotline/</v>
       </c>
       <c r="C145">
         <v>200</v>
@@ -2415,7 +2415,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B146" t="str">
-        <v>https://www.caa.go.jp/policies/policy/local_cooperation/local_consumer_administration/hotline/</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016402.html</v>
       </c>
       <c r="C146">
         <v>200</v>
@@ -2429,7 +2429,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B147" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016402.html</v>
+        <v>https://www.nic-nagoya.or.jp/</v>
       </c>
       <c r="C147">
         <v>200</v>
@@ -2443,7 +2443,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B148" t="str">
-        <v>https://www.nic-nagoya.or.jp/</v>
+        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
       </c>
       <c r="C148">
         <v>200</v>
@@ -2457,7 +2457,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B149" t="str">
-        <v>https://www.nic-nagoya.or.jp/japanese/servicecounter/administration/post.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016399.html</v>
       </c>
       <c r="C149">
         <v>200</v>
@@ -2471,10 +2471,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B150" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016399.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016734.html</v>
       </c>
       <c r="C150">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="D150" t="str">
         <v>data/services.js</v>
@@ -2485,10 +2485,10 @@
         <v>✅ 正常</v>
       </c>
       <c r="B151" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016734.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008983/1008984.html</v>
       </c>
       <c r="C151">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="D151" t="str">
         <v>data/services.js</v>
@@ -2499,7 +2499,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B152" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008983/1008984.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009388.html</v>
       </c>
       <c r="C152">
         <v>200</v>
@@ -2513,7 +2513,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B153" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009388.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009391.html</v>
       </c>
       <c r="C153">
         <v>200</v>
@@ -2527,7 +2527,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B154" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009391.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009381/1009382.html</v>
       </c>
       <c r="C154">
         <v>200</v>
@@ -2541,7 +2541,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B155" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009381/1009382.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009334.html</v>
       </c>
       <c r="C155">
         <v>200</v>
@@ -2555,7 +2555,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B156" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009332/1009334.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009389.html</v>
       </c>
       <c r="C156">
         <v>200</v>
@@ -2569,7 +2569,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B157" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009389.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009374.html</v>
       </c>
       <c r="C157">
         <v>200</v>
@@ -2583,7 +2583,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B158" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009320/1009372/1009374.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1016449/index.html</v>
       </c>
       <c r="C158">
         <v>200</v>
@@ -2597,7 +2597,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B159" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1016449/index.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/</v>
       </c>
       <c r="C159">
         <v>200</v>
@@ -2611,13 +2611,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B160" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/jouhou/1036432/1013386.html</v>
       </c>
       <c r="C160">
         <v>200</v>
       </c>
       <c r="D160" t="str">
-        <v>data/services.js</v>
+        <v>data/services.js, screens/DisasterScreen.js</v>
       </c>
     </row>
     <row r="161">
@@ -2625,13 +2625,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B161" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/jouhou/1036432/1013386.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/kyoujo/1036451/1013567.html</v>
       </c>
       <c r="C161">
         <v>200</v>
       </c>
       <c r="D161" t="str">
-        <v>data/services.js, screens/DisasterScreen.js</v>
+        <v>data/services.js</v>
       </c>
     </row>
     <row r="162">
@@ -2639,7 +2639,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B162" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/kyoujo/1036451/1013567.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008962/1008963.html</v>
       </c>
       <c r="C162">
         <v>200</v>
@@ -2653,7 +2653,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B163" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008962/1008963.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016506/1016510/1016511.html</v>
       </c>
       <c r="C163">
         <v>200</v>
@@ -2667,7 +2667,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B164" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016506/1016510/1016511.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009502/1034108.html</v>
       </c>
       <c r="C164">
         <v>200</v>
@@ -2681,7 +2681,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B165" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009502/1034108.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/todokede/1007816/1007817.html</v>
       </c>
       <c r="C165">
         <v>200</v>
@@ -2695,7 +2695,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B166" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/todokede/1007816/1007817.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011854/index.html</v>
       </c>
       <c r="C166">
         <v>200</v>
@@ -2709,7 +2709,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B167" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011854/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011868.html</v>
       </c>
       <c r="C167">
         <v>200</v>
@@ -2723,7 +2723,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B168" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011868.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011870.html</v>
       </c>
       <c r="C168">
         <v>200</v>
@@ -2737,7 +2737,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B169" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011866/1011870.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/index.html</v>
       </c>
       <c r="C169">
         <v>200</v>
@@ -2751,7 +2751,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B170" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1035058/1012184/1046468/index.html</v>
       </c>
       <c r="C170">
         <v>200</v>
@@ -2765,7 +2765,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B171" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/gomi/1012183/1035058/1012184/1046468/index.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016573/index.html</v>
       </c>
       <c r="C171">
         <v>200</v>
@@ -2779,7 +2779,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B172" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016573/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/pet/1015473/index.html</v>
       </c>
       <c r="C172">
         <v>200</v>
@@ -2793,7 +2793,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B173" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/pet/1015473/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011763/1011768.html</v>
       </c>
       <c r="C173">
         <v>200</v>
@@ -2807,7 +2807,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B174" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011763/1011768.html</v>
+        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000135090_00001.html</v>
       </c>
       <c r="C174">
         <v>200</v>
@@ -2821,7 +2821,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B175" t="str">
-        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000135090_00001.html</v>
+        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000158665.html</v>
       </c>
       <c r="C175">
         <v>200</v>
@@ -2835,7 +2835,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B176" t="str">
-        <v>https://www.mhlw.go.jp/stf/seisakunitsuite/bunya/0000158665.html</v>
+        <v>https://www.kyoukaikenpo.or.jp/benefit/injury_and_sickness_allowance/index.html</v>
       </c>
       <c r="C176">
         <v>200</v>
@@ -2849,7 +2849,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B177" t="str">
-        <v>https://www.kyoukaikenpo.or.jp/benefit/injury_and_sickness_allowance/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011851/1011853.html</v>
       </c>
       <c r="C177">
         <v>200</v>
@@ -2863,7 +2863,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B178" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011851/1011853.html</v>
+        <v>https://www.nenkin.go.jp/service/jukyu/seido/sonota-kyufu/shienkyufukin/20190805.html</v>
       </c>
       <c r="C178">
         <v>200</v>
@@ -2877,7 +2877,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B179" t="str">
-        <v>https://www.nenkin.go.jp/service/jukyu/seido/sonota-kyufu/shienkyufukin/20190805.html</v>
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm</v>
       </c>
       <c r="C179">
         <v>200</v>
@@ -2891,7 +2891,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B180" t="str">
-        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm</v>
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm#mushoukaLink2</v>
       </c>
       <c r="C180">
         <v>200</v>
@@ -2905,7 +2905,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B181" t="str">
-        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm#mushoukaLink2</v>
+        <v>https://www.jasso.go.jp/shogakukin/</v>
       </c>
       <c r="C181">
         <v>200</v>
@@ -2919,7 +2919,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B182" t="str">
-        <v>https://www.jasso.go.jp/shogakukin/</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008946.html</v>
       </c>
       <c r="C182">
         <v>200</v>
@@ -2933,7 +2933,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B183" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/iryou/1008919/1008946.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016801.html</v>
       </c>
       <c r="C183">
         <v>200</v>
@@ -2947,7 +2947,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B184" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016801.html</v>
+        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/801/r8syougakukin.pdf</v>
       </c>
       <c r="C184">
         <v>200</v>
@@ -2961,7 +2961,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B185" t="str">
-        <v>https://www.city.nagoya.jp/_res/projects/default_project/_page_/001/016/801/r8syougakukin.pdf</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016798.html</v>
       </c>
       <c r="C185">
         <v>200</v>
@@ -2975,7 +2975,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B186" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016797/1016798.html</v>
+        <v>https://www.city.nagoya.jp/shisei/keikaku/1034903/1004666/1004670.html</v>
       </c>
       <c r="C186">
         <v>200</v>
@@ -2989,7 +2989,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B187" t="str">
-        <v>https://www.city.nagoya.jp/shisei/keikaku/1034903/1004666/1004670.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1049088.html</v>
       </c>
       <c r="C187">
         <v>200</v>
@@ -3003,7 +3003,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B188" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009396/1049088.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1050641.html</v>
       </c>
       <c r="C188">
         <v>200</v>
@@ -3017,7 +3017,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B189" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shigoto/1016699/1050641.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016987.html</v>
       </c>
       <c r="C189">
         <v>200</v>
@@ -3031,7 +3031,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B190" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016987.html</v>
+        <v>https://nagoyalink.net/</v>
       </c>
       <c r="C190">
         <v>200</v>
@@ -3045,7 +3045,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B191" t="str">
-        <v>https://nagoyalink.net/</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016705.html</v>
       </c>
       <c r="C191">
         <v>200</v>
@@ -3059,7 +3059,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B192" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016705.html</v>
+        <v>https://nagosapo.icds.jp/</v>
       </c>
       <c r="C192">
         <v>200</v>
@@ -3073,7 +3073,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B193" t="str">
-        <v>https://nagosapo.icds.jp/</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016706.html</v>
       </c>
       <c r="C193">
         <v>200</v>
@@ -3087,7 +3087,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B194" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016706.html</v>
+        <v>https://maejob.icds.jp/index.html</v>
       </c>
       <c r="C194">
         <v>200</v>
@@ -3101,7 +3101,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B195" t="str">
-        <v>https://maejob.icds.jp/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1011883/1011892.html</v>
       </c>
       <c r="C195">
         <v>200</v>
@@ -3115,7 +3115,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B196" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/zeikin/1037356/1011880/1011883/1011892.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011842/1011845.html</v>
       </c>
       <c r="C196">
         <v>200</v>
@@ -3129,7 +3129,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B197" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011824/1011841/1011842/1011845.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011769/1011773.html</v>
       </c>
       <c r="C197">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B198" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/hoken/1011736/1011758/1011769/1011773.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009386.html</v>
       </c>
       <c r="C198">
         <v>200</v>
@@ -3157,7 +3157,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B199" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009385/1009386.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009394.html</v>
       </c>
       <c r="C199">
         <v>200</v>
@@ -3171,7 +3171,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B200" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/hitorioya/1009392/1009394.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017010/1017016.html</v>
       </c>
       <c r="C200">
         <v>200</v>
@@ -3185,7 +3185,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B201" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017010/1017016.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016972/1016979.html</v>
       </c>
       <c r="C201">
         <v>200</v>
@@ -3199,7 +3199,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B202" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1016972/1016979.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017053.html</v>
       </c>
       <c r="C202">
         <v>200</v>
@@ -3213,7 +3213,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B203" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017053.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017056.html</v>
       </c>
       <c r="C203">
         <v>200</v>
@@ -3227,7 +3227,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B204" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1017052/1017056.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008983/1042086.html</v>
       </c>
       <c r="C204">
         <v>200</v>
@@ -3241,7 +3241,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B205" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/ninshin/1008983/1042086.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016704.html</v>
       </c>
       <c r="C205">
         <v>200</v>
@@ -3255,7 +3255,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B206" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1034346/1016984/1016704.html</v>
+        <v>https://www.kosodate-ouen.city.nagoya.jp/</v>
       </c>
       <c r="C206">
         <v>200</v>
@@ -3269,7 +3269,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B207" t="str">
-        <v>https://www.kosodate-ouen.city.nagoya.jp/</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009108/1009109.html</v>
       </c>
       <c r="C207">
         <v>200</v>
@@ -3283,7 +3283,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B208" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009023/1009108/1009109.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009280.html</v>
       </c>
       <c r="C208">
         <v>200</v>
@@ -3297,7 +3297,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B209" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009115/1034344/1009280.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016448/1016483.html</v>
       </c>
       <c r="C209">
         <v>200</v>
@@ -3311,7 +3311,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B210" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016448/1016483.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009410/1040316.html</v>
       </c>
       <c r="C210">
         <v>200</v>
@@ -3325,7 +3325,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B211" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009410/1040316.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009525/1009528.html</v>
       </c>
       <c r="C211">
         <v>200</v>
@@ -3339,7 +3339,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B212" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009525/1009528.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009525/1033517.html</v>
       </c>
       <c r="C212">
         <v>200</v>
@@ -3353,7 +3353,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B213" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009525/1033517.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009535/1009537.html</v>
       </c>
       <c r="C213">
         <v>200</v>
@@ -3367,7 +3367,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B214" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009535/1009537.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009535/1009539.html</v>
       </c>
       <c r="C214">
         <v>200</v>
@@ -3381,7 +3381,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B215" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009535/1009539.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1045911/1045913.html</v>
       </c>
       <c r="C215">
         <v>200</v>
@@ -3395,7 +3395,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B216" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1045911/1045913.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016443.html</v>
       </c>
       <c r="C216">
         <v>200</v>
@@ -3409,7 +3409,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B217" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016427/1016443.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016553/1016554.html</v>
       </c>
       <c r="C217">
         <v>200</v>
@@ -3423,7 +3423,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B218" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016553/1016554.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016553/1034838.html</v>
       </c>
       <c r="C218">
         <v>200</v>
@@ -3437,7 +3437,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B219" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016553/1034838.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016663.html</v>
       </c>
       <c r="C219">
         <v>200</v>
@@ -3451,7 +3451,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B220" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016663.html</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016738.html</v>
       </c>
       <c r="C220">
         <v>200</v>
@@ -3465,13 +3465,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B221" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/fukushi/1016735/1016738.html</v>
+        <v>https://www.city.nagoya.jp/</v>
       </c>
       <c r="C221">
         <v>200</v>
       </c>
       <c r="D221" t="str">
-        <v>data/services.js</v>
+        <v>screens/DetailScreen.js</v>
       </c>
     </row>
     <row r="222">
@@ -3479,7 +3479,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B222" t="str">
-        <v>https://www.city.nagoya.jp/</v>
+        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/jigyosho/</v>
       </c>
       <c r="C222">
         <v>200</v>
@@ -3493,13 +3493,13 @@
         <v>✅ 正常</v>
       </c>
       <c r="B223" t="str">
-        <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/jigyosho/</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/1013492.html</v>
       </c>
       <c r="C223">
         <v>200</v>
       </c>
       <c r="D223" t="str">
-        <v>screens/DetailScreen.js</v>
+        <v>screens/DisasterScreen.js</v>
       </c>
     </row>
     <row r="224">
@@ -3507,7 +3507,7 @@
         <v>✅ 正常</v>
       </c>
       <c r="B224" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/1013492.html</v>
+        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036428.html</v>
       </c>
       <c r="C224">
         <v>200</v>
@@ -3516,30 +3516,16 @@
         <v>screens/DisasterScreen.js</v>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" t="str">
-        <v>✅ 正常</v>
-      </c>
-      <c r="B225" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hazardmap/1036428.html</v>
-      </c>
-      <c r="C225">
-        <v>200</v>
-      </c>
-      <c r="D225" t="str">
-        <v>screens/DisasterScreen.js</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D225"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D224"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3557,13 +3543,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>https://webc.sjc.ne.jp/nagoyasj/job2_7</v>
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
       </c>
       <c r="B2" t="str">
-        <v>ひとに、ときめきを。公益社団法人名古屋市シルバー人材センター【公式】</v>
+        <v>【準備中】令和8年度高齢者を対象としたインフルエンザ予防接種｜名古屋市公式ウェブサイト</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>令和8年度高齢者を対象としたインフルエンザ予防接種｜名古屋市公式ウェブサイト</v>
       </c>
       <c r="D2" t="str">
         <v>data/services.js</v>
@@ -3571,13 +3557,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>https://www.bes-c.com/</v>
+        <v>https://hikikomori.city.nagoya.jp/</v>
       </c>
       <c r="B3" t="str">
-        <v>名古屋市高齢者就業支援センター</v>
+        <v>あなたが抱える困難を少しでも軽く 少しでも元気が出る相談を大切にしています - re&amp;#x1f331;link</v>
       </c>
       <c r="C3" t="str">
-        <v>名古屋市高齢者就業支援センター</v>
+        <v>あなたが抱える困難を少しでも軽く 少しでも元気が出る相談を大切にしています - re&amp;#x1f331;link</v>
       </c>
       <c r="D3" t="str">
         <v>data/services.js</v>
@@ -3585,28 +3571,84 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>https://www.city.nagoya.jp/bousaiportal/hinan/1013390/1013492.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016781.html</v>
       </c>
       <c r="B4" t="str">
-        <v>指定緊急避難場所・指定避難所の指定｜名古屋市公式ウェブサイト</v>
+        <v>就学援助（未来まなび応援金）｜名古屋市公式ウェブサイト</v>
       </c>
       <c r="C4" t="str">
-        <v>指定緊急避難場所・指定避難所の指定｜名古屋市公式ウェブサイト</v>
+        <v>未来まなび応援金（就学援助制度）｜名古屋市公式ウェブサイト</v>
       </c>
       <c r="D4" t="str">
-        <v>screens/DisasterScreen.js</v>
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm</v>
+      </c>
+      <c r="B5" t="str">
+        <v>高校生等への修学支援：文部科学省</v>
+      </c>
+      <c r="C5" t="str">
+        <v>高校生等への修学支援：文部科学省</v>
+      </c>
+      <c r="D5" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm#mushoukaLink2</v>
+      </c>
+      <c r="B6" t="str">
+        <v>高校生等への修学支援：文部科学省</v>
+      </c>
+      <c r="C6" t="str">
+        <v>高校生等への修学支援：文部科学省</v>
+      </c>
+      <c r="D6" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009535/1009537.html</v>
+      </c>
+      <c r="B7" t="str">
+        <v>妊娠希望の方等への任意風しん及び麻しんの抗体検査及び予防接種の費用助成｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="C7" t="str">
+        <v>妊娠希望の方等への任意風しん及び麻しんの抗体検査及び予防接種の費用助成｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="D7" t="str">
+        <v>data/services.js</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009535/1009539.html</v>
+      </c>
+      <c r="B8" t="str">
+        <v>おたふくかぜ予防接種の費用助成(任意予防接種)｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="C8" t="str">
+        <v>おたふくかぜ予防接種(任意予防接種)｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="D8" t="str">
+        <v>data/services.js</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D8"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3636,10 +3678,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D2" t="str">
-        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012834/1044832/1052173.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1013036/1034523/1053567.html</v>
       </c>
       <c r="E2" t="str">
-        <v>令和8年 中区消防団連合観閲式のお知らせ</v>
+        <v>入ろう！消防団（みなみちゃんと学ぼう【動画紹介】#16）</v>
       </c>
     </row>
     <row r="3">
@@ -3650,47 +3692,47 @@
         <v>https://www.city.nagoya.jp/bousai/index.html</v>
       </c>
       <c r="C3" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D3" t="str">
-        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014550/1034531/1014557.html</v>
+        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014550/1042337.html</v>
       </c>
       <c r="E3" t="str">
-        <v>名古屋市老朽危険空家等除却費補助金</v>
+        <v>空き家情報冊子の無償提供者の募集</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>くらし・手続き</v>
+        <v>防災・安全安心</v>
       </c>
       <c r="B4" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
       </c>
       <c r="C4" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D4" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/douro/1014853/1014872/1052271.html</v>
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1050595/index.html</v>
       </c>
       <c r="E4" t="str">
-        <v>スポーツ教室開催計画書・地元説明報告書の提出先</v>
+        <v>熱田区の消防団について</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>くらし・手続き</v>
+        <v>防災・安全安心</v>
       </c>
       <c r="B5" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
       </c>
       <c r="C5" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D5" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/douro/1014853/1014872/1052148.html</v>
+        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014550/1034531/1014563.html</v>
       </c>
       <c r="E5" t="str">
-        <v>公園でスポーツ教室を開催したい</v>
+        <v>空き家の発生を抑制するための特例措置（令和6年1月1日以降の譲渡）</v>
       </c>
     </row>
     <row r="6">
@@ -3704,10 +3746,10 @@
         <v>➕ 追加</v>
       </c>
       <c r="D6" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051352.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/shiminsanka/1011147/1052890.html</v>
       </c>
       <c r="E6" t="str">
-        <v>森づくり体験会 炭焼き窯で竹炭ができるまでを体験しよう（大高緑地）</v>
+        <v>令和8年8月千葉豪雨災害義援金の募集について（千葉県共同募金会）</v>
       </c>
     </row>
     <row r="7">
@@ -3718,13 +3760,13 @@
         <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C7" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D7" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/shiminsanka/1011147/1052643.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/douro/1015622/1015702/1052241.html</v>
       </c>
       <c r="E7" t="str">
-        <v>令和8年熊本地震名古屋市義援金</v>
+        <v>港土木だより第29号</v>
       </c>
     </row>
     <row r="8">
@@ -3735,13 +3777,13 @@
         <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C8" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D8" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/kankyou/1012463/1034808/1051962.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/douro/1014853/1053663.html</v>
       </c>
       <c r="E8" t="str">
-        <v>藤前干潟わくわくフェスタ 見て・知って・守ろう！</v>
+        <v>公園配置図</v>
       </c>
     </row>
     <row r="9">
@@ -3755,61 +3797,61 @@
         <v>➖ 削除</v>
       </c>
       <c r="D9" t="str">
-        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1052454.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/douro/1014853/1014872/1052271.html</v>
       </c>
       <c r="E9" t="str">
-        <v>アジア競技大会・アジアパラ競技大会 競技会場巡礼ウォーク</v>
+        <v>スポーツ教室開催計画書・地元説明報告書の提出先</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>子ども・子育て・教育</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B10" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C10" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D10" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1034096.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/douro/1014853/1014872/1052148.html</v>
       </c>
       <c r="E10" t="str">
-        <v>幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+        <v>公園でスポーツ教室を開催したい</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>子ども・子育て・教育</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B11" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C11" t="str">
-        <v>➕ 追加</v>
+        <v>➖ 削除</v>
       </c>
       <c r="D11" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1052121.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051352.html</v>
       </c>
       <c r="E11" t="str">
-        <v>令和8年8月25日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+        <v>森づくり体験会 炭焼き窯で竹炭ができるまでを体験しよう（大高緑地）</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>子ども・子育て・教育</v>
+        <v>くらし・手続き</v>
       </c>
       <c r="B12" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
       </c>
       <c r="C12" t="str">
-        <v>➖ 削除</v>
+        <v>🔁 変更</v>
       </c>
       <c r="D12" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1016995/1016810/1016833/1016858/1052437.html</v>
+        <v>https://www.city.nagoya.jp/kurashi/douro/1010455/index.html</v>
       </c>
       <c r="E12" t="str">
-        <v>本地丘小学校、森孝東小学校及び森孝西小学校の統合並びに森孝中学校との併設に関する個別プラン（答申）(令和8年8月6日)</v>
+        <v>道路資産の有効活用の取組み → 道路・公園資産の有効活用の取組み</v>
       </c>
     </row>
     <row r="13">
@@ -3820,59 +3862,212 @@
         <v>https://www.city.nagoya.jp/kodomo/index.html</v>
       </c>
       <c r="C13" t="str">
-        <v>➖ 削除</v>
+        <v>➕ 追加</v>
       </c>
       <c r="D13" t="str">
-        <v>https://www.city.nagoya.jp/kodomo/schools/1027693/1016995/1016810/1016811/1016816/1052451.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017036/1053560.html</v>
       </c>
       <c r="E13" t="str">
-        <v>令和8年度第2回名古屋市子どもいきいき学校づくり推進審議会 令和8年8月6日</v>
+        <v>体験活動プログラム「好きなこと、やっちゃえ！」</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>健康・医療・福祉</v>
+        <v>子ども・子育て・教育</v>
       </c>
       <c r="B14" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
       </c>
       <c r="C14" t="str">
         <v>➕ 追加</v>
       </c>
       <c r="D14" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015269/1034849/1034132/1052633.html</v>
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1037089/1037092/1040311.html</v>
       </c>
       <c r="E14" t="str">
-        <v>令和8年度「衛研だより」</v>
+        <v>令和8年度 「さわって！遊んで！学ぼう！なごや子ども・若者わくわくフェスタ！」（名古屋市青少年育成市民大会）を開催しました</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="B15" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="C15" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D15" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009312/1053475.html</v>
+      </c>
+      <c r="E15" t="str">
+        <v>こどもホスピス支援事業</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="B16" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="C16" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D16" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1034096.html</v>
+      </c>
+      <c r="E16" t="str">
+        <v>幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="B17" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="C17" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D17" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1052121.html</v>
+      </c>
+      <c r="E17" t="str">
+        <v>令和8年8月25日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="B18" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="C18" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D18" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017010/1051545.html</v>
+      </c>
+      <c r="E18" t="str">
+        <v>特別支援学校および特別支援学級・通級指導教室の設置校一覧</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
         <v>健康・医療・福祉</v>
       </c>
-      <c r="B15" t="str">
+      <c r="B19" t="str">
         <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
       </c>
-      <c r="C15" t="str">
+      <c r="C19" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D19" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015421/1015431/1052399.html</v>
+      </c>
+      <c r="E19" t="str">
+        <v>「夏休み親子体験教室」（食品安全・安心学習センター）を開催しました（令和8年7月31日、8月3日、6日、13日、17日、21日）</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="B20" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="C20" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D20" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/1016644/1053611/index.html</v>
+      </c>
+      <c r="E20" t="str">
+        <v>台風等による警報発令時における、りんくす名古屋が主催する講習会・研修の開催</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="B21" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="C21" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="D21" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015269/1015388/1051978/index.html</v>
+      </c>
+      <c r="E21" t="str">
+        <v>愛知県・名古屋アジア・アジアパラ競技大会における感染症関連情報</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="B22" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="C22" t="str">
         <v>➖ 削除</v>
       </c>
-      <c r="D15" t="str">
-        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1035053/1051909.html</v>
-      </c>
-      <c r="E15" t="str">
-        <v>令和8年度音訳ボランティア養成講座</v>
+      <c r="D22" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015269/1034849/1034132/1052633.html</v>
+      </c>
+      <c r="E22" t="str">
+        <v>令和8年度「衛研だより」</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="B23" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="C23" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D23" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1035053/1052496.html</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Zoomによる初めてのオンライン手話講座（令和8年9月金曜コース）</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="B24" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="C24" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="D24" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016414/1051383.html</v>
+      </c>
+      <c r="E24" t="str">
+        <v>令和8年度「敬老の日」における市民利用施設の無料開放等実施のお知らせ</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E24"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M156"/>
+  <dimension ref="A1:M186"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7213,9 +7408,678 @@
         <v>令和8年度音訳ボランティア養成講座</v>
       </c>
     </row>
+    <row r="157">
+      <c r="B157" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C157" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D157" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
+      </c>
+      <c r="F157" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G157" t="str">
+        <v>【準備中】令和8年度高齢者を対象としたインフルエンザ予防接種｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="H157" t="str">
+        <v>令和8年度高齢者を対象としたインフルエンザ予防接種｜名古屋市公式ウェブサイト</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C158" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D158" t="str">
+        <v>https://hikikomori.city.nagoya.jp/</v>
+      </c>
+      <c r="F158" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G158" t="str">
+        <v>あなたが抱える困難を少しでも軽く 少しでも元気が出る相談を大切にしています - re&amp;#x1f331;link</v>
+      </c>
+      <c r="H158" t="str">
+        <v>あなたが抱える困難を少しでも軽く 少しでも元気が出る相談を大切にしています - re&amp;#x1f331;link</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C159" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D159" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1016760/1016781.html</v>
+      </c>
+      <c r="F159" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G159" t="str">
+        <v>就学援助（未来まなび応援金）｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="H159" t="str">
+        <v>未来まなび応援金（就学援助制度）｜名古屋市公式ウェブサイト</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C160" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D160" t="str">
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm</v>
+      </c>
+      <c r="F160" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G160" t="str">
+        <v>高校生等への修学支援：文部科学省</v>
+      </c>
+      <c r="H160" t="str">
+        <v>高校生等への修学支援：文部科学省</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C161" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D161" t="str">
+        <v>https://www.mext.go.jp/a_menu/shotou/mushouka/index.htm#mushoukaLink2</v>
+      </c>
+      <c r="F161" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G161" t="str">
+        <v>高校生等への修学支援：文部科学省</v>
+      </c>
+      <c r="H161" t="str">
+        <v>高校生等への修学支援：文部科学省</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C162" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D162" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009535/1009537.html</v>
+      </c>
+      <c r="F162" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G162" t="str">
+        <v>妊娠希望の方等への任意風しん及び麻しんの抗体検査及び予防接種の費用助成｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="H162" t="str">
+        <v>妊娠希望の方等への任意風しん及び麻しんの抗体検査及び予防接種の費用助成｜名古屋市公式ウェブサイト</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C163" t="str">
+        <v>内容変更</v>
+      </c>
+      <c r="D163" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009501/1009535/1009539.html</v>
+      </c>
+      <c r="F163" t="str">
+        <v>data/services.js</v>
+      </c>
+      <c r="G163" t="str">
+        <v>おたふくかぜ予防接種の費用助成(任意予防接種)｜名古屋市公式ウェブサイト</v>
+      </c>
+      <c r="H163" t="str">
+        <v>おたふくかぜ予防接種(任意予防接種)｜名古屋市公式ウェブサイト</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C164" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I164" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J164" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K164" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L164" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1013036/1034523/1053567.html</v>
+      </c>
+      <c r="M164" t="str">
+        <v>入ろう！消防団（みなみちゃんと学ぼう【動画紹介】#16）</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C165" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I165" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J165" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K165" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L165" t="str">
+        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014550/1042337.html</v>
+      </c>
+      <c r="M165" t="str">
+        <v>空き家情報冊子の無償提供者の募集</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C166" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I166" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J166" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K166" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L166" t="str">
+        <v>https://www.city.nagoya.jp/bousai/shoubou/1012732/1012733/1012943/1050595/index.html</v>
+      </c>
+      <c r="M166" t="str">
+        <v>熱田区の消防団について</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C167" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I167" t="str">
+        <v>防災・安全安心</v>
+      </c>
+      <c r="J167" t="str">
+        <v>https://www.city.nagoya.jp/bousai/index.html</v>
+      </c>
+      <c r="K167" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L167" t="str">
+        <v>https://www.city.nagoya.jp/bousai/anzen/1034530/1014550/1034531/1014563.html</v>
+      </c>
+      <c r="M167" t="str">
+        <v>空き家の発生を抑制するための特例措置（令和6年1月1日以降の譲渡）</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C168" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I168" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J168" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K168" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L168" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/shiminsanka/1011147/1052890.html</v>
+      </c>
+      <c r="M168" t="str">
+        <v>令和8年8月千葉豪雨災害義援金の募集について（千葉県共同募金会）</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C169" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I169" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J169" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K169" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L169" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/douro/1015622/1015702/1052241.html</v>
+      </c>
+      <c r="M169" t="str">
+        <v>港土木だより第29号</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C170" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I170" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J170" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K170" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L170" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/douro/1014853/1053663.html</v>
+      </c>
+      <c r="M170" t="str">
+        <v>公園配置図</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C171" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I171" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J171" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K171" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L171" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/douro/1014853/1014872/1052271.html</v>
+      </c>
+      <c r="M171" t="str">
+        <v>スポーツ教室開催計画書・地元説明報告書の提出先</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C172" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I172" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J172" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K172" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L172" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/douro/1014853/1014872/1052148.html</v>
+      </c>
+      <c r="M172" t="str">
+        <v>公園でスポーツ教室を開催したい</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C173" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I173" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J173" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K173" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L173" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/boshu/1017843/1051352.html</v>
+      </c>
+      <c r="M173" t="str">
+        <v>森づくり体験会 炭焼き窯で竹炭ができるまでを体験しよう（大高緑地）</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C174" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I174" t="str">
+        <v>くらし・手続き</v>
+      </c>
+      <c r="J174" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/index.html</v>
+      </c>
+      <c r="K174" t="str">
+        <v>🔁 変更</v>
+      </c>
+      <c r="L174" t="str">
+        <v>https://www.city.nagoya.jp/kurashi/douro/1010455/index.html</v>
+      </c>
+      <c r="M174" t="str">
+        <v>道路資産の有効活用の取組み → 道路・公園資産の有効活用の取組み</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C175" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I175" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J175" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K175" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L175" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017036/1053560.html</v>
+      </c>
+      <c r="M175" t="str">
+        <v>体験活動プログラム「好きなこと、やっちゃえ！」</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C176" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I176" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J176" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K176" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L176" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1037089/1037092/1040311.html</v>
+      </c>
+      <c r="M176" t="str">
+        <v>令和8年度 「さわって！遊んで！学ぼう！なごや子ども・若者わくわくフェスタ！」（名古屋市青少年育成市民大会）を開催しました</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C177" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I177" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J177" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K177" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L177" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/kosodate/1009312/1053475.html</v>
+      </c>
+      <c r="M177" t="str">
+        <v>こどもホスピス支援事業</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C178" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I178" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J178" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K178" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L178" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1034096.html</v>
+      </c>
+      <c r="M178" t="str">
+        <v>幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C179" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I179" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J179" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K179" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L179" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/wakamono/1017035/1017060/1052121.html</v>
+      </c>
+      <c r="M179" t="str">
+        <v>令和8年8月25日掲載分 幼児・児童・生徒向けのイベント、作品募集等に関するご案内(デジタルチラシ)</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C180" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I180" t="str">
+        <v>子ども・子育て・教育</v>
+      </c>
+      <c r="J180" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/index.html</v>
+      </c>
+      <c r="K180" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L180" t="str">
+        <v>https://www.city.nagoya.jp/kodomo/schools/1017010/1051545.html</v>
+      </c>
+      <c r="M180" t="str">
+        <v>特別支援学校および特別支援学級・通級指導教室の設置校一覧</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C181" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I181" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J181" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K181" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L181" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015421/1015431/1052399.html</v>
+      </c>
+      <c r="M181" t="str">
+        <v>「夏休み親子体験教室」（食品安全・安心学習センター）を開催しました（令和8年7月31日、8月3日、6日、13日、17日、21日）</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C182" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I182" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J182" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K182" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L182" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/1016644/1053611/index.html</v>
+      </c>
+      <c r="M182" t="str">
+        <v>台風等による警報発令時における、りんくす名古屋が主催する講習会・研修の開催</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C183" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I183" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J183" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K183" t="str">
+        <v>➕ 追加</v>
+      </c>
+      <c r="L183" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015269/1015388/1051978/index.html</v>
+      </c>
+      <c r="M183" t="str">
+        <v>愛知県・名古屋アジア・アジアパラ競技大会における感染症関連情報</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C184" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I184" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J184" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K184" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L184" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/eisei/1015269/1034849/1034132/1052633.html</v>
+      </c>
+      <c r="M184" t="str">
+        <v>令和8年度「衛研だより」</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C185" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I185" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J185" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K185" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L185" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1035053/1052496.html</v>
+      </c>
+      <c r="M185" t="str">
+        <v>Zoomによる初めてのオンライン手話講座（令和8年9月金曜コース）</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="str">
+        <v>2026-09-07</v>
+      </c>
+      <c r="C186" t="str">
+        <v>カテゴリ変更</v>
+      </c>
+      <c r="I186" t="str">
+        <v>健康・医療・福祉</v>
+      </c>
+      <c r="J186" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/index.html</v>
+      </c>
+      <c r="K186" t="str">
+        <v>➖ 削除</v>
+      </c>
+      <c r="L186" t="str">
+        <v>https://www.city.nagoya.jp/kenkofukushi/koureisha/1016414/1051383.html</v>
+      </c>
+      <c r="M186" t="str">
+        <v>令和8年度「敬老の日」における市民利用施設の無料開放等実施のお知らせ</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M156"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M186"/>
   </ignoredErrors>
 </worksheet>
 </file>